--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_dev\Seal-Report\Repository\Settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B00C90-9A4D-4348-872B-EEF57F95968D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9F0A79-57BA-409E-A2EC-A4B00734C07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32145" yWindow="285" windowWidth="26145" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31155" yWindow="750" windowWidth="26445" windowHeight="14655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Translations" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$D$390</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$D$392</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="673">
   <si>
     <t>Context</t>
   </si>
@@ -2043,6 +2043,18 @@
   </si>
   <si>
     <t>Error: the destination file name contains invalid characters.</t>
+  </si>
+  <si>
+    <t>Upload</t>
+  </si>
+  <si>
+    <t>Charger</t>
+  </si>
+  <si>
+    <t>Download report</t>
+  </si>
+  <si>
+    <t>Télécharger le rapport</t>
   </si>
 </sst>
 </file>
@@ -2897,7 +2909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D390"/>
+  <dimension ref="A1:D392"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -5982,10 +5994,10 @@
         <v>284</v>
       </c>
       <c r="B280" t="s">
-        <v>412</v>
+        <v>669</v>
       </c>
       <c r="D280" t="s">
-        <v>413</v>
+        <v>670</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
@@ -5993,10 +6005,10 @@
         <v>284</v>
       </c>
       <c r="B281" t="s">
-        <v>632</v>
+        <v>412</v>
       </c>
       <c r="D281" t="s">
-        <v>645</v>
+        <v>413</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
@@ -6004,10 +6016,10 @@
         <v>284</v>
       </c>
       <c r="B282" t="s">
-        <v>414</v>
+        <v>632</v>
       </c>
       <c r="D282" t="s">
-        <v>415</v>
+        <v>645</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
@@ -6015,10 +6027,10 @@
         <v>284</v>
       </c>
       <c r="B283" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D283" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
@@ -6026,10 +6038,10 @@
         <v>284</v>
       </c>
       <c r="B284" t="s">
-        <v>553</v>
+        <v>416</v>
       </c>
       <c r="D284" t="s">
-        <v>568</v>
+        <v>417</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
@@ -6037,21 +6049,21 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>418</v>
+        <v>553</v>
       </c>
       <c r="D285" t="s">
-        <v>419</v>
+        <v>568</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="D286" t="s">
-        <v>22</v>
+        <v>419</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
@@ -6059,10 +6071,10 @@
         <v>420</v>
       </c>
       <c r="B287" t="s">
-        <v>421</v>
+        <v>21</v>
       </c>
       <c r="D287" t="s">
-        <v>421</v>
+        <v>22</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
@@ -6070,10 +6082,10 @@
         <v>420</v>
       </c>
       <c r="B288" t="s">
-        <v>30</v>
+        <v>421</v>
       </c>
       <c r="D288" t="s">
-        <v>31</v>
+        <v>421</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
@@ -6081,10 +6093,10 @@
         <v>420</v>
       </c>
       <c r="B289" t="s">
-        <v>546</v>
+        <v>30</v>
       </c>
       <c r="D289" t="s">
-        <v>422</v>
+        <v>31</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
@@ -6092,10 +6104,10 @@
         <v>420</v>
       </c>
       <c r="B290" t="s">
-        <v>44</v>
+        <v>546</v>
       </c>
       <c r="D290" t="s">
-        <v>45</v>
+        <v>422</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
@@ -6103,10 +6115,10 @@
         <v>420</v>
       </c>
       <c r="B291" t="s">
-        <v>589</v>
+        <v>44</v>
       </c>
       <c r="D291" t="s">
-        <v>610</v>
+        <v>45</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -6114,10 +6126,10 @@
         <v>420</v>
       </c>
       <c r="B292" t="s">
-        <v>50</v>
+        <v>589</v>
       </c>
       <c r="D292" t="s">
-        <v>51</v>
+        <v>610</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
@@ -6125,10 +6137,10 @@
         <v>420</v>
       </c>
       <c r="B293" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D293" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
@@ -6136,10 +6148,10 @@
         <v>420</v>
       </c>
       <c r="B294" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D294" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
@@ -6147,10 +6159,10 @@
         <v>420</v>
       </c>
       <c r="B295" t="s">
-        <v>296</v>
+        <v>52</v>
       </c>
       <c r="D295" t="s">
-        <v>519</v>
+        <v>53</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
@@ -6158,10 +6170,10 @@
         <v>420</v>
       </c>
       <c r="B296" t="s">
-        <v>523</v>
+        <v>296</v>
       </c>
       <c r="D296" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -6169,10 +6181,10 @@
         <v>420</v>
       </c>
       <c r="B297" t="s">
-        <v>423</v>
+        <v>523</v>
       </c>
       <c r="D297" t="s">
-        <v>424</v>
+        <v>520</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
@@ -6180,10 +6192,10 @@
         <v>420</v>
       </c>
       <c r="B298" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D298" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -6191,10 +6203,10 @@
         <v>420</v>
       </c>
       <c r="B299" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D299" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
@@ -6202,10 +6214,10 @@
         <v>420</v>
       </c>
       <c r="B300" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D300" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
@@ -6213,10 +6225,10 @@
         <v>420</v>
       </c>
       <c r="B301" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D301" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
@@ -6224,10 +6236,10 @@
         <v>420</v>
       </c>
       <c r="B302" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D302" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
@@ -6235,10 +6247,10 @@
         <v>420</v>
       </c>
       <c r="B303" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D303" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
@@ -6246,10 +6258,10 @@
         <v>420</v>
       </c>
       <c r="B304" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D304" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
@@ -6257,10 +6269,10 @@
         <v>420</v>
       </c>
       <c r="B305" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D305" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
@@ -6268,10 +6280,10 @@
         <v>420</v>
       </c>
       <c r="B306" t="s">
-        <v>61</v>
+        <v>439</v>
       </c>
       <c r="D306" t="s">
-        <v>62</v>
+        <v>440</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
@@ -6279,10 +6291,10 @@
         <v>420</v>
       </c>
       <c r="B307" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D307" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
@@ -6290,10 +6302,10 @@
         <v>420</v>
       </c>
       <c r="B308" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D308" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
@@ -6301,10 +6313,10 @@
         <v>420</v>
       </c>
       <c r="B309" t="s">
-        <v>441</v>
+        <v>63</v>
       </c>
       <c r="D309" t="s">
-        <v>442</v>
+        <v>64</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
@@ -6312,10 +6324,10 @@
         <v>420</v>
       </c>
       <c r="B310" t="s">
-        <v>588</v>
+        <v>671</v>
       </c>
       <c r="D310" t="s">
-        <v>609</v>
+        <v>672</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
@@ -6323,10 +6335,10 @@
         <v>420</v>
       </c>
       <c r="B311" t="s">
-        <v>587</v>
+        <v>441</v>
       </c>
       <c r="D311" t="s">
-        <v>608</v>
+        <v>442</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
@@ -6334,10 +6346,10 @@
         <v>420</v>
       </c>
       <c r="B312" t="s">
-        <v>75</v>
+        <v>588</v>
       </c>
       <c r="D312" t="s">
-        <v>76</v>
+        <v>609</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
@@ -6345,10 +6357,10 @@
         <v>420</v>
       </c>
       <c r="B313" t="s">
-        <v>77</v>
+        <v>587</v>
       </c>
       <c r="D313" t="s">
-        <v>78</v>
+        <v>608</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
@@ -6356,10 +6368,10 @@
         <v>420</v>
       </c>
       <c r="B314" t="s">
-        <v>326</v>
+        <v>75</v>
       </c>
       <c r="D314" t="s">
-        <v>327</v>
+        <v>76</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
@@ -6367,10 +6379,10 @@
         <v>420</v>
       </c>
       <c r="B315" t="s">
-        <v>449</v>
+        <v>77</v>
       </c>
       <c r="D315" t="s">
-        <v>443</v>
+        <v>78</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
@@ -6378,10 +6390,10 @@
         <v>420</v>
       </c>
       <c r="B316" t="s">
-        <v>545</v>
+        <v>326</v>
       </c>
       <c r="D316" t="s">
-        <v>444</v>
+        <v>327</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
@@ -6389,10 +6401,10 @@
         <v>420</v>
       </c>
       <c r="B317" t="s">
-        <v>585</v>
+        <v>449</v>
       </c>
       <c r="D317" t="s">
-        <v>606</v>
+        <v>443</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
@@ -6400,10 +6412,10 @@
         <v>420</v>
       </c>
       <c r="B318" t="s">
-        <v>586</v>
+        <v>545</v>
       </c>
       <c r="D318" t="s">
-        <v>607</v>
+        <v>444</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
@@ -6411,10 +6423,10 @@
         <v>420</v>
       </c>
       <c r="B319" t="s">
-        <v>445</v>
+        <v>585</v>
       </c>
       <c r="D319" t="s">
-        <v>446</v>
+        <v>606</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
@@ -6422,10 +6434,10 @@
         <v>420</v>
       </c>
       <c r="B320" t="s">
-        <v>447</v>
+        <v>586</v>
       </c>
       <c r="D320" t="s">
-        <v>448</v>
+        <v>607</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
@@ -6433,10 +6445,10 @@
         <v>420</v>
       </c>
       <c r="B321" t="s">
-        <v>654</v>
+        <v>445</v>
       </c>
       <c r="D321" t="s">
-        <v>655</v>
+        <v>446</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -6444,10 +6456,10 @@
         <v>420</v>
       </c>
       <c r="B322" t="s">
-        <v>332</v>
+        <v>447</v>
       </c>
       <c r="D322" t="s">
-        <v>333</v>
+        <v>448</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
@@ -6455,10 +6467,10 @@
         <v>420</v>
       </c>
       <c r="B323" t="s">
-        <v>101</v>
+        <v>654</v>
       </c>
       <c r="D323" t="s">
-        <v>102</v>
+        <v>655</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
@@ -6466,10 +6478,10 @@
         <v>420</v>
       </c>
       <c r="B324" t="s">
-        <v>103</v>
+        <v>332</v>
       </c>
       <c r="D324" t="s">
-        <v>104</v>
+        <v>333</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -6477,10 +6489,10 @@
         <v>420</v>
       </c>
       <c r="B325" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D325" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -6488,10 +6500,10 @@
         <v>420</v>
       </c>
       <c r="B326" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D326" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -6499,10 +6511,10 @@
         <v>420</v>
       </c>
       <c r="B327" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D327" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -6510,10 +6522,10 @@
         <v>420</v>
       </c>
       <c r="B328" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D328" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
@@ -6521,10 +6533,10 @@
         <v>420</v>
       </c>
       <c r="B329" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D329" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
@@ -6532,10 +6544,10 @@
         <v>420</v>
       </c>
       <c r="B330" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D330" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
@@ -6543,10 +6555,10 @@
         <v>420</v>
       </c>
       <c r="B331" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D331" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -6554,10 +6566,10 @@
         <v>420</v>
       </c>
       <c r="B332" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D332" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
@@ -6565,10 +6577,10 @@
         <v>420</v>
       </c>
       <c r="B333" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D333" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
@@ -6576,10 +6588,10 @@
         <v>420</v>
       </c>
       <c r="B334" t="s">
-        <v>450</v>
+        <v>119</v>
       </c>
       <c r="D334" t="s">
-        <v>451</v>
+        <v>120</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -6587,10 +6599,10 @@
         <v>420</v>
       </c>
       <c r="B335" t="s">
-        <v>549</v>
+        <v>121</v>
       </c>
       <c r="D335" t="s">
-        <v>550</v>
+        <v>122</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -6598,10 +6610,10 @@
         <v>420</v>
       </c>
       <c r="B336" t="s">
-        <v>129</v>
+        <v>450</v>
       </c>
       <c r="D336" t="s">
-        <v>130</v>
+        <v>451</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -6609,10 +6621,10 @@
         <v>420</v>
       </c>
       <c r="B337" t="s">
-        <v>592</v>
+        <v>549</v>
       </c>
       <c r="D337" t="s">
-        <v>612</v>
+        <v>550</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
@@ -6620,10 +6632,10 @@
         <v>420</v>
       </c>
       <c r="B338" t="s">
-        <v>622</v>
+        <v>129</v>
       </c>
       <c r="D338" t="s">
-        <v>623</v>
+        <v>130</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
@@ -6631,10 +6643,10 @@
         <v>420</v>
       </c>
       <c r="B339" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D339" t="s">
-        <v>626</v>
+        <v>612</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -6642,10 +6654,10 @@
         <v>420</v>
       </c>
       <c r="B340" t="s">
-        <v>452</v>
+        <v>622</v>
       </c>
       <c r="D340" t="s">
-        <v>453</v>
+        <v>623</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
@@ -6653,10 +6665,10 @@
         <v>420</v>
       </c>
       <c r="B341" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="D341" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -6664,10 +6676,10 @@
         <v>420</v>
       </c>
       <c r="B342" t="s">
-        <v>590</v>
+        <v>452</v>
       </c>
       <c r="D342" t="s">
-        <v>611</v>
+        <v>453</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
@@ -6675,10 +6687,10 @@
         <v>420</v>
       </c>
       <c r="B343" t="s">
-        <v>659</v>
+        <v>598</v>
       </c>
       <c r="D343" t="s">
-        <v>660</v>
+        <v>618</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -6686,10 +6698,10 @@
         <v>420</v>
       </c>
       <c r="B344" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="D344" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -6697,10 +6709,10 @@
         <v>420</v>
       </c>
       <c r="B345" t="s">
-        <v>584</v>
+        <v>659</v>
       </c>
       <c r="D345" t="s">
-        <v>605</v>
+        <v>660</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
@@ -6708,10 +6720,10 @@
         <v>420</v>
       </c>
       <c r="B346" t="s">
-        <v>455</v>
+        <v>595</v>
       </c>
       <c r="D346" t="s">
-        <v>456</v>
+        <v>615</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
@@ -6719,10 +6731,10 @@
         <v>420</v>
       </c>
       <c r="B347" t="s">
-        <v>457</v>
+        <v>584</v>
       </c>
       <c r="D347" t="s">
-        <v>454</v>
+        <v>605</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -6730,10 +6742,10 @@
         <v>420</v>
       </c>
       <c r="B348" t="s">
-        <v>362</v>
+        <v>455</v>
       </c>
       <c r="D348" t="s">
-        <v>362</v>
+        <v>456</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
@@ -6741,10 +6753,10 @@
         <v>420</v>
       </c>
       <c r="B349" t="s">
-        <v>368</v>
+        <v>457</v>
       </c>
       <c r="D349" t="s">
-        <v>368</v>
+        <v>454</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
@@ -6752,10 +6764,10 @@
         <v>420</v>
       </c>
       <c r="B350" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="D350" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
@@ -6763,10 +6775,10 @@
         <v>420</v>
       </c>
       <c r="B351" t="s">
-        <v>596</v>
+        <v>368</v>
       </c>
       <c r="D351" t="s">
-        <v>616</v>
+        <v>368</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
@@ -6774,10 +6786,10 @@
         <v>420</v>
       </c>
       <c r="B352" t="s">
-        <v>597</v>
+        <v>369</v>
       </c>
       <c r="D352" t="s">
-        <v>617</v>
+        <v>370</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
@@ -6785,10 +6797,10 @@
         <v>420</v>
       </c>
       <c r="B353" t="s">
-        <v>377</v>
+        <v>596</v>
       </c>
       <c r="D353" t="s">
-        <v>378</v>
+        <v>616</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
@@ -6796,10 +6808,10 @@
         <v>420</v>
       </c>
       <c r="B354" t="s">
-        <v>156</v>
+        <v>597</v>
       </c>
       <c r="D354" t="s">
-        <v>157</v>
+        <v>617</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
@@ -6807,10 +6819,10 @@
         <v>420</v>
       </c>
       <c r="B355" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D355" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
@@ -6818,10 +6830,10 @@
         <v>420</v>
       </c>
       <c r="B356" t="s">
-        <v>656</v>
+        <v>156</v>
       </c>
       <c r="D356" t="s">
-        <v>657</v>
+        <v>157</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
@@ -6829,10 +6841,10 @@
         <v>420</v>
       </c>
       <c r="B357" t="s">
-        <v>17</v>
+        <v>379</v>
       </c>
       <c r="D357" t="s">
-        <v>164</v>
+        <v>380</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
@@ -6840,10 +6852,10 @@
         <v>420</v>
       </c>
       <c r="B358" t="s">
-        <v>458</v>
+        <v>656</v>
       </c>
       <c r="D358" t="s">
-        <v>459</v>
+        <v>657</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
@@ -6851,10 +6863,10 @@
         <v>420</v>
       </c>
       <c r="B359" t="s">
-        <v>460</v>
+        <v>17</v>
       </c>
       <c r="D359" t="s">
-        <v>461</v>
+        <v>164</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
@@ -6862,10 +6874,10 @@
         <v>420</v>
       </c>
       <c r="B360" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D360" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
@@ -6873,10 +6885,10 @@
         <v>420</v>
       </c>
       <c r="B361" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="D361" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
@@ -6884,10 +6896,10 @@
         <v>420</v>
       </c>
       <c r="B362" t="s">
-        <v>399</v>
+        <v>462</v>
       </c>
       <c r="D362" t="s">
-        <v>400</v>
+        <v>463</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
@@ -6895,10 +6907,10 @@
         <v>420</v>
       </c>
       <c r="B363" t="s">
-        <v>407</v>
+        <v>464</v>
       </c>
       <c r="D363" t="s">
-        <v>408</v>
+        <v>465</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
@@ -6906,10 +6918,10 @@
         <v>420</v>
       </c>
       <c r="B364" t="s">
-        <v>466</v>
+        <v>399</v>
       </c>
       <c r="D364" t="s">
-        <v>467</v>
+        <v>400</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
@@ -6917,10 +6929,10 @@
         <v>420</v>
       </c>
       <c r="B365" t="s">
-        <v>187</v>
+        <v>407</v>
       </c>
       <c r="D365" t="s">
-        <v>188</v>
+        <v>408</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
@@ -6928,10 +6940,10 @@
         <v>420</v>
       </c>
       <c r="B366" t="s">
-        <v>196</v>
+        <v>466</v>
       </c>
       <c r="D366" t="s">
-        <v>197</v>
+        <v>467</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -6939,10 +6951,10 @@
         <v>420</v>
       </c>
       <c r="B367" t="s">
-        <v>601</v>
+        <v>187</v>
       </c>
       <c r="D367" t="s">
-        <v>621</v>
+        <v>188</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
@@ -6950,10 +6962,10 @@
         <v>420</v>
       </c>
       <c r="B368" t="s">
-        <v>468</v>
+        <v>196</v>
       </c>
       <c r="D368" t="s">
-        <v>469</v>
+        <v>197</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
@@ -6961,10 +6973,10 @@
         <v>420</v>
       </c>
       <c r="B369" t="s">
-        <v>470</v>
+        <v>601</v>
       </c>
       <c r="D369" t="s">
-        <v>471</v>
+        <v>621</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -6972,10 +6984,10 @@
         <v>420</v>
       </c>
       <c r="B370" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="D370" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
@@ -6983,10 +6995,10 @@
         <v>420</v>
       </c>
       <c r="B371" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D371" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
@@ -6994,10 +7006,10 @@
         <v>420</v>
       </c>
       <c r="B372" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="D372" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -7005,10 +7017,10 @@
         <v>420</v>
       </c>
       <c r="B373" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="D373" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
@@ -7016,10 +7028,10 @@
         <v>420</v>
       </c>
       <c r="B374" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="D374" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -7027,10 +7039,10 @@
         <v>420</v>
       </c>
       <c r="B375" t="s">
-        <v>599</v>
+        <v>478</v>
       </c>
       <c r="D375" t="s">
-        <v>619</v>
+        <v>479</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -7038,10 +7050,10 @@
         <v>420</v>
       </c>
       <c r="B376" t="s">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="D376" t="s">
-        <v>620</v>
+        <v>481</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
@@ -7049,10 +7061,10 @@
         <v>420</v>
       </c>
       <c r="B377" t="s">
-        <v>482</v>
+        <v>599</v>
       </c>
       <c r="D377" t="s">
-        <v>483</v>
+        <v>619</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
@@ -7060,10 +7072,10 @@
         <v>420</v>
       </c>
       <c r="B378" t="s">
-        <v>484</v>
+        <v>600</v>
       </c>
       <c r="D378" t="s">
-        <v>485</v>
+        <v>620</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
@@ -7071,10 +7083,10 @@
         <v>420</v>
       </c>
       <c r="B379" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D379" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
@@ -7082,10 +7094,10 @@
         <v>420</v>
       </c>
       <c r="B380" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D380" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
@@ -7093,10 +7105,10 @@
         <v>420</v>
       </c>
       <c r="B381" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="D381" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
@@ -7104,10 +7116,10 @@
         <v>420</v>
       </c>
       <c r="B382" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="D382" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
@@ -7115,10 +7127,10 @@
         <v>420</v>
       </c>
       <c r="B383" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="D383" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
@@ -7126,10 +7138,10 @@
         <v>420</v>
       </c>
       <c r="B384" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="D384" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
@@ -7137,10 +7149,10 @@
         <v>420</v>
       </c>
       <c r="B385" t="s">
-        <v>582</v>
+        <v>494</v>
       </c>
       <c r="D385" t="s">
-        <v>658</v>
+        <v>495</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
@@ -7148,10 +7160,10 @@
         <v>420</v>
       </c>
       <c r="B386" t="s">
-        <v>583</v>
+        <v>496</v>
       </c>
       <c r="D386" t="s">
-        <v>604</v>
+        <v>497</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
@@ -7159,10 +7171,10 @@
         <v>420</v>
       </c>
       <c r="B387" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D387" t="s">
-        <v>603</v>
+        <v>658</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
@@ -7170,10 +7182,10 @@
         <v>420</v>
       </c>
       <c r="B388" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D388" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
@@ -7181,10 +7193,10 @@
         <v>420</v>
       </c>
       <c r="B389" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="D389" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
@@ -7192,22 +7204,44 @@
         <v>420</v>
       </c>
       <c r="B390" t="s">
+        <v>580</v>
+      </c>
+      <c r="D390" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>420</v>
+      </c>
+      <c r="B391" t="s">
+        <v>594</v>
+      </c>
+      <c r="D391" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>420</v>
+      </c>
+      <c r="B392" t="s">
         <v>593</v>
       </c>
-      <c r="D390" t="s">
+      <c r="D392" t="s">
         <v>613</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D390" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D390">
-      <sortCondition ref="A2:A390"/>
-      <sortCondition ref="B2:B390"/>
+  <autoFilter ref="A1:D392" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D392">
+      <sortCondition ref="A2:A392"/>
+      <sortCondition ref="B2:B392"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A254:D390">
-    <sortCondition ref="A2:A395"/>
-    <sortCondition ref="B2:B395"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A254:D392">
+    <sortCondition ref="A2:A397"/>
+    <sortCondition ref="B2:B397"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_dev\Seal-Report\Repository\Settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9F0A79-57BA-409E-A2EC-A4B00734C07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D631D2-3337-45C8-8B07-36A62594317C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31155" yWindow="750" windowWidth="26445" windowHeight="14655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2130" yWindow="1050" windowWidth="25530" windowHeight="16515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Translations" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$D$392</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$D$394</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="721">
   <si>
     <t>Context</t>
   </si>
@@ -2055,6 +2055,150 @@
   </si>
   <si>
     <t>Télécharger le rapport</t>
+  </si>
+  <si>
+    <t>Report description</t>
+  </si>
+  <si>
+    <t>Display: Information messages</t>
+  </si>
+  <si>
+    <t>Display: Execution messages</t>
+  </si>
+  <si>
+    <t>HTML Print: Show report information</t>
+  </si>
+  <si>
+    <t>HTML Print: Show messages</t>
+  </si>
+  <si>
+    <t>Description du rapport</t>
+  </si>
+  <si>
+    <t>Affichage : Messages d'information</t>
+  </si>
+  <si>
+    <t>Affichage : Messages d'exécution</t>
+  </si>
+  <si>
+    <t>Impression HTML : Afficher les informations du rapport</t>
+  </si>
+  <si>
+    <t>Impression HTML : Afficher les messages</t>
+  </si>
+  <si>
+    <t>Auto Fit columns</t>
+  </si>
+  <si>
+    <t>Ajustement automatique des colonnes</t>
+  </si>
+  <si>
+    <t>Print: Page orientation</t>
+  </si>
+  <si>
+    <t>Impression : Orientation de la page</t>
+  </si>
+  <si>
+    <t>Print: Show logo</t>
+  </si>
+  <si>
+    <t>Impression : Afficher le logo</t>
+  </si>
+  <si>
+    <t>Show messages</t>
+  </si>
+  <si>
+    <t>Afficher les messages</t>
+  </si>
+  <si>
+    <t>Show report information</t>
+  </si>
+  <si>
+    <t>Afficher les informations du rapport</t>
+  </si>
+  <si>
+    <t>Display header footer</t>
+  </si>
+  <si>
+    <t>Landscape</t>
+  </si>
+  <si>
+    <t>Scale</t>
+  </si>
+  <si>
+    <t>Page orientation</t>
+  </si>
+  <si>
+    <t>Orientation de la page</t>
+  </si>
+  <si>
+    <t>Page size</t>
+  </si>
+  <si>
+    <t>Taille de la page</t>
+  </si>
+  <si>
+    <t>Information panel enabled</t>
+  </si>
+  <si>
+    <t>Information panel enabled and shown</t>
+  </si>
+  <si>
+    <t>Information panel hidden</t>
+  </si>
+  <si>
+    <t>Messages panel enabled and shown</t>
+  </si>
+  <si>
+    <t>Messages panel enabled and shown only during execution</t>
+  </si>
+  <si>
+    <t>Messages panel hidden</t>
+  </si>
+  <si>
+    <t>Messages panel enabled</t>
+  </si>
+  <si>
+    <t>Panneau d'information activé</t>
+  </si>
+  <si>
+    <t>Panneau d'information activé et affiché</t>
+  </si>
+  <si>
+    <t>Panneau d'information masqué</t>
+  </si>
+  <si>
+    <t>Panneau de messages activé</t>
+  </si>
+  <si>
+    <t>Panneau de messages activé et affiché</t>
+  </si>
+  <si>
+    <t>Panneau de messages activé et affiché uniquement pendant l'exécution</t>
+  </si>
+  <si>
+    <t>Panneau de messages masqué</t>
+  </si>
+  <si>
+    <t>Afficher l'en-tête et le pied de page</t>
+  </si>
+  <si>
+    <t>Paysage</t>
+  </si>
+  <si>
+    <t>Échelle</t>
+  </si>
+  <si>
+    <t>Tabs to show</t>
+  </si>
+  <si>
+    <t>Onglets visibles</t>
+  </si>
+  <si>
+    <t>Report result options</t>
+  </si>
+  <si>
+    <t>Options du résultat du rapport</t>
   </si>
 </sst>
 </file>
@@ -2909,7 +3053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D392"/>
+  <dimension ref="A1:D425"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -3134,10 +3278,10 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>683</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>684</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3145,10 +3289,10 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -3156,10 +3300,10 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -3167,10 +3311,10 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -3178,10 +3322,10 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -3189,10 +3333,10 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -3200,10 +3344,10 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -3211,10 +3355,10 @@
         <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>245</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -3222,10 +3366,10 @@
         <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>244</v>
       </c>
       <c r="D28" t="s">
-        <v>59</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -3233,10 +3377,10 @@
         <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -3244,10 +3388,10 @@
         <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3255,10 +3399,10 @@
         <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -3266,10 +3410,10 @@
         <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>517</v>
+        <v>52</v>
       </c>
       <c r="D32" t="s">
-        <v>518</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3277,10 +3421,10 @@
         <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>517</v>
       </c>
       <c r="D33" t="s">
-        <v>57</v>
+        <v>518</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3288,10 +3432,10 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>272</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>273</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3299,10 +3443,10 @@
         <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>60</v>
+        <v>272</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -3310,10 +3454,10 @@
         <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D36" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -3321,10 +3465,10 @@
         <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>693</v>
       </c>
       <c r="D37" t="s">
-        <v>66</v>
+        <v>714</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -3332,10 +3476,10 @@
         <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>63</v>
+        <v>675</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>680</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -3343,10 +3487,10 @@
         <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>67</v>
+        <v>675</v>
       </c>
       <c r="D39" t="s">
-        <v>68</v>
+        <v>680</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -3354,10 +3498,10 @@
         <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>674</v>
       </c>
       <c r="D40" t="s">
-        <v>70</v>
+        <v>679</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3365,10 +3509,10 @@
         <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>539</v>
+        <v>674</v>
       </c>
       <c r="D41" t="s">
-        <v>540</v>
+        <v>679</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -3376,10 +3520,10 @@
         <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D42" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -3387,10 +3531,10 @@
         <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D43" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -3398,10 +3542,10 @@
         <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D44" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -3409,10 +3553,10 @@
         <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -3420,10 +3564,10 @@
         <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D46" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -3431,10 +3575,10 @@
         <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>81</v>
+        <v>539</v>
       </c>
       <c r="D47" t="s">
-        <v>82</v>
+        <v>540</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -3442,10 +3586,10 @@
         <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D48" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -3453,10 +3597,10 @@
         <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -3464,10 +3608,10 @@
         <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D50" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -3475,10 +3619,10 @@
         <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D51" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -3486,10 +3630,10 @@
         <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D52" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -3497,10 +3641,10 @@
         <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>242</v>
+        <v>81</v>
       </c>
       <c r="D53" t="s">
-        <v>243</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -3508,10 +3652,10 @@
         <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D54" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -3519,10 +3663,10 @@
         <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D55" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3530,10 +3674,10 @@
         <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>270</v>
+        <v>87</v>
       </c>
       <c r="D56" t="s">
-        <v>271</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3541,10 +3685,10 @@
         <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D57" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -3552,10 +3696,10 @@
         <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D58" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -3563,10 +3707,10 @@
         <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>101</v>
+        <v>242</v>
       </c>
       <c r="D59" t="s">
-        <v>102</v>
+        <v>243</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -3574,10 +3718,10 @@
         <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>661</v>
+        <v>93</v>
       </c>
       <c r="D60" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -3585,10 +3729,10 @@
         <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>662</v>
+        <v>95</v>
       </c>
       <c r="D61" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -3596,10 +3740,10 @@
         <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>103</v>
+        <v>677</v>
       </c>
       <c r="D62" t="s">
-        <v>104</v>
+        <v>682</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -3607,10 +3751,10 @@
         <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>105</v>
+        <v>677</v>
       </c>
       <c r="D63" t="s">
-        <v>106</v>
+        <v>682</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -3618,10 +3762,10 @@
         <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>107</v>
+        <v>676</v>
       </c>
       <c r="D64" t="s">
-        <v>108</v>
+        <v>681</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -3629,10 +3773,10 @@
         <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>109</v>
+        <v>676</v>
       </c>
       <c r="D65" t="s">
-        <v>110</v>
+        <v>681</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -3640,10 +3784,10 @@
         <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="D66" t="s">
-        <v>112</v>
+        <v>271</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -3651,10 +3795,10 @@
         <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>113</v>
+        <v>700</v>
       </c>
       <c r="D67" t="s">
-        <v>114</v>
+        <v>707</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -3662,10 +3806,10 @@
         <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>115</v>
+        <v>701</v>
       </c>
       <c r="D68" t="s">
-        <v>116</v>
+        <v>708</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -3673,10 +3817,10 @@
         <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>117</v>
+        <v>702</v>
       </c>
       <c r="D69" t="s">
-        <v>118</v>
+        <v>709</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -3684,10 +3828,10 @@
         <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="D70" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -3695,10 +3839,10 @@
         <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D71" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -3706,10 +3850,10 @@
         <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="D72" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -3717,10 +3861,10 @@
         <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>125</v>
+        <v>661</v>
       </c>
       <c r="D73" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -3728,10 +3872,10 @@
         <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="D74" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -3739,10 +3883,10 @@
         <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="D75" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -3750,10 +3894,10 @@
         <v>17</v>
       </c>
       <c r="B76" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="D76" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -3761,10 +3905,10 @@
         <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="D77" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -3772,10 +3916,10 @@
         <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="D78" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -3783,10 +3927,10 @@
         <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>266</v>
+        <v>662</v>
       </c>
       <c r="D79" t="s">
-        <v>267</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -3794,10 +3938,10 @@
         <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>262</v>
+        <v>113</v>
       </c>
       <c r="D80" t="s">
-        <v>263</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -3805,10 +3949,10 @@
         <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="D81" t="s">
-        <v>251</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -3816,10 +3960,10 @@
         <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>256</v>
+        <v>117</v>
       </c>
       <c r="D82" t="s">
-        <v>257</v>
+        <v>118</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -3827,10 +3971,10 @@
         <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D83" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -3838,10 +3982,10 @@
         <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="D84" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -3849,10 +3993,10 @@
         <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>141</v>
+        <v>694</v>
       </c>
       <c r="D85" t="s">
-        <v>142</v>
+        <v>715</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -3860,10 +4004,10 @@
         <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="D86" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -3871,10 +4015,10 @@
         <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D87" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -3882,10 +4026,10 @@
         <v>17</v>
       </c>
       <c r="B88" t="s">
-        <v>147</v>
+        <v>706</v>
       </c>
       <c r="D88" t="s">
-        <v>62</v>
+        <v>710</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -3893,10 +4037,10 @@
         <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>148</v>
+        <v>703</v>
       </c>
       <c r="D89" t="s">
-        <v>149</v>
+        <v>711</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -3904,10 +4048,10 @@
         <v>17</v>
       </c>
       <c r="B90" t="s">
-        <v>150</v>
+        <v>704</v>
       </c>
       <c r="D90" t="s">
-        <v>150</v>
+        <v>712</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -3915,10 +4059,10 @@
         <v>17</v>
       </c>
       <c r="B91" t="s">
-        <v>151</v>
+        <v>705</v>
       </c>
       <c r="D91" t="s">
-        <v>152</v>
+        <v>713</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -3926,10 +4070,10 @@
         <v>17</v>
       </c>
       <c r="B92" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="D92" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -3937,10 +4081,10 @@
         <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>268</v>
+        <v>129</v>
       </c>
       <c r="D93" t="s">
-        <v>269</v>
+        <v>130</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -3948,10 +4092,10 @@
         <v>17</v>
       </c>
       <c r="B94" t="s">
-        <v>274</v>
+        <v>131</v>
       </c>
       <c r="D94" t="s">
-        <v>275</v>
+        <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -3959,10 +4103,10 @@
         <v>17</v>
       </c>
       <c r="B95" t="s">
-        <v>276</v>
+        <v>133</v>
       </c>
       <c r="D95" t="s">
-        <v>277</v>
+        <v>134</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -3970,10 +4114,10 @@
         <v>17</v>
       </c>
       <c r="B96" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="D96" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -3981,10 +4125,10 @@
         <v>17</v>
       </c>
       <c r="B97" t="s">
-        <v>503</v>
+        <v>266</v>
       </c>
       <c r="D97" t="s">
-        <v>504</v>
+        <v>267</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -3992,10 +4136,10 @@
         <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>154</v>
+        <v>262</v>
       </c>
       <c r="D98" t="s">
-        <v>155</v>
+        <v>263</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -4003,10 +4147,10 @@
         <v>17</v>
       </c>
       <c r="B99" t="s">
-        <v>502</v>
+        <v>250</v>
       </c>
       <c r="D99" t="s">
-        <v>507</v>
+        <v>251</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -4014,10 +4158,10 @@
         <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>511</v>
+        <v>256</v>
       </c>
       <c r="D100" t="s">
-        <v>512</v>
+        <v>257</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -4025,10 +4169,10 @@
         <v>17</v>
       </c>
       <c r="B101" t="s">
-        <v>264</v>
+        <v>452</v>
       </c>
       <c r="D101" t="s">
-        <v>265</v>
+        <v>453</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -4036,10 +4180,10 @@
         <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>260</v>
+        <v>137</v>
       </c>
       <c r="D102" t="s">
-        <v>261</v>
+        <v>138</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -4047,10 +4191,10 @@
         <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>248</v>
+        <v>139</v>
       </c>
       <c r="D103" t="s">
-        <v>249</v>
+        <v>140</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -4058,10 +4202,10 @@
         <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>254</v>
+        <v>141</v>
       </c>
       <c r="D104" t="s">
-        <v>255</v>
+        <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -4069,10 +4213,10 @@
         <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="D105" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -4080,10 +4224,10 @@
         <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="D106" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -4091,10 +4235,10 @@
         <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="D107" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -4102,10 +4246,10 @@
         <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>230</v>
+        <v>148</v>
       </c>
       <c r="D108" t="s">
-        <v>231</v>
+        <v>149</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -4113,10 +4257,10 @@
         <v>17</v>
       </c>
       <c r="B109" t="s">
-        <v>17</v>
+        <v>368</v>
       </c>
       <c r="D109" t="s">
-        <v>164</v>
+        <v>368</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -4124,10 +4268,10 @@
         <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>165</v>
+        <v>663</v>
       </c>
       <c r="D110" t="s">
-        <v>166</v>
+        <v>664</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -4135,10 +4279,10 @@
         <v>17</v>
       </c>
       <c r="B111" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D111" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -4146,10 +4290,10 @@
         <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="D112" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -4157,10 +4301,10 @@
         <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>171</v>
+        <v>696</v>
       </c>
       <c r="D113" t="s">
-        <v>172</v>
+        <v>697</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -4168,10 +4312,10 @@
         <v>17</v>
       </c>
       <c r="B114" t="s">
-        <v>173</v>
+        <v>698</v>
       </c>
       <c r="D114" t="s">
-        <v>174</v>
+        <v>699</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -4179,10 +4323,10 @@
         <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="D115" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -4190,10 +4334,10 @@
         <v>17</v>
       </c>
       <c r="B116" t="s">
-        <v>176</v>
+        <v>268</v>
       </c>
       <c r="D116" t="s">
-        <v>177</v>
+        <v>269</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -4201,10 +4345,10 @@
         <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>178</v>
+        <v>274</v>
       </c>
       <c r="D117" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -4212,10 +4356,10 @@
         <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>180</v>
+        <v>276</v>
       </c>
       <c r="D118" t="s">
-        <v>181</v>
+        <v>277</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -4223,10 +4367,10 @@
         <v>17</v>
       </c>
       <c r="B119" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="D119" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -4234,10 +4378,10 @@
         <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>258</v>
+        <v>503</v>
       </c>
       <c r="D120" t="s">
-        <v>259</v>
+        <v>504</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -4245,10 +4389,10 @@
         <v>17</v>
       </c>
       <c r="B121" t="s">
-        <v>246</v>
+        <v>154</v>
       </c>
       <c r="D121" t="s">
-        <v>247</v>
+        <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -4256,10 +4400,10 @@
         <v>17</v>
       </c>
       <c r="B122" t="s">
-        <v>280</v>
+        <v>502</v>
       </c>
       <c r="D122" t="s">
-        <v>281</v>
+        <v>507</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -4267,10 +4411,10 @@
         <v>17</v>
       </c>
       <c r="B123" t="s">
-        <v>252</v>
+        <v>511</v>
       </c>
       <c r="D123" t="s">
-        <v>253</v>
+        <v>512</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -4278,10 +4422,10 @@
         <v>17</v>
       </c>
       <c r="B124" t="s">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="D124" t="s">
-        <v>184</v>
+        <v>265</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -4289,10 +4433,10 @@
         <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>187</v>
+        <v>260</v>
       </c>
       <c r="D125" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -4300,10 +4444,10 @@
         <v>17</v>
       </c>
       <c r="B126" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="D126" t="s">
-        <v>190</v>
+        <v>249</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -4311,10 +4455,10 @@
         <v>17</v>
       </c>
       <c r="B127" t="s">
-        <v>185</v>
+        <v>254</v>
       </c>
       <c r="D127" t="s">
-        <v>186</v>
+        <v>255</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -4322,10 +4466,10 @@
         <v>17</v>
       </c>
       <c r="B128" t="s">
-        <v>191</v>
+        <v>685</v>
       </c>
       <c r="D128" t="s">
-        <v>192</v>
+        <v>686</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
@@ -4333,10 +4477,10 @@
         <v>17</v>
       </c>
       <c r="B129" t="s">
-        <v>193</v>
+        <v>687</v>
       </c>
       <c r="D129" t="s">
-        <v>194</v>
+        <v>688</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -4344,10 +4488,10 @@
         <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
       <c r="D130" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
@@ -4355,10 +4499,10 @@
         <v>17</v>
       </c>
       <c r="B131" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="D131" t="s">
-        <v>197</v>
+        <v>159</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
@@ -4366,10 +4510,10 @@
         <v>17</v>
       </c>
       <c r="B132" t="s">
-        <v>282</v>
+        <v>162</v>
       </c>
       <c r="D132" t="s">
-        <v>283</v>
+        <v>163</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
@@ -4377,10 +4521,10 @@
         <v>17</v>
       </c>
       <c r="B133" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="D133" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
@@ -4388,10 +4532,10 @@
         <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="D134" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -4399,10 +4543,10 @@
         <v>17</v>
       </c>
       <c r="B135" t="s">
-        <v>202</v>
+        <v>673</v>
       </c>
       <c r="D135" t="s">
-        <v>201</v>
+        <v>678</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -4410,10 +4554,10 @@
         <v>17</v>
       </c>
       <c r="B136" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="D136" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -4421,10 +4565,10 @@
         <v>17</v>
       </c>
       <c r="B137" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="D137" t="s">
-        <v>206</v>
+        <v>168</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
@@ -4432,10 +4576,10 @@
         <v>17</v>
       </c>
       <c r="B138" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="D138" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -4443,10 +4587,10 @@
         <v>17</v>
       </c>
       <c r="B139" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="D139" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
@@ -4454,10 +4598,10 @@
         <v>17</v>
       </c>
       <c r="B140" t="s">
-        <v>223</v>
+        <v>719</v>
       </c>
       <c r="D140" t="s">
-        <v>224</v>
+        <v>720</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
@@ -4465,10 +4609,10 @@
         <v>17</v>
       </c>
       <c r="B141" t="s">
-        <v>221</v>
+        <v>173</v>
       </c>
       <c r="D141" t="s">
-        <v>222</v>
+        <v>174</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -4476,10 +4620,10 @@
         <v>17</v>
       </c>
       <c r="B142" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="D142" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -4487,10 +4631,10 @@
         <v>17</v>
       </c>
       <c r="B143" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="D143" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -4498,10 +4642,10 @@
         <v>17</v>
       </c>
       <c r="B144" t="s">
-        <v>219</v>
+        <v>695</v>
       </c>
       <c r="D144" t="s">
-        <v>220</v>
+        <v>716</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -4509,10 +4653,10 @@
         <v>17</v>
       </c>
       <c r="B145" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="D145" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -4520,10 +4664,10 @@
         <v>17</v>
       </c>
       <c r="B146" t="s">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="D146" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
@@ -4531,10 +4675,10 @@
         <v>17</v>
       </c>
       <c r="B147" t="s">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="D147" t="s">
-        <v>226</v>
+        <v>33</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
@@ -4542,10 +4686,10 @@
         <v>17</v>
       </c>
       <c r="B148" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="D148" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -4553,10 +4697,10 @@
         <v>17</v>
       </c>
       <c r="B149" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="D149" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -4564,10 +4708,10 @@
         <v>17</v>
       </c>
       <c r="B150" t="s">
-        <v>228</v>
+        <v>280</v>
       </c>
       <c r="D150" t="s">
-        <v>229</v>
+        <v>281</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
@@ -4575,10 +4719,10 @@
         <v>17</v>
       </c>
       <c r="B151" t="s">
-        <v>482</v>
+        <v>252</v>
       </c>
       <c r="D151" t="s">
-        <v>483</v>
+        <v>253</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
@@ -4586,10 +4730,10 @@
         <v>17</v>
       </c>
       <c r="B152" t="s">
-        <v>232</v>
+        <v>183</v>
       </c>
       <c r="D152" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
@@ -4597,10 +4741,10 @@
         <v>17</v>
       </c>
       <c r="B153" t="s">
-        <v>535</v>
+        <v>187</v>
       </c>
       <c r="D153" t="s">
-        <v>536</v>
+        <v>188</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
@@ -4608,10 +4752,10 @@
         <v>17</v>
       </c>
       <c r="B154" t="s">
-        <v>234</v>
+        <v>189</v>
       </c>
       <c r="D154" t="s">
-        <v>235</v>
+        <v>190</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
@@ -4619,10 +4763,10 @@
         <v>17</v>
       </c>
       <c r="B155" t="s">
-        <v>525</v>
+        <v>689</v>
       </c>
       <c r="D155" t="s">
-        <v>526</v>
+        <v>690</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
@@ -4630,10 +4774,10 @@
         <v>17</v>
       </c>
       <c r="B156" t="s">
-        <v>236</v>
+        <v>689</v>
       </c>
       <c r="D156" t="s">
-        <v>237</v>
+        <v>690</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -4641,10 +4785,10 @@
         <v>17</v>
       </c>
       <c r="B157" t="s">
-        <v>527</v>
+        <v>691</v>
       </c>
       <c r="D157" t="s">
-        <v>528</v>
+        <v>692</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
@@ -4652,10 +4796,10 @@
         <v>17</v>
       </c>
       <c r="B158" t="s">
-        <v>534</v>
+        <v>691</v>
       </c>
       <c r="D158" t="s">
-        <v>533</v>
+        <v>692</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
@@ -4663,10 +4807,10 @@
         <v>17</v>
       </c>
       <c r="B159" t="s">
-        <v>537</v>
+        <v>185</v>
       </c>
       <c r="D159" t="s">
-        <v>538</v>
+        <v>186</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
@@ -4674,10 +4818,10 @@
         <v>17</v>
       </c>
       <c r="B160" t="s">
-        <v>238</v>
+        <v>191</v>
       </c>
       <c r="D160" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -4685,10 +4829,10 @@
         <v>17</v>
       </c>
       <c r="B161" t="s">
-        <v>240</v>
+        <v>193</v>
       </c>
       <c r="D161" t="s">
-        <v>241</v>
+        <v>194</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
@@ -4696,10 +4840,10 @@
         <v>17</v>
       </c>
       <c r="B162" t="s">
-        <v>529</v>
+        <v>195</v>
       </c>
       <c r="D162" t="s">
-        <v>530</v>
+        <v>82</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -4707,10 +4851,10 @@
         <v>17</v>
       </c>
       <c r="B163" t="s">
-        <v>531</v>
+        <v>196</v>
       </c>
       <c r="D163" t="s">
-        <v>532</v>
+        <v>197</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
@@ -4718,43 +4862,43 @@
         <v>17</v>
       </c>
       <c r="B164" t="s">
-        <v>541</v>
+        <v>282</v>
       </c>
       <c r="D164" t="s">
-        <v>542</v>
+        <v>283</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B165" t="s">
-        <v>285</v>
+        <v>198</v>
       </c>
       <c r="D165" t="s">
-        <v>286</v>
+        <v>199</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B166" t="s">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="D166" t="s">
-        <v>33</v>
+        <v>201</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B167" t="s">
-        <v>287</v>
+        <v>202</v>
       </c>
       <c r="D167" t="s">
-        <v>288</v>
+        <v>201</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
@@ -4762,340 +4906,340 @@
         <v>17</v>
       </c>
       <c r="B168" t="s">
-        <v>663</v>
+        <v>717</v>
       </c>
       <c r="D168" t="s">
-        <v>664</v>
+        <v>718</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B169" t="s">
-        <v>629</v>
+        <v>203</v>
       </c>
       <c r="D169" t="s">
-        <v>642</v>
+        <v>204</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B170" t="s">
-        <v>44</v>
+        <v>205</v>
       </c>
       <c r="D170" t="s">
-        <v>45</v>
+        <v>206</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B171" t="s">
-        <v>565</v>
+        <v>207</v>
       </c>
       <c r="D171" t="s">
-        <v>577</v>
+        <v>208</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B172" t="s">
-        <v>565</v>
+        <v>209</v>
       </c>
       <c r="D172" t="s">
-        <v>577</v>
+        <v>210</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B173" t="s">
-        <v>638</v>
+        <v>223</v>
       </c>
       <c r="D173" t="s">
-        <v>650</v>
+        <v>224</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B174" t="s">
-        <v>289</v>
+        <v>221</v>
       </c>
       <c r="D174" t="s">
-        <v>290</v>
+        <v>222</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B175" t="s">
-        <v>58</v>
+        <v>211</v>
       </c>
       <c r="D175" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B176" t="s">
-        <v>291</v>
+        <v>217</v>
       </c>
       <c r="D176" t="s">
-        <v>292</v>
+        <v>218</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>637</v>
+        <v>219</v>
       </c>
       <c r="D177" t="s">
-        <v>649</v>
+        <v>220</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>296</v>
+        <v>213</v>
       </c>
       <c r="D178" t="s">
-        <v>297</v>
+        <v>214</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>298</v>
+        <v>215</v>
       </c>
       <c r="D179" t="s">
-        <v>299</v>
+        <v>216</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="D180" t="s">
-        <v>301</v>
+        <v>226</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>521</v>
+        <v>278</v>
       </c>
       <c r="D181" t="s">
-        <v>522</v>
+        <v>279</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>302</v>
+        <v>227</v>
       </c>
       <c r="D182" t="s">
-        <v>302</v>
+        <v>227</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>640</v>
+        <v>228</v>
       </c>
       <c r="D183" t="s">
-        <v>652</v>
+        <v>229</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>303</v>
+        <v>482</v>
       </c>
       <c r="D184" t="s">
-        <v>304</v>
+        <v>483</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>305</v>
+        <v>232</v>
       </c>
       <c r="D185" t="s">
-        <v>306</v>
+        <v>233</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>307</v>
+        <v>535</v>
       </c>
       <c r="D186" t="s">
-        <v>308</v>
+        <v>536</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>309</v>
+        <v>234</v>
       </c>
       <c r="D187" t="s">
-        <v>310</v>
+        <v>235</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>311</v>
+        <v>525</v>
       </c>
       <c r="D188" t="s">
-        <v>312</v>
+        <v>526</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>60</v>
+        <v>236</v>
       </c>
       <c r="D189" t="s">
-        <v>60</v>
+        <v>237</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>313</v>
+        <v>527</v>
       </c>
       <c r="D190" t="s">
-        <v>314</v>
+        <v>528</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>315</v>
+        <v>534</v>
       </c>
       <c r="D191" t="s">
-        <v>316</v>
+        <v>533</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>317</v>
+        <v>537</v>
       </c>
       <c r="D192" t="s">
-        <v>318</v>
+        <v>538</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>515</v>
+        <v>238</v>
       </c>
       <c r="D193" t="s">
-        <v>516</v>
+        <v>239</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>555</v>
+        <v>240</v>
       </c>
       <c r="D194" t="s">
-        <v>571</v>
+        <v>241</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="D195" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>556</v>
+        <v>531</v>
       </c>
       <c r="D196" t="s">
-        <v>570</v>
+        <v>532</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>319</v>
+        <v>541</v>
       </c>
       <c r="D197" t="s">
-        <v>319</v>
+        <v>542</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>566</v>
+        <v>496</v>
       </c>
       <c r="D198" t="s">
-        <v>578</v>
+        <v>497</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
@@ -5103,10 +5247,10 @@
         <v>284</v>
       </c>
       <c r="B199" t="s">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="D199" t="s">
-        <v>321</v>
+        <v>286</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
@@ -5114,10 +5258,10 @@
         <v>284</v>
       </c>
       <c r="B200" t="s">
-        <v>322</v>
+        <v>32</v>
       </c>
       <c r="D200" t="s">
-        <v>323</v>
+        <v>33</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
@@ -5125,10 +5269,10 @@
         <v>284</v>
       </c>
       <c r="B201" t="s">
-        <v>639</v>
+        <v>287</v>
       </c>
       <c r="D201" t="s">
-        <v>651</v>
+        <v>288</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
@@ -5136,10 +5280,10 @@
         <v>284</v>
       </c>
       <c r="B202" t="s">
-        <v>324</v>
+        <v>629</v>
       </c>
       <c r="D202" t="s">
-        <v>325</v>
+        <v>642</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
@@ -5147,10 +5291,10 @@
         <v>284</v>
       </c>
       <c r="B203" t="s">
-        <v>635</v>
+        <v>44</v>
       </c>
       <c r="D203" t="s">
-        <v>647</v>
+        <v>45</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
@@ -5158,10 +5302,10 @@
         <v>284</v>
       </c>
       <c r="B204" t="s">
-        <v>498</v>
+        <v>565</v>
       </c>
       <c r="D204" t="s">
-        <v>499</v>
+        <v>577</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
@@ -5169,10 +5313,10 @@
         <v>284</v>
       </c>
       <c r="B205" t="s">
-        <v>631</v>
+        <v>565</v>
       </c>
       <c r="D205" t="s">
-        <v>644</v>
+        <v>577</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
@@ -5180,10 +5324,10 @@
         <v>284</v>
       </c>
       <c r="B206" t="s">
-        <v>326</v>
+        <v>638</v>
       </c>
       <c r="D206" t="s">
-        <v>327</v>
+        <v>650</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -5191,10 +5335,10 @@
         <v>284</v>
       </c>
       <c r="B207" t="s">
-        <v>328</v>
+        <v>289</v>
       </c>
       <c r="D207" t="s">
-        <v>329</v>
+        <v>290</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
@@ -5202,10 +5346,10 @@
         <v>284</v>
       </c>
       <c r="B208" t="s">
-        <v>667</v>
+        <v>58</v>
       </c>
       <c r="D208" t="s">
-        <v>666</v>
+        <v>59</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
@@ -5213,10 +5357,10 @@
         <v>284</v>
       </c>
       <c r="B209" t="s">
-        <v>668</v>
+        <v>291</v>
       </c>
       <c r="D209" t="s">
-        <v>665</v>
+        <v>292</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
@@ -5224,10 +5368,10 @@
         <v>284</v>
       </c>
       <c r="B210" t="s">
-        <v>561</v>
+        <v>637</v>
       </c>
       <c r="D210" t="s">
-        <v>575</v>
+        <v>649</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -5235,10 +5379,10 @@
         <v>284</v>
       </c>
       <c r="B211" t="s">
-        <v>330</v>
+        <v>296</v>
       </c>
       <c r="D211" t="s">
-        <v>331</v>
+        <v>297</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
@@ -5246,10 +5390,10 @@
         <v>284</v>
       </c>
       <c r="B212" t="s">
-        <v>562</v>
+        <v>298</v>
       </c>
       <c r="D212" t="s">
-        <v>627</v>
+        <v>299</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -5257,10 +5401,10 @@
         <v>284</v>
       </c>
       <c r="B213" t="s">
-        <v>558</v>
+        <v>300</v>
       </c>
       <c r="D213" t="s">
-        <v>573</v>
+        <v>301</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
@@ -5268,10 +5412,10 @@
         <v>284</v>
       </c>
       <c r="B214" t="s">
-        <v>334</v>
+        <v>521</v>
       </c>
       <c r="D214" t="s">
-        <v>333</v>
+        <v>522</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -5279,10 +5423,10 @@
         <v>284</v>
       </c>
       <c r="B215" t="s">
-        <v>628</v>
+        <v>302</v>
       </c>
       <c r="D215" t="s">
-        <v>641</v>
+        <v>302</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
@@ -5290,10 +5434,10 @@
         <v>284</v>
       </c>
       <c r="B216" t="s">
-        <v>335</v>
+        <v>640</v>
       </c>
       <c r="D216" t="s">
-        <v>336</v>
+        <v>652</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -5301,10 +5445,10 @@
         <v>284</v>
       </c>
       <c r="B217" t="s">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="D217" t="s">
-        <v>336</v>
+        <v>304</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
@@ -5312,10 +5456,10 @@
         <v>284</v>
       </c>
       <c r="B218" t="s">
-        <v>554</v>
+        <v>305</v>
       </c>
       <c r="D218" t="s">
-        <v>569</v>
+        <v>306</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
@@ -5323,10 +5467,10 @@
         <v>284</v>
       </c>
       <c r="B219" t="s">
-        <v>554</v>
+        <v>307</v>
       </c>
       <c r="D219" t="s">
-        <v>569</v>
+        <v>308</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -5334,10 +5478,10 @@
         <v>284</v>
       </c>
       <c r="B220" t="s">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="D220" t="s">
-        <v>338</v>
+        <v>310</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -5345,10 +5489,10 @@
         <v>284</v>
       </c>
       <c r="B221" t="s">
-        <v>339</v>
+        <v>311</v>
       </c>
       <c r="D221" t="s">
-        <v>340</v>
+        <v>312</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -5356,10 +5500,10 @@
         <v>284</v>
       </c>
       <c r="B222" t="s">
-        <v>510</v>
+        <v>60</v>
       </c>
       <c r="D222" t="s">
-        <v>510</v>
+        <v>60</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -5367,10 +5511,10 @@
         <v>284</v>
       </c>
       <c r="B223" t="s">
-        <v>500</v>
+        <v>313</v>
       </c>
       <c r="D223" t="s">
-        <v>501</v>
+        <v>314</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
@@ -5378,10 +5522,10 @@
         <v>284</v>
       </c>
       <c r="B224" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="D224" t="s">
-        <v>342</v>
+        <v>316</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -5389,10 +5533,10 @@
         <v>284</v>
       </c>
       <c r="B225" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="D225" t="s">
-        <v>344</v>
+        <v>318</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -5400,10 +5544,10 @@
         <v>284</v>
       </c>
       <c r="B226" t="s">
-        <v>345</v>
+        <v>515</v>
       </c>
       <c r="D226" t="s">
-        <v>346</v>
+        <v>516</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
@@ -5411,10 +5555,10 @@
         <v>284</v>
       </c>
       <c r="B227" t="s">
-        <v>347</v>
+        <v>555</v>
       </c>
       <c r="D227" t="s">
-        <v>348</v>
+        <v>571</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
@@ -5422,10 +5566,10 @@
         <v>284</v>
       </c>
       <c r="B228" t="s">
-        <v>349</v>
+        <v>513</v>
       </c>
       <c r="D228" t="s">
-        <v>293</v>
+        <v>514</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -5433,10 +5577,10 @@
         <v>284</v>
       </c>
       <c r="B229" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="D229" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
@@ -5444,10 +5588,10 @@
         <v>284</v>
       </c>
       <c r="B230" t="s">
-        <v>563</v>
+        <v>319</v>
       </c>
       <c r="D230" t="s">
-        <v>417</v>
+        <v>319</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -5455,10 +5599,10 @@
         <v>284</v>
       </c>
       <c r="B231" t="s">
-        <v>350</v>
+        <v>566</v>
       </c>
       <c r="D231" t="s">
-        <v>351</v>
+        <v>578</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -5466,10 +5610,10 @@
         <v>284</v>
       </c>
       <c r="B232" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="D232" t="s">
-        <v>353</v>
+        <v>321</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
@@ -5477,10 +5621,10 @@
         <v>284</v>
       </c>
       <c r="B233" t="s">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="D233" t="s">
-        <v>355</v>
+        <v>323</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -5488,10 +5632,10 @@
         <v>284</v>
       </c>
       <c r="B234" t="s">
-        <v>559</v>
+        <v>639</v>
       </c>
       <c r="D234" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -5499,10 +5643,10 @@
         <v>284</v>
       </c>
       <c r="B235" t="s">
-        <v>356</v>
+        <v>324</v>
       </c>
       <c r="D235" t="s">
-        <v>357</v>
+        <v>325</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
@@ -5510,10 +5654,10 @@
         <v>284</v>
       </c>
       <c r="B236" t="s">
-        <v>358</v>
+        <v>635</v>
       </c>
       <c r="D236" t="s">
-        <v>359</v>
+        <v>647</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
@@ -5521,10 +5665,10 @@
         <v>284</v>
       </c>
       <c r="B237" t="s">
-        <v>547</v>
+        <v>498</v>
       </c>
       <c r="D237" t="s">
-        <v>361</v>
+        <v>499</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -5532,10 +5676,10 @@
         <v>284</v>
       </c>
       <c r="B238" t="s">
-        <v>360</v>
+        <v>631</v>
       </c>
       <c r="D238" t="s">
-        <v>548</v>
+        <v>644</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -5543,10 +5687,10 @@
         <v>284</v>
       </c>
       <c r="B239" t="s">
-        <v>636</v>
+        <v>326</v>
       </c>
       <c r="D239" t="s">
-        <v>648</v>
+        <v>327</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -5554,10 +5698,10 @@
         <v>284</v>
       </c>
       <c r="B240" t="s">
-        <v>455</v>
+        <v>328</v>
       </c>
       <c r="D240" t="s">
-        <v>456</v>
+        <v>329</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
@@ -5565,10 +5709,10 @@
         <v>284</v>
       </c>
       <c r="B241" t="s">
-        <v>362</v>
+        <v>668</v>
       </c>
       <c r="D241" t="s">
-        <v>362</v>
+        <v>665</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
@@ -5576,10 +5720,10 @@
         <v>284</v>
       </c>
       <c r="B242" t="s">
-        <v>363</v>
+        <v>667</v>
       </c>
       <c r="D242" t="s">
-        <v>364</v>
+        <v>666</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
@@ -5587,10 +5731,10 @@
         <v>284</v>
       </c>
       <c r="B243" t="s">
-        <v>524</v>
+        <v>561</v>
       </c>
       <c r="D243" t="s">
-        <v>367</v>
+        <v>575</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -5598,10 +5742,10 @@
         <v>284</v>
       </c>
       <c r="B244" t="s">
-        <v>365</v>
+        <v>330</v>
       </c>
       <c r="D244" t="s">
-        <v>366</v>
+        <v>331</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -5609,10 +5753,10 @@
         <v>284</v>
       </c>
       <c r="B245" t="s">
-        <v>369</v>
+        <v>562</v>
       </c>
       <c r="D245" t="s">
-        <v>370</v>
+        <v>627</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -5620,10 +5764,10 @@
         <v>284</v>
       </c>
       <c r="B246" t="s">
-        <v>371</v>
+        <v>558</v>
       </c>
       <c r="D246" t="s">
-        <v>372</v>
+        <v>573</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -5631,10 +5775,10 @@
         <v>284</v>
       </c>
       <c r="B247" t="s">
-        <v>373</v>
+        <v>334</v>
       </c>
       <c r="D247" t="s">
-        <v>374</v>
+        <v>333</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
@@ -5642,10 +5786,10 @@
         <v>284</v>
       </c>
       <c r="B248" t="s">
-        <v>294</v>
+        <v>628</v>
       </c>
       <c r="D248" t="s">
-        <v>295</v>
+        <v>641</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -5653,10 +5797,10 @@
         <v>284</v>
       </c>
       <c r="B249" t="s">
-        <v>375</v>
+        <v>335</v>
       </c>
       <c r="D249" t="s">
-        <v>376</v>
+        <v>336</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -5664,10 +5808,10 @@
         <v>284</v>
       </c>
       <c r="B250" t="s">
-        <v>557</v>
+        <v>335</v>
       </c>
       <c r="D250" t="s">
-        <v>572</v>
+        <v>336</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -5675,10 +5819,10 @@
         <v>284</v>
       </c>
       <c r="B251" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="D251" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
@@ -5686,10 +5830,10 @@
         <v>284</v>
       </c>
       <c r="B252" t="s">
-        <v>377</v>
+        <v>554</v>
       </c>
       <c r="D252" t="s">
-        <v>378</v>
+        <v>569</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
@@ -5697,10 +5841,10 @@
         <v>284</v>
       </c>
       <c r="B253" t="s">
-        <v>379</v>
+        <v>337</v>
       </c>
       <c r="D253" t="s">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
@@ -5708,10 +5852,10 @@
         <v>284</v>
       </c>
       <c r="B254" t="s">
-        <v>381</v>
+        <v>339</v>
       </c>
       <c r="D254" t="s">
-        <v>382</v>
+        <v>340</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
@@ -5719,10 +5863,10 @@
         <v>284</v>
       </c>
       <c r="B255" t="s">
-        <v>230</v>
+        <v>510</v>
       </c>
       <c r="D255" t="s">
-        <v>231</v>
+        <v>510</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -5730,10 +5874,10 @@
         <v>284</v>
       </c>
       <c r="B256" t="s">
-        <v>634</v>
+        <v>500</v>
       </c>
       <c r="D256" t="s">
-        <v>643</v>
+        <v>501</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
@@ -5741,10 +5885,10 @@
         <v>284</v>
       </c>
       <c r="B257" t="s">
-        <v>383</v>
+        <v>341</v>
       </c>
       <c r="D257" t="s">
-        <v>384</v>
+        <v>342</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -5752,10 +5896,10 @@
         <v>284</v>
       </c>
       <c r="B258" t="s">
-        <v>385</v>
+        <v>343</v>
       </c>
       <c r="D258" t="s">
-        <v>386</v>
+        <v>344</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -5763,10 +5907,10 @@
         <v>284</v>
       </c>
       <c r="B259" t="s">
-        <v>387</v>
+        <v>345</v>
       </c>
       <c r="D259" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
@@ -5774,10 +5918,10 @@
         <v>284</v>
       </c>
       <c r="B260" t="s">
-        <v>389</v>
+        <v>347</v>
       </c>
       <c r="D260" t="s">
-        <v>390</v>
+        <v>348</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
@@ -5785,10 +5929,10 @@
         <v>284</v>
       </c>
       <c r="B261" t="s">
-        <v>17</v>
+        <v>349</v>
       </c>
       <c r="D261" t="s">
-        <v>164</v>
+        <v>293</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
@@ -5796,10 +5940,10 @@
         <v>284</v>
       </c>
       <c r="B262" t="s">
-        <v>391</v>
+        <v>564</v>
       </c>
       <c r="D262" t="s">
-        <v>392</v>
+        <v>576</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -5807,10 +5951,10 @@
         <v>284</v>
       </c>
       <c r="B263" t="s">
-        <v>393</v>
+        <v>563</v>
       </c>
       <c r="D263" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -5818,10 +5962,10 @@
         <v>284</v>
       </c>
       <c r="B264" t="s">
-        <v>395</v>
+        <v>350</v>
       </c>
       <c r="D264" t="s">
-        <v>396</v>
+        <v>351</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
@@ -5829,10 +5973,10 @@
         <v>284</v>
       </c>
       <c r="B265" t="s">
-        <v>397</v>
+        <v>352</v>
       </c>
       <c r="D265" t="s">
-        <v>398</v>
+        <v>353</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -5840,10 +5984,10 @@
         <v>284</v>
       </c>
       <c r="B266" t="s">
-        <v>399</v>
+        <v>354</v>
       </c>
       <c r="D266" t="s">
-        <v>400</v>
+        <v>355</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
@@ -5851,10 +5995,10 @@
         <v>284</v>
       </c>
       <c r="B267" t="s">
-        <v>401</v>
+        <v>559</v>
       </c>
       <c r="D267" t="s">
-        <v>402</v>
+        <v>653</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -5862,10 +6006,10 @@
         <v>284</v>
       </c>
       <c r="B268" t="s">
-        <v>403</v>
+        <v>356</v>
       </c>
       <c r="D268" t="s">
-        <v>404</v>
+        <v>357</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -5873,10 +6017,10 @@
         <v>284</v>
       </c>
       <c r="B269" t="s">
-        <v>633</v>
+        <v>358</v>
       </c>
       <c r="D269" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -5884,10 +6028,10 @@
         <v>284</v>
       </c>
       <c r="B270" t="s">
-        <v>630</v>
+        <v>547</v>
       </c>
       <c r="D270" t="s">
-        <v>643</v>
+        <v>361</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -5895,10 +6039,10 @@
         <v>284</v>
       </c>
       <c r="B271" t="s">
-        <v>405</v>
+        <v>360</v>
       </c>
       <c r="D271" t="s">
-        <v>406</v>
+        <v>548</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -5906,10 +6050,10 @@
         <v>284</v>
       </c>
       <c r="B272" t="s">
-        <v>409</v>
+        <v>636</v>
       </c>
       <c r="D272" t="s">
-        <v>410</v>
+        <v>648</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -5917,10 +6061,10 @@
         <v>284</v>
       </c>
       <c r="B273" t="s">
-        <v>508</v>
+        <v>455</v>
       </c>
       <c r="D273" t="s">
-        <v>509</v>
+        <v>456</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -5928,10 +6072,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
-        <v>560</v>
+        <v>362</v>
       </c>
       <c r="D274" t="s">
-        <v>574</v>
+        <v>362</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
@@ -5939,10 +6083,10 @@
         <v>284</v>
       </c>
       <c r="B275" t="s">
-        <v>543</v>
+        <v>363</v>
       </c>
       <c r="D275" t="s">
-        <v>544</v>
+        <v>364</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
@@ -5950,10 +6094,10 @@
         <v>284</v>
       </c>
       <c r="B276" t="s">
-        <v>552</v>
+        <v>524</v>
       </c>
       <c r="D276" t="s">
-        <v>551</v>
+        <v>367</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -5961,10 +6105,10 @@
         <v>284</v>
       </c>
       <c r="B277" t="s">
-        <v>505</v>
+        <v>365</v>
       </c>
       <c r="D277" t="s">
-        <v>506</v>
+        <v>366</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -5972,10 +6116,10 @@
         <v>284</v>
       </c>
       <c r="B278" t="s">
-        <v>411</v>
+        <v>369</v>
       </c>
       <c r="D278" t="s">
-        <v>411</v>
+        <v>370</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
@@ -5983,10 +6127,10 @@
         <v>284</v>
       </c>
       <c r="B279" t="s">
-        <v>624</v>
+        <v>371</v>
       </c>
       <c r="D279" t="s">
-        <v>625</v>
+        <v>372</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
@@ -5994,10 +6138,10 @@
         <v>284</v>
       </c>
       <c r="B280" t="s">
-        <v>669</v>
+        <v>373</v>
       </c>
       <c r="D280" t="s">
-        <v>670</v>
+        <v>374</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
@@ -6005,10 +6149,10 @@
         <v>284</v>
       </c>
       <c r="B281" t="s">
-        <v>412</v>
+        <v>294</v>
       </c>
       <c r="D281" t="s">
-        <v>413</v>
+        <v>295</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
@@ -6016,10 +6160,10 @@
         <v>284</v>
       </c>
       <c r="B282" t="s">
-        <v>632</v>
+        <v>375</v>
       </c>
       <c r="D282" t="s">
-        <v>645</v>
+        <v>376</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
@@ -6027,10 +6171,10 @@
         <v>284</v>
       </c>
       <c r="B283" t="s">
-        <v>414</v>
+        <v>557</v>
       </c>
       <c r="D283" t="s">
-        <v>415</v>
+        <v>572</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
@@ -6038,10 +6182,10 @@
         <v>284</v>
       </c>
       <c r="B284" t="s">
-        <v>416</v>
+        <v>567</v>
       </c>
       <c r="D284" t="s">
-        <v>417</v>
+        <v>579</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
@@ -6049,10 +6193,10 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>553</v>
+        <v>377</v>
       </c>
       <c r="D285" t="s">
-        <v>568</v>
+        <v>378</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
@@ -6060,373 +6204,373 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>418</v>
+        <v>379</v>
       </c>
       <c r="D286" t="s">
-        <v>419</v>
+        <v>380</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B287" t="s">
-        <v>21</v>
+        <v>381</v>
       </c>
       <c r="D287" t="s">
-        <v>22</v>
+        <v>382</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B288" t="s">
-        <v>421</v>
+        <v>230</v>
       </c>
       <c r="D288" t="s">
-        <v>421</v>
+        <v>231</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B289" t="s">
-        <v>30</v>
+        <v>634</v>
       </c>
       <c r="D289" t="s">
-        <v>31</v>
+        <v>643</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B290" t="s">
-        <v>546</v>
+        <v>383</v>
       </c>
       <c r="D290" t="s">
-        <v>422</v>
+        <v>384</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B291" t="s">
-        <v>44</v>
+        <v>385</v>
       </c>
       <c r="D291" t="s">
-        <v>45</v>
+        <v>386</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B292" t="s">
-        <v>589</v>
+        <v>387</v>
       </c>
       <c r="D292" t="s">
-        <v>610</v>
+        <v>388</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B293" t="s">
-        <v>50</v>
+        <v>389</v>
       </c>
       <c r="D293" t="s">
-        <v>51</v>
+        <v>390</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B294" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D294" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B295" t="s">
-        <v>52</v>
+        <v>391</v>
       </c>
       <c r="D295" t="s">
-        <v>53</v>
+        <v>392</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>393</v>
       </c>
       <c r="D296" t="s">
-        <v>519</v>
+        <v>394</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B297" t="s">
-        <v>523</v>
+        <v>395</v>
       </c>
       <c r="D297" t="s">
-        <v>520</v>
+        <v>396</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B298" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="D298" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B299" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="D299" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B300" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="D300" t="s">
-        <v>428</v>
+        <v>402</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B301" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="D301" t="s">
-        <v>430</v>
+        <v>404</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B302" t="s">
-        <v>431</v>
+        <v>633</v>
       </c>
       <c r="D302" t="s">
-        <v>432</v>
+        <v>646</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B303" t="s">
-        <v>433</v>
+        <v>630</v>
       </c>
       <c r="D303" t="s">
-        <v>434</v>
+        <v>643</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B304" t="s">
-        <v>435</v>
+        <v>405</v>
       </c>
       <c r="D304" t="s">
-        <v>436</v>
+        <v>406</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B305" t="s">
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="D305" t="s">
-        <v>438</v>
+        <v>410</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B306" t="s">
-        <v>439</v>
+        <v>508</v>
       </c>
       <c r="D306" t="s">
-        <v>440</v>
+        <v>509</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B307" t="s">
-        <v>61</v>
+        <v>560</v>
       </c>
       <c r="D307" t="s">
-        <v>62</v>
+        <v>574</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B308" t="s">
-        <v>65</v>
+        <v>543</v>
       </c>
       <c r="D308" t="s">
-        <v>66</v>
+        <v>544</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B309" t="s">
-        <v>63</v>
+        <v>552</v>
       </c>
       <c r="D309" t="s">
-        <v>64</v>
+        <v>551</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B310" t="s">
-        <v>671</v>
+        <v>505</v>
       </c>
       <c r="D310" t="s">
-        <v>672</v>
+        <v>506</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B311" t="s">
-        <v>441</v>
+        <v>411</v>
       </c>
       <c r="D311" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B312" t="s">
-        <v>588</v>
+        <v>624</v>
       </c>
       <c r="D312" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B313" t="s">
-        <v>587</v>
+        <v>669</v>
       </c>
       <c r="D313" t="s">
-        <v>608</v>
+        <v>670</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B314" t="s">
-        <v>75</v>
+        <v>412</v>
       </c>
       <c r="D314" t="s">
-        <v>76</v>
+        <v>413</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B315" t="s">
-        <v>77</v>
+        <v>632</v>
       </c>
       <c r="D315" t="s">
-        <v>78</v>
+        <v>645</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B316" t="s">
-        <v>326</v>
+        <v>414</v>
       </c>
       <c r="D316" t="s">
-        <v>327</v>
+        <v>415</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B317" t="s">
-        <v>449</v>
+        <v>416</v>
       </c>
       <c r="D317" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B318" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="D318" t="s">
-        <v>444</v>
+        <v>568</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B319" t="s">
-        <v>585</v>
+        <v>418</v>
       </c>
       <c r="D319" t="s">
-        <v>606</v>
+        <v>419</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
@@ -6434,10 +6578,10 @@
         <v>420</v>
       </c>
       <c r="B320" t="s">
-        <v>586</v>
+        <v>21</v>
       </c>
       <c r="D320" t="s">
-        <v>607</v>
+        <v>22</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
@@ -6445,10 +6589,10 @@
         <v>420</v>
       </c>
       <c r="B321" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="D321" t="s">
-        <v>446</v>
+        <v>421</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -6456,10 +6600,10 @@
         <v>420</v>
       </c>
       <c r="B322" t="s">
-        <v>447</v>
+        <v>30</v>
       </c>
       <c r="D322" t="s">
-        <v>448</v>
+        <v>31</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
@@ -6467,10 +6611,10 @@
         <v>420</v>
       </c>
       <c r="B323" t="s">
-        <v>654</v>
+        <v>546</v>
       </c>
       <c r="D323" t="s">
-        <v>655</v>
+        <v>422</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
@@ -6478,10 +6622,10 @@
         <v>420</v>
       </c>
       <c r="B324" t="s">
-        <v>332</v>
+        <v>44</v>
       </c>
       <c r="D324" t="s">
-        <v>333</v>
+        <v>45</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -6489,10 +6633,10 @@
         <v>420</v>
       </c>
       <c r="B325" t="s">
-        <v>101</v>
+        <v>589</v>
       </c>
       <c r="D325" t="s">
-        <v>102</v>
+        <v>610</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -6500,10 +6644,10 @@
         <v>420</v>
       </c>
       <c r="B326" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="D326" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -6511,10 +6655,10 @@
         <v>420</v>
       </c>
       <c r="B327" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="D327" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -6522,10 +6666,10 @@
         <v>420</v>
       </c>
       <c r="B328" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="D328" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
@@ -6533,10 +6677,10 @@
         <v>420</v>
       </c>
       <c r="B329" t="s">
-        <v>109</v>
+        <v>296</v>
       </c>
       <c r="D329" t="s">
-        <v>110</v>
+        <v>519</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
@@ -6544,10 +6688,10 @@
         <v>420</v>
       </c>
       <c r="B330" t="s">
-        <v>111</v>
+        <v>523</v>
       </c>
       <c r="D330" t="s">
-        <v>112</v>
+        <v>520</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
@@ -6555,10 +6699,10 @@
         <v>420</v>
       </c>
       <c r="B331" t="s">
-        <v>113</v>
+        <v>423</v>
       </c>
       <c r="D331" t="s">
-        <v>114</v>
+        <v>424</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -6566,10 +6710,10 @@
         <v>420</v>
       </c>
       <c r="B332" t="s">
-        <v>115</v>
+        <v>425</v>
       </c>
       <c r="D332" t="s">
-        <v>116</v>
+        <v>426</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
@@ -6577,10 +6721,10 @@
         <v>420</v>
       </c>
       <c r="B333" t="s">
-        <v>117</v>
+        <v>427</v>
       </c>
       <c r="D333" t="s">
-        <v>118</v>
+        <v>428</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
@@ -6588,10 +6732,10 @@
         <v>420</v>
       </c>
       <c r="B334" t="s">
-        <v>119</v>
+        <v>429</v>
       </c>
       <c r="D334" t="s">
-        <v>120</v>
+        <v>430</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -6599,10 +6743,10 @@
         <v>420</v>
       </c>
       <c r="B335" t="s">
-        <v>121</v>
+        <v>431</v>
       </c>
       <c r="D335" t="s">
-        <v>122</v>
+        <v>432</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -6610,10 +6754,10 @@
         <v>420</v>
       </c>
       <c r="B336" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="D336" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -6621,10 +6765,10 @@
         <v>420</v>
       </c>
       <c r="B337" t="s">
-        <v>549</v>
+        <v>435</v>
       </c>
       <c r="D337" t="s">
-        <v>550</v>
+        <v>436</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
@@ -6632,10 +6776,10 @@
         <v>420</v>
       </c>
       <c r="B338" t="s">
-        <v>129</v>
+        <v>437</v>
       </c>
       <c r="D338" t="s">
-        <v>130</v>
+        <v>438</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
@@ -6643,10 +6787,10 @@
         <v>420</v>
       </c>
       <c r="B339" t="s">
-        <v>592</v>
+        <v>439</v>
       </c>
       <c r="D339" t="s">
-        <v>612</v>
+        <v>440</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -6654,10 +6798,10 @@
         <v>420</v>
       </c>
       <c r="B340" t="s">
-        <v>622</v>
+        <v>61</v>
       </c>
       <c r="D340" t="s">
-        <v>623</v>
+        <v>62</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
@@ -6665,10 +6809,10 @@
         <v>420</v>
       </c>
       <c r="B341" t="s">
-        <v>591</v>
+        <v>65</v>
       </c>
       <c r="D341" t="s">
-        <v>626</v>
+        <v>66</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -6676,10 +6820,10 @@
         <v>420</v>
       </c>
       <c r="B342" t="s">
-        <v>452</v>
+        <v>63</v>
       </c>
       <c r="D342" t="s">
-        <v>453</v>
+        <v>64</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
@@ -6687,10 +6831,10 @@
         <v>420</v>
       </c>
       <c r="B343" t="s">
-        <v>598</v>
+        <v>671</v>
       </c>
       <c r="D343" t="s">
-        <v>618</v>
+        <v>672</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -6698,10 +6842,10 @@
         <v>420</v>
       </c>
       <c r="B344" t="s">
-        <v>590</v>
+        <v>441</v>
       </c>
       <c r="D344" t="s">
-        <v>611</v>
+        <v>442</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -6709,10 +6853,10 @@
         <v>420</v>
       </c>
       <c r="B345" t="s">
-        <v>659</v>
+        <v>588</v>
       </c>
       <c r="D345" t="s">
-        <v>660</v>
+        <v>609</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
@@ -6720,10 +6864,10 @@
         <v>420</v>
       </c>
       <c r="B346" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="D346" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
@@ -6731,10 +6875,10 @@
         <v>420</v>
       </c>
       <c r="B347" t="s">
-        <v>584</v>
+        <v>75</v>
       </c>
       <c r="D347" t="s">
-        <v>605</v>
+        <v>76</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -6742,10 +6886,10 @@
         <v>420</v>
       </c>
       <c r="B348" t="s">
-        <v>455</v>
+        <v>77</v>
       </c>
       <c r="D348" t="s">
-        <v>456</v>
+        <v>78</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
@@ -6753,10 +6897,10 @@
         <v>420</v>
       </c>
       <c r="B349" t="s">
-        <v>457</v>
+        <v>326</v>
       </c>
       <c r="D349" t="s">
-        <v>454</v>
+        <v>327</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
@@ -6764,10 +6908,10 @@
         <v>420</v>
       </c>
       <c r="B350" t="s">
-        <v>362</v>
+        <v>449</v>
       </c>
       <c r="D350" t="s">
-        <v>362</v>
+        <v>443</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
@@ -6775,10 +6919,10 @@
         <v>420</v>
       </c>
       <c r="B351" t="s">
-        <v>368</v>
+        <v>545</v>
       </c>
       <c r="D351" t="s">
-        <v>368</v>
+        <v>444</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
@@ -6786,10 +6930,10 @@
         <v>420</v>
       </c>
       <c r="B352" t="s">
-        <v>369</v>
+        <v>585</v>
       </c>
       <c r="D352" t="s">
-        <v>370</v>
+        <v>606</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
@@ -6797,10 +6941,10 @@
         <v>420</v>
       </c>
       <c r="B353" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="D353" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
@@ -6808,10 +6952,10 @@
         <v>420</v>
       </c>
       <c r="B354" t="s">
-        <v>597</v>
+        <v>445</v>
       </c>
       <c r="D354" t="s">
-        <v>617</v>
+        <v>446</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
@@ -6819,10 +6963,10 @@
         <v>420</v>
       </c>
       <c r="B355" t="s">
-        <v>377</v>
+        <v>447</v>
       </c>
       <c r="D355" t="s">
-        <v>378</v>
+        <v>448</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
@@ -6830,10 +6974,10 @@
         <v>420</v>
       </c>
       <c r="B356" t="s">
-        <v>156</v>
+        <v>654</v>
       </c>
       <c r="D356" t="s">
-        <v>157</v>
+        <v>655</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
@@ -6841,10 +6985,10 @@
         <v>420</v>
       </c>
       <c r="B357" t="s">
-        <v>379</v>
+        <v>332</v>
       </c>
       <c r="D357" t="s">
-        <v>380</v>
+        <v>333</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
@@ -6852,10 +6996,10 @@
         <v>420</v>
       </c>
       <c r="B358" t="s">
-        <v>656</v>
+        <v>101</v>
       </c>
       <c r="D358" t="s">
-        <v>657</v>
+        <v>102</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
@@ -6863,10 +7007,10 @@
         <v>420</v>
       </c>
       <c r="B359" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="D359" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
@@ -6874,10 +7018,10 @@
         <v>420</v>
       </c>
       <c r="B360" t="s">
-        <v>458</v>
+        <v>105</v>
       </c>
       <c r="D360" t="s">
-        <v>459</v>
+        <v>106</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
@@ -6885,10 +7029,10 @@
         <v>420</v>
       </c>
       <c r="B361" t="s">
-        <v>460</v>
+        <v>107</v>
       </c>
       <c r="D361" t="s">
-        <v>461</v>
+        <v>108</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
@@ -6896,10 +7040,10 @@
         <v>420</v>
       </c>
       <c r="B362" t="s">
-        <v>462</v>
+        <v>109</v>
       </c>
       <c r="D362" t="s">
-        <v>463</v>
+        <v>110</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
@@ -6907,10 +7051,10 @@
         <v>420</v>
       </c>
       <c r="B363" t="s">
-        <v>464</v>
+        <v>111</v>
       </c>
       <c r="D363" t="s">
-        <v>465</v>
+        <v>112</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
@@ -6918,10 +7062,10 @@
         <v>420</v>
       </c>
       <c r="B364" t="s">
-        <v>399</v>
+        <v>113</v>
       </c>
       <c r="D364" t="s">
-        <v>400</v>
+        <v>114</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
@@ -6929,10 +7073,10 @@
         <v>420</v>
       </c>
       <c r="B365" t="s">
-        <v>407</v>
+        <v>115</v>
       </c>
       <c r="D365" t="s">
-        <v>408</v>
+        <v>116</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
@@ -6940,10 +7084,10 @@
         <v>420</v>
       </c>
       <c r="B366" t="s">
-        <v>466</v>
+        <v>117</v>
       </c>
       <c r="D366" t="s">
-        <v>467</v>
+        <v>118</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -6951,10 +7095,10 @@
         <v>420</v>
       </c>
       <c r="B367" t="s">
-        <v>187</v>
+        <v>119</v>
       </c>
       <c r="D367" t="s">
-        <v>188</v>
+        <v>120</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
@@ -6962,10 +7106,10 @@
         <v>420</v>
       </c>
       <c r="B368" t="s">
-        <v>196</v>
+        <v>121</v>
       </c>
       <c r="D368" t="s">
-        <v>197</v>
+        <v>122</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
@@ -6973,10 +7117,10 @@
         <v>420</v>
       </c>
       <c r="B369" t="s">
-        <v>601</v>
+        <v>450</v>
       </c>
       <c r="D369" t="s">
-        <v>621</v>
+        <v>451</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -6984,10 +7128,10 @@
         <v>420</v>
       </c>
       <c r="B370" t="s">
-        <v>468</v>
+        <v>549</v>
       </c>
       <c r="D370" t="s">
-        <v>469</v>
+        <v>550</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
@@ -6995,10 +7139,10 @@
         <v>420</v>
       </c>
       <c r="B371" t="s">
-        <v>470</v>
+        <v>129</v>
       </c>
       <c r="D371" t="s">
-        <v>471</v>
+        <v>130</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
@@ -7006,10 +7150,10 @@
         <v>420</v>
       </c>
       <c r="B372" t="s">
-        <v>472</v>
+        <v>592</v>
       </c>
       <c r="D372" t="s">
-        <v>473</v>
+        <v>612</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -7017,10 +7161,10 @@
         <v>420</v>
       </c>
       <c r="B373" t="s">
-        <v>474</v>
+        <v>622</v>
       </c>
       <c r="D373" t="s">
-        <v>475</v>
+        <v>623</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
@@ -7028,10 +7172,10 @@
         <v>420</v>
       </c>
       <c r="B374" t="s">
-        <v>476</v>
+        <v>591</v>
       </c>
       <c r="D374" t="s">
-        <v>477</v>
+        <v>626</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -7039,10 +7183,10 @@
         <v>420</v>
       </c>
       <c r="B375" t="s">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="D375" t="s">
-        <v>479</v>
+        <v>453</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -7050,10 +7194,10 @@
         <v>420</v>
       </c>
       <c r="B376" t="s">
-        <v>480</v>
+        <v>598</v>
       </c>
       <c r="D376" t="s">
-        <v>481</v>
+        <v>618</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
@@ -7061,10 +7205,10 @@
         <v>420</v>
       </c>
       <c r="B377" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="D377" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
@@ -7072,10 +7216,10 @@
         <v>420</v>
       </c>
       <c r="B378" t="s">
-        <v>600</v>
+        <v>659</v>
       </c>
       <c r="D378" t="s">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
@@ -7083,10 +7227,10 @@
         <v>420</v>
       </c>
       <c r="B379" t="s">
-        <v>482</v>
+        <v>595</v>
       </c>
       <c r="D379" t="s">
-        <v>483</v>
+        <v>615</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
@@ -7094,10 +7238,10 @@
         <v>420</v>
       </c>
       <c r="B380" t="s">
-        <v>484</v>
+        <v>584</v>
       </c>
       <c r="D380" t="s">
-        <v>485</v>
+        <v>605</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
@@ -7105,10 +7249,10 @@
         <v>420</v>
       </c>
       <c r="B381" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="D381" t="s">
-        <v>487</v>
+        <v>456</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
@@ -7116,10 +7260,10 @@
         <v>420</v>
       </c>
       <c r="B382" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="D382" t="s">
-        <v>489</v>
+        <v>454</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
@@ -7127,10 +7271,10 @@
         <v>420</v>
       </c>
       <c r="B383" t="s">
-        <v>490</v>
+        <v>362</v>
       </c>
       <c r="D383" t="s">
-        <v>491</v>
+        <v>362</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
@@ -7138,10 +7282,10 @@
         <v>420</v>
       </c>
       <c r="B384" t="s">
-        <v>492</v>
+        <v>368</v>
       </c>
       <c r="D384" t="s">
-        <v>493</v>
+        <v>368</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
@@ -7149,10 +7293,10 @@
         <v>420</v>
       </c>
       <c r="B385" t="s">
-        <v>494</v>
+        <v>369</v>
       </c>
       <c r="D385" t="s">
-        <v>495</v>
+        <v>370</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
@@ -7160,10 +7304,10 @@
         <v>420</v>
       </c>
       <c r="B386" t="s">
-        <v>496</v>
+        <v>596</v>
       </c>
       <c r="D386" t="s">
-        <v>497</v>
+        <v>616</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
@@ -7171,10 +7315,10 @@
         <v>420</v>
       </c>
       <c r="B387" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="D387" t="s">
-        <v>658</v>
+        <v>617</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
@@ -7182,10 +7326,10 @@
         <v>420</v>
       </c>
       <c r="B388" t="s">
-        <v>583</v>
+        <v>377</v>
       </c>
       <c r="D388" t="s">
-        <v>604</v>
+        <v>378</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
@@ -7193,10 +7337,10 @@
         <v>420</v>
       </c>
       <c r="B389" t="s">
-        <v>581</v>
+        <v>156</v>
       </c>
       <c r="D389" t="s">
-        <v>603</v>
+        <v>157</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
@@ -7204,10 +7348,10 @@
         <v>420</v>
       </c>
       <c r="B390" t="s">
-        <v>580</v>
+        <v>379</v>
       </c>
       <c r="D390" t="s">
-        <v>602</v>
+        <v>380</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
@@ -7215,10 +7359,10 @@
         <v>420</v>
       </c>
       <c r="B391" t="s">
-        <v>594</v>
+        <v>656</v>
       </c>
       <c r="D391" t="s">
-        <v>614</v>
+        <v>657</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
@@ -7226,22 +7370,380 @@
         <v>420</v>
       </c>
       <c r="B392" t="s">
+        <v>17</v>
+      </c>
+      <c r="D392" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>420</v>
+      </c>
+      <c r="B393" t="s">
+        <v>458</v>
+      </c>
+      <c r="D393" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>420</v>
+      </c>
+      <c r="B394" t="s">
+        <v>460</v>
+      </c>
+      <c r="D394" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>420</v>
+      </c>
+      <c r="B395" t="s">
+        <v>462</v>
+      </c>
+      <c r="D395" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>420</v>
+      </c>
+      <c r="B396" t="s">
+        <v>464</v>
+      </c>
+      <c r="D396" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>420</v>
+      </c>
+      <c r="B397" t="s">
+        <v>399</v>
+      </c>
+      <c r="D397" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>420</v>
+      </c>
+      <c r="B398" t="s">
+        <v>407</v>
+      </c>
+      <c r="D398" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>420</v>
+      </c>
+      <c r="B399" t="s">
+        <v>466</v>
+      </c>
+      <c r="D399" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>420</v>
+      </c>
+      <c r="B400" t="s">
+        <v>187</v>
+      </c>
+      <c r="D400" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>420</v>
+      </c>
+      <c r="B401" t="s">
+        <v>196</v>
+      </c>
+      <c r="D401" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>420</v>
+      </c>
+      <c r="B402" t="s">
+        <v>601</v>
+      </c>
+      <c r="D402" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>420</v>
+      </c>
+      <c r="B403" t="s">
+        <v>468</v>
+      </c>
+      <c r="D403" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>420</v>
+      </c>
+      <c r="B404" t="s">
+        <v>470</v>
+      </c>
+      <c r="D404" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>420</v>
+      </c>
+      <c r="B405" t="s">
+        <v>472</v>
+      </c>
+      <c r="D405" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>420</v>
+      </c>
+      <c r="B406" t="s">
+        <v>474</v>
+      </c>
+      <c r="D406" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>420</v>
+      </c>
+      <c r="B407" t="s">
+        <v>476</v>
+      </c>
+      <c r="D407" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>420</v>
+      </c>
+      <c r="B408" t="s">
+        <v>478</v>
+      </c>
+      <c r="D408" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>420</v>
+      </c>
+      <c r="B409" t="s">
+        <v>480</v>
+      </c>
+      <c r="D409" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>420</v>
+      </c>
+      <c r="B410" t="s">
+        <v>599</v>
+      </c>
+      <c r="D410" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>420</v>
+      </c>
+      <c r="B411" t="s">
+        <v>600</v>
+      </c>
+      <c r="D411" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>420</v>
+      </c>
+      <c r="B412" t="s">
+        <v>482</v>
+      </c>
+      <c r="D412" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>420</v>
+      </c>
+      <c r="B413" t="s">
+        <v>484</v>
+      </c>
+      <c r="D413" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>420</v>
+      </c>
+      <c r="B414" t="s">
+        <v>486</v>
+      </c>
+      <c r="D414" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>420</v>
+      </c>
+      <c r="B415" t="s">
+        <v>488</v>
+      </c>
+      <c r="D415" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>420</v>
+      </c>
+      <c r="B416" t="s">
+        <v>490</v>
+      </c>
+      <c r="D416" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>420</v>
+      </c>
+      <c r="B417" t="s">
+        <v>492</v>
+      </c>
+      <c r="D417" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>420</v>
+      </c>
+      <c r="B418" t="s">
+        <v>494</v>
+      </c>
+      <c r="D418" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>420</v>
+      </c>
+      <c r="B419" t="s">
+        <v>496</v>
+      </c>
+      <c r="D419" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>420</v>
+      </c>
+      <c r="B420" t="s">
+        <v>582</v>
+      </c>
+      <c r="D420" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>420</v>
+      </c>
+      <c r="B421" t="s">
+        <v>583</v>
+      </c>
+      <c r="D421" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>420</v>
+      </c>
+      <c r="B422" t="s">
+        <v>581</v>
+      </c>
+      <c r="D422" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>420</v>
+      </c>
+      <c r="B423" t="s">
+        <v>580</v>
+      </c>
+      <c r="D423" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>420</v>
+      </c>
+      <c r="B424" t="s">
+        <v>594</v>
+      </c>
+      <c r="D424" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>420</v>
+      </c>
+      <c r="B425" t="s">
         <v>593</v>
       </c>
-      <c r="D392" t="s">
+      <c r="D425" t="s">
         <v>613</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D392" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D392">
-      <sortCondition ref="A2:A392"/>
-      <sortCondition ref="B2:B392"/>
-    </sortState>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A254:D392">
-    <sortCondition ref="A2:A397"/>
-    <sortCondition ref="B2:B397"/>
+  <autoFilter ref="A1:D394" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D425">
+    <sortCondition ref="A2:A425"/>
+    <sortCondition ref="B2:B425"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_dev\Seal-Report\Repository\Settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D631D2-3337-45C8-8B07-36A62594317C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40486C0C-BA8E-44D2-94C6-7DA736B84841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2130" yWindow="1050" windowWidth="25530" windowHeight="16515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2475" yWindow="1395" windowWidth="33390" windowHeight="18030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Translations" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="723">
   <si>
     <t>Context</t>
   </si>
@@ -2199,6 +2199,12 @@
   </si>
   <si>
     <t>Options du résultat du rapport</t>
+  </si>
+  <si>
+    <t>HTML to PDF</t>
+  </si>
+  <si>
+    <t>HTML en PDF</t>
   </si>
 </sst>
 </file>
@@ -3053,7 +3059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D425"/>
+  <dimension ref="A1:D426"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -3784,10 +3790,10 @@
         <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>270</v>
+        <v>721</v>
       </c>
       <c r="D66" t="s">
-        <v>271</v>
+        <v>722</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -3795,10 +3801,10 @@
         <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>700</v>
+        <v>270</v>
       </c>
       <c r="D67" t="s">
-        <v>707</v>
+        <v>271</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -3806,10 +3812,10 @@
         <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D68" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -3817,10 +3823,10 @@
         <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D69" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -3828,10 +3834,10 @@
         <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>97</v>
+        <v>702</v>
       </c>
       <c r="D70" t="s">
-        <v>98</v>
+        <v>709</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -3839,10 +3845,10 @@
         <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D71" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -3850,10 +3856,10 @@
         <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D72" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -3861,10 +3867,10 @@
         <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>661</v>
+        <v>101</v>
       </c>
       <c r="D73" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -3872,10 +3878,10 @@
         <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>103</v>
+        <v>661</v>
       </c>
       <c r="D74" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -3883,10 +3889,10 @@
         <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D75" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -3894,10 +3900,10 @@
         <v>17</v>
       </c>
       <c r="B76" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D76" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -3905,10 +3911,10 @@
         <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D77" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -3916,10 +3922,10 @@
         <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D78" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -3927,10 +3933,10 @@
         <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>662</v>
+        <v>111</v>
       </c>
       <c r="D79" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -3938,7 +3944,7 @@
         <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>113</v>
+        <v>662</v>
       </c>
       <c r="D80" t="s">
         <v>114</v>
@@ -3949,10 +3955,10 @@
         <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D81" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -3960,10 +3966,10 @@
         <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D82" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -3971,10 +3977,10 @@
         <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D83" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -3982,10 +3988,10 @@
         <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D84" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -3993,10 +3999,10 @@
         <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>694</v>
+        <v>121</v>
       </c>
       <c r="D85" t="s">
-        <v>715</v>
+        <v>122</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -4004,10 +4010,10 @@
         <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>123</v>
+        <v>694</v>
       </c>
       <c r="D86" t="s">
-        <v>124</v>
+        <v>715</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -4015,10 +4021,10 @@
         <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D87" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -4026,10 +4032,10 @@
         <v>17</v>
       </c>
       <c r="B88" t="s">
-        <v>706</v>
+        <v>125</v>
       </c>
       <c r="D88" t="s">
-        <v>710</v>
+        <v>126</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -4037,10 +4043,10 @@
         <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D89" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -4048,10 +4054,10 @@
         <v>17</v>
       </c>
       <c r="B90" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D90" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -4059,10 +4065,10 @@
         <v>17</v>
       </c>
       <c r="B91" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D91" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -4070,10 +4076,10 @@
         <v>17</v>
       </c>
       <c r="B92" t="s">
-        <v>127</v>
+        <v>705</v>
       </c>
       <c r="D92" t="s">
-        <v>128</v>
+        <v>713</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -4081,10 +4087,10 @@
         <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D93" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -4092,10 +4098,10 @@
         <v>17</v>
       </c>
       <c r="B94" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D94" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -4103,10 +4109,10 @@
         <v>17</v>
       </c>
       <c r="B95" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D95" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -4114,10 +4120,10 @@
         <v>17</v>
       </c>
       <c r="B96" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D96" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -4125,10 +4131,10 @@
         <v>17</v>
       </c>
       <c r="B97" t="s">
-        <v>266</v>
+        <v>135</v>
       </c>
       <c r="D97" t="s">
-        <v>267</v>
+        <v>136</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -4136,10 +4142,10 @@
         <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D98" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -4147,10 +4153,10 @@
         <v>17</v>
       </c>
       <c r="B99" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D99" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -4158,10 +4164,10 @@
         <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D100" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -4169,10 +4175,10 @@
         <v>17</v>
       </c>
       <c r="B101" t="s">
-        <v>452</v>
+        <v>256</v>
       </c>
       <c r="D101" t="s">
-        <v>453</v>
+        <v>257</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -4180,10 +4186,10 @@
         <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>137</v>
+        <v>452</v>
       </c>
       <c r="D102" t="s">
-        <v>138</v>
+        <v>453</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -4191,10 +4197,10 @@
         <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D103" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -4202,10 +4208,10 @@
         <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D104" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -4213,10 +4219,10 @@
         <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D105" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -4224,10 +4230,10 @@
         <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D106" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -4235,10 +4241,10 @@
         <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D107" t="s">
-        <v>62</v>
+        <v>146</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -4246,10 +4252,10 @@
         <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D108" t="s">
-        <v>149</v>
+        <v>62</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -4257,10 +4263,10 @@
         <v>17</v>
       </c>
       <c r="B109" t="s">
-        <v>368</v>
+        <v>148</v>
       </c>
       <c r="D109" t="s">
-        <v>368</v>
+        <v>149</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -4268,10 +4274,10 @@
         <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>663</v>
+        <v>368</v>
       </c>
       <c r="D110" t="s">
-        <v>664</v>
+        <v>368</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -4279,10 +4285,10 @@
         <v>17</v>
       </c>
       <c r="B111" t="s">
-        <v>150</v>
+        <v>663</v>
       </c>
       <c r="D111" t="s">
-        <v>150</v>
+        <v>664</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -4290,10 +4296,10 @@
         <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D112" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -4301,10 +4307,10 @@
         <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>696</v>
+        <v>151</v>
       </c>
       <c r="D113" t="s">
-        <v>697</v>
+        <v>152</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -4312,10 +4318,10 @@
         <v>17</v>
       </c>
       <c r="B114" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D114" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -4323,10 +4329,10 @@
         <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>153</v>
+        <v>698</v>
       </c>
       <c r="D115" t="s">
-        <v>153</v>
+        <v>699</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -4334,10 +4340,10 @@
         <v>17</v>
       </c>
       <c r="B116" t="s">
-        <v>268</v>
+        <v>153</v>
       </c>
       <c r="D116" t="s">
-        <v>269</v>
+        <v>153</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -4345,10 +4351,10 @@
         <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D117" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -4356,10 +4362,10 @@
         <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D118" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -4367,10 +4373,10 @@
         <v>17</v>
       </c>
       <c r="B119" t="s">
-        <v>160</v>
+        <v>276</v>
       </c>
       <c r="D119" t="s">
-        <v>161</v>
+        <v>277</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -4378,10 +4384,10 @@
         <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>503</v>
+        <v>160</v>
       </c>
       <c r="D120" t="s">
-        <v>504</v>
+        <v>161</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -4389,10 +4395,10 @@
         <v>17</v>
       </c>
       <c r="B121" t="s">
-        <v>154</v>
+        <v>503</v>
       </c>
       <c r="D121" t="s">
-        <v>155</v>
+        <v>504</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -4400,10 +4406,10 @@
         <v>17</v>
       </c>
       <c r="B122" t="s">
-        <v>502</v>
+        <v>154</v>
       </c>
       <c r="D122" t="s">
-        <v>507</v>
+        <v>155</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -4411,10 +4417,10 @@
         <v>17</v>
       </c>
       <c r="B123" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="D123" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -4422,10 +4428,10 @@
         <v>17</v>
       </c>
       <c r="B124" t="s">
-        <v>264</v>
+        <v>511</v>
       </c>
       <c r="D124" t="s">
-        <v>265</v>
+        <v>512</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -4433,10 +4439,10 @@
         <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D125" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -4444,10 +4450,10 @@
         <v>17</v>
       </c>
       <c r="B126" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D126" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -4455,10 +4461,10 @@
         <v>17</v>
       </c>
       <c r="B127" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D127" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -4466,10 +4472,10 @@
         <v>17</v>
       </c>
       <c r="B128" t="s">
-        <v>685</v>
+        <v>254</v>
       </c>
       <c r="D128" t="s">
-        <v>686</v>
+        <v>255</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
@@ -4477,10 +4483,10 @@
         <v>17</v>
       </c>
       <c r="B129" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D129" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -4488,10 +4494,10 @@
         <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>156</v>
+        <v>687</v>
       </c>
       <c r="D130" t="s">
-        <v>157</v>
+        <v>688</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
@@ -4499,10 +4505,10 @@
         <v>17</v>
       </c>
       <c r="B131" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D131" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
@@ -4510,10 +4516,10 @@
         <v>17</v>
       </c>
       <c r="B132" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D132" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
@@ -4521,10 +4527,10 @@
         <v>17</v>
       </c>
       <c r="B133" t="s">
-        <v>230</v>
+        <v>162</v>
       </c>
       <c r="D133" t="s">
-        <v>231</v>
+        <v>163</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
@@ -4532,10 +4538,10 @@
         <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>17</v>
+        <v>230</v>
       </c>
       <c r="D134" t="s">
-        <v>164</v>
+        <v>231</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -4543,10 +4549,10 @@
         <v>17</v>
       </c>
       <c r="B135" t="s">
-        <v>673</v>
+        <v>17</v>
       </c>
       <c r="D135" t="s">
-        <v>678</v>
+        <v>164</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -4554,10 +4560,10 @@
         <v>17</v>
       </c>
       <c r="B136" t="s">
-        <v>165</v>
+        <v>673</v>
       </c>
       <c r="D136" t="s">
-        <v>166</v>
+        <v>678</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -4565,10 +4571,10 @@
         <v>17</v>
       </c>
       <c r="B137" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D137" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
@@ -4576,10 +4582,10 @@
         <v>17</v>
       </c>
       <c r="B138" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D138" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -4587,10 +4593,10 @@
         <v>17</v>
       </c>
       <c r="B139" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D139" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
@@ -4598,10 +4604,10 @@
         <v>17</v>
       </c>
       <c r="B140" t="s">
-        <v>719</v>
+        <v>171</v>
       </c>
       <c r="D140" t="s">
-        <v>720</v>
+        <v>172</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
@@ -4609,10 +4615,10 @@
         <v>17</v>
       </c>
       <c r="B141" t="s">
-        <v>173</v>
+        <v>719</v>
       </c>
       <c r="D141" t="s">
-        <v>174</v>
+        <v>720</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -4620,10 +4626,10 @@
         <v>17</v>
       </c>
       <c r="B142" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D142" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -4631,10 +4637,10 @@
         <v>17</v>
       </c>
       <c r="B143" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D143" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -4642,10 +4648,10 @@
         <v>17</v>
       </c>
       <c r="B144" t="s">
-        <v>695</v>
+        <v>176</v>
       </c>
       <c r="D144" t="s">
-        <v>716</v>
+        <v>177</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -4653,10 +4659,10 @@
         <v>17</v>
       </c>
       <c r="B145" t="s">
-        <v>178</v>
+        <v>695</v>
       </c>
       <c r="D145" t="s">
-        <v>179</v>
+        <v>716</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -4664,10 +4670,10 @@
         <v>17</v>
       </c>
       <c r="B146" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D146" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
@@ -4675,10 +4681,10 @@
         <v>17</v>
       </c>
       <c r="B147" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D147" t="s">
-        <v>33</v>
+        <v>181</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
@@ -4686,10 +4692,10 @@
         <v>17</v>
       </c>
       <c r="B148" t="s">
-        <v>258</v>
+        <v>182</v>
       </c>
       <c r="D148" t="s">
-        <v>259</v>
+        <v>33</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -4697,10 +4703,10 @@
         <v>17</v>
       </c>
       <c r="B149" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D149" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -4708,10 +4714,10 @@
         <v>17</v>
       </c>
       <c r="B150" t="s">
-        <v>280</v>
+        <v>246</v>
       </c>
       <c r="D150" t="s">
-        <v>281</v>
+        <v>247</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
@@ -4719,10 +4725,10 @@
         <v>17</v>
       </c>
       <c r="B151" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="D151" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
@@ -4730,10 +4736,10 @@
         <v>17</v>
       </c>
       <c r="B152" t="s">
-        <v>183</v>
+        <v>252</v>
       </c>
       <c r="D152" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
@@ -4741,10 +4747,10 @@
         <v>17</v>
       </c>
       <c r="B153" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D153" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
@@ -4752,10 +4758,10 @@
         <v>17</v>
       </c>
       <c r="B154" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D154" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
@@ -4763,10 +4769,10 @@
         <v>17</v>
       </c>
       <c r="B155" t="s">
-        <v>689</v>
+        <v>189</v>
       </c>
       <c r="D155" t="s">
-        <v>690</v>
+        <v>190</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
@@ -4785,10 +4791,10 @@
         <v>17</v>
       </c>
       <c r="B157" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D157" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
@@ -4807,10 +4813,10 @@
         <v>17</v>
       </c>
       <c r="B159" t="s">
-        <v>185</v>
+        <v>691</v>
       </c>
       <c r="D159" t="s">
-        <v>186</v>
+        <v>692</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
@@ -4818,10 +4824,10 @@
         <v>17</v>
       </c>
       <c r="B160" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D160" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -4829,10 +4835,10 @@
         <v>17</v>
       </c>
       <c r="B161" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D161" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
@@ -4840,10 +4846,10 @@
         <v>17</v>
       </c>
       <c r="B162" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D162" t="s">
-        <v>82</v>
+        <v>194</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -4851,10 +4857,10 @@
         <v>17</v>
       </c>
       <c r="B163" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D163" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
@@ -4862,10 +4868,10 @@
         <v>17</v>
       </c>
       <c r="B164" t="s">
-        <v>282</v>
+        <v>196</v>
       </c>
       <c r="D164" t="s">
-        <v>283</v>
+        <v>197</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
@@ -4873,10 +4879,10 @@
         <v>17</v>
       </c>
       <c r="B165" t="s">
-        <v>198</v>
+        <v>282</v>
       </c>
       <c r="D165" t="s">
-        <v>199</v>
+        <v>283</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -4884,10 +4890,10 @@
         <v>17</v>
       </c>
       <c r="B166" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D166" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
@@ -4895,7 +4901,7 @@
         <v>17</v>
       </c>
       <c r="B167" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D167" t="s">
         <v>201</v>
@@ -4906,10 +4912,10 @@
         <v>17</v>
       </c>
       <c r="B168" t="s">
-        <v>717</v>
+        <v>202</v>
       </c>
       <c r="D168" t="s">
-        <v>718</v>
+        <v>201</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
@@ -4917,10 +4923,10 @@
         <v>17</v>
       </c>
       <c r="B169" t="s">
-        <v>203</v>
+        <v>717</v>
       </c>
       <c r="D169" t="s">
-        <v>204</v>
+        <v>718</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
@@ -4928,10 +4934,10 @@
         <v>17</v>
       </c>
       <c r="B170" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D170" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
@@ -4939,10 +4945,10 @@
         <v>17</v>
       </c>
       <c r="B171" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D171" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
@@ -4950,10 +4956,10 @@
         <v>17</v>
       </c>
       <c r="B172" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D172" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
@@ -4961,10 +4967,10 @@
         <v>17</v>
       </c>
       <c r="B173" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D173" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
@@ -4972,10 +4978,10 @@
         <v>17</v>
       </c>
       <c r="B174" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D174" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
@@ -4983,10 +4989,10 @@
         <v>17</v>
       </c>
       <c r="B175" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D175" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
@@ -4994,10 +5000,10 @@
         <v>17</v>
       </c>
       <c r="B176" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D176" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
@@ -5005,10 +5011,10 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D177" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -5016,10 +5022,10 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D178" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
@@ -5027,10 +5033,10 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D179" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
@@ -5038,10 +5044,10 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D180" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
@@ -5049,10 +5055,10 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="D181" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
@@ -5060,10 +5066,10 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
       <c r="D182" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
@@ -5071,10 +5077,10 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D183" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
@@ -5082,10 +5088,10 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>482</v>
+        <v>228</v>
       </c>
       <c r="D184" t="s">
-        <v>483</v>
+        <v>229</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
@@ -5093,10 +5099,10 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>232</v>
+        <v>482</v>
       </c>
       <c r="D185" t="s">
-        <v>233</v>
+        <v>483</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
@@ -5104,10 +5110,10 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>535</v>
+        <v>232</v>
       </c>
       <c r="D186" t="s">
-        <v>536</v>
+        <v>233</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
@@ -5115,10 +5121,10 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>234</v>
+        <v>535</v>
       </c>
       <c r="D187" t="s">
-        <v>235</v>
+        <v>536</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
@@ -5126,10 +5132,10 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>525</v>
+        <v>234</v>
       </c>
       <c r="D188" t="s">
-        <v>526</v>
+        <v>235</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
@@ -5137,10 +5143,10 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>236</v>
+        <v>525</v>
       </c>
       <c r="D189" t="s">
-        <v>237</v>
+        <v>526</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
@@ -5148,10 +5154,10 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>527</v>
+        <v>236</v>
       </c>
       <c r="D190" t="s">
-        <v>528</v>
+        <v>237</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
@@ -5159,10 +5165,10 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="D191" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
@@ -5170,10 +5176,10 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D192" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
@@ -5181,10 +5187,10 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>238</v>
+        <v>537</v>
       </c>
       <c r="D193" t="s">
-        <v>239</v>
+        <v>538</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
@@ -5192,10 +5198,10 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D194" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
@@ -5203,10 +5209,10 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>529</v>
+        <v>240</v>
       </c>
       <c r="D195" t="s">
-        <v>530</v>
+        <v>241</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
@@ -5214,10 +5220,10 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D196" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
@@ -5225,10 +5231,10 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="D197" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
@@ -5236,21 +5242,21 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>496</v>
+        <v>541</v>
       </c>
       <c r="D198" t="s">
-        <v>497</v>
+        <v>542</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>285</v>
+        <v>496</v>
       </c>
       <c r="D199" t="s">
-        <v>286</v>
+        <v>497</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
@@ -5258,10 +5264,10 @@
         <v>284</v>
       </c>
       <c r="B200" t="s">
-        <v>32</v>
+        <v>285</v>
       </c>
       <c r="D200" t="s">
-        <v>33</v>
+        <v>286</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
@@ -5269,10 +5275,10 @@
         <v>284</v>
       </c>
       <c r="B201" t="s">
-        <v>287</v>
+        <v>32</v>
       </c>
       <c r="D201" t="s">
-        <v>288</v>
+        <v>33</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
@@ -5280,10 +5286,10 @@
         <v>284</v>
       </c>
       <c r="B202" t="s">
-        <v>629</v>
+        <v>287</v>
       </c>
       <c r="D202" t="s">
-        <v>642</v>
+        <v>288</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
@@ -5291,10 +5297,10 @@
         <v>284</v>
       </c>
       <c r="B203" t="s">
-        <v>44</v>
+        <v>629</v>
       </c>
       <c r="D203" t="s">
-        <v>45</v>
+        <v>642</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
@@ -5302,10 +5308,10 @@
         <v>284</v>
       </c>
       <c r="B204" t="s">
-        <v>565</v>
+        <v>44</v>
       </c>
       <c r="D204" t="s">
-        <v>577</v>
+        <v>45</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
@@ -5324,10 +5330,10 @@
         <v>284</v>
       </c>
       <c r="B206" t="s">
-        <v>638</v>
+        <v>565</v>
       </c>
       <c r="D206" t="s">
-        <v>650</v>
+        <v>577</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -5335,10 +5341,10 @@
         <v>284</v>
       </c>
       <c r="B207" t="s">
-        <v>289</v>
+        <v>638</v>
       </c>
       <c r="D207" t="s">
-        <v>290</v>
+        <v>650</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
@@ -5346,10 +5352,10 @@
         <v>284</v>
       </c>
       <c r="B208" t="s">
-        <v>58</v>
+        <v>289</v>
       </c>
       <c r="D208" t="s">
-        <v>59</v>
+        <v>290</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
@@ -5357,10 +5363,10 @@
         <v>284</v>
       </c>
       <c r="B209" t="s">
-        <v>291</v>
+        <v>58</v>
       </c>
       <c r="D209" t="s">
-        <v>292</v>
+        <v>59</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
@@ -5368,10 +5374,10 @@
         <v>284</v>
       </c>
       <c r="B210" t="s">
-        <v>637</v>
+        <v>291</v>
       </c>
       <c r="D210" t="s">
-        <v>649</v>
+        <v>292</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -5379,10 +5385,10 @@
         <v>284</v>
       </c>
       <c r="B211" t="s">
-        <v>296</v>
+        <v>637</v>
       </c>
       <c r="D211" t="s">
-        <v>297</v>
+        <v>649</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
@@ -5390,10 +5396,10 @@
         <v>284</v>
       </c>
       <c r="B212" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D212" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -5401,10 +5407,10 @@
         <v>284</v>
       </c>
       <c r="B213" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D213" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
@@ -5412,10 +5418,10 @@
         <v>284</v>
       </c>
       <c r="B214" t="s">
-        <v>521</v>
+        <v>300</v>
       </c>
       <c r="D214" t="s">
-        <v>522</v>
+        <v>301</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -5423,10 +5429,10 @@
         <v>284</v>
       </c>
       <c r="B215" t="s">
-        <v>302</v>
+        <v>521</v>
       </c>
       <c r="D215" t="s">
-        <v>302</v>
+        <v>522</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
@@ -5434,10 +5440,10 @@
         <v>284</v>
       </c>
       <c r="B216" t="s">
-        <v>640</v>
+        <v>302</v>
       </c>
       <c r="D216" t="s">
-        <v>652</v>
+        <v>302</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -5445,10 +5451,10 @@
         <v>284</v>
       </c>
       <c r="B217" t="s">
-        <v>303</v>
+        <v>640</v>
       </c>
       <c r="D217" t="s">
-        <v>304</v>
+        <v>652</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
@@ -5456,10 +5462,10 @@
         <v>284</v>
       </c>
       <c r="B218" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D218" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
@@ -5467,10 +5473,10 @@
         <v>284</v>
       </c>
       <c r="B219" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D219" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -5478,10 +5484,10 @@
         <v>284</v>
       </c>
       <c r="B220" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D220" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -5489,10 +5495,10 @@
         <v>284</v>
       </c>
       <c r="B221" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D221" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -5500,10 +5506,10 @@
         <v>284</v>
       </c>
       <c r="B222" t="s">
-        <v>60</v>
+        <v>311</v>
       </c>
       <c r="D222" t="s">
-        <v>60</v>
+        <v>312</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -5511,10 +5517,10 @@
         <v>284</v>
       </c>
       <c r="B223" t="s">
-        <v>313</v>
+        <v>60</v>
       </c>
       <c r="D223" t="s">
-        <v>314</v>
+        <v>60</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
@@ -5522,10 +5528,10 @@
         <v>284</v>
       </c>
       <c r="B224" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D224" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -5533,10 +5539,10 @@
         <v>284</v>
       </c>
       <c r="B225" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D225" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -5544,10 +5550,10 @@
         <v>284</v>
       </c>
       <c r="B226" t="s">
-        <v>515</v>
+        <v>317</v>
       </c>
       <c r="D226" t="s">
-        <v>516</v>
+        <v>318</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
@@ -5555,10 +5561,10 @@
         <v>284</v>
       </c>
       <c r="B227" t="s">
-        <v>555</v>
+        <v>515</v>
       </c>
       <c r="D227" t="s">
-        <v>571</v>
+        <v>516</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
@@ -5566,10 +5572,10 @@
         <v>284</v>
       </c>
       <c r="B228" t="s">
-        <v>513</v>
+        <v>555</v>
       </c>
       <c r="D228" t="s">
-        <v>514</v>
+        <v>571</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -5577,10 +5583,10 @@
         <v>284</v>
       </c>
       <c r="B229" t="s">
-        <v>556</v>
+        <v>513</v>
       </c>
       <c r="D229" t="s">
-        <v>570</v>
+        <v>514</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
@@ -5588,10 +5594,10 @@
         <v>284</v>
       </c>
       <c r="B230" t="s">
-        <v>319</v>
+        <v>556</v>
       </c>
       <c r="D230" t="s">
-        <v>319</v>
+        <v>570</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -5599,10 +5605,10 @@
         <v>284</v>
       </c>
       <c r="B231" t="s">
-        <v>566</v>
+        <v>319</v>
       </c>
       <c r="D231" t="s">
-        <v>578</v>
+        <v>319</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -5610,10 +5616,10 @@
         <v>284</v>
       </c>
       <c r="B232" t="s">
-        <v>320</v>
+        <v>566</v>
       </c>
       <c r="D232" t="s">
-        <v>321</v>
+        <v>578</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
@@ -5621,10 +5627,10 @@
         <v>284</v>
       </c>
       <c r="B233" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D233" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -5632,10 +5638,10 @@
         <v>284</v>
       </c>
       <c r="B234" t="s">
-        <v>639</v>
+        <v>322</v>
       </c>
       <c r="D234" t="s">
-        <v>651</v>
+        <v>323</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -5643,10 +5649,10 @@
         <v>284</v>
       </c>
       <c r="B235" t="s">
-        <v>324</v>
+        <v>639</v>
       </c>
       <c r="D235" t="s">
-        <v>325</v>
+        <v>651</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
@@ -5654,10 +5660,10 @@
         <v>284</v>
       </c>
       <c r="B236" t="s">
-        <v>635</v>
+        <v>324</v>
       </c>
       <c r="D236" t="s">
-        <v>647</v>
+        <v>325</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
@@ -5665,10 +5671,10 @@
         <v>284</v>
       </c>
       <c r="B237" t="s">
-        <v>498</v>
+        <v>635</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>647</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -5676,10 +5682,10 @@
         <v>284</v>
       </c>
       <c r="B238" t="s">
-        <v>631</v>
+        <v>498</v>
       </c>
       <c r="D238" t="s">
-        <v>644</v>
+        <v>499</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -5687,10 +5693,10 @@
         <v>284</v>
       </c>
       <c r="B239" t="s">
-        <v>326</v>
+        <v>631</v>
       </c>
       <c r="D239" t="s">
-        <v>327</v>
+        <v>644</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -5698,10 +5704,10 @@
         <v>284</v>
       </c>
       <c r="B240" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D240" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
@@ -5709,10 +5715,10 @@
         <v>284</v>
       </c>
       <c r="B241" t="s">
-        <v>668</v>
+        <v>328</v>
       </c>
       <c r="D241" t="s">
-        <v>665</v>
+        <v>329</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
@@ -5720,10 +5726,10 @@
         <v>284</v>
       </c>
       <c r="B242" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D242" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
@@ -5731,10 +5737,10 @@
         <v>284</v>
       </c>
       <c r="B243" t="s">
-        <v>561</v>
+        <v>667</v>
       </c>
       <c r="D243" t="s">
-        <v>575</v>
+        <v>666</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -5742,10 +5748,10 @@
         <v>284</v>
       </c>
       <c r="B244" t="s">
-        <v>330</v>
+        <v>561</v>
       </c>
       <c r="D244" t="s">
-        <v>331</v>
+        <v>575</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -5753,10 +5759,10 @@
         <v>284</v>
       </c>
       <c r="B245" t="s">
-        <v>562</v>
+        <v>330</v>
       </c>
       <c r="D245" t="s">
-        <v>627</v>
+        <v>331</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -5764,10 +5770,10 @@
         <v>284</v>
       </c>
       <c r="B246" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D246" t="s">
-        <v>573</v>
+        <v>627</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -5775,10 +5781,10 @@
         <v>284</v>
       </c>
       <c r="B247" t="s">
-        <v>334</v>
+        <v>558</v>
       </c>
       <c r="D247" t="s">
-        <v>333</v>
+        <v>573</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
@@ -5786,10 +5792,10 @@
         <v>284</v>
       </c>
       <c r="B248" t="s">
-        <v>628</v>
+        <v>334</v>
       </c>
       <c r="D248" t="s">
-        <v>641</v>
+        <v>333</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -5797,10 +5803,10 @@
         <v>284</v>
       </c>
       <c r="B249" t="s">
-        <v>335</v>
+        <v>628</v>
       </c>
       <c r="D249" t="s">
-        <v>336</v>
+        <v>641</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -5819,10 +5825,10 @@
         <v>284</v>
       </c>
       <c r="B251" t="s">
-        <v>554</v>
+        <v>335</v>
       </c>
       <c r="D251" t="s">
-        <v>569</v>
+        <v>336</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
@@ -5841,10 +5847,10 @@
         <v>284</v>
       </c>
       <c r="B253" t="s">
-        <v>337</v>
+        <v>554</v>
       </c>
       <c r="D253" t="s">
-        <v>338</v>
+        <v>569</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
@@ -5852,10 +5858,10 @@
         <v>284</v>
       </c>
       <c r="B254" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D254" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
@@ -5863,10 +5869,10 @@
         <v>284</v>
       </c>
       <c r="B255" t="s">
-        <v>510</v>
+        <v>339</v>
       </c>
       <c r="D255" t="s">
-        <v>510</v>
+        <v>340</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -5874,10 +5880,10 @@
         <v>284</v>
       </c>
       <c r="B256" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="D256" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
@@ -5885,10 +5891,10 @@
         <v>284</v>
       </c>
       <c r="B257" t="s">
-        <v>341</v>
+        <v>500</v>
       </c>
       <c r="D257" t="s">
-        <v>342</v>
+        <v>501</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -5896,10 +5902,10 @@
         <v>284</v>
       </c>
       <c r="B258" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D258" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -5907,10 +5913,10 @@
         <v>284</v>
       </c>
       <c r="B259" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D259" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
@@ -5918,10 +5924,10 @@
         <v>284</v>
       </c>
       <c r="B260" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D260" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
@@ -5929,10 +5935,10 @@
         <v>284</v>
       </c>
       <c r="B261" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D261" t="s">
-        <v>293</v>
+        <v>348</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
@@ -5940,10 +5946,10 @@
         <v>284</v>
       </c>
       <c r="B262" t="s">
-        <v>564</v>
+        <v>349</v>
       </c>
       <c r="D262" t="s">
-        <v>576</v>
+        <v>293</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -5951,10 +5957,10 @@
         <v>284</v>
       </c>
       <c r="B263" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D263" t="s">
-        <v>417</v>
+        <v>576</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -5962,10 +5968,10 @@
         <v>284</v>
       </c>
       <c r="B264" t="s">
-        <v>350</v>
+        <v>563</v>
       </c>
       <c r="D264" t="s">
-        <v>351</v>
+        <v>417</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
@@ -5973,10 +5979,10 @@
         <v>284</v>
       </c>
       <c r="B265" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D265" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -5984,10 +5990,10 @@
         <v>284</v>
       </c>
       <c r="B266" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D266" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
@@ -5995,10 +6001,10 @@
         <v>284</v>
       </c>
       <c r="B267" t="s">
-        <v>559</v>
+        <v>354</v>
       </c>
       <c r="D267" t="s">
-        <v>653</v>
+        <v>355</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -6006,10 +6012,10 @@
         <v>284</v>
       </c>
       <c r="B268" t="s">
-        <v>356</v>
+        <v>559</v>
       </c>
       <c r="D268" t="s">
-        <v>357</v>
+        <v>653</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -6017,10 +6023,10 @@
         <v>284</v>
       </c>
       <c r="B269" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D269" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -6028,10 +6034,10 @@
         <v>284</v>
       </c>
       <c r="B270" t="s">
-        <v>547</v>
+        <v>358</v>
       </c>
       <c r="D270" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -6039,10 +6045,10 @@
         <v>284</v>
       </c>
       <c r="B271" t="s">
-        <v>360</v>
+        <v>547</v>
       </c>
       <c r="D271" t="s">
-        <v>548</v>
+        <v>361</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -6050,10 +6056,10 @@
         <v>284</v>
       </c>
       <c r="B272" t="s">
-        <v>636</v>
+        <v>360</v>
       </c>
       <c r="D272" t="s">
-        <v>648</v>
+        <v>548</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -6061,10 +6067,10 @@
         <v>284</v>
       </c>
       <c r="B273" t="s">
-        <v>455</v>
+        <v>636</v>
       </c>
       <c r="D273" t="s">
-        <v>456</v>
+        <v>648</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -6072,10 +6078,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
-        <v>362</v>
+        <v>455</v>
       </c>
       <c r="D274" t="s">
-        <v>362</v>
+        <v>456</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
@@ -6083,10 +6089,10 @@
         <v>284</v>
       </c>
       <c r="B275" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D275" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
@@ -6094,10 +6100,10 @@
         <v>284</v>
       </c>
       <c r="B276" t="s">
-        <v>524</v>
+        <v>363</v>
       </c>
       <c r="D276" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -6105,10 +6111,10 @@
         <v>284</v>
       </c>
       <c r="B277" t="s">
-        <v>365</v>
+        <v>524</v>
       </c>
       <c r="D277" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -6116,10 +6122,10 @@
         <v>284</v>
       </c>
       <c r="B278" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D278" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
@@ -6127,10 +6133,10 @@
         <v>284</v>
       </c>
       <c r="B279" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D279" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
@@ -6138,10 +6144,10 @@
         <v>284</v>
       </c>
       <c r="B280" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D280" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
@@ -6149,10 +6155,10 @@
         <v>284</v>
       </c>
       <c r="B281" t="s">
-        <v>294</v>
+        <v>373</v>
       </c>
       <c r="D281" t="s">
-        <v>295</v>
+        <v>374</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
@@ -6160,10 +6166,10 @@
         <v>284</v>
       </c>
       <c r="B282" t="s">
-        <v>375</v>
+        <v>294</v>
       </c>
       <c r="D282" t="s">
-        <v>376</v>
+        <v>295</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
@@ -6171,10 +6177,10 @@
         <v>284</v>
       </c>
       <c r="B283" t="s">
-        <v>557</v>
+        <v>375</v>
       </c>
       <c r="D283" t="s">
-        <v>572</v>
+        <v>376</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
@@ -6182,10 +6188,10 @@
         <v>284</v>
       </c>
       <c r="B284" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="D284" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
@@ -6193,10 +6199,10 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>377</v>
+        <v>567</v>
       </c>
       <c r="D285" t="s">
-        <v>378</v>
+        <v>579</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
@@ -6204,10 +6210,10 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D286" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
@@ -6215,10 +6221,10 @@
         <v>284</v>
       </c>
       <c r="B287" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D287" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
@@ -6226,10 +6232,10 @@
         <v>284</v>
       </c>
       <c r="B288" t="s">
-        <v>230</v>
+        <v>381</v>
       </c>
       <c r="D288" t="s">
-        <v>231</v>
+        <v>382</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
@@ -6237,10 +6243,10 @@
         <v>284</v>
       </c>
       <c r="B289" t="s">
-        <v>634</v>
+        <v>230</v>
       </c>
       <c r="D289" t="s">
-        <v>643</v>
+        <v>231</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
@@ -6248,10 +6254,10 @@
         <v>284</v>
       </c>
       <c r="B290" t="s">
-        <v>383</v>
+        <v>634</v>
       </c>
       <c r="D290" t="s">
-        <v>384</v>
+        <v>643</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
@@ -6259,10 +6265,10 @@
         <v>284</v>
       </c>
       <c r="B291" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D291" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -6270,10 +6276,10 @@
         <v>284</v>
       </c>
       <c r="B292" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D292" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
@@ -6281,10 +6287,10 @@
         <v>284</v>
       </c>
       <c r="B293" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D293" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
@@ -6292,10 +6298,10 @@
         <v>284</v>
       </c>
       <c r="B294" t="s">
-        <v>17</v>
+        <v>389</v>
       </c>
       <c r="D294" t="s">
-        <v>164</v>
+        <v>390</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
@@ -6303,10 +6309,10 @@
         <v>284</v>
       </c>
       <c r="B295" t="s">
-        <v>391</v>
+        <v>17</v>
       </c>
       <c r="D295" t="s">
-        <v>392</v>
+        <v>164</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
@@ -6314,10 +6320,10 @@
         <v>284</v>
       </c>
       <c r="B296" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D296" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -6325,10 +6331,10 @@
         <v>284</v>
       </c>
       <c r="B297" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D297" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
@@ -6336,10 +6342,10 @@
         <v>284</v>
       </c>
       <c r="B298" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D298" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -6347,10 +6353,10 @@
         <v>284</v>
       </c>
       <c r="B299" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D299" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
@@ -6358,10 +6364,10 @@
         <v>284</v>
       </c>
       <c r="B300" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D300" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
@@ -6369,10 +6375,10 @@
         <v>284</v>
       </c>
       <c r="B301" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D301" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
@@ -6380,10 +6386,10 @@
         <v>284</v>
       </c>
       <c r="B302" t="s">
-        <v>633</v>
+        <v>403</v>
       </c>
       <c r="D302" t="s">
-        <v>646</v>
+        <v>404</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
@@ -6391,10 +6397,10 @@
         <v>284</v>
       </c>
       <c r="B303" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D303" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
@@ -6402,10 +6408,10 @@
         <v>284</v>
       </c>
       <c r="B304" t="s">
-        <v>405</v>
+        <v>630</v>
       </c>
       <c r="D304" t="s">
-        <v>406</v>
+        <v>643</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
@@ -6413,10 +6419,10 @@
         <v>284</v>
       </c>
       <c r="B305" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D305" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
@@ -6424,10 +6430,10 @@
         <v>284</v>
       </c>
       <c r="B306" t="s">
-        <v>508</v>
+        <v>409</v>
       </c>
       <c r="D306" t="s">
-        <v>509</v>
+        <v>410</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
@@ -6435,10 +6441,10 @@
         <v>284</v>
       </c>
       <c r="B307" t="s">
-        <v>560</v>
+        <v>508</v>
       </c>
       <c r="D307" t="s">
-        <v>574</v>
+        <v>509</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
@@ -6446,10 +6452,10 @@
         <v>284</v>
       </c>
       <c r="B308" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="D308" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
@@ -6457,10 +6463,10 @@
         <v>284</v>
       </c>
       <c r="B309" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="D309" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
@@ -6468,10 +6474,10 @@
         <v>284</v>
       </c>
       <c r="B310" t="s">
-        <v>505</v>
+        <v>552</v>
       </c>
       <c r="D310" t="s">
-        <v>506</v>
+        <v>551</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
@@ -6479,10 +6485,10 @@
         <v>284</v>
       </c>
       <c r="B311" t="s">
-        <v>411</v>
+        <v>505</v>
       </c>
       <c r="D311" t="s">
-        <v>411</v>
+        <v>506</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
@@ -6490,10 +6496,10 @@
         <v>284</v>
       </c>
       <c r="B312" t="s">
-        <v>624</v>
+        <v>411</v>
       </c>
       <c r="D312" t="s">
-        <v>625</v>
+        <v>411</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
@@ -6501,10 +6507,10 @@
         <v>284</v>
       </c>
       <c r="B313" t="s">
-        <v>669</v>
+        <v>624</v>
       </c>
       <c r="D313" t="s">
-        <v>670</v>
+        <v>625</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
@@ -6512,10 +6518,10 @@
         <v>284</v>
       </c>
       <c r="B314" t="s">
-        <v>412</v>
+        <v>669</v>
       </c>
       <c r="D314" t="s">
-        <v>413</v>
+        <v>670</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
@@ -6523,10 +6529,10 @@
         <v>284</v>
       </c>
       <c r="B315" t="s">
-        <v>632</v>
+        <v>412</v>
       </c>
       <c r="D315" t="s">
-        <v>645</v>
+        <v>413</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
@@ -6534,10 +6540,10 @@
         <v>284</v>
       </c>
       <c r="B316" t="s">
-        <v>414</v>
+        <v>632</v>
       </c>
       <c r="D316" t="s">
-        <v>415</v>
+        <v>645</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
@@ -6545,10 +6551,10 @@
         <v>284</v>
       </c>
       <c r="B317" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D317" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
@@ -6556,10 +6562,10 @@
         <v>284</v>
       </c>
       <c r="B318" t="s">
-        <v>553</v>
+        <v>416</v>
       </c>
       <c r="D318" t="s">
-        <v>568</v>
+        <v>417</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
@@ -6567,21 +6573,21 @@
         <v>284</v>
       </c>
       <c r="B319" t="s">
-        <v>418</v>
+        <v>553</v>
       </c>
       <c r="D319" t="s">
-        <v>419</v>
+        <v>568</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B320" t="s">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="D320" t="s">
-        <v>22</v>
+        <v>419</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
@@ -6589,10 +6595,10 @@
         <v>420</v>
       </c>
       <c r="B321" t="s">
-        <v>421</v>
+        <v>21</v>
       </c>
       <c r="D321" t="s">
-        <v>421</v>
+        <v>22</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -6600,10 +6606,10 @@
         <v>420</v>
       </c>
       <c r="B322" t="s">
-        <v>30</v>
+        <v>421</v>
       </c>
       <c r="D322" t="s">
-        <v>31</v>
+        <v>421</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
@@ -6611,10 +6617,10 @@
         <v>420</v>
       </c>
       <c r="B323" t="s">
-        <v>546</v>
+        <v>30</v>
       </c>
       <c r="D323" t="s">
-        <v>422</v>
+        <v>31</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
@@ -6622,10 +6628,10 @@
         <v>420</v>
       </c>
       <c r="B324" t="s">
-        <v>44</v>
+        <v>546</v>
       </c>
       <c r="D324" t="s">
-        <v>45</v>
+        <v>422</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -6633,10 +6639,10 @@
         <v>420</v>
       </c>
       <c r="B325" t="s">
-        <v>589</v>
+        <v>44</v>
       </c>
       <c r="D325" t="s">
-        <v>610</v>
+        <v>45</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -6644,10 +6650,10 @@
         <v>420</v>
       </c>
       <c r="B326" t="s">
-        <v>50</v>
+        <v>589</v>
       </c>
       <c r="D326" t="s">
-        <v>51</v>
+        <v>610</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -6655,10 +6661,10 @@
         <v>420</v>
       </c>
       <c r="B327" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D327" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -6666,10 +6672,10 @@
         <v>420</v>
       </c>
       <c r="B328" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D328" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
@@ -6677,10 +6683,10 @@
         <v>420</v>
       </c>
       <c r="B329" t="s">
-        <v>296</v>
+        <v>52</v>
       </c>
       <c r="D329" t="s">
-        <v>519</v>
+        <v>53</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
@@ -6688,10 +6694,10 @@
         <v>420</v>
       </c>
       <c r="B330" t="s">
-        <v>523</v>
+        <v>296</v>
       </c>
       <c r="D330" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
@@ -6699,10 +6705,10 @@
         <v>420</v>
       </c>
       <c r="B331" t="s">
-        <v>423</v>
+        <v>523</v>
       </c>
       <c r="D331" t="s">
-        <v>424</v>
+        <v>520</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -6710,10 +6716,10 @@
         <v>420</v>
       </c>
       <c r="B332" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D332" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
@@ -6721,10 +6727,10 @@
         <v>420</v>
       </c>
       <c r="B333" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D333" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
@@ -6732,10 +6738,10 @@
         <v>420</v>
       </c>
       <c r="B334" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D334" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -6743,10 +6749,10 @@
         <v>420</v>
       </c>
       <c r="B335" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D335" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -6754,10 +6760,10 @@
         <v>420</v>
       </c>
       <c r="B336" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D336" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -6765,10 +6771,10 @@
         <v>420</v>
       </c>
       <c r="B337" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D337" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
@@ -6776,10 +6782,10 @@
         <v>420</v>
       </c>
       <c r="B338" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D338" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
@@ -6787,10 +6793,10 @@
         <v>420</v>
       </c>
       <c r="B339" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D339" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -6798,10 +6804,10 @@
         <v>420</v>
       </c>
       <c r="B340" t="s">
-        <v>61</v>
+        <v>439</v>
       </c>
       <c r="D340" t="s">
-        <v>62</v>
+        <v>440</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
@@ -6809,10 +6815,10 @@
         <v>420</v>
       </c>
       <c r="B341" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D341" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -6820,10 +6826,10 @@
         <v>420</v>
       </c>
       <c r="B342" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D342" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
@@ -6831,10 +6837,10 @@
         <v>420</v>
       </c>
       <c r="B343" t="s">
-        <v>671</v>
+        <v>63</v>
       </c>
       <c r="D343" t="s">
-        <v>672</v>
+        <v>64</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -6842,10 +6848,10 @@
         <v>420</v>
       </c>
       <c r="B344" t="s">
-        <v>441</v>
+        <v>671</v>
       </c>
       <c r="D344" t="s">
-        <v>442</v>
+        <v>672</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -6853,10 +6859,10 @@
         <v>420</v>
       </c>
       <c r="B345" t="s">
-        <v>588</v>
+        <v>441</v>
       </c>
       <c r="D345" t="s">
-        <v>609</v>
+        <v>442</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
@@ -6864,10 +6870,10 @@
         <v>420</v>
       </c>
       <c r="B346" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D346" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
@@ -6875,10 +6881,10 @@
         <v>420</v>
       </c>
       <c r="B347" t="s">
-        <v>75</v>
+        <v>587</v>
       </c>
       <c r="D347" t="s">
-        <v>76</v>
+        <v>608</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -6886,10 +6892,10 @@
         <v>420</v>
       </c>
       <c r="B348" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D348" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
@@ -6897,10 +6903,10 @@
         <v>420</v>
       </c>
       <c r="B349" t="s">
-        <v>326</v>
+        <v>77</v>
       </c>
       <c r="D349" t="s">
-        <v>327</v>
+        <v>78</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
@@ -6908,10 +6914,10 @@
         <v>420</v>
       </c>
       <c r="B350" t="s">
-        <v>449</v>
+        <v>326</v>
       </c>
       <c r="D350" t="s">
-        <v>443</v>
+        <v>327</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
@@ -6919,10 +6925,10 @@
         <v>420</v>
       </c>
       <c r="B351" t="s">
-        <v>545</v>
+        <v>449</v>
       </c>
       <c r="D351" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
@@ -6930,10 +6936,10 @@
         <v>420</v>
       </c>
       <c r="B352" t="s">
-        <v>585</v>
+        <v>545</v>
       </c>
       <c r="D352" t="s">
-        <v>606</v>
+        <v>444</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
@@ -6941,10 +6947,10 @@
         <v>420</v>
       </c>
       <c r="B353" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D353" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
@@ -6952,10 +6958,10 @@
         <v>420</v>
       </c>
       <c r="B354" t="s">
-        <v>445</v>
+        <v>586</v>
       </c>
       <c r="D354" t="s">
-        <v>446</v>
+        <v>607</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
@@ -6963,10 +6969,10 @@
         <v>420</v>
       </c>
       <c r="B355" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D355" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
@@ -6974,10 +6980,10 @@
         <v>420</v>
       </c>
       <c r="B356" t="s">
-        <v>654</v>
+        <v>447</v>
       </c>
       <c r="D356" t="s">
-        <v>655</v>
+        <v>448</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
@@ -6985,10 +6991,10 @@
         <v>420</v>
       </c>
       <c r="B357" t="s">
-        <v>332</v>
+        <v>654</v>
       </c>
       <c r="D357" t="s">
-        <v>333</v>
+        <v>655</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
@@ -6996,10 +7002,10 @@
         <v>420</v>
       </c>
       <c r="B358" t="s">
-        <v>101</v>
+        <v>332</v>
       </c>
       <c r="D358" t="s">
-        <v>102</v>
+        <v>333</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
@@ -7007,10 +7013,10 @@
         <v>420</v>
       </c>
       <c r="B359" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D359" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
@@ -7018,10 +7024,10 @@
         <v>420</v>
       </c>
       <c r="B360" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D360" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
@@ -7029,10 +7035,10 @@
         <v>420</v>
       </c>
       <c r="B361" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D361" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
@@ -7040,10 +7046,10 @@
         <v>420</v>
       </c>
       <c r="B362" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D362" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
@@ -7051,10 +7057,10 @@
         <v>420</v>
       </c>
       <c r="B363" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D363" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
@@ -7062,10 +7068,10 @@
         <v>420</v>
       </c>
       <c r="B364" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D364" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
@@ -7073,10 +7079,10 @@
         <v>420</v>
       </c>
       <c r="B365" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D365" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
@@ -7084,10 +7090,10 @@
         <v>420</v>
       </c>
       <c r="B366" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D366" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -7095,10 +7101,10 @@
         <v>420</v>
       </c>
       <c r="B367" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D367" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
@@ -7106,10 +7112,10 @@
         <v>420</v>
       </c>
       <c r="B368" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D368" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
@@ -7117,10 +7123,10 @@
         <v>420</v>
       </c>
       <c r="B369" t="s">
-        <v>450</v>
+        <v>121</v>
       </c>
       <c r="D369" t="s">
-        <v>451</v>
+        <v>122</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -7128,10 +7134,10 @@
         <v>420</v>
       </c>
       <c r="B370" t="s">
-        <v>549</v>
+        <v>450</v>
       </c>
       <c r="D370" t="s">
-        <v>550</v>
+        <v>451</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
@@ -7139,10 +7145,10 @@
         <v>420</v>
       </c>
       <c r="B371" t="s">
-        <v>129</v>
+        <v>549</v>
       </c>
       <c r="D371" t="s">
-        <v>130</v>
+        <v>550</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
@@ -7150,10 +7156,10 @@
         <v>420</v>
       </c>
       <c r="B372" t="s">
-        <v>592</v>
+        <v>129</v>
       </c>
       <c r="D372" t="s">
-        <v>612</v>
+        <v>130</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -7161,10 +7167,10 @@
         <v>420</v>
       </c>
       <c r="B373" t="s">
-        <v>622</v>
+        <v>592</v>
       </c>
       <c r="D373" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
@@ -7172,10 +7178,10 @@
         <v>420</v>
       </c>
       <c r="B374" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="D374" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -7183,10 +7189,10 @@
         <v>420</v>
       </c>
       <c r="B375" t="s">
-        <v>452</v>
+        <v>591</v>
       </c>
       <c r="D375" t="s">
-        <v>453</v>
+        <v>626</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -7194,10 +7200,10 @@
         <v>420</v>
       </c>
       <c r="B376" t="s">
-        <v>598</v>
+        <v>452</v>
       </c>
       <c r="D376" t="s">
-        <v>618</v>
+        <v>453</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
@@ -7205,10 +7211,10 @@
         <v>420</v>
       </c>
       <c r="B377" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="D377" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
@@ -7216,10 +7222,10 @@
         <v>420</v>
       </c>
       <c r="B378" t="s">
-        <v>659</v>
+        <v>590</v>
       </c>
       <c r="D378" t="s">
-        <v>660</v>
+        <v>611</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
@@ -7227,10 +7233,10 @@
         <v>420</v>
       </c>
       <c r="B379" t="s">
-        <v>595</v>
+        <v>659</v>
       </c>
       <c r="D379" t="s">
-        <v>615</v>
+        <v>660</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
@@ -7238,10 +7244,10 @@
         <v>420</v>
       </c>
       <c r="B380" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="D380" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
@@ -7249,10 +7255,10 @@
         <v>420</v>
       </c>
       <c r="B381" t="s">
-        <v>455</v>
+        <v>584</v>
       </c>
       <c r="D381" t="s">
-        <v>456</v>
+        <v>605</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
@@ -7260,10 +7266,10 @@
         <v>420</v>
       </c>
       <c r="B382" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D382" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
@@ -7271,10 +7277,10 @@
         <v>420</v>
       </c>
       <c r="B383" t="s">
-        <v>362</v>
+        <v>457</v>
       </c>
       <c r="D383" t="s">
-        <v>362</v>
+        <v>454</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
@@ -7282,10 +7288,10 @@
         <v>420</v>
       </c>
       <c r="B384" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D384" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
@@ -7293,10 +7299,10 @@
         <v>420</v>
       </c>
       <c r="B385" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D385" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
@@ -7304,10 +7310,10 @@
         <v>420</v>
       </c>
       <c r="B386" t="s">
-        <v>596</v>
+        <v>369</v>
       </c>
       <c r="D386" t="s">
-        <v>616</v>
+        <v>370</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
@@ -7315,10 +7321,10 @@
         <v>420</v>
       </c>
       <c r="B387" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D387" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
@@ -7326,10 +7332,10 @@
         <v>420</v>
       </c>
       <c r="B388" t="s">
-        <v>377</v>
+        <v>597</v>
       </c>
       <c r="D388" t="s">
-        <v>378</v>
+        <v>617</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
@@ -7337,10 +7343,10 @@
         <v>420</v>
       </c>
       <c r="B389" t="s">
-        <v>156</v>
+        <v>377</v>
       </c>
       <c r="D389" t="s">
-        <v>157</v>
+        <v>378</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
@@ -7348,10 +7354,10 @@
         <v>420</v>
       </c>
       <c r="B390" t="s">
-        <v>379</v>
+        <v>156</v>
       </c>
       <c r="D390" t="s">
-        <v>380</v>
+        <v>157</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
@@ -7359,10 +7365,10 @@
         <v>420</v>
       </c>
       <c r="B391" t="s">
-        <v>656</v>
+        <v>379</v>
       </c>
       <c r="D391" t="s">
-        <v>657</v>
+        <v>380</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
@@ -7370,10 +7376,10 @@
         <v>420</v>
       </c>
       <c r="B392" t="s">
-        <v>17</v>
+        <v>656</v>
       </c>
       <c r="D392" t="s">
-        <v>164</v>
+        <v>657</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
@@ -7381,10 +7387,10 @@
         <v>420</v>
       </c>
       <c r="B393" t="s">
-        <v>458</v>
+        <v>17</v>
       </c>
       <c r="D393" t="s">
-        <v>459</v>
+        <v>164</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -7392,10 +7398,10 @@
         <v>420</v>
       </c>
       <c r="B394" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D394" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
@@ -7403,10 +7409,10 @@
         <v>420</v>
       </c>
       <c r="B395" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D395" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
@@ -7414,10 +7420,10 @@
         <v>420</v>
       </c>
       <c r="B396" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D396" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
@@ -7425,10 +7431,10 @@
         <v>420</v>
       </c>
       <c r="B397" t="s">
-        <v>399</v>
+        <v>464</v>
       </c>
       <c r="D397" t="s">
-        <v>400</v>
+        <v>465</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
@@ -7436,10 +7442,10 @@
         <v>420</v>
       </c>
       <c r="B398" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="D398" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
@@ -7447,10 +7453,10 @@
         <v>420</v>
       </c>
       <c r="B399" t="s">
-        <v>466</v>
+        <v>407</v>
       </c>
       <c r="D399" t="s">
-        <v>467</v>
+        <v>408</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
@@ -7458,10 +7464,10 @@
         <v>420</v>
       </c>
       <c r="B400" t="s">
-        <v>187</v>
+        <v>466</v>
       </c>
       <c r="D400" t="s">
-        <v>188</v>
+        <v>467</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
@@ -7469,10 +7475,10 @@
         <v>420</v>
       </c>
       <c r="B401" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D401" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
@@ -7480,10 +7486,10 @@
         <v>420</v>
       </c>
       <c r="B402" t="s">
-        <v>601</v>
+        <v>196</v>
       </c>
       <c r="D402" t="s">
-        <v>621</v>
+        <v>197</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
@@ -7491,10 +7497,10 @@
         <v>420</v>
       </c>
       <c r="B403" t="s">
-        <v>468</v>
+        <v>601</v>
       </c>
       <c r="D403" t="s">
-        <v>469</v>
+        <v>621</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
@@ -7502,10 +7508,10 @@
         <v>420</v>
       </c>
       <c r="B404" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D404" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
@@ -7513,10 +7519,10 @@
         <v>420</v>
       </c>
       <c r="B405" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D405" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
@@ -7524,10 +7530,10 @@
         <v>420</v>
       </c>
       <c r="B406" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D406" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
@@ -7535,10 +7541,10 @@
         <v>420</v>
       </c>
       <c r="B407" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D407" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
@@ -7546,10 +7552,10 @@
         <v>420</v>
       </c>
       <c r="B408" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D408" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
@@ -7557,10 +7563,10 @@
         <v>420</v>
       </c>
       <c r="B409" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D409" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
@@ -7568,10 +7574,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
-        <v>599</v>
+        <v>480</v>
       </c>
       <c r="D410" t="s">
-        <v>619</v>
+        <v>481</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
@@ -7579,10 +7585,10 @@
         <v>420</v>
       </c>
       <c r="B411" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D411" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
@@ -7590,10 +7596,10 @@
         <v>420</v>
       </c>
       <c r="B412" t="s">
-        <v>482</v>
+        <v>600</v>
       </c>
       <c r="D412" t="s">
-        <v>483</v>
+        <v>620</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
@@ -7601,10 +7607,10 @@
         <v>420</v>
       </c>
       <c r="B413" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D413" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
@@ -7612,10 +7618,10 @@
         <v>420</v>
       </c>
       <c r="B414" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D414" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
@@ -7623,10 +7629,10 @@
         <v>420</v>
       </c>
       <c r="B415" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D415" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
@@ -7634,10 +7640,10 @@
         <v>420</v>
       </c>
       <c r="B416" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D416" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
@@ -7645,10 +7651,10 @@
         <v>420</v>
       </c>
       <c r="B417" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D417" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
@@ -7656,10 +7662,10 @@
         <v>420</v>
       </c>
       <c r="B418" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D418" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
@@ -7667,10 +7673,10 @@
         <v>420</v>
       </c>
       <c r="B419" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D419" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
@@ -7678,10 +7684,10 @@
         <v>420</v>
       </c>
       <c r="B420" t="s">
-        <v>582</v>
+        <v>496</v>
       </c>
       <c r="D420" t="s">
-        <v>658</v>
+        <v>497</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
@@ -7689,10 +7695,10 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D421" t="s">
-        <v>604</v>
+        <v>658</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
@@ -7700,10 +7706,10 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D422" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
@@ -7711,10 +7717,10 @@
         <v>420</v>
       </c>
       <c r="B423" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D423" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
@@ -7722,10 +7728,10 @@
         <v>420</v>
       </c>
       <c r="B424" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="D424" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
@@ -7733,17 +7739,28 @@
         <v>420</v>
       </c>
       <c r="B425" t="s">
+        <v>594</v>
+      </c>
+      <c r="D425" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>420</v>
+      </c>
+      <c r="B426" t="s">
         <v>593</v>
       </c>
-      <c r="D425" t="s">
+      <c r="D426" t="s">
         <v>613</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D394" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D425">
-    <sortCondition ref="A2:A425"/>
-    <sortCondition ref="B2:B425"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D426">
+    <sortCondition ref="A2:A426"/>
+    <sortCondition ref="B2:B426"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_dev\Seal-Report\Repository\Settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40486C0C-BA8E-44D2-94C6-7DA736B84841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD59B78-FA1D-4C81-AD07-04EFCDBE8C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2475" yWindow="1395" windowWidth="33390" windowHeight="18030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13230" yWindow="1665" windowWidth="27240" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Translations" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$D$394</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$D$395</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="725">
   <si>
     <t>Context</t>
   </si>
@@ -2205,6 +2205,12 @@
   </si>
   <si>
     <t>HTML en PDF</t>
+  </si>
+  <si>
+    <t>Report summary</t>
+  </si>
+  <si>
+    <t>Résumé du rapport</t>
   </si>
 </sst>
 </file>
@@ -3059,7 +3065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D426"/>
+  <dimension ref="A1:D427"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -4637,10 +4643,10 @@
         <v>17</v>
       </c>
       <c r="B143" t="s">
-        <v>175</v>
+        <v>723</v>
       </c>
       <c r="D143" t="s">
-        <v>175</v>
+        <v>724</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -4648,10 +4654,10 @@
         <v>17</v>
       </c>
       <c r="B144" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D144" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -4659,10 +4665,10 @@
         <v>17</v>
       </c>
       <c r="B145" t="s">
-        <v>695</v>
+        <v>176</v>
       </c>
       <c r="D145" t="s">
-        <v>716</v>
+        <v>177</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -4670,10 +4676,10 @@
         <v>17</v>
       </c>
       <c r="B146" t="s">
-        <v>178</v>
+        <v>695</v>
       </c>
       <c r="D146" t="s">
-        <v>179</v>
+        <v>716</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
@@ -4681,10 +4687,10 @@
         <v>17</v>
       </c>
       <c r="B147" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D147" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
@@ -4692,10 +4698,10 @@
         <v>17</v>
       </c>
       <c r="B148" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D148" t="s">
-        <v>33</v>
+        <v>181</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -4703,10 +4709,10 @@
         <v>17</v>
       </c>
       <c r="B149" t="s">
-        <v>258</v>
+        <v>182</v>
       </c>
       <c r="D149" t="s">
-        <v>259</v>
+        <v>33</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -4714,10 +4720,10 @@
         <v>17</v>
       </c>
       <c r="B150" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D150" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
@@ -4725,10 +4731,10 @@
         <v>17</v>
       </c>
       <c r="B151" t="s">
-        <v>280</v>
+        <v>246</v>
       </c>
       <c r="D151" t="s">
-        <v>281</v>
+        <v>247</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
@@ -4736,10 +4742,10 @@
         <v>17</v>
       </c>
       <c r="B152" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="D152" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
@@ -4747,10 +4753,10 @@
         <v>17</v>
       </c>
       <c r="B153" t="s">
-        <v>183</v>
+        <v>252</v>
       </c>
       <c r="D153" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
@@ -4758,10 +4764,10 @@
         <v>17</v>
       </c>
       <c r="B154" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D154" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
@@ -4769,10 +4775,10 @@
         <v>17</v>
       </c>
       <c r="B155" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D155" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
@@ -4780,10 +4786,10 @@
         <v>17</v>
       </c>
       <c r="B156" t="s">
-        <v>689</v>
+        <v>189</v>
       </c>
       <c r="D156" t="s">
-        <v>690</v>
+        <v>190</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -4802,10 +4808,10 @@
         <v>17</v>
       </c>
       <c r="B158" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D158" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
@@ -4824,10 +4830,10 @@
         <v>17</v>
       </c>
       <c r="B160" t="s">
-        <v>185</v>
+        <v>691</v>
       </c>
       <c r="D160" t="s">
-        <v>186</v>
+        <v>692</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -4835,10 +4841,10 @@
         <v>17</v>
       </c>
       <c r="B161" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D161" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
@@ -4846,10 +4852,10 @@
         <v>17</v>
       </c>
       <c r="B162" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D162" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -4857,10 +4863,10 @@
         <v>17</v>
       </c>
       <c r="B163" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D163" t="s">
-        <v>82</v>
+        <v>194</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
@@ -4868,10 +4874,10 @@
         <v>17</v>
       </c>
       <c r="B164" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D164" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
@@ -4879,10 +4885,10 @@
         <v>17</v>
       </c>
       <c r="B165" t="s">
-        <v>282</v>
+        <v>196</v>
       </c>
       <c r="D165" t="s">
-        <v>283</v>
+        <v>197</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -4890,10 +4896,10 @@
         <v>17</v>
       </c>
       <c r="B166" t="s">
-        <v>198</v>
+        <v>282</v>
       </c>
       <c r="D166" t="s">
-        <v>199</v>
+        <v>283</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
@@ -4901,10 +4907,10 @@
         <v>17</v>
       </c>
       <c r="B167" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D167" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
@@ -4912,7 +4918,7 @@
         <v>17</v>
       </c>
       <c r="B168" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D168" t="s">
         <v>201</v>
@@ -4923,10 +4929,10 @@
         <v>17</v>
       </c>
       <c r="B169" t="s">
-        <v>717</v>
+        <v>202</v>
       </c>
       <c r="D169" t="s">
-        <v>718</v>
+        <v>201</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
@@ -4934,10 +4940,10 @@
         <v>17</v>
       </c>
       <c r="B170" t="s">
-        <v>203</v>
+        <v>717</v>
       </c>
       <c r="D170" t="s">
-        <v>204</v>
+        <v>718</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
@@ -4945,10 +4951,10 @@
         <v>17</v>
       </c>
       <c r="B171" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D171" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
@@ -4956,10 +4962,10 @@
         <v>17</v>
       </c>
       <c r="B172" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D172" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
@@ -4967,10 +4973,10 @@
         <v>17</v>
       </c>
       <c r="B173" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D173" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
@@ -4978,10 +4984,10 @@
         <v>17</v>
       </c>
       <c r="B174" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D174" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
@@ -4989,10 +4995,10 @@
         <v>17</v>
       </c>
       <c r="B175" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D175" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
@@ -5000,10 +5006,10 @@
         <v>17</v>
       </c>
       <c r="B176" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D176" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
@@ -5011,10 +5017,10 @@
         <v>17</v>
       </c>
       <c r="B177" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D177" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -5022,10 +5028,10 @@
         <v>17</v>
       </c>
       <c r="B178" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D178" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
@@ -5033,10 +5039,10 @@
         <v>17</v>
       </c>
       <c r="B179" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D179" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
@@ -5044,10 +5050,10 @@
         <v>17</v>
       </c>
       <c r="B180" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D180" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
@@ -5055,10 +5061,10 @@
         <v>17</v>
       </c>
       <c r="B181" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D181" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
@@ -5066,10 +5072,10 @@
         <v>17</v>
       </c>
       <c r="B182" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="D182" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
@@ -5077,10 +5083,10 @@
         <v>17</v>
       </c>
       <c r="B183" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
       <c r="D183" t="s">
-        <v>227</v>
+        <v>279</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
@@ -5088,10 +5094,10 @@
         <v>17</v>
       </c>
       <c r="B184" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D184" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
@@ -5099,10 +5105,10 @@
         <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>482</v>
+        <v>228</v>
       </c>
       <c r="D185" t="s">
-        <v>483</v>
+        <v>229</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
@@ -5110,10 +5116,10 @@
         <v>17</v>
       </c>
       <c r="B186" t="s">
-        <v>232</v>
+        <v>482</v>
       </c>
       <c r="D186" t="s">
-        <v>233</v>
+        <v>483</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
@@ -5121,10 +5127,10 @@
         <v>17</v>
       </c>
       <c r="B187" t="s">
-        <v>535</v>
+        <v>232</v>
       </c>
       <c r="D187" t="s">
-        <v>536</v>
+        <v>233</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
@@ -5132,10 +5138,10 @@
         <v>17</v>
       </c>
       <c r="B188" t="s">
-        <v>234</v>
+        <v>535</v>
       </c>
       <c r="D188" t="s">
-        <v>235</v>
+        <v>536</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
@@ -5143,10 +5149,10 @@
         <v>17</v>
       </c>
       <c r="B189" t="s">
-        <v>525</v>
+        <v>234</v>
       </c>
       <c r="D189" t="s">
-        <v>526</v>
+        <v>235</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
@@ -5154,10 +5160,10 @@
         <v>17</v>
       </c>
       <c r="B190" t="s">
-        <v>236</v>
+        <v>525</v>
       </c>
       <c r="D190" t="s">
-        <v>237</v>
+        <v>526</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
@@ -5165,10 +5171,10 @@
         <v>17</v>
       </c>
       <c r="B191" t="s">
-        <v>527</v>
+        <v>236</v>
       </c>
       <c r="D191" t="s">
-        <v>528</v>
+        <v>237</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
@@ -5176,10 +5182,10 @@
         <v>17</v>
       </c>
       <c r="B192" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="D192" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
@@ -5187,10 +5193,10 @@
         <v>17</v>
       </c>
       <c r="B193" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D193" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
@@ -5198,10 +5204,10 @@
         <v>17</v>
       </c>
       <c r="B194" t="s">
-        <v>238</v>
+        <v>537</v>
       </c>
       <c r="D194" t="s">
-        <v>239</v>
+        <v>538</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
@@ -5209,10 +5215,10 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D195" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
@@ -5220,10 +5226,10 @@
         <v>17</v>
       </c>
       <c r="B196" t="s">
-        <v>529</v>
+        <v>240</v>
       </c>
       <c r="D196" t="s">
-        <v>530</v>
+        <v>241</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
@@ -5231,10 +5237,10 @@
         <v>17</v>
       </c>
       <c r="B197" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D197" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
@@ -5242,10 +5248,10 @@
         <v>17</v>
       </c>
       <c r="B198" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="D198" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
@@ -5253,21 +5259,21 @@
         <v>17</v>
       </c>
       <c r="B199" t="s">
-        <v>496</v>
+        <v>541</v>
       </c>
       <c r="D199" t="s">
-        <v>497</v>
+        <v>542</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
       <c r="B200" t="s">
-        <v>285</v>
+        <v>496</v>
       </c>
       <c r="D200" t="s">
-        <v>286</v>
+        <v>497</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
@@ -5275,10 +5281,10 @@
         <v>284</v>
       </c>
       <c r="B201" t="s">
-        <v>32</v>
+        <v>285</v>
       </c>
       <c r="D201" t="s">
-        <v>33</v>
+        <v>286</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
@@ -5286,10 +5292,10 @@
         <v>284</v>
       </c>
       <c r="B202" t="s">
-        <v>287</v>
+        <v>32</v>
       </c>
       <c r="D202" t="s">
-        <v>288</v>
+        <v>33</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
@@ -5297,10 +5303,10 @@
         <v>284</v>
       </c>
       <c r="B203" t="s">
-        <v>629</v>
+        <v>287</v>
       </c>
       <c r="D203" t="s">
-        <v>642</v>
+        <v>288</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
@@ -5308,10 +5314,10 @@
         <v>284</v>
       </c>
       <c r="B204" t="s">
-        <v>44</v>
+        <v>629</v>
       </c>
       <c r="D204" t="s">
-        <v>45</v>
+        <v>642</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
@@ -5319,10 +5325,10 @@
         <v>284</v>
       </c>
       <c r="B205" t="s">
-        <v>565</v>
+        <v>44</v>
       </c>
       <c r="D205" t="s">
-        <v>577</v>
+        <v>45</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
@@ -5341,10 +5347,10 @@
         <v>284</v>
       </c>
       <c r="B207" t="s">
-        <v>638</v>
+        <v>565</v>
       </c>
       <c r="D207" t="s">
-        <v>650</v>
+        <v>577</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
@@ -5352,10 +5358,10 @@
         <v>284</v>
       </c>
       <c r="B208" t="s">
-        <v>289</v>
+        <v>638</v>
       </c>
       <c r="D208" t="s">
-        <v>290</v>
+        <v>650</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
@@ -5363,10 +5369,10 @@
         <v>284</v>
       </c>
       <c r="B209" t="s">
-        <v>58</v>
+        <v>289</v>
       </c>
       <c r="D209" t="s">
-        <v>59</v>
+        <v>290</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
@@ -5374,10 +5380,10 @@
         <v>284</v>
       </c>
       <c r="B210" t="s">
-        <v>291</v>
+        <v>58</v>
       </c>
       <c r="D210" t="s">
-        <v>292</v>
+        <v>59</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -5385,10 +5391,10 @@
         <v>284</v>
       </c>
       <c r="B211" t="s">
-        <v>637</v>
+        <v>291</v>
       </c>
       <c r="D211" t="s">
-        <v>649</v>
+        <v>292</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
@@ -5396,10 +5402,10 @@
         <v>284</v>
       </c>
       <c r="B212" t="s">
-        <v>296</v>
+        <v>637</v>
       </c>
       <c r="D212" t="s">
-        <v>297</v>
+        <v>649</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -5407,10 +5413,10 @@
         <v>284</v>
       </c>
       <c r="B213" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D213" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
@@ -5418,10 +5424,10 @@
         <v>284</v>
       </c>
       <c r="B214" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D214" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -5429,10 +5435,10 @@
         <v>284</v>
       </c>
       <c r="B215" t="s">
-        <v>521</v>
+        <v>300</v>
       </c>
       <c r="D215" t="s">
-        <v>522</v>
+        <v>301</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
@@ -5440,10 +5446,10 @@
         <v>284</v>
       </c>
       <c r="B216" t="s">
-        <v>302</v>
+        <v>521</v>
       </c>
       <c r="D216" t="s">
-        <v>302</v>
+        <v>522</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -5451,10 +5457,10 @@
         <v>284</v>
       </c>
       <c r="B217" t="s">
-        <v>640</v>
+        <v>302</v>
       </c>
       <c r="D217" t="s">
-        <v>652</v>
+        <v>302</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
@@ -5462,10 +5468,10 @@
         <v>284</v>
       </c>
       <c r="B218" t="s">
-        <v>303</v>
+        <v>640</v>
       </c>
       <c r="D218" t="s">
-        <v>304</v>
+        <v>652</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
@@ -5473,10 +5479,10 @@
         <v>284</v>
       </c>
       <c r="B219" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D219" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -5484,10 +5490,10 @@
         <v>284</v>
       </c>
       <c r="B220" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D220" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -5495,10 +5501,10 @@
         <v>284</v>
       </c>
       <c r="B221" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D221" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -5506,10 +5512,10 @@
         <v>284</v>
       </c>
       <c r="B222" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D222" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -5517,10 +5523,10 @@
         <v>284</v>
       </c>
       <c r="B223" t="s">
-        <v>60</v>
+        <v>311</v>
       </c>
       <c r="D223" t="s">
-        <v>60</v>
+        <v>312</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
@@ -5528,10 +5534,10 @@
         <v>284</v>
       </c>
       <c r="B224" t="s">
-        <v>313</v>
+        <v>60</v>
       </c>
       <c r="D224" t="s">
-        <v>314</v>
+        <v>60</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -5539,10 +5545,10 @@
         <v>284</v>
       </c>
       <c r="B225" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D225" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -5550,10 +5556,10 @@
         <v>284</v>
       </c>
       <c r="B226" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D226" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
@@ -5561,10 +5567,10 @@
         <v>284</v>
       </c>
       <c r="B227" t="s">
-        <v>515</v>
+        <v>317</v>
       </c>
       <c r="D227" t="s">
-        <v>516</v>
+        <v>318</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
@@ -5572,10 +5578,10 @@
         <v>284</v>
       </c>
       <c r="B228" t="s">
-        <v>555</v>
+        <v>515</v>
       </c>
       <c r="D228" t="s">
-        <v>571</v>
+        <v>516</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -5583,10 +5589,10 @@
         <v>284</v>
       </c>
       <c r="B229" t="s">
-        <v>513</v>
+        <v>555</v>
       </c>
       <c r="D229" t="s">
-        <v>514</v>
+        <v>571</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
@@ -5594,10 +5600,10 @@
         <v>284</v>
       </c>
       <c r="B230" t="s">
-        <v>556</v>
+        <v>513</v>
       </c>
       <c r="D230" t="s">
-        <v>570</v>
+        <v>514</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -5605,10 +5611,10 @@
         <v>284</v>
       </c>
       <c r="B231" t="s">
-        <v>319</v>
+        <v>556</v>
       </c>
       <c r="D231" t="s">
-        <v>319</v>
+        <v>570</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -5616,10 +5622,10 @@
         <v>284</v>
       </c>
       <c r="B232" t="s">
-        <v>566</v>
+        <v>319</v>
       </c>
       <c r="D232" t="s">
-        <v>578</v>
+        <v>319</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
@@ -5627,10 +5633,10 @@
         <v>284</v>
       </c>
       <c r="B233" t="s">
-        <v>320</v>
+        <v>566</v>
       </c>
       <c r="D233" t="s">
-        <v>321</v>
+        <v>578</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -5638,10 +5644,10 @@
         <v>284</v>
       </c>
       <c r="B234" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D234" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -5649,10 +5655,10 @@
         <v>284</v>
       </c>
       <c r="B235" t="s">
-        <v>639</v>
+        <v>322</v>
       </c>
       <c r="D235" t="s">
-        <v>651</v>
+        <v>323</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
@@ -5660,10 +5666,10 @@
         <v>284</v>
       </c>
       <c r="B236" t="s">
-        <v>324</v>
+        <v>639</v>
       </c>
       <c r="D236" t="s">
-        <v>325</v>
+        <v>651</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
@@ -5671,10 +5677,10 @@
         <v>284</v>
       </c>
       <c r="B237" t="s">
-        <v>635</v>
+        <v>324</v>
       </c>
       <c r="D237" t="s">
-        <v>647</v>
+        <v>325</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -5682,10 +5688,10 @@
         <v>284</v>
       </c>
       <c r="B238" t="s">
-        <v>498</v>
+        <v>635</v>
       </c>
       <c r="D238" t="s">
-        <v>499</v>
+        <v>647</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -5693,10 +5699,10 @@
         <v>284</v>
       </c>
       <c r="B239" t="s">
-        <v>631</v>
+        <v>498</v>
       </c>
       <c r="D239" t="s">
-        <v>644</v>
+        <v>499</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -5704,10 +5710,10 @@
         <v>284</v>
       </c>
       <c r="B240" t="s">
-        <v>326</v>
+        <v>631</v>
       </c>
       <c r="D240" t="s">
-        <v>327</v>
+        <v>644</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
@@ -5715,10 +5721,10 @@
         <v>284</v>
       </c>
       <c r="B241" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D241" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
@@ -5726,10 +5732,10 @@
         <v>284</v>
       </c>
       <c r="B242" t="s">
-        <v>668</v>
+        <v>328</v>
       </c>
       <c r="D242" t="s">
-        <v>665</v>
+        <v>329</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
@@ -5737,10 +5743,10 @@
         <v>284</v>
       </c>
       <c r="B243" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D243" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -5748,10 +5754,10 @@
         <v>284</v>
       </c>
       <c r="B244" t="s">
-        <v>561</v>
+        <v>667</v>
       </c>
       <c r="D244" t="s">
-        <v>575</v>
+        <v>666</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -5759,10 +5765,10 @@
         <v>284</v>
       </c>
       <c r="B245" t="s">
-        <v>330</v>
+        <v>561</v>
       </c>
       <c r="D245" t="s">
-        <v>331</v>
+        <v>575</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -5770,10 +5776,10 @@
         <v>284</v>
       </c>
       <c r="B246" t="s">
-        <v>562</v>
+        <v>330</v>
       </c>
       <c r="D246" t="s">
-        <v>627</v>
+        <v>331</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -5781,10 +5787,10 @@
         <v>284</v>
       </c>
       <c r="B247" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D247" t="s">
-        <v>573</v>
+        <v>627</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
@@ -5792,10 +5798,10 @@
         <v>284</v>
       </c>
       <c r="B248" t="s">
-        <v>334</v>
+        <v>558</v>
       </c>
       <c r="D248" t="s">
-        <v>333</v>
+        <v>573</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -5803,10 +5809,10 @@
         <v>284</v>
       </c>
       <c r="B249" t="s">
-        <v>628</v>
+        <v>334</v>
       </c>
       <c r="D249" t="s">
-        <v>641</v>
+        <v>333</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -5814,10 +5820,10 @@
         <v>284</v>
       </c>
       <c r="B250" t="s">
-        <v>335</v>
+        <v>628</v>
       </c>
       <c r="D250" t="s">
-        <v>336</v>
+        <v>641</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -5836,10 +5842,10 @@
         <v>284</v>
       </c>
       <c r="B252" t="s">
-        <v>554</v>
+        <v>335</v>
       </c>
       <c r="D252" t="s">
-        <v>569</v>
+        <v>336</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
@@ -5858,10 +5864,10 @@
         <v>284</v>
       </c>
       <c r="B254" t="s">
-        <v>337</v>
+        <v>554</v>
       </c>
       <c r="D254" t="s">
-        <v>338</v>
+        <v>569</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
@@ -5869,10 +5875,10 @@
         <v>284</v>
       </c>
       <c r="B255" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D255" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -5880,10 +5886,10 @@
         <v>284</v>
       </c>
       <c r="B256" t="s">
-        <v>510</v>
+        <v>339</v>
       </c>
       <c r="D256" t="s">
-        <v>510</v>
+        <v>340</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
@@ -5891,10 +5897,10 @@
         <v>284</v>
       </c>
       <c r="B257" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="D257" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -5902,10 +5908,10 @@
         <v>284</v>
       </c>
       <c r="B258" t="s">
-        <v>341</v>
+        <v>500</v>
       </c>
       <c r="D258" t="s">
-        <v>342</v>
+        <v>501</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -5913,10 +5919,10 @@
         <v>284</v>
       </c>
       <c r="B259" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D259" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
@@ -5924,10 +5930,10 @@
         <v>284</v>
       </c>
       <c r="B260" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D260" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
@@ -5935,10 +5941,10 @@
         <v>284</v>
       </c>
       <c r="B261" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D261" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
@@ -5946,10 +5952,10 @@
         <v>284</v>
       </c>
       <c r="B262" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D262" t="s">
-        <v>293</v>
+        <v>348</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -5957,10 +5963,10 @@
         <v>284</v>
       </c>
       <c r="B263" t="s">
-        <v>564</v>
+        <v>349</v>
       </c>
       <c r="D263" t="s">
-        <v>576</v>
+        <v>293</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -5968,10 +5974,10 @@
         <v>284</v>
       </c>
       <c r="B264" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D264" t="s">
-        <v>417</v>
+        <v>576</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
@@ -5979,10 +5985,10 @@
         <v>284</v>
       </c>
       <c r="B265" t="s">
-        <v>350</v>
+        <v>563</v>
       </c>
       <c r="D265" t="s">
-        <v>351</v>
+        <v>417</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -5990,10 +5996,10 @@
         <v>284</v>
       </c>
       <c r="B266" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D266" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
@@ -6001,10 +6007,10 @@
         <v>284</v>
       </c>
       <c r="B267" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D267" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -6012,10 +6018,10 @@
         <v>284</v>
       </c>
       <c r="B268" t="s">
-        <v>559</v>
+        <v>354</v>
       </c>
       <c r="D268" t="s">
-        <v>653</v>
+        <v>355</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -6023,10 +6029,10 @@
         <v>284</v>
       </c>
       <c r="B269" t="s">
-        <v>356</v>
+        <v>559</v>
       </c>
       <c r="D269" t="s">
-        <v>357</v>
+        <v>653</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -6034,10 +6040,10 @@
         <v>284</v>
       </c>
       <c r="B270" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D270" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -6045,10 +6051,10 @@
         <v>284</v>
       </c>
       <c r="B271" t="s">
-        <v>547</v>
+        <v>358</v>
       </c>
       <c r="D271" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -6056,10 +6062,10 @@
         <v>284</v>
       </c>
       <c r="B272" t="s">
-        <v>360</v>
+        <v>547</v>
       </c>
       <c r="D272" t="s">
-        <v>548</v>
+        <v>361</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -6067,10 +6073,10 @@
         <v>284</v>
       </c>
       <c r="B273" t="s">
-        <v>636</v>
+        <v>360</v>
       </c>
       <c r="D273" t="s">
-        <v>648</v>
+        <v>548</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -6078,10 +6084,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
-        <v>455</v>
+        <v>636</v>
       </c>
       <c r="D274" t="s">
-        <v>456</v>
+        <v>648</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
@@ -6089,10 +6095,10 @@
         <v>284</v>
       </c>
       <c r="B275" t="s">
-        <v>362</v>
+        <v>455</v>
       </c>
       <c r="D275" t="s">
-        <v>362</v>
+        <v>456</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
@@ -6100,10 +6106,10 @@
         <v>284</v>
       </c>
       <c r="B276" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D276" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -6111,10 +6117,10 @@
         <v>284</v>
       </c>
       <c r="B277" t="s">
-        <v>524</v>
+        <v>363</v>
       </c>
       <c r="D277" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -6122,10 +6128,10 @@
         <v>284</v>
       </c>
       <c r="B278" t="s">
-        <v>365</v>
+        <v>524</v>
       </c>
       <c r="D278" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
@@ -6133,10 +6139,10 @@
         <v>284</v>
       </c>
       <c r="B279" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D279" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
@@ -6144,10 +6150,10 @@
         <v>284</v>
       </c>
       <c r="B280" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D280" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
@@ -6155,10 +6161,10 @@
         <v>284</v>
       </c>
       <c r="B281" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D281" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
@@ -6166,10 +6172,10 @@
         <v>284</v>
       </c>
       <c r="B282" t="s">
-        <v>294</v>
+        <v>373</v>
       </c>
       <c r="D282" t="s">
-        <v>295</v>
+        <v>374</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
@@ -6177,10 +6183,10 @@
         <v>284</v>
       </c>
       <c r="B283" t="s">
-        <v>375</v>
+        <v>294</v>
       </c>
       <c r="D283" t="s">
-        <v>376</v>
+        <v>295</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
@@ -6188,10 +6194,10 @@
         <v>284</v>
       </c>
       <c r="B284" t="s">
-        <v>557</v>
+        <v>375</v>
       </c>
       <c r="D284" t="s">
-        <v>572</v>
+        <v>376</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
@@ -6199,10 +6205,10 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="D285" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
@@ -6210,10 +6216,10 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>377</v>
+        <v>567</v>
       </c>
       <c r="D286" t="s">
-        <v>378</v>
+        <v>579</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
@@ -6221,10 +6227,10 @@
         <v>284</v>
       </c>
       <c r="B287" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D287" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
@@ -6232,10 +6238,10 @@
         <v>284</v>
       </c>
       <c r="B288" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D288" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
@@ -6243,10 +6249,10 @@
         <v>284</v>
       </c>
       <c r="B289" t="s">
-        <v>230</v>
+        <v>381</v>
       </c>
       <c r="D289" t="s">
-        <v>231</v>
+        <v>382</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
@@ -6254,10 +6260,10 @@
         <v>284</v>
       </c>
       <c r="B290" t="s">
-        <v>634</v>
+        <v>230</v>
       </c>
       <c r="D290" t="s">
-        <v>643</v>
+        <v>231</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
@@ -6265,10 +6271,10 @@
         <v>284</v>
       </c>
       <c r="B291" t="s">
-        <v>383</v>
+        <v>634</v>
       </c>
       <c r="D291" t="s">
-        <v>384</v>
+        <v>643</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -6276,10 +6282,10 @@
         <v>284</v>
       </c>
       <c r="B292" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D292" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
@@ -6287,10 +6293,10 @@
         <v>284</v>
       </c>
       <c r="B293" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D293" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
@@ -6298,10 +6304,10 @@
         <v>284</v>
       </c>
       <c r="B294" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D294" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
@@ -6309,10 +6315,10 @@
         <v>284</v>
       </c>
       <c r="B295" t="s">
-        <v>17</v>
+        <v>389</v>
       </c>
       <c r="D295" t="s">
-        <v>164</v>
+        <v>390</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
@@ -6320,10 +6326,10 @@
         <v>284</v>
       </c>
       <c r="B296" t="s">
-        <v>391</v>
+        <v>17</v>
       </c>
       <c r="D296" t="s">
-        <v>392</v>
+        <v>164</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -6331,10 +6337,10 @@
         <v>284</v>
       </c>
       <c r="B297" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D297" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
@@ -6342,10 +6348,10 @@
         <v>284</v>
       </c>
       <c r="B298" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D298" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -6353,10 +6359,10 @@
         <v>284</v>
       </c>
       <c r="B299" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D299" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
@@ -6364,10 +6370,10 @@
         <v>284</v>
       </c>
       <c r="B300" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D300" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
@@ -6375,10 +6381,10 @@
         <v>284</v>
       </c>
       <c r="B301" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D301" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
@@ -6386,10 +6392,10 @@
         <v>284</v>
       </c>
       <c r="B302" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D302" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
@@ -6397,10 +6403,10 @@
         <v>284</v>
       </c>
       <c r="B303" t="s">
-        <v>633</v>
+        <v>403</v>
       </c>
       <c r="D303" t="s">
-        <v>646</v>
+        <v>404</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
@@ -6408,10 +6414,10 @@
         <v>284</v>
       </c>
       <c r="B304" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D304" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
@@ -6419,10 +6425,10 @@
         <v>284</v>
       </c>
       <c r="B305" t="s">
-        <v>405</v>
+        <v>630</v>
       </c>
       <c r="D305" t="s">
-        <v>406</v>
+        <v>643</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
@@ -6430,10 +6436,10 @@
         <v>284</v>
       </c>
       <c r="B306" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D306" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
@@ -6441,10 +6447,10 @@
         <v>284</v>
       </c>
       <c r="B307" t="s">
-        <v>508</v>
+        <v>409</v>
       </c>
       <c r="D307" t="s">
-        <v>509</v>
+        <v>410</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
@@ -6452,10 +6458,10 @@
         <v>284</v>
       </c>
       <c r="B308" t="s">
-        <v>560</v>
+        <v>508</v>
       </c>
       <c r="D308" t="s">
-        <v>574</v>
+        <v>509</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
@@ -6463,10 +6469,10 @@
         <v>284</v>
       </c>
       <c r="B309" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="D309" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
@@ -6474,10 +6480,10 @@
         <v>284</v>
       </c>
       <c r="B310" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="D310" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
@@ -6485,10 +6491,10 @@
         <v>284</v>
       </c>
       <c r="B311" t="s">
-        <v>505</v>
+        <v>552</v>
       </c>
       <c r="D311" t="s">
-        <v>506</v>
+        <v>551</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
@@ -6496,10 +6502,10 @@
         <v>284</v>
       </c>
       <c r="B312" t="s">
-        <v>411</v>
+        <v>505</v>
       </c>
       <c r="D312" t="s">
-        <v>411</v>
+        <v>506</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
@@ -6507,10 +6513,10 @@
         <v>284</v>
       </c>
       <c r="B313" t="s">
-        <v>624</v>
+        <v>411</v>
       </c>
       <c r="D313" t="s">
-        <v>625</v>
+        <v>411</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
@@ -6518,10 +6524,10 @@
         <v>284</v>
       </c>
       <c r="B314" t="s">
-        <v>669</v>
+        <v>624</v>
       </c>
       <c r="D314" t="s">
-        <v>670</v>
+        <v>625</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
@@ -6529,10 +6535,10 @@
         <v>284</v>
       </c>
       <c r="B315" t="s">
-        <v>412</v>
+        <v>669</v>
       </c>
       <c r="D315" t="s">
-        <v>413</v>
+        <v>670</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
@@ -6540,10 +6546,10 @@
         <v>284</v>
       </c>
       <c r="B316" t="s">
-        <v>632</v>
+        <v>412</v>
       </c>
       <c r="D316" t="s">
-        <v>645</v>
+        <v>413</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
@@ -6551,10 +6557,10 @@
         <v>284</v>
       </c>
       <c r="B317" t="s">
-        <v>414</v>
+        <v>632</v>
       </c>
       <c r="D317" t="s">
-        <v>415</v>
+        <v>645</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
@@ -6562,10 +6568,10 @@
         <v>284</v>
       </c>
       <c r="B318" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D318" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
@@ -6573,10 +6579,10 @@
         <v>284</v>
       </c>
       <c r="B319" t="s">
-        <v>553</v>
+        <v>416</v>
       </c>
       <c r="D319" t="s">
-        <v>568</v>
+        <v>417</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
@@ -6584,21 +6590,21 @@
         <v>284</v>
       </c>
       <c r="B320" t="s">
-        <v>418</v>
+        <v>553</v>
       </c>
       <c r="D320" t="s">
-        <v>419</v>
+        <v>568</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B321" t="s">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="D321" t="s">
-        <v>22</v>
+        <v>419</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -6606,10 +6612,10 @@
         <v>420</v>
       </c>
       <c r="B322" t="s">
-        <v>421</v>
+        <v>21</v>
       </c>
       <c r="D322" t="s">
-        <v>421</v>
+        <v>22</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
@@ -6617,10 +6623,10 @@
         <v>420</v>
       </c>
       <c r="B323" t="s">
-        <v>30</v>
+        <v>421</v>
       </c>
       <c r="D323" t="s">
-        <v>31</v>
+        <v>421</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
@@ -6628,10 +6634,10 @@
         <v>420</v>
       </c>
       <c r="B324" t="s">
-        <v>546</v>
+        <v>30</v>
       </c>
       <c r="D324" t="s">
-        <v>422</v>
+        <v>31</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -6639,10 +6645,10 @@
         <v>420</v>
       </c>
       <c r="B325" t="s">
-        <v>44</v>
+        <v>546</v>
       </c>
       <c r="D325" t="s">
-        <v>45</v>
+        <v>422</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -6650,10 +6656,10 @@
         <v>420</v>
       </c>
       <c r="B326" t="s">
-        <v>589</v>
+        <v>44</v>
       </c>
       <c r="D326" t="s">
-        <v>610</v>
+        <v>45</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -6661,10 +6667,10 @@
         <v>420</v>
       </c>
       <c r="B327" t="s">
-        <v>50</v>
+        <v>589</v>
       </c>
       <c r="D327" t="s">
-        <v>51</v>
+        <v>610</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -6672,10 +6678,10 @@
         <v>420</v>
       </c>
       <c r="B328" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D328" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
@@ -6683,10 +6689,10 @@
         <v>420</v>
       </c>
       <c r="B329" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D329" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
@@ -6694,10 +6700,10 @@
         <v>420</v>
       </c>
       <c r="B330" t="s">
-        <v>296</v>
+        <v>52</v>
       </c>
       <c r="D330" t="s">
-        <v>519</v>
+        <v>53</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
@@ -6705,10 +6711,10 @@
         <v>420</v>
       </c>
       <c r="B331" t="s">
-        <v>523</v>
+        <v>296</v>
       </c>
       <c r="D331" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -6716,10 +6722,10 @@
         <v>420</v>
       </c>
       <c r="B332" t="s">
-        <v>423</v>
+        <v>523</v>
       </c>
       <c r="D332" t="s">
-        <v>424</v>
+        <v>520</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
@@ -6727,10 +6733,10 @@
         <v>420</v>
       </c>
       <c r="B333" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D333" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
@@ -6738,10 +6744,10 @@
         <v>420</v>
       </c>
       <c r="B334" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D334" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -6749,10 +6755,10 @@
         <v>420</v>
       </c>
       <c r="B335" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D335" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -6760,10 +6766,10 @@
         <v>420</v>
       </c>
       <c r="B336" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D336" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -6771,10 +6777,10 @@
         <v>420</v>
       </c>
       <c r="B337" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D337" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
@@ -6782,10 +6788,10 @@
         <v>420</v>
       </c>
       <c r="B338" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D338" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
@@ -6793,10 +6799,10 @@
         <v>420</v>
       </c>
       <c r="B339" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D339" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -6804,10 +6810,10 @@
         <v>420</v>
       </c>
       <c r="B340" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D340" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
@@ -6815,10 +6821,10 @@
         <v>420</v>
       </c>
       <c r="B341" t="s">
-        <v>61</v>
+        <v>439</v>
       </c>
       <c r="D341" t="s">
-        <v>62</v>
+        <v>440</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -6826,10 +6832,10 @@
         <v>420</v>
       </c>
       <c r="B342" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D342" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
@@ -6837,10 +6843,10 @@
         <v>420</v>
       </c>
       <c r="B343" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D343" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -6848,10 +6854,10 @@
         <v>420</v>
       </c>
       <c r="B344" t="s">
-        <v>671</v>
+        <v>63</v>
       </c>
       <c r="D344" t="s">
-        <v>672</v>
+        <v>64</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -6859,10 +6865,10 @@
         <v>420</v>
       </c>
       <c r="B345" t="s">
-        <v>441</v>
+        <v>671</v>
       </c>
       <c r="D345" t="s">
-        <v>442</v>
+        <v>672</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
@@ -6870,10 +6876,10 @@
         <v>420</v>
       </c>
       <c r="B346" t="s">
-        <v>588</v>
+        <v>441</v>
       </c>
       <c r="D346" t="s">
-        <v>609</v>
+        <v>442</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
@@ -6881,10 +6887,10 @@
         <v>420</v>
       </c>
       <c r="B347" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D347" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -6892,10 +6898,10 @@
         <v>420</v>
       </c>
       <c r="B348" t="s">
-        <v>75</v>
+        <v>587</v>
       </c>
       <c r="D348" t="s">
-        <v>76</v>
+        <v>608</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
@@ -6903,10 +6909,10 @@
         <v>420</v>
       </c>
       <c r="B349" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D349" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
@@ -6914,10 +6920,10 @@
         <v>420</v>
       </c>
       <c r="B350" t="s">
-        <v>326</v>
+        <v>77</v>
       </c>
       <c r="D350" t="s">
-        <v>327</v>
+        <v>78</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
@@ -6925,10 +6931,10 @@
         <v>420</v>
       </c>
       <c r="B351" t="s">
-        <v>449</v>
+        <v>326</v>
       </c>
       <c r="D351" t="s">
-        <v>443</v>
+        <v>327</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
@@ -6936,10 +6942,10 @@
         <v>420</v>
       </c>
       <c r="B352" t="s">
-        <v>545</v>
+        <v>449</v>
       </c>
       <c r="D352" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
@@ -6947,10 +6953,10 @@
         <v>420</v>
       </c>
       <c r="B353" t="s">
-        <v>585</v>
+        <v>545</v>
       </c>
       <c r="D353" t="s">
-        <v>606</v>
+        <v>444</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
@@ -6958,10 +6964,10 @@
         <v>420</v>
       </c>
       <c r="B354" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D354" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
@@ -6969,10 +6975,10 @@
         <v>420</v>
       </c>
       <c r="B355" t="s">
-        <v>445</v>
+        <v>586</v>
       </c>
       <c r="D355" t="s">
-        <v>446</v>
+        <v>607</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
@@ -6980,10 +6986,10 @@
         <v>420</v>
       </c>
       <c r="B356" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D356" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
@@ -6991,10 +6997,10 @@
         <v>420</v>
       </c>
       <c r="B357" t="s">
-        <v>654</v>
+        <v>447</v>
       </c>
       <c r="D357" t="s">
-        <v>655</v>
+        <v>448</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
@@ -7002,10 +7008,10 @@
         <v>420</v>
       </c>
       <c r="B358" t="s">
-        <v>332</v>
+        <v>654</v>
       </c>
       <c r="D358" t="s">
-        <v>333</v>
+        <v>655</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
@@ -7013,10 +7019,10 @@
         <v>420</v>
       </c>
       <c r="B359" t="s">
-        <v>101</v>
+        <v>332</v>
       </c>
       <c r="D359" t="s">
-        <v>102</v>
+        <v>333</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
@@ -7024,10 +7030,10 @@
         <v>420</v>
       </c>
       <c r="B360" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D360" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
@@ -7035,10 +7041,10 @@
         <v>420</v>
       </c>
       <c r="B361" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D361" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
@@ -7046,10 +7052,10 @@
         <v>420</v>
       </c>
       <c r="B362" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D362" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
@@ -7057,10 +7063,10 @@
         <v>420</v>
       </c>
       <c r="B363" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D363" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
@@ -7068,10 +7074,10 @@
         <v>420</v>
       </c>
       <c r="B364" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D364" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
@@ -7079,10 +7085,10 @@
         <v>420</v>
       </c>
       <c r="B365" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D365" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
@@ -7090,10 +7096,10 @@
         <v>420</v>
       </c>
       <c r="B366" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D366" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -7101,10 +7107,10 @@
         <v>420</v>
       </c>
       <c r="B367" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D367" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
@@ -7112,10 +7118,10 @@
         <v>420</v>
       </c>
       <c r="B368" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D368" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
@@ -7123,10 +7129,10 @@
         <v>420</v>
       </c>
       <c r="B369" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D369" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -7134,10 +7140,10 @@
         <v>420</v>
       </c>
       <c r="B370" t="s">
-        <v>450</v>
+        <v>121</v>
       </c>
       <c r="D370" t="s">
-        <v>451</v>
+        <v>122</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
@@ -7145,10 +7151,10 @@
         <v>420</v>
       </c>
       <c r="B371" t="s">
-        <v>549</v>
+        <v>450</v>
       </c>
       <c r="D371" t="s">
-        <v>550</v>
+        <v>451</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
@@ -7156,10 +7162,10 @@
         <v>420</v>
       </c>
       <c r="B372" t="s">
-        <v>129</v>
+        <v>549</v>
       </c>
       <c r="D372" t="s">
-        <v>130</v>
+        <v>550</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -7167,10 +7173,10 @@
         <v>420</v>
       </c>
       <c r="B373" t="s">
-        <v>592</v>
+        <v>129</v>
       </c>
       <c r="D373" t="s">
-        <v>612</v>
+        <v>130</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
@@ -7178,10 +7184,10 @@
         <v>420</v>
       </c>
       <c r="B374" t="s">
-        <v>622</v>
+        <v>592</v>
       </c>
       <c r="D374" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -7189,10 +7195,10 @@
         <v>420</v>
       </c>
       <c r="B375" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="D375" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -7200,10 +7206,10 @@
         <v>420</v>
       </c>
       <c r="B376" t="s">
-        <v>452</v>
+        <v>591</v>
       </c>
       <c r="D376" t="s">
-        <v>453</v>
+        <v>626</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
@@ -7211,10 +7217,10 @@
         <v>420</v>
       </c>
       <c r="B377" t="s">
-        <v>598</v>
+        <v>452</v>
       </c>
       <c r="D377" t="s">
-        <v>618</v>
+        <v>453</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
@@ -7222,10 +7228,10 @@
         <v>420</v>
       </c>
       <c r="B378" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="D378" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
@@ -7233,10 +7239,10 @@
         <v>420</v>
       </c>
       <c r="B379" t="s">
-        <v>659</v>
+        <v>590</v>
       </c>
       <c r="D379" t="s">
-        <v>660</v>
+        <v>611</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
@@ -7244,10 +7250,10 @@
         <v>420</v>
       </c>
       <c r="B380" t="s">
-        <v>595</v>
+        <v>659</v>
       </c>
       <c r="D380" t="s">
-        <v>615</v>
+        <v>660</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
@@ -7255,10 +7261,10 @@
         <v>420</v>
       </c>
       <c r="B381" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="D381" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
@@ -7266,10 +7272,10 @@
         <v>420</v>
       </c>
       <c r="B382" t="s">
-        <v>455</v>
+        <v>584</v>
       </c>
       <c r="D382" t="s">
-        <v>456</v>
+        <v>605</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
@@ -7277,10 +7283,10 @@
         <v>420</v>
       </c>
       <c r="B383" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D383" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
@@ -7288,10 +7294,10 @@
         <v>420</v>
       </c>
       <c r="B384" t="s">
-        <v>362</v>
+        <v>457</v>
       </c>
       <c r="D384" t="s">
-        <v>362</v>
+        <v>454</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
@@ -7299,10 +7305,10 @@
         <v>420</v>
       </c>
       <c r="B385" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D385" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
@@ -7310,10 +7316,10 @@
         <v>420</v>
       </c>
       <c r="B386" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D386" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
@@ -7321,10 +7327,10 @@
         <v>420</v>
       </c>
       <c r="B387" t="s">
-        <v>596</v>
+        <v>369</v>
       </c>
       <c r="D387" t="s">
-        <v>616</v>
+        <v>370</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
@@ -7332,10 +7338,10 @@
         <v>420</v>
       </c>
       <c r="B388" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D388" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
@@ -7343,10 +7349,10 @@
         <v>420</v>
       </c>
       <c r="B389" t="s">
-        <v>377</v>
+        <v>597</v>
       </c>
       <c r="D389" t="s">
-        <v>378</v>
+        <v>617</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
@@ -7354,10 +7360,10 @@
         <v>420</v>
       </c>
       <c r="B390" t="s">
-        <v>156</v>
+        <v>377</v>
       </c>
       <c r="D390" t="s">
-        <v>157</v>
+        <v>378</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
@@ -7365,10 +7371,10 @@
         <v>420</v>
       </c>
       <c r="B391" t="s">
-        <v>379</v>
+        <v>156</v>
       </c>
       <c r="D391" t="s">
-        <v>380</v>
+        <v>157</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
@@ -7376,10 +7382,10 @@
         <v>420</v>
       </c>
       <c r="B392" t="s">
-        <v>656</v>
+        <v>379</v>
       </c>
       <c r="D392" t="s">
-        <v>657</v>
+        <v>380</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
@@ -7387,10 +7393,10 @@
         <v>420</v>
       </c>
       <c r="B393" t="s">
-        <v>17</v>
+        <v>656</v>
       </c>
       <c r="D393" t="s">
-        <v>164</v>
+        <v>657</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -7398,10 +7404,10 @@
         <v>420</v>
       </c>
       <c r="B394" t="s">
-        <v>458</v>
+        <v>17</v>
       </c>
       <c r="D394" t="s">
-        <v>459</v>
+        <v>164</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
@@ -7409,10 +7415,10 @@
         <v>420</v>
       </c>
       <c r="B395" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D395" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
@@ -7420,10 +7426,10 @@
         <v>420</v>
       </c>
       <c r="B396" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D396" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
@@ -7431,10 +7437,10 @@
         <v>420</v>
       </c>
       <c r="B397" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D397" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
@@ -7442,10 +7448,10 @@
         <v>420</v>
       </c>
       <c r="B398" t="s">
-        <v>399</v>
+        <v>464</v>
       </c>
       <c r="D398" t="s">
-        <v>400</v>
+        <v>465</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
@@ -7453,10 +7459,10 @@
         <v>420</v>
       </c>
       <c r="B399" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="D399" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
@@ -7464,10 +7470,10 @@
         <v>420</v>
       </c>
       <c r="B400" t="s">
-        <v>466</v>
+        <v>407</v>
       </c>
       <c r="D400" t="s">
-        <v>467</v>
+        <v>408</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
@@ -7475,10 +7481,10 @@
         <v>420</v>
       </c>
       <c r="B401" t="s">
-        <v>187</v>
+        <v>466</v>
       </c>
       <c r="D401" t="s">
-        <v>188</v>
+        <v>467</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
@@ -7486,10 +7492,10 @@
         <v>420</v>
       </c>
       <c r="B402" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D402" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
@@ -7497,10 +7503,10 @@
         <v>420</v>
       </c>
       <c r="B403" t="s">
-        <v>601</v>
+        <v>196</v>
       </c>
       <c r="D403" t="s">
-        <v>621</v>
+        <v>197</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
@@ -7508,10 +7514,10 @@
         <v>420</v>
       </c>
       <c r="B404" t="s">
-        <v>468</v>
+        <v>601</v>
       </c>
       <c r="D404" t="s">
-        <v>469</v>
+        <v>621</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
@@ -7519,10 +7525,10 @@
         <v>420</v>
       </c>
       <c r="B405" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D405" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
@@ -7530,10 +7536,10 @@
         <v>420</v>
       </c>
       <c r="B406" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D406" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
@@ -7541,10 +7547,10 @@
         <v>420</v>
       </c>
       <c r="B407" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D407" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
@@ -7552,10 +7558,10 @@
         <v>420</v>
       </c>
       <c r="B408" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D408" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
@@ -7563,10 +7569,10 @@
         <v>420</v>
       </c>
       <c r="B409" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D409" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
@@ -7574,10 +7580,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D410" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
@@ -7585,10 +7591,10 @@
         <v>420</v>
       </c>
       <c r="B411" t="s">
-        <v>599</v>
+        <v>480</v>
       </c>
       <c r="D411" t="s">
-        <v>619</v>
+        <v>481</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
@@ -7596,10 +7602,10 @@
         <v>420</v>
       </c>
       <c r="B412" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D412" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
@@ -7607,10 +7613,10 @@
         <v>420</v>
       </c>
       <c r="B413" t="s">
-        <v>482</v>
+        <v>600</v>
       </c>
       <c r="D413" t="s">
-        <v>483</v>
+        <v>620</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
@@ -7618,10 +7624,10 @@
         <v>420</v>
       </c>
       <c r="B414" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D414" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
@@ -7629,10 +7635,10 @@
         <v>420</v>
       </c>
       <c r="B415" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D415" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
@@ -7640,10 +7646,10 @@
         <v>420</v>
       </c>
       <c r="B416" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D416" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
@@ -7651,10 +7657,10 @@
         <v>420</v>
       </c>
       <c r="B417" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D417" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
@@ -7662,10 +7668,10 @@
         <v>420</v>
       </c>
       <c r="B418" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D418" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
@@ -7673,10 +7679,10 @@
         <v>420</v>
       </c>
       <c r="B419" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D419" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
@@ -7684,10 +7690,10 @@
         <v>420</v>
       </c>
       <c r="B420" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D420" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
@@ -7695,10 +7701,10 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>582</v>
+        <v>496</v>
       </c>
       <c r="D421" t="s">
-        <v>658</v>
+        <v>497</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
@@ -7706,10 +7712,10 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D422" t="s">
-        <v>604</v>
+        <v>658</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
@@ -7717,10 +7723,10 @@
         <v>420</v>
       </c>
       <c r="B423" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D423" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
@@ -7728,10 +7734,10 @@
         <v>420</v>
       </c>
       <c r="B424" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D424" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
@@ -7739,10 +7745,10 @@
         <v>420</v>
       </c>
       <c r="B425" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="D425" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
@@ -7750,17 +7756,28 @@
         <v>420</v>
       </c>
       <c r="B426" t="s">
+        <v>594</v>
+      </c>
+      <c r="D426" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>420</v>
+      </c>
+      <c r="B427" t="s">
         <v>593</v>
       </c>
-      <c r="D426" t="s">
+      <c r="D427" t="s">
         <v>613</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D394" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D426">
-    <sortCondition ref="A2:A426"/>
-    <sortCondition ref="B2:B426"/>
+  <autoFilter ref="A1:D395" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D427">
+    <sortCondition ref="A2:A427"/>
+    <sortCondition ref="B2:B427"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_dev\Seal-Report\Repository\Settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD59B78-FA1D-4C81-AD07-04EFCDBE8C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BF45D9-9C20-4A10-96A2-20EBED90EF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13230" yWindow="1665" windowWidth="27240" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9225" yWindow="2475" windowWidth="24375" windowHeight="15855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Translations" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$D$395</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$D$502</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="852">
   <si>
     <t>Context</t>
   </si>
@@ -2211,6 +2211,387 @@
   </si>
   <si>
     <t>Résumé du rapport</t>
+  </si>
+  <si>
+    <t>Select assistant</t>
+  </si>
+  <si>
+    <t>Sélectionner l'assistant</t>
+  </si>
+  <si>
+    <t>No favorites yet</t>
+  </si>
+  <si>
+    <t>Aucun favori pour le moment</t>
+  </si>
+  <si>
+    <t>Recent</t>
+  </si>
+  <si>
+    <t>No recent items</t>
+  </si>
+  <si>
+    <t>Aucun élément récent</t>
+  </si>
+  <si>
+    <t>New conversation</t>
+  </si>
+  <si>
+    <t>Nouvelle conversation</t>
+  </si>
+  <si>
+    <t>Sample prompts</t>
+  </si>
+  <si>
+    <t>Exemples de prompts</t>
+  </si>
+  <si>
+    <t>Sample Prompts</t>
+  </si>
+  <si>
+    <t>No sample prompts defined</t>
+  </si>
+  <si>
+    <t>Aucun exemple de prompt défini</t>
+  </si>
+  <si>
+    <t>AI Assistant</t>
+  </si>
+  <si>
+    <t>Assistant IA</t>
+  </si>
+  <si>
+    <t>Favorites &amp; Recent</t>
+  </si>
+  <si>
+    <t>Favoris et récents</t>
+  </si>
+  <si>
+    <t>Hide panel</t>
+  </si>
+  <si>
+    <t>Masquer le panneau</t>
+  </si>
+  <si>
+    <t>Ask the AI assistant…</t>
+  </si>
+  <si>
+    <t>Posez une question à l'assistant IA…</t>
+  </si>
+  <si>
+    <t>Confirm Deletion</t>
+  </si>
+  <si>
+    <t>Confirmer la suppression</t>
+  </si>
+  <si>
+    <t>This action is irreversible. Are you sure you want to delete this item?</t>
+  </si>
+  <si>
+    <t>Cette action est irréversible. Voulez-vous vraiment supprimer cet élément ?</t>
+  </si>
+  <si>
+    <t>Data Source</t>
+  </si>
+  <si>
+    <t>Source de données</t>
+  </si>
+  <si>
+    <t>Report Assistants</t>
+  </si>
+  <si>
+    <t>Assistants de rapport</t>
+  </si>
+  <si>
+    <t>Select Tables or Views</t>
+  </si>
+  <si>
+    <t>Sélectionner les tables ou les vues</t>
+  </si>
+  <si>
+    <t>Filter tables...</t>
+  </si>
+  <si>
+    <t>Filtrer les tables...</t>
+  </si>
+  <si>
+    <t>Select All</t>
+  </si>
+  <si>
+    <t>Tout sélectionner</t>
+  </si>
+  <si>
+    <t>Deselect All</t>
+  </si>
+  <si>
+    <t>Tout désélectionner</t>
+  </si>
+  <si>
+    <t>tables selected</t>
+  </si>
+  <si>
+    <t>tables sélectionnées</t>
+  </si>
+  <si>
+    <t>Prompt Shortcuts</t>
+  </si>
+  <si>
+    <t>Raccourcis de prompts</t>
+  </si>
+  <si>
+    <t>How can Seal AI help you today ?</t>
+  </si>
+  <si>
+    <t>Comment Seal AI peut-il vous aider aujourd'hui ?</t>
+  </si>
+  <si>
+    <t>No current items available</t>
+  </si>
+  <si>
+    <t>Aucun élément courant disponible</t>
+  </si>
+  <si>
+    <t>Current items will appear here when saved</t>
+  </si>
+  <si>
+    <t>Les éléments courants apparaîtront ici une fois enregistrés</t>
+  </si>
+  <si>
+    <t>Drafts</t>
+  </si>
+  <si>
+    <t>Brouillons</t>
+  </si>
+  <si>
+    <t>No draft items available</t>
+  </si>
+  <si>
+    <t>Aucun brouillon disponible</t>
+  </si>
+  <si>
+    <t>Upload files or create new items with the assistant to see them here</t>
+  </si>
+  <si>
+    <t>Téléversez des fichiers ou créez des éléments avec l'assistant pour les voir ici</t>
+  </si>
+  <si>
+    <t>Item Details</t>
+  </si>
+  <si>
+    <t>Détails de l'élément</t>
+  </si>
+  <si>
+    <t>Loading detail. Please wait...</t>
+  </si>
+  <si>
+    <t>Chargement des détails. Veuillez patienter...</t>
+  </si>
+  <si>
+    <t>Select a row from the table to view its details</t>
+  </si>
+  <si>
+    <t>Sélectionnez une ligne du tableau pour afficher ses détails</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>Vérifier</t>
+  </si>
+  <si>
+    <t>Download</t>
+  </si>
+  <si>
+    <t>Télécharger</t>
+  </si>
+  <si>
+    <t>Reports Assistant</t>
+  </si>
+  <si>
+    <t>Assistant de rapports</t>
+  </si>
+  <si>
+    <t>Connection type</t>
+  </si>
+  <si>
+    <t>Type de connexion</t>
+  </si>
+  <si>
+    <t>Connection string</t>
+  </si>
+  <si>
+    <t>Chaîne de connexion</t>
+  </si>
+  <si>
+    <t>Tables or views</t>
+  </si>
+  <si>
+    <t>Tables ou vues</t>
+  </si>
+  <si>
+    <t>Report Assistant</t>
+  </si>
+  <si>
+    <t>Assistant de rapport</t>
+  </si>
+  <si>
+    <t>AI Provider</t>
+  </si>
+  <si>
+    <t>Fournisseur IA</t>
+  </si>
+  <si>
+    <t>AI model</t>
+  </si>
+  <si>
+    <t>Modèle IA</t>
+  </si>
+  <si>
+    <t>AI model name (overrides default))</t>
+  </si>
+  <si>
+    <t>Nom du modèle IA (remplace la valeur par défaut)</t>
+  </si>
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>Température</t>
+  </si>
+  <si>
+    <t>Model temperature</t>
+  </si>
+  <si>
+    <t>Température du modèle</t>
+  </si>
+  <si>
+    <t>System prompt</t>
+  </si>
+  <si>
+    <t>Prompt système</t>
+  </si>
+  <si>
+    <t>Optional sytem prompt for the assistant</t>
+  </si>
+  <si>
+    <t>Prompt système optionnel pour l'assistant</t>
+  </si>
+  <si>
+    <t>User prompt</t>
+  </si>
+  <si>
+    <t>Prompt utilisateur</t>
+  </si>
+  <si>
+    <t>Default user prompts (if empty default values configured are taken)</t>
+  </si>
+  <si>
+    <t>Prompts utilisateur par défaut (si vide, les valeurs par défaut configurées sont utilisées)</t>
+  </si>
+  <si>
+    <t>User Groups allowed (No selection means no restriction)</t>
+  </si>
+  <si>
+    <t>Groupes d'utilisateurs autorisés (aucune sélection = aucune restriction)</t>
+  </si>
+  <si>
+    <t>Scan options</t>
+  </si>
+  <si>
+    <t>Options d'analyse</t>
+  </si>
+  <si>
+    <t>When to scan</t>
+  </si>
+  <si>
+    <t>Quand analyser</t>
+  </si>
+  <si>
+    <t>Cache duration (days)</t>
+  </si>
+  <si>
+    <t>Durée du cache (jours)</t>
+  </si>
+  <si>
+    <t>Cache duration (days) for scanned data</t>
+  </si>
+  <si>
+    <t>Durée du cache (jours) pour les données analysées</t>
+  </si>
+  <si>
+    <t>Tables to scan (no selection means all tables)</t>
+  </si>
+  <si>
+    <t>Tables à analyser (aucune sélection = toutes les tables)</t>
+  </si>
+  <si>
+    <t>Records to scan</t>
+  </si>
+  <si>
+    <t>Enregistrements à analyser</t>
+  </si>
+  <si>
+    <t>Number of records used for scan</t>
+  </si>
+  <si>
+    <t>Nombre d'enregistrements utilisés pour l'analyse</t>
+  </si>
+  <si>
+    <t>Scan Data Now</t>
+  </si>
+  <si>
+    <t>Analyser les données maintenant</t>
+  </si>
+  <si>
+    <t>Elements:</t>
+  </si>
+  <si>
+    <t>Éléments :</t>
+  </si>
+  <si>
+    <t>Restrictions:</t>
+  </si>
+  <si>
+    <t>Restrictions :</t>
+  </si>
+  <si>
+    <t>Hide AI Assistant</t>
+  </si>
+  <si>
+    <t>Masquer l'assistant IA</t>
+  </si>
+  <si>
+    <t>Running</t>
+  </si>
+  <si>
+    <t>Request cancelled.</t>
+  </si>
+  <si>
+    <t>Demande annulée.</t>
+  </si>
+  <si>
+    <t>Remove from favorites</t>
+  </si>
+  <si>
+    <t>Retirer des favoris</t>
+  </si>
+  <si>
+    <t>Configuration</t>
+  </si>
+  <si>
+    <t>Download/Upload</t>
+  </si>
+  <si>
+    <t>Télécharger/Téléverser</t>
+  </si>
+  <si>
+    <t>Assistants</t>
+  </si>
+  <si>
+    <t>Rights</t>
+  </si>
+  <si>
+    <t>Droits</t>
   </si>
 </sst>
 </file>
@@ -3065,7 +3446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D427"/>
+  <dimension ref="A1:D502"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -5314,10 +5695,10 @@
         <v>284</v>
       </c>
       <c r="B204" t="s">
-        <v>629</v>
+        <v>849</v>
       </c>
       <c r="D204" t="s">
-        <v>642</v>
+        <v>849</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
@@ -5325,10 +5706,10 @@
         <v>284</v>
       </c>
       <c r="B205" t="s">
-        <v>44</v>
+        <v>629</v>
       </c>
       <c r="D205" t="s">
-        <v>45</v>
+        <v>642</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
@@ -5336,10 +5717,10 @@
         <v>284</v>
       </c>
       <c r="B206" t="s">
-        <v>565</v>
+        <v>44</v>
       </c>
       <c r="D206" t="s">
-        <v>577</v>
+        <v>45</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -5358,10 +5739,10 @@
         <v>284</v>
       </c>
       <c r="B208" t="s">
-        <v>638</v>
+        <v>565</v>
       </c>
       <c r="D208" t="s">
-        <v>650</v>
+        <v>577</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
@@ -5369,10 +5750,10 @@
         <v>284</v>
       </c>
       <c r="B209" t="s">
-        <v>289</v>
+        <v>638</v>
       </c>
       <c r="D209" t="s">
-        <v>290</v>
+        <v>650</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
@@ -5380,10 +5761,10 @@
         <v>284</v>
       </c>
       <c r="B210" t="s">
-        <v>58</v>
+        <v>289</v>
       </c>
       <c r="D210" t="s">
-        <v>59</v>
+        <v>290</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -5391,10 +5772,10 @@
         <v>284</v>
       </c>
       <c r="B211" t="s">
-        <v>291</v>
+        <v>58</v>
       </c>
       <c r="D211" t="s">
-        <v>292</v>
+        <v>59</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
@@ -5402,10 +5783,10 @@
         <v>284</v>
       </c>
       <c r="B212" t="s">
-        <v>637</v>
+        <v>291</v>
       </c>
       <c r="D212" t="s">
-        <v>649</v>
+        <v>292</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -5413,10 +5794,10 @@
         <v>284</v>
       </c>
       <c r="B213" t="s">
-        <v>296</v>
+        <v>637</v>
       </c>
       <c r="D213" t="s">
-        <v>297</v>
+        <v>649</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
@@ -5424,10 +5805,10 @@
         <v>284</v>
       </c>
       <c r="B214" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D214" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -5435,10 +5816,10 @@
         <v>284</v>
       </c>
       <c r="B215" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D215" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
@@ -5446,10 +5827,10 @@
         <v>284</v>
       </c>
       <c r="B216" t="s">
-        <v>521</v>
+        <v>300</v>
       </c>
       <c r="D216" t="s">
-        <v>522</v>
+        <v>301</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -5457,10 +5838,10 @@
         <v>284</v>
       </c>
       <c r="B217" t="s">
-        <v>302</v>
+        <v>521</v>
       </c>
       <c r="D217" t="s">
-        <v>302</v>
+        <v>522</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
@@ -5468,10 +5849,10 @@
         <v>284</v>
       </c>
       <c r="B218" t="s">
-        <v>640</v>
+        <v>302</v>
       </c>
       <c r="D218" t="s">
-        <v>652</v>
+        <v>302</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
@@ -5479,10 +5860,10 @@
         <v>284</v>
       </c>
       <c r="B219" t="s">
-        <v>303</v>
+        <v>640</v>
       </c>
       <c r="D219" t="s">
-        <v>304</v>
+        <v>652</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -5490,10 +5871,10 @@
         <v>284</v>
       </c>
       <c r="B220" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D220" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -5501,10 +5882,10 @@
         <v>284</v>
       </c>
       <c r="B221" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D221" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -5512,10 +5893,10 @@
         <v>284</v>
       </c>
       <c r="B222" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D222" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -5523,10 +5904,10 @@
         <v>284</v>
       </c>
       <c r="B223" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D223" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
@@ -5534,10 +5915,10 @@
         <v>284</v>
       </c>
       <c r="B224" t="s">
-        <v>60</v>
+        <v>311</v>
       </c>
       <c r="D224" t="s">
-        <v>60</v>
+        <v>312</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -5545,10 +5926,10 @@
         <v>284</v>
       </c>
       <c r="B225" t="s">
-        <v>313</v>
+        <v>60</v>
       </c>
       <c r="D225" t="s">
-        <v>314</v>
+        <v>60</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -5556,10 +5937,10 @@
         <v>284</v>
       </c>
       <c r="B226" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D226" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
@@ -5567,10 +5948,10 @@
         <v>284</v>
       </c>
       <c r="B227" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D227" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
@@ -5578,10 +5959,10 @@
         <v>284</v>
       </c>
       <c r="B228" t="s">
-        <v>515</v>
+        <v>317</v>
       </c>
       <c r="D228" t="s">
-        <v>516</v>
+        <v>318</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -5589,10 +5970,10 @@
         <v>284</v>
       </c>
       <c r="B229" t="s">
-        <v>555</v>
+        <v>515</v>
       </c>
       <c r="D229" t="s">
-        <v>571</v>
+        <v>516</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
@@ -5600,10 +5981,10 @@
         <v>284</v>
       </c>
       <c r="B230" t="s">
-        <v>513</v>
+        <v>555</v>
       </c>
       <c r="D230" t="s">
-        <v>514</v>
+        <v>571</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -5611,10 +5992,10 @@
         <v>284</v>
       </c>
       <c r="B231" t="s">
-        <v>556</v>
+        <v>513</v>
       </c>
       <c r="D231" t="s">
-        <v>570</v>
+        <v>514</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -5622,10 +6003,10 @@
         <v>284</v>
       </c>
       <c r="B232" t="s">
-        <v>319</v>
+        <v>556</v>
       </c>
       <c r="D232" t="s">
-        <v>319</v>
+        <v>570</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
@@ -5633,10 +6014,10 @@
         <v>284</v>
       </c>
       <c r="B233" t="s">
-        <v>566</v>
+        <v>319</v>
       </c>
       <c r="D233" t="s">
-        <v>578</v>
+        <v>319</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -5644,10 +6025,10 @@
         <v>284</v>
       </c>
       <c r="B234" t="s">
-        <v>320</v>
+        <v>566</v>
       </c>
       <c r="D234" t="s">
-        <v>321</v>
+        <v>578</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -5655,10 +6036,10 @@
         <v>284</v>
       </c>
       <c r="B235" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D235" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
@@ -5666,10 +6047,10 @@
         <v>284</v>
       </c>
       <c r="B236" t="s">
-        <v>639</v>
+        <v>322</v>
       </c>
       <c r="D236" t="s">
-        <v>651</v>
+        <v>323</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
@@ -5677,10 +6058,10 @@
         <v>284</v>
       </c>
       <c r="B237" t="s">
-        <v>324</v>
+        <v>639</v>
       </c>
       <c r="D237" t="s">
-        <v>325</v>
+        <v>651</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -5688,10 +6069,10 @@
         <v>284</v>
       </c>
       <c r="B238" t="s">
-        <v>635</v>
+        <v>324</v>
       </c>
       <c r="D238" t="s">
-        <v>647</v>
+        <v>325</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -5699,10 +6080,10 @@
         <v>284</v>
       </c>
       <c r="B239" t="s">
-        <v>498</v>
+        <v>635</v>
       </c>
       <c r="D239" t="s">
-        <v>499</v>
+        <v>647</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -5710,10 +6091,10 @@
         <v>284</v>
       </c>
       <c r="B240" t="s">
-        <v>631</v>
+        <v>498</v>
       </c>
       <c r="D240" t="s">
-        <v>644</v>
+        <v>499</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
@@ -5721,10 +6102,10 @@
         <v>284</v>
       </c>
       <c r="B241" t="s">
-        <v>326</v>
+        <v>631</v>
       </c>
       <c r="D241" t="s">
-        <v>327</v>
+        <v>644</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
@@ -5732,10 +6113,10 @@
         <v>284</v>
       </c>
       <c r="B242" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D242" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
@@ -5743,10 +6124,10 @@
         <v>284</v>
       </c>
       <c r="B243" t="s">
-        <v>668</v>
+        <v>328</v>
       </c>
       <c r="D243" t="s">
-        <v>665</v>
+        <v>329</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -5754,10 +6135,10 @@
         <v>284</v>
       </c>
       <c r="B244" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D244" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -5765,10 +6146,10 @@
         <v>284</v>
       </c>
       <c r="B245" t="s">
-        <v>561</v>
+        <v>667</v>
       </c>
       <c r="D245" t="s">
-        <v>575</v>
+        <v>666</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -5776,10 +6157,10 @@
         <v>284</v>
       </c>
       <c r="B246" t="s">
-        <v>330</v>
+        <v>561</v>
       </c>
       <c r="D246" t="s">
-        <v>331</v>
+        <v>575</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -5787,10 +6168,10 @@
         <v>284</v>
       </c>
       <c r="B247" t="s">
-        <v>562</v>
+        <v>330</v>
       </c>
       <c r="D247" t="s">
-        <v>627</v>
+        <v>331</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
@@ -5798,10 +6179,10 @@
         <v>284</v>
       </c>
       <c r="B248" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D248" t="s">
-        <v>573</v>
+        <v>627</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -5809,10 +6190,10 @@
         <v>284</v>
       </c>
       <c r="B249" t="s">
-        <v>334</v>
+        <v>558</v>
       </c>
       <c r="D249" t="s">
-        <v>333</v>
+        <v>573</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -5820,10 +6201,10 @@
         <v>284</v>
       </c>
       <c r="B250" t="s">
-        <v>628</v>
+        <v>334</v>
       </c>
       <c r="D250" t="s">
-        <v>641</v>
+        <v>333</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -5831,10 +6212,10 @@
         <v>284</v>
       </c>
       <c r="B251" t="s">
-        <v>335</v>
+        <v>628</v>
       </c>
       <c r="D251" t="s">
-        <v>336</v>
+        <v>641</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
@@ -5853,10 +6234,10 @@
         <v>284</v>
       </c>
       <c r="B253" t="s">
-        <v>554</v>
+        <v>335</v>
       </c>
       <c r="D253" t="s">
-        <v>569</v>
+        <v>336</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
@@ -5875,10 +6256,10 @@
         <v>284</v>
       </c>
       <c r="B255" t="s">
-        <v>337</v>
+        <v>554</v>
       </c>
       <c r="D255" t="s">
-        <v>338</v>
+        <v>569</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -5886,10 +6267,10 @@
         <v>284</v>
       </c>
       <c r="B256" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D256" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
@@ -5897,10 +6278,10 @@
         <v>284</v>
       </c>
       <c r="B257" t="s">
-        <v>510</v>
+        <v>339</v>
       </c>
       <c r="D257" t="s">
-        <v>510</v>
+        <v>340</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -5908,10 +6289,10 @@
         <v>284</v>
       </c>
       <c r="B258" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="D258" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -5919,10 +6300,10 @@
         <v>284</v>
       </c>
       <c r="B259" t="s">
-        <v>341</v>
+        <v>500</v>
       </c>
       <c r="D259" t="s">
-        <v>342</v>
+        <v>501</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
@@ -5930,10 +6311,10 @@
         <v>284</v>
       </c>
       <c r="B260" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D260" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
@@ -5941,10 +6322,10 @@
         <v>284</v>
       </c>
       <c r="B261" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D261" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
@@ -5952,10 +6333,10 @@
         <v>284</v>
       </c>
       <c r="B262" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D262" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -5963,10 +6344,10 @@
         <v>284</v>
       </c>
       <c r="B263" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D263" t="s">
-        <v>293</v>
+        <v>348</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -5974,10 +6355,10 @@
         <v>284</v>
       </c>
       <c r="B264" t="s">
-        <v>564</v>
+        <v>349</v>
       </c>
       <c r="D264" t="s">
-        <v>576</v>
+        <v>293</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
@@ -5985,10 +6366,10 @@
         <v>284</v>
       </c>
       <c r="B265" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D265" t="s">
-        <v>417</v>
+        <v>576</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -5996,10 +6377,10 @@
         <v>284</v>
       </c>
       <c r="B266" t="s">
-        <v>350</v>
+        <v>563</v>
       </c>
       <c r="D266" t="s">
-        <v>351</v>
+        <v>417</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
@@ -6007,10 +6388,10 @@
         <v>284</v>
       </c>
       <c r="B267" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D267" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -6018,10 +6399,10 @@
         <v>284</v>
       </c>
       <c r="B268" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D268" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -6029,10 +6410,10 @@
         <v>284</v>
       </c>
       <c r="B269" t="s">
-        <v>559</v>
+        <v>354</v>
       </c>
       <c r="D269" t="s">
-        <v>653</v>
+        <v>355</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -6040,10 +6421,10 @@
         <v>284</v>
       </c>
       <c r="B270" t="s">
-        <v>356</v>
+        <v>559</v>
       </c>
       <c r="D270" t="s">
-        <v>357</v>
+        <v>653</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -6051,10 +6432,10 @@
         <v>284</v>
       </c>
       <c r="B271" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D271" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -6062,10 +6443,10 @@
         <v>284</v>
       </c>
       <c r="B272" t="s">
-        <v>547</v>
+        <v>358</v>
       </c>
       <c r="D272" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -6073,10 +6454,10 @@
         <v>284</v>
       </c>
       <c r="B273" t="s">
-        <v>360</v>
+        <v>547</v>
       </c>
       <c r="D273" t="s">
-        <v>548</v>
+        <v>361</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -6084,10 +6465,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
-        <v>636</v>
+        <v>360</v>
       </c>
       <c r="D274" t="s">
-        <v>648</v>
+        <v>548</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
@@ -6095,10 +6476,10 @@
         <v>284</v>
       </c>
       <c r="B275" t="s">
-        <v>455</v>
+        <v>636</v>
       </c>
       <c r="D275" t="s">
-        <v>456</v>
+        <v>648</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
@@ -6106,10 +6487,10 @@
         <v>284</v>
       </c>
       <c r="B276" t="s">
-        <v>362</v>
+        <v>455</v>
       </c>
       <c r="D276" t="s">
-        <v>362</v>
+        <v>456</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -6117,10 +6498,10 @@
         <v>284</v>
       </c>
       <c r="B277" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D277" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -6128,10 +6509,10 @@
         <v>284</v>
       </c>
       <c r="B278" t="s">
-        <v>524</v>
+        <v>363</v>
       </c>
       <c r="D278" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
@@ -6139,10 +6520,10 @@
         <v>284</v>
       </c>
       <c r="B279" t="s">
-        <v>365</v>
+        <v>524</v>
       </c>
       <c r="D279" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
@@ -6150,10 +6531,10 @@
         <v>284</v>
       </c>
       <c r="B280" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D280" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
@@ -6161,10 +6542,10 @@
         <v>284</v>
       </c>
       <c r="B281" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D281" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
@@ -6172,10 +6553,10 @@
         <v>284</v>
       </c>
       <c r="B282" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D282" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
@@ -6183,10 +6564,10 @@
         <v>284</v>
       </c>
       <c r="B283" t="s">
-        <v>294</v>
+        <v>373</v>
       </c>
       <c r="D283" t="s">
-        <v>295</v>
+        <v>374</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
@@ -6194,10 +6575,10 @@
         <v>284</v>
       </c>
       <c r="B284" t="s">
-        <v>375</v>
+        <v>294</v>
       </c>
       <c r="D284" t="s">
-        <v>376</v>
+        <v>295</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
@@ -6205,10 +6586,10 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>557</v>
+        <v>375</v>
       </c>
       <c r="D285" t="s">
-        <v>572</v>
+        <v>376</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
@@ -6216,10 +6597,10 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="D286" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
@@ -6227,10 +6608,10 @@
         <v>284</v>
       </c>
       <c r="B287" t="s">
-        <v>377</v>
+        <v>567</v>
       </c>
       <c r="D287" t="s">
-        <v>378</v>
+        <v>579</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
@@ -6238,10 +6619,10 @@
         <v>284</v>
       </c>
       <c r="B288" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D288" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
@@ -6249,10 +6630,10 @@
         <v>284</v>
       </c>
       <c r="B289" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D289" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
@@ -6260,10 +6641,10 @@
         <v>284</v>
       </c>
       <c r="B290" t="s">
-        <v>230</v>
+        <v>381</v>
       </c>
       <c r="D290" t="s">
-        <v>231</v>
+        <v>382</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
@@ -6271,10 +6652,10 @@
         <v>284</v>
       </c>
       <c r="B291" t="s">
-        <v>634</v>
+        <v>230</v>
       </c>
       <c r="D291" t="s">
-        <v>643</v>
+        <v>231</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -6282,10 +6663,10 @@
         <v>284</v>
       </c>
       <c r="B292" t="s">
-        <v>383</v>
+        <v>634</v>
       </c>
       <c r="D292" t="s">
-        <v>384</v>
+        <v>643</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
@@ -6293,10 +6674,10 @@
         <v>284</v>
       </c>
       <c r="B293" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D293" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
@@ -6304,10 +6685,10 @@
         <v>284</v>
       </c>
       <c r="B294" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D294" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
@@ -6315,10 +6696,10 @@
         <v>284</v>
       </c>
       <c r="B295" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D295" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
@@ -6326,10 +6707,10 @@
         <v>284</v>
       </c>
       <c r="B296" t="s">
-        <v>17</v>
+        <v>389</v>
       </c>
       <c r="D296" t="s">
-        <v>164</v>
+        <v>390</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -6337,10 +6718,10 @@
         <v>284</v>
       </c>
       <c r="B297" t="s">
-        <v>391</v>
+        <v>17</v>
       </c>
       <c r="D297" t="s">
-        <v>392</v>
+        <v>164</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
@@ -6348,10 +6729,10 @@
         <v>284</v>
       </c>
       <c r="B298" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D298" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -6359,10 +6740,10 @@
         <v>284</v>
       </c>
       <c r="B299" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D299" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
@@ -6370,10 +6751,10 @@
         <v>284</v>
       </c>
       <c r="B300" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D300" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
@@ -6381,10 +6762,10 @@
         <v>284</v>
       </c>
       <c r="B301" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D301" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
@@ -6392,10 +6773,10 @@
         <v>284</v>
       </c>
       <c r="B302" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D302" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
@@ -6403,10 +6784,10 @@
         <v>284</v>
       </c>
       <c r="B303" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D303" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
@@ -6414,10 +6795,10 @@
         <v>284</v>
       </c>
       <c r="B304" t="s">
-        <v>633</v>
+        <v>403</v>
       </c>
       <c r="D304" t="s">
-        <v>646</v>
+        <v>404</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
@@ -6425,10 +6806,10 @@
         <v>284</v>
       </c>
       <c r="B305" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D305" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
@@ -6436,10 +6817,10 @@
         <v>284</v>
       </c>
       <c r="B306" t="s">
-        <v>405</v>
+        <v>630</v>
       </c>
       <c r="D306" t="s">
-        <v>406</v>
+        <v>643</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
@@ -6447,10 +6828,10 @@
         <v>284</v>
       </c>
       <c r="B307" t="s">
-        <v>409</v>
+        <v>850</v>
       </c>
       <c r="D307" t="s">
-        <v>410</v>
+        <v>851</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
@@ -6458,10 +6839,10 @@
         <v>284</v>
       </c>
       <c r="B308" t="s">
-        <v>508</v>
+        <v>405</v>
       </c>
       <c r="D308" t="s">
-        <v>509</v>
+        <v>406</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
@@ -6469,10 +6850,10 @@
         <v>284</v>
       </c>
       <c r="B309" t="s">
-        <v>560</v>
+        <v>409</v>
       </c>
       <c r="D309" t="s">
-        <v>574</v>
+        <v>410</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
@@ -6480,10 +6861,10 @@
         <v>284</v>
       </c>
       <c r="B310" t="s">
-        <v>543</v>
+        <v>508</v>
       </c>
       <c r="D310" t="s">
-        <v>544</v>
+        <v>509</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
@@ -6491,10 +6872,10 @@
         <v>284</v>
       </c>
       <c r="B311" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D311" t="s">
-        <v>551</v>
+        <v>574</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
@@ -6502,10 +6883,10 @@
         <v>284</v>
       </c>
       <c r="B312" t="s">
-        <v>505</v>
+        <v>543</v>
       </c>
       <c r="D312" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
@@ -6513,10 +6894,10 @@
         <v>284</v>
       </c>
       <c r="B313" t="s">
-        <v>411</v>
+        <v>552</v>
       </c>
       <c r="D313" t="s">
-        <v>411</v>
+        <v>551</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
@@ -6524,10 +6905,10 @@
         <v>284</v>
       </c>
       <c r="B314" t="s">
-        <v>624</v>
+        <v>505</v>
       </c>
       <c r="D314" t="s">
-        <v>625</v>
+        <v>506</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
@@ -6535,10 +6916,10 @@
         <v>284</v>
       </c>
       <c r="B315" t="s">
-        <v>669</v>
+        <v>411</v>
       </c>
       <c r="D315" t="s">
-        <v>670</v>
+        <v>411</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
@@ -6546,10 +6927,10 @@
         <v>284</v>
       </c>
       <c r="B316" t="s">
-        <v>412</v>
+        <v>624</v>
       </c>
       <c r="D316" t="s">
-        <v>413</v>
+        <v>625</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
@@ -6557,10 +6938,10 @@
         <v>284</v>
       </c>
       <c r="B317" t="s">
-        <v>632</v>
+        <v>669</v>
       </c>
       <c r="D317" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
@@ -6568,10 +6949,10 @@
         <v>284</v>
       </c>
       <c r="B318" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D318" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
@@ -6579,10 +6960,10 @@
         <v>284</v>
       </c>
       <c r="B319" t="s">
-        <v>416</v>
+        <v>632</v>
       </c>
       <c r="D319" t="s">
-        <v>417</v>
+        <v>645</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
@@ -6590,10 +6971,10 @@
         <v>284</v>
       </c>
       <c r="B320" t="s">
-        <v>553</v>
+        <v>414</v>
       </c>
       <c r="D320" t="s">
-        <v>568</v>
+        <v>415</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
@@ -6601,32 +6982,32 @@
         <v>284</v>
       </c>
       <c r="B321" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D321" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B322" t="s">
-        <v>21</v>
+        <v>553</v>
       </c>
       <c r="D322" t="s">
-        <v>22</v>
+        <v>568</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B323" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D323" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
@@ -6634,10 +7015,10 @@
         <v>420</v>
       </c>
       <c r="B324" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D324" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -6645,10 +7026,10 @@
         <v>420</v>
       </c>
       <c r="B325" t="s">
-        <v>546</v>
+        <v>421</v>
       </c>
       <c r="D325" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -6656,10 +7037,10 @@
         <v>420</v>
       </c>
       <c r="B326" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D326" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -6667,10 +7048,10 @@
         <v>420</v>
       </c>
       <c r="B327" t="s">
-        <v>589</v>
+        <v>546</v>
       </c>
       <c r="D327" t="s">
-        <v>610</v>
+        <v>422</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -6678,10 +7059,10 @@
         <v>420</v>
       </c>
       <c r="B328" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D328" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
@@ -6689,10 +7070,10 @@
         <v>420</v>
       </c>
       <c r="B329" t="s">
-        <v>54</v>
+        <v>589</v>
       </c>
       <c r="D329" t="s">
-        <v>55</v>
+        <v>610</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
@@ -6700,10 +7081,10 @@
         <v>420</v>
       </c>
       <c r="B330" t="s">
-        <v>52</v>
+        <v>846</v>
       </c>
       <c r="D330" t="s">
-        <v>53</v>
+        <v>846</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
@@ -6711,10 +7092,10 @@
         <v>420</v>
       </c>
       <c r="B331" t="s">
-        <v>296</v>
+        <v>50</v>
       </c>
       <c r="D331" t="s">
-        <v>519</v>
+        <v>51</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -6722,10 +7103,10 @@
         <v>420</v>
       </c>
       <c r="B332" t="s">
-        <v>523</v>
+        <v>54</v>
       </c>
       <c r="D332" t="s">
-        <v>520</v>
+        <v>55</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
@@ -6733,10 +7114,10 @@
         <v>420</v>
       </c>
       <c r="B333" t="s">
-        <v>423</v>
+        <v>52</v>
       </c>
       <c r="D333" t="s">
-        <v>424</v>
+        <v>53</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
@@ -6744,10 +7125,10 @@
         <v>420</v>
       </c>
       <c r="B334" t="s">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="D334" t="s">
-        <v>426</v>
+        <v>519</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -6755,10 +7136,10 @@
         <v>420</v>
       </c>
       <c r="B335" t="s">
-        <v>427</v>
+        <v>523</v>
       </c>
       <c r="D335" t="s">
-        <v>428</v>
+        <v>520</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -6766,10 +7147,10 @@
         <v>420</v>
       </c>
       <c r="B336" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="D336" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -6777,10 +7158,10 @@
         <v>420</v>
       </c>
       <c r="B337" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="D337" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
@@ -6788,10 +7169,10 @@
         <v>420</v>
       </c>
       <c r="B338" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="D338" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
@@ -6799,10 +7180,10 @@
         <v>420</v>
       </c>
       <c r="B339" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="D339" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -6810,10 +7191,10 @@
         <v>420</v>
       </c>
       <c r="B340" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="D340" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
@@ -6821,10 +7202,10 @@
         <v>420</v>
       </c>
       <c r="B341" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="D341" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -6832,10 +7213,10 @@
         <v>420</v>
       </c>
       <c r="B342" t="s">
-        <v>61</v>
+        <v>435</v>
       </c>
       <c r="D342" t="s">
-        <v>62</v>
+        <v>436</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
@@ -6843,10 +7224,10 @@
         <v>420</v>
       </c>
       <c r="B343" t="s">
-        <v>65</v>
+        <v>437</v>
       </c>
       <c r="D343" t="s">
-        <v>66</v>
+        <v>438</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -6854,10 +7235,10 @@
         <v>420</v>
       </c>
       <c r="B344" t="s">
-        <v>63</v>
+        <v>439</v>
       </c>
       <c r="D344" t="s">
-        <v>64</v>
+        <v>440</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -6865,10 +7246,10 @@
         <v>420</v>
       </c>
       <c r="B345" t="s">
-        <v>671</v>
+        <v>61</v>
       </c>
       <c r="D345" t="s">
-        <v>672</v>
+        <v>62</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
@@ -6876,10 +7257,10 @@
         <v>420</v>
       </c>
       <c r="B346" t="s">
-        <v>441</v>
+        <v>65</v>
       </c>
       <c r="D346" t="s">
-        <v>442</v>
+        <v>66</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
@@ -6887,10 +7268,10 @@
         <v>420</v>
       </c>
       <c r="B347" t="s">
-        <v>588</v>
+        <v>63</v>
       </c>
       <c r="D347" t="s">
-        <v>609</v>
+        <v>64</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -6898,10 +7279,10 @@
         <v>420</v>
       </c>
       <c r="B348" t="s">
-        <v>587</v>
+        <v>671</v>
       </c>
       <c r="D348" t="s">
-        <v>608</v>
+        <v>672</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
@@ -6909,10 +7290,10 @@
         <v>420</v>
       </c>
       <c r="B349" t="s">
-        <v>75</v>
+        <v>441</v>
       </c>
       <c r="D349" t="s">
-        <v>76</v>
+        <v>442</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
@@ -6920,10 +7301,10 @@
         <v>420</v>
       </c>
       <c r="B350" t="s">
-        <v>77</v>
+        <v>588</v>
       </c>
       <c r="D350" t="s">
-        <v>78</v>
+        <v>609</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
@@ -6931,10 +7312,10 @@
         <v>420</v>
       </c>
       <c r="B351" t="s">
-        <v>326</v>
+        <v>587</v>
       </c>
       <c r="D351" t="s">
-        <v>327</v>
+        <v>608</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
@@ -6942,10 +7323,10 @@
         <v>420</v>
       </c>
       <c r="B352" t="s">
-        <v>449</v>
+        <v>75</v>
       </c>
       <c r="D352" t="s">
-        <v>443</v>
+        <v>76</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
@@ -6953,10 +7334,10 @@
         <v>420</v>
       </c>
       <c r="B353" t="s">
-        <v>545</v>
+        <v>77</v>
       </c>
       <c r="D353" t="s">
-        <v>444</v>
+        <v>78</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
@@ -6964,10 +7345,10 @@
         <v>420</v>
       </c>
       <c r="B354" t="s">
-        <v>585</v>
+        <v>326</v>
       </c>
       <c r="D354" t="s">
-        <v>606</v>
+        <v>327</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
@@ -6975,10 +7356,10 @@
         <v>420</v>
       </c>
       <c r="B355" t="s">
-        <v>586</v>
+        <v>449</v>
       </c>
       <c r="D355" t="s">
-        <v>607</v>
+        <v>443</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
@@ -6986,10 +7367,10 @@
         <v>420</v>
       </c>
       <c r="B356" t="s">
-        <v>445</v>
+        <v>545</v>
       </c>
       <c r="D356" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
@@ -6997,10 +7378,10 @@
         <v>420</v>
       </c>
       <c r="B357" t="s">
-        <v>447</v>
+        <v>585</v>
       </c>
       <c r="D357" t="s">
-        <v>448</v>
+        <v>606</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
@@ -7008,10 +7389,10 @@
         <v>420</v>
       </c>
       <c r="B358" t="s">
-        <v>654</v>
+        <v>586</v>
       </c>
       <c r="D358" t="s">
-        <v>655</v>
+        <v>607</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
@@ -7019,10 +7400,10 @@
         <v>420</v>
       </c>
       <c r="B359" t="s">
-        <v>332</v>
+        <v>445</v>
       </c>
       <c r="D359" t="s">
-        <v>333</v>
+        <v>446</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
@@ -7030,10 +7411,10 @@
         <v>420</v>
       </c>
       <c r="B360" t="s">
-        <v>101</v>
+        <v>447</v>
       </c>
       <c r="D360" t="s">
-        <v>102</v>
+        <v>448</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
@@ -7041,10 +7422,10 @@
         <v>420</v>
       </c>
       <c r="B361" t="s">
-        <v>103</v>
+        <v>654</v>
       </c>
       <c r="D361" t="s">
-        <v>104</v>
+        <v>655</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
@@ -7052,10 +7433,10 @@
         <v>420</v>
       </c>
       <c r="B362" t="s">
-        <v>105</v>
+        <v>332</v>
       </c>
       <c r="D362" t="s">
-        <v>106</v>
+        <v>333</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
@@ -7063,10 +7444,10 @@
         <v>420</v>
       </c>
       <c r="B363" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D363" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
@@ -7074,10 +7455,10 @@
         <v>420</v>
       </c>
       <c r="B364" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D364" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
@@ -7085,10 +7466,10 @@
         <v>420</v>
       </c>
       <c r="B365" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D365" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
@@ -7096,10 +7477,10 @@
         <v>420</v>
       </c>
       <c r="B366" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D366" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -7107,10 +7488,10 @@
         <v>420</v>
       </c>
       <c r="B367" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D367" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
@@ -7118,10 +7499,10 @@
         <v>420</v>
       </c>
       <c r="B368" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D368" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
@@ -7129,10 +7510,10 @@
         <v>420</v>
       </c>
       <c r="B369" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D369" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -7140,10 +7521,10 @@
         <v>420</v>
       </c>
       <c r="B370" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D370" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
@@ -7151,10 +7532,10 @@
         <v>420</v>
       </c>
       <c r="B371" t="s">
-        <v>450</v>
+        <v>117</v>
       </c>
       <c r="D371" t="s">
-        <v>451</v>
+        <v>118</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
@@ -7162,10 +7543,10 @@
         <v>420</v>
       </c>
       <c r="B372" t="s">
-        <v>549</v>
+        <v>119</v>
       </c>
       <c r="D372" t="s">
-        <v>550</v>
+        <v>120</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -7173,10 +7554,10 @@
         <v>420</v>
       </c>
       <c r="B373" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D373" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
@@ -7184,10 +7565,10 @@
         <v>420</v>
       </c>
       <c r="B374" t="s">
-        <v>592</v>
+        <v>450</v>
       </c>
       <c r="D374" t="s">
-        <v>612</v>
+        <v>451</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -7195,10 +7576,10 @@
         <v>420</v>
       </c>
       <c r="B375" t="s">
-        <v>622</v>
+        <v>549</v>
       </c>
       <c r="D375" t="s">
-        <v>623</v>
+        <v>550</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -7206,10 +7587,10 @@
         <v>420</v>
       </c>
       <c r="B376" t="s">
-        <v>591</v>
+        <v>129</v>
       </c>
       <c r="D376" t="s">
-        <v>626</v>
+        <v>130</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
@@ -7217,10 +7598,10 @@
         <v>420</v>
       </c>
       <c r="B377" t="s">
-        <v>452</v>
+        <v>592</v>
       </c>
       <c r="D377" t="s">
-        <v>453</v>
+        <v>612</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
@@ -7228,10 +7609,10 @@
         <v>420</v>
       </c>
       <c r="B378" t="s">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="D378" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
@@ -7239,10 +7620,10 @@
         <v>420</v>
       </c>
       <c r="B379" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D379" t="s">
-        <v>611</v>
+        <v>626</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
@@ -7250,10 +7631,10 @@
         <v>420</v>
       </c>
       <c r="B380" t="s">
-        <v>659</v>
+        <v>452</v>
       </c>
       <c r="D380" t="s">
-        <v>660</v>
+        <v>453</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
@@ -7261,10 +7642,10 @@
         <v>420</v>
       </c>
       <c r="B381" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D381" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
@@ -7272,10 +7653,10 @@
         <v>420</v>
       </c>
       <c r="B382" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="D382" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
@@ -7283,10 +7664,10 @@
         <v>420</v>
       </c>
       <c r="B383" t="s">
-        <v>455</v>
+        <v>659</v>
       </c>
       <c r="D383" t="s">
-        <v>456</v>
+        <v>660</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
@@ -7294,10 +7675,10 @@
         <v>420</v>
       </c>
       <c r="B384" t="s">
-        <v>457</v>
+        <v>595</v>
       </c>
       <c r="D384" t="s">
-        <v>454</v>
+        <v>615</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
@@ -7305,10 +7686,10 @@
         <v>420</v>
       </c>
       <c r="B385" t="s">
-        <v>362</v>
+        <v>584</v>
       </c>
       <c r="D385" t="s">
-        <v>362</v>
+        <v>605</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
@@ -7316,10 +7697,10 @@
         <v>420</v>
       </c>
       <c r="B386" t="s">
-        <v>368</v>
+        <v>455</v>
       </c>
       <c r="D386" t="s">
-        <v>368</v>
+        <v>456</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
@@ -7327,10 +7708,10 @@
         <v>420</v>
       </c>
       <c r="B387" t="s">
-        <v>369</v>
+        <v>457</v>
       </c>
       <c r="D387" t="s">
-        <v>370</v>
+        <v>454</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
@@ -7338,10 +7719,10 @@
         <v>420</v>
       </c>
       <c r="B388" t="s">
-        <v>596</v>
+        <v>362</v>
       </c>
       <c r="D388" t="s">
-        <v>616</v>
+        <v>362</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
@@ -7349,10 +7730,10 @@
         <v>420</v>
       </c>
       <c r="B389" t="s">
-        <v>597</v>
+        <v>368</v>
       </c>
       <c r="D389" t="s">
-        <v>617</v>
+        <v>368</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
@@ -7360,10 +7741,10 @@
         <v>420</v>
       </c>
       <c r="B390" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="D390" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
@@ -7371,10 +7752,10 @@
         <v>420</v>
       </c>
       <c r="B391" t="s">
-        <v>156</v>
+        <v>596</v>
       </c>
       <c r="D391" t="s">
-        <v>157</v>
+        <v>616</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
@@ -7382,10 +7763,10 @@
         <v>420</v>
       </c>
       <c r="B392" t="s">
-        <v>379</v>
+        <v>597</v>
       </c>
       <c r="D392" t="s">
-        <v>380</v>
+        <v>617</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
@@ -7393,10 +7774,10 @@
         <v>420</v>
       </c>
       <c r="B393" t="s">
-        <v>656</v>
+        <v>377</v>
       </c>
       <c r="D393" t="s">
-        <v>657</v>
+        <v>378</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -7404,10 +7785,10 @@
         <v>420</v>
       </c>
       <c r="B394" t="s">
-        <v>17</v>
+        <v>156</v>
       </c>
       <c r="D394" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
@@ -7415,10 +7796,10 @@
         <v>420</v>
       </c>
       <c r="B395" t="s">
-        <v>458</v>
+        <v>379</v>
       </c>
       <c r="D395" t="s">
-        <v>459</v>
+        <v>380</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
@@ -7426,10 +7807,10 @@
         <v>420</v>
       </c>
       <c r="B396" t="s">
-        <v>460</v>
+        <v>656</v>
       </c>
       <c r="D396" t="s">
-        <v>461</v>
+        <v>657</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
@@ -7437,10 +7818,10 @@
         <v>420</v>
       </c>
       <c r="B397" t="s">
-        <v>462</v>
+        <v>17</v>
       </c>
       <c r="D397" t="s">
-        <v>463</v>
+        <v>164</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
@@ -7448,10 +7829,10 @@
         <v>420</v>
       </c>
       <c r="B398" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="D398" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
@@ -7459,10 +7840,10 @@
         <v>420</v>
       </c>
       <c r="B399" t="s">
-        <v>399</v>
+        <v>460</v>
       </c>
       <c r="D399" t="s">
-        <v>400</v>
+        <v>461</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
@@ -7470,10 +7851,10 @@
         <v>420</v>
       </c>
       <c r="B400" t="s">
-        <v>407</v>
+        <v>462</v>
       </c>
       <c r="D400" t="s">
-        <v>408</v>
+        <v>463</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
@@ -7481,10 +7862,10 @@
         <v>420</v>
       </c>
       <c r="B401" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D401" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
@@ -7492,10 +7873,10 @@
         <v>420</v>
       </c>
       <c r="B402" t="s">
-        <v>187</v>
+        <v>399</v>
       </c>
       <c r="D402" t="s">
-        <v>188</v>
+        <v>400</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
@@ -7503,10 +7884,10 @@
         <v>420</v>
       </c>
       <c r="B403" t="s">
-        <v>196</v>
+        <v>407</v>
       </c>
       <c r="D403" t="s">
-        <v>197</v>
+        <v>408</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
@@ -7514,10 +7895,10 @@
         <v>420</v>
       </c>
       <c r="B404" t="s">
-        <v>601</v>
+        <v>466</v>
       </c>
       <c r="D404" t="s">
-        <v>621</v>
+        <v>467</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
@@ -7525,10 +7906,10 @@
         <v>420</v>
       </c>
       <c r="B405" t="s">
-        <v>468</v>
+        <v>187</v>
       </c>
       <c r="D405" t="s">
-        <v>469</v>
+        <v>188</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
@@ -7536,10 +7917,10 @@
         <v>420</v>
       </c>
       <c r="B406" t="s">
-        <v>470</v>
+        <v>196</v>
       </c>
       <c r="D406" t="s">
-        <v>471</v>
+        <v>197</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
@@ -7547,10 +7928,10 @@
         <v>420</v>
       </c>
       <c r="B407" t="s">
-        <v>472</v>
+        <v>601</v>
       </c>
       <c r="D407" t="s">
-        <v>473</v>
+        <v>621</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
@@ -7558,10 +7939,10 @@
         <v>420</v>
       </c>
       <c r="B408" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="D408" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
@@ -7569,10 +7950,10 @@
         <v>420</v>
       </c>
       <c r="B409" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="D409" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
@@ -7580,10 +7961,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="D410" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
@@ -7591,10 +7972,10 @@
         <v>420</v>
       </c>
       <c r="B411" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="D411" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
@@ -7602,10 +7983,10 @@
         <v>420</v>
       </c>
       <c r="B412" t="s">
-        <v>599</v>
+        <v>476</v>
       </c>
       <c r="D412" t="s">
-        <v>619</v>
+        <v>477</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
@@ -7613,10 +7994,10 @@
         <v>420</v>
       </c>
       <c r="B413" t="s">
-        <v>600</v>
+        <v>478</v>
       </c>
       <c r="D413" t="s">
-        <v>620</v>
+        <v>479</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
@@ -7624,10 +8005,10 @@
         <v>420</v>
       </c>
       <c r="B414" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D414" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
@@ -7635,10 +8016,10 @@
         <v>420</v>
       </c>
       <c r="B415" t="s">
-        <v>484</v>
+        <v>599</v>
       </c>
       <c r="D415" t="s">
-        <v>485</v>
+        <v>619</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
@@ -7646,10 +8027,10 @@
         <v>420</v>
       </c>
       <c r="B416" t="s">
-        <v>486</v>
+        <v>600</v>
       </c>
       <c r="D416" t="s">
-        <v>487</v>
+        <v>620</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
@@ -7657,10 +8038,10 @@
         <v>420</v>
       </c>
       <c r="B417" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D417" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
@@ -7668,10 +8049,10 @@
         <v>420</v>
       </c>
       <c r="B418" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="D418" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
@@ -7679,10 +8060,10 @@
         <v>420</v>
       </c>
       <c r="B419" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="D419" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
@@ -7690,10 +8071,10 @@
         <v>420</v>
       </c>
       <c r="B420" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="D420" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
@@ -7701,10 +8082,10 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="D421" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
@@ -7712,10 +8093,10 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>582</v>
+        <v>492</v>
       </c>
       <c r="D422" t="s">
-        <v>658</v>
+        <v>493</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
@@ -7723,10 +8104,10 @@
         <v>420</v>
       </c>
       <c r="B423" t="s">
-        <v>583</v>
+        <v>494</v>
       </c>
       <c r="D423" t="s">
-        <v>604</v>
+        <v>495</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
@@ -7734,10 +8115,10 @@
         <v>420</v>
       </c>
       <c r="B424" t="s">
-        <v>581</v>
+        <v>496</v>
       </c>
       <c r="D424" t="s">
-        <v>603</v>
+        <v>497</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
@@ -7745,10 +8126,10 @@
         <v>420</v>
       </c>
       <c r="B425" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D425" t="s">
-        <v>602</v>
+        <v>658</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
@@ -7756,10 +8137,10 @@
         <v>420</v>
       </c>
       <c r="B426" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="D426" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
@@ -7767,17 +8148,842 @@
         <v>420</v>
       </c>
       <c r="B427" t="s">
+        <v>581</v>
+      </c>
+      <c r="D427" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>420</v>
+      </c>
+      <c r="B428" t="s">
+        <v>580</v>
+      </c>
+      <c r="D428" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>420</v>
+      </c>
+      <c r="B429" t="s">
+        <v>594</v>
+      </c>
+      <c r="D429" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>420</v>
+      </c>
+      <c r="B430" t="s">
         <v>593</v>
       </c>
-      <c r="D427" t="s">
+      <c r="D430" t="s">
         <v>613</v>
       </c>
     </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>284</v>
+      </c>
+      <c r="B431" t="s">
+        <v>725</v>
+      </c>
+      <c r="D431" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>284</v>
+      </c>
+      <c r="B432" t="s">
+        <v>549</v>
+      </c>
+      <c r="D432" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>284</v>
+      </c>
+      <c r="B433" t="s">
+        <v>654</v>
+      </c>
+      <c r="D433" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>284</v>
+      </c>
+      <c r="B434" t="s">
+        <v>727</v>
+      </c>
+      <c r="D434" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>284</v>
+      </c>
+      <c r="B435" t="s">
+        <v>729</v>
+      </c>
+      <c r="D435" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>284</v>
+      </c>
+      <c r="B436" t="s">
+        <v>730</v>
+      </c>
+      <c r="D436" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>284</v>
+      </c>
+      <c r="B437" t="s">
+        <v>732</v>
+      </c>
+      <c r="D437" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>284</v>
+      </c>
+      <c r="B438" t="s">
+        <v>734</v>
+      </c>
+      <c r="D438" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>284</v>
+      </c>
+      <c r="B439" t="s">
+        <v>736</v>
+      </c>
+      <c r="D439" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>284</v>
+      </c>
+      <c r="B440" t="s">
+        <v>737</v>
+      </c>
+      <c r="D440" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>284</v>
+      </c>
+      <c r="B441" t="s">
+        <v>739</v>
+      </c>
+      <c r="D441" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>284</v>
+      </c>
+      <c r="B442" t="s">
+        <v>741</v>
+      </c>
+      <c r="D442" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>284</v>
+      </c>
+      <c r="B443" t="s">
+        <v>743</v>
+      </c>
+      <c r="D443" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>284</v>
+      </c>
+      <c r="B444" t="s">
+        <v>745</v>
+      </c>
+      <c r="D444" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>284</v>
+      </c>
+      <c r="B445" t="s">
+        <v>747</v>
+      </c>
+      <c r="D445" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>284</v>
+      </c>
+      <c r="B446" t="s">
+        <v>749</v>
+      </c>
+      <c r="D446" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>284</v>
+      </c>
+      <c r="B447" t="s">
+        <v>751</v>
+      </c>
+      <c r="D447" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>284</v>
+      </c>
+      <c r="B448" t="s">
+        <v>753</v>
+      </c>
+      <c r="D448" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>284</v>
+      </c>
+      <c r="B449" t="s">
+        <v>755</v>
+      </c>
+      <c r="D449" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>284</v>
+      </c>
+      <c r="B450" t="s">
+        <v>757</v>
+      </c>
+      <c r="D450" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>284</v>
+      </c>
+      <c r="B451" t="s">
+        <v>759</v>
+      </c>
+      <c r="D451" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>284</v>
+      </c>
+      <c r="B452" t="s">
+        <v>761</v>
+      </c>
+      <c r="D452" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>284</v>
+      </c>
+      <c r="B453" t="s">
+        <v>763</v>
+      </c>
+      <c r="D453" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>284</v>
+      </c>
+      <c r="B454" t="s">
+        <v>765</v>
+      </c>
+      <c r="D454" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>284</v>
+      </c>
+      <c r="B455" t="s">
+        <v>767</v>
+      </c>
+      <c r="D455" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>284</v>
+      </c>
+      <c r="B456" t="s">
+        <v>769</v>
+      </c>
+      <c r="D456" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>284</v>
+      </c>
+      <c r="B457" t="s">
+        <v>771</v>
+      </c>
+      <c r="D457" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>284</v>
+      </c>
+      <c r="B458" t="s">
+        <v>773</v>
+      </c>
+      <c r="D458" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>284</v>
+      </c>
+      <c r="B459" t="s">
+        <v>775</v>
+      </c>
+      <c r="D459" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>284</v>
+      </c>
+      <c r="B460" t="s">
+        <v>777</v>
+      </c>
+      <c r="D460" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>284</v>
+      </c>
+      <c r="B461" t="s">
+        <v>779</v>
+      </c>
+      <c r="D461" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>284</v>
+      </c>
+      <c r="B462" t="s">
+        <v>781</v>
+      </c>
+      <c r="D462" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>284</v>
+      </c>
+      <c r="B463" t="s">
+        <v>783</v>
+      </c>
+      <c r="D463" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>284</v>
+      </c>
+      <c r="B464" t="s">
+        <v>785</v>
+      </c>
+      <c r="D464" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>284</v>
+      </c>
+      <c r="B465" t="s">
+        <v>787</v>
+      </c>
+      <c r="D465" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>284</v>
+      </c>
+      <c r="B466" t="s">
+        <v>789</v>
+      </c>
+      <c r="D466" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>284</v>
+      </c>
+      <c r="B467" t="s">
+        <v>791</v>
+      </c>
+      <c r="D467" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>284</v>
+      </c>
+      <c r="B468" t="s">
+        <v>793</v>
+      </c>
+      <c r="D468" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>284</v>
+      </c>
+      <c r="B469" t="s">
+        <v>795</v>
+      </c>
+      <c r="D469" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>284</v>
+      </c>
+      <c r="B470" t="s">
+        <v>797</v>
+      </c>
+      <c r="D470" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>284</v>
+      </c>
+      <c r="B471" t="s">
+        <v>799</v>
+      </c>
+      <c r="D471" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>284</v>
+      </c>
+      <c r="B472" t="s">
+        <v>801</v>
+      </c>
+      <c r="D472" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>284</v>
+      </c>
+      <c r="B473" t="s">
+        <v>803</v>
+      </c>
+      <c r="D473" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>284</v>
+      </c>
+      <c r="B474" t="s">
+        <v>805</v>
+      </c>
+      <c r="D474" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>284</v>
+      </c>
+      <c r="B475" t="s">
+        <v>807</v>
+      </c>
+      <c r="D475" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>284</v>
+      </c>
+      <c r="B476" t="s">
+        <v>809</v>
+      </c>
+      <c r="D476" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>284</v>
+      </c>
+      <c r="B477" t="s">
+        <v>811</v>
+      </c>
+      <c r="D477" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>284</v>
+      </c>
+      <c r="B478" t="s">
+        <v>813</v>
+      </c>
+      <c r="D478" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>284</v>
+      </c>
+      <c r="B479" t="s">
+        <v>815</v>
+      </c>
+      <c r="D479" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>284</v>
+      </c>
+      <c r="B480" t="s">
+        <v>817</v>
+      </c>
+      <c r="D480" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>284</v>
+      </c>
+      <c r="B481" t="s">
+        <v>819</v>
+      </c>
+      <c r="D481" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>284</v>
+      </c>
+      <c r="B482" t="s">
+        <v>821</v>
+      </c>
+      <c r="D482" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>284</v>
+      </c>
+      <c r="B483" t="s">
+        <v>823</v>
+      </c>
+      <c r="D483" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>284</v>
+      </c>
+      <c r="B484" t="s">
+        <v>825</v>
+      </c>
+      <c r="D484" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>284</v>
+      </c>
+      <c r="B485" t="s">
+        <v>827</v>
+      </c>
+      <c r="D485" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>284</v>
+      </c>
+      <c r="B486" t="s">
+        <v>829</v>
+      </c>
+      <c r="D486" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>284</v>
+      </c>
+      <c r="B487" t="s">
+        <v>831</v>
+      </c>
+      <c r="D487" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>284</v>
+      </c>
+      <c r="B488" t="s">
+        <v>833</v>
+      </c>
+      <c r="D488" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>284</v>
+      </c>
+      <c r="B489" t="s">
+        <v>79</v>
+      </c>
+      <c r="D489" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>284</v>
+      </c>
+      <c r="B490" t="s">
+        <v>835</v>
+      </c>
+      <c r="D490" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>284</v>
+      </c>
+      <c r="B491" t="s">
+        <v>837</v>
+      </c>
+      <c r="D491" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>420</v>
+      </c>
+      <c r="B492" t="s">
+        <v>839</v>
+      </c>
+      <c r="D492" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>420</v>
+      </c>
+      <c r="B493" t="s">
+        <v>739</v>
+      </c>
+      <c r="D493" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>420</v>
+      </c>
+      <c r="B494" t="s">
+        <v>841</v>
+      </c>
+      <c r="D494" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>420</v>
+      </c>
+      <c r="B495" t="s">
+        <v>842</v>
+      </c>
+      <c r="D495" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>420</v>
+      </c>
+      <c r="B496" t="s">
+        <v>844</v>
+      </c>
+      <c r="D496" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>420</v>
+      </c>
+      <c r="B497" t="s">
+        <v>737</v>
+      </c>
+      <c r="D497" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>420</v>
+      </c>
+      <c r="B498" t="s">
+        <v>385</v>
+      </c>
+      <c r="D498" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>420</v>
+      </c>
+      <c r="B499" t="s">
+        <v>309</v>
+      </c>
+      <c r="D499" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>420</v>
+      </c>
+      <c r="B500" t="s">
+        <v>727</v>
+      </c>
+      <c r="D500" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>420</v>
+      </c>
+      <c r="B501" t="s">
+        <v>730</v>
+      </c>
+      <c r="D501" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>284</v>
+      </c>
+      <c r="B502" t="s">
+        <v>847</v>
+      </c>
+      <c r="D502" t="s">
+        <v>848</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D395" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D427">
-    <sortCondition ref="A2:A427"/>
-    <sortCondition ref="B2:B427"/>
+  <autoFilter ref="A1:D502" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D501">
+    <sortCondition ref="A2:A501"/>
+    <sortCondition ref="B2:B501"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_dev\Seal-Report\Repository\Settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BF45D9-9C20-4A10-96A2-20EBED90EF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA82394C-1BFF-463E-833F-A0B18AC5DD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9225" yWindow="2475" windowWidth="24375" windowHeight="15855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18270" yWindow="2220" windowWidth="24375" windowHeight="15855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Translations" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$D$502</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$D$503</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="860">
   <si>
     <t>Context</t>
   </si>
@@ -2592,6 +2592,30 @@
   </si>
   <si>
     <t>Droits</t>
+  </si>
+  <si>
+    <t>Configuration and security</t>
+  </si>
+  <si>
+    <t>Configuration et sécurité</t>
+  </si>
+  <si>
+    <t>Drag to resize</t>
+  </si>
+  <si>
+    <t>Glisser pour redimensionner</t>
+  </si>
+  <si>
+    <t>Copy and paste</t>
+  </si>
+  <si>
+    <t>Copier et coller</t>
+  </si>
+  <si>
+    <t>Copy, paste and send</t>
+  </si>
+  <si>
+    <t>Copier, coller et envoyer</t>
   </si>
 </sst>
 </file>
@@ -3446,7 +3470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D502"/>
+  <dimension ref="A1:D506"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -5805,10 +5829,10 @@
         <v>284</v>
       </c>
       <c r="B214" t="s">
-        <v>296</v>
+        <v>852</v>
       </c>
       <c r="D214" t="s">
-        <v>297</v>
+        <v>853</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -5816,10 +5840,10 @@
         <v>284</v>
       </c>
       <c r="B215" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D215" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
@@ -5827,10 +5851,10 @@
         <v>284</v>
       </c>
       <c r="B216" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D216" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -5838,10 +5862,10 @@
         <v>284</v>
       </c>
       <c r="B217" t="s">
-        <v>521</v>
+        <v>300</v>
       </c>
       <c r="D217" t="s">
-        <v>522</v>
+        <v>301</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
@@ -5849,10 +5873,10 @@
         <v>284</v>
       </c>
       <c r="B218" t="s">
-        <v>302</v>
+        <v>521</v>
       </c>
       <c r="D218" t="s">
-        <v>302</v>
+        <v>522</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
@@ -5860,10 +5884,10 @@
         <v>284</v>
       </c>
       <c r="B219" t="s">
-        <v>640</v>
+        <v>302</v>
       </c>
       <c r="D219" t="s">
-        <v>652</v>
+        <v>302</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -5871,10 +5895,10 @@
         <v>284</v>
       </c>
       <c r="B220" t="s">
-        <v>303</v>
+        <v>640</v>
       </c>
       <c r="D220" t="s">
-        <v>304</v>
+        <v>652</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -5882,10 +5906,10 @@
         <v>284</v>
       </c>
       <c r="B221" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D221" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -5893,10 +5917,10 @@
         <v>284</v>
       </c>
       <c r="B222" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D222" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -5904,10 +5928,10 @@
         <v>284</v>
       </c>
       <c r="B223" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D223" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
@@ -5915,10 +5939,10 @@
         <v>284</v>
       </c>
       <c r="B224" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D224" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -5926,10 +5950,10 @@
         <v>284</v>
       </c>
       <c r="B225" t="s">
-        <v>60</v>
+        <v>311</v>
       </c>
       <c r="D225" t="s">
-        <v>60</v>
+        <v>312</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -5937,10 +5961,10 @@
         <v>284</v>
       </c>
       <c r="B226" t="s">
-        <v>313</v>
+        <v>60</v>
       </c>
       <c r="D226" t="s">
-        <v>314</v>
+        <v>60</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
@@ -5948,10 +5972,10 @@
         <v>284</v>
       </c>
       <c r="B227" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D227" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
@@ -5959,10 +5983,10 @@
         <v>284</v>
       </c>
       <c r="B228" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D228" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -5970,10 +5994,10 @@
         <v>284</v>
       </c>
       <c r="B229" t="s">
-        <v>515</v>
+        <v>317</v>
       </c>
       <c r="D229" t="s">
-        <v>516</v>
+        <v>318</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
@@ -5981,10 +6005,10 @@
         <v>284</v>
       </c>
       <c r="B230" t="s">
-        <v>555</v>
+        <v>515</v>
       </c>
       <c r="D230" t="s">
-        <v>571</v>
+        <v>516</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -5992,10 +6016,10 @@
         <v>284</v>
       </c>
       <c r="B231" t="s">
-        <v>513</v>
+        <v>555</v>
       </c>
       <c r="D231" t="s">
-        <v>514</v>
+        <v>571</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -6003,10 +6027,10 @@
         <v>284</v>
       </c>
       <c r="B232" t="s">
-        <v>556</v>
+        <v>513</v>
       </c>
       <c r="D232" t="s">
-        <v>570</v>
+        <v>514</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
@@ -6014,10 +6038,10 @@
         <v>284</v>
       </c>
       <c r="B233" t="s">
-        <v>319</v>
+        <v>556</v>
       </c>
       <c r="D233" t="s">
-        <v>319</v>
+        <v>570</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -6025,10 +6049,10 @@
         <v>284</v>
       </c>
       <c r="B234" t="s">
-        <v>566</v>
+        <v>319</v>
       </c>
       <c r="D234" t="s">
-        <v>578</v>
+        <v>319</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -6036,10 +6060,10 @@
         <v>284</v>
       </c>
       <c r="B235" t="s">
-        <v>320</v>
+        <v>566</v>
       </c>
       <c r="D235" t="s">
-        <v>321</v>
+        <v>578</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
@@ -6047,10 +6071,10 @@
         <v>284</v>
       </c>
       <c r="B236" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D236" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
@@ -6058,10 +6082,10 @@
         <v>284</v>
       </c>
       <c r="B237" t="s">
-        <v>639</v>
+        <v>322</v>
       </c>
       <c r="D237" t="s">
-        <v>651</v>
+        <v>323</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -6069,10 +6093,10 @@
         <v>284</v>
       </c>
       <c r="B238" t="s">
-        <v>324</v>
+        <v>639</v>
       </c>
       <c r="D238" t="s">
-        <v>325</v>
+        <v>651</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -6080,10 +6104,10 @@
         <v>284</v>
       </c>
       <c r="B239" t="s">
-        <v>635</v>
+        <v>324</v>
       </c>
       <c r="D239" t="s">
-        <v>647</v>
+        <v>325</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -6091,10 +6115,10 @@
         <v>284</v>
       </c>
       <c r="B240" t="s">
-        <v>498</v>
+        <v>635</v>
       </c>
       <c r="D240" t="s">
-        <v>499</v>
+        <v>647</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
@@ -6102,10 +6126,10 @@
         <v>284</v>
       </c>
       <c r="B241" t="s">
-        <v>631</v>
+        <v>498</v>
       </c>
       <c r="D241" t="s">
-        <v>644</v>
+        <v>499</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
@@ -6113,10 +6137,10 @@
         <v>284</v>
       </c>
       <c r="B242" t="s">
-        <v>326</v>
+        <v>631</v>
       </c>
       <c r="D242" t="s">
-        <v>327</v>
+        <v>644</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
@@ -6124,10 +6148,10 @@
         <v>284</v>
       </c>
       <c r="B243" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D243" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -6135,10 +6159,10 @@
         <v>284</v>
       </c>
       <c r="B244" t="s">
-        <v>668</v>
+        <v>328</v>
       </c>
       <c r="D244" t="s">
-        <v>665</v>
+        <v>329</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -6146,10 +6170,10 @@
         <v>284</v>
       </c>
       <c r="B245" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D245" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -6157,10 +6181,10 @@
         <v>284</v>
       </c>
       <c r="B246" t="s">
-        <v>561</v>
+        <v>667</v>
       </c>
       <c r="D246" t="s">
-        <v>575</v>
+        <v>666</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -6168,10 +6192,10 @@
         <v>284</v>
       </c>
       <c r="B247" t="s">
-        <v>330</v>
+        <v>561</v>
       </c>
       <c r="D247" t="s">
-        <v>331</v>
+        <v>575</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
@@ -6179,10 +6203,10 @@
         <v>284</v>
       </c>
       <c r="B248" t="s">
-        <v>562</v>
+        <v>330</v>
       </c>
       <c r="D248" t="s">
-        <v>627</v>
+        <v>331</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -6190,10 +6214,10 @@
         <v>284</v>
       </c>
       <c r="B249" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D249" t="s">
-        <v>573</v>
+        <v>627</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -6201,10 +6225,10 @@
         <v>284</v>
       </c>
       <c r="B250" t="s">
-        <v>334</v>
+        <v>558</v>
       </c>
       <c r="D250" t="s">
-        <v>333</v>
+        <v>573</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -6212,10 +6236,10 @@
         <v>284</v>
       </c>
       <c r="B251" t="s">
-        <v>628</v>
+        <v>334</v>
       </c>
       <c r="D251" t="s">
-        <v>641</v>
+        <v>333</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
@@ -6223,10 +6247,10 @@
         <v>284</v>
       </c>
       <c r="B252" t="s">
-        <v>335</v>
+        <v>628</v>
       </c>
       <c r="D252" t="s">
-        <v>336</v>
+        <v>641</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
@@ -6245,10 +6269,10 @@
         <v>284</v>
       </c>
       <c r="B254" t="s">
-        <v>554</v>
+        <v>335</v>
       </c>
       <c r="D254" t="s">
-        <v>569</v>
+        <v>336</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
@@ -6267,10 +6291,10 @@
         <v>284</v>
       </c>
       <c r="B256" t="s">
-        <v>337</v>
+        <v>554</v>
       </c>
       <c r="D256" t="s">
-        <v>338</v>
+        <v>569</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
@@ -6278,10 +6302,10 @@
         <v>284</v>
       </c>
       <c r="B257" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D257" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -6289,10 +6313,10 @@
         <v>284</v>
       </c>
       <c r="B258" t="s">
-        <v>510</v>
+        <v>339</v>
       </c>
       <c r="D258" t="s">
-        <v>510</v>
+        <v>340</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -6300,10 +6324,10 @@
         <v>284</v>
       </c>
       <c r="B259" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="D259" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
@@ -6311,10 +6335,10 @@
         <v>284</v>
       </c>
       <c r="B260" t="s">
-        <v>341</v>
+        <v>500</v>
       </c>
       <c r="D260" t="s">
-        <v>342</v>
+        <v>501</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
@@ -6322,10 +6346,10 @@
         <v>284</v>
       </c>
       <c r="B261" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D261" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
@@ -6333,10 +6357,10 @@
         <v>284</v>
       </c>
       <c r="B262" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D262" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -6344,10 +6368,10 @@
         <v>284</v>
       </c>
       <c r="B263" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D263" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -6355,10 +6379,10 @@
         <v>284</v>
       </c>
       <c r="B264" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D264" t="s">
-        <v>293</v>
+        <v>348</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
@@ -6366,10 +6390,10 @@
         <v>284</v>
       </c>
       <c r="B265" t="s">
-        <v>564</v>
+        <v>349</v>
       </c>
       <c r="D265" t="s">
-        <v>576</v>
+        <v>293</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -6377,10 +6401,10 @@
         <v>284</v>
       </c>
       <c r="B266" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D266" t="s">
-        <v>417</v>
+        <v>576</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
@@ -6388,10 +6412,10 @@
         <v>284</v>
       </c>
       <c r="B267" t="s">
-        <v>350</v>
+        <v>563</v>
       </c>
       <c r="D267" t="s">
-        <v>351</v>
+        <v>417</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -6399,10 +6423,10 @@
         <v>284</v>
       </c>
       <c r="B268" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D268" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -6410,10 +6434,10 @@
         <v>284</v>
       </c>
       <c r="B269" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D269" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -6421,10 +6445,10 @@
         <v>284</v>
       </c>
       <c r="B270" t="s">
-        <v>559</v>
+        <v>354</v>
       </c>
       <c r="D270" t="s">
-        <v>653</v>
+        <v>355</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -6432,10 +6456,10 @@
         <v>284</v>
       </c>
       <c r="B271" t="s">
-        <v>356</v>
+        <v>559</v>
       </c>
       <c r="D271" t="s">
-        <v>357</v>
+        <v>653</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -6443,10 +6467,10 @@
         <v>284</v>
       </c>
       <c r="B272" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D272" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -6454,10 +6478,10 @@
         <v>284</v>
       </c>
       <c r="B273" t="s">
-        <v>547</v>
+        <v>358</v>
       </c>
       <c r="D273" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -6465,10 +6489,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
-        <v>360</v>
+        <v>547</v>
       </c>
       <c r="D274" t="s">
-        <v>548</v>
+        <v>361</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
@@ -6476,10 +6500,10 @@
         <v>284</v>
       </c>
       <c r="B275" t="s">
-        <v>636</v>
+        <v>360</v>
       </c>
       <c r="D275" t="s">
-        <v>648</v>
+        <v>548</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
@@ -6487,10 +6511,10 @@
         <v>284</v>
       </c>
       <c r="B276" t="s">
-        <v>455</v>
+        <v>636</v>
       </c>
       <c r="D276" t="s">
-        <v>456</v>
+        <v>648</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -6498,10 +6522,10 @@
         <v>284</v>
       </c>
       <c r="B277" t="s">
-        <v>362</v>
+        <v>455</v>
       </c>
       <c r="D277" t="s">
-        <v>362</v>
+        <v>456</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -6509,10 +6533,10 @@
         <v>284</v>
       </c>
       <c r="B278" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D278" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
@@ -6520,10 +6544,10 @@
         <v>284</v>
       </c>
       <c r="B279" t="s">
-        <v>524</v>
+        <v>363</v>
       </c>
       <c r="D279" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
@@ -6531,10 +6555,10 @@
         <v>284</v>
       </c>
       <c r="B280" t="s">
-        <v>365</v>
+        <v>524</v>
       </c>
       <c r="D280" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
@@ -6542,10 +6566,10 @@
         <v>284</v>
       </c>
       <c r="B281" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D281" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
@@ -6553,10 +6577,10 @@
         <v>284</v>
       </c>
       <c r="B282" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D282" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
@@ -6564,10 +6588,10 @@
         <v>284</v>
       </c>
       <c r="B283" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D283" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
@@ -6575,10 +6599,10 @@
         <v>284</v>
       </c>
       <c r="B284" t="s">
-        <v>294</v>
+        <v>373</v>
       </c>
       <c r="D284" t="s">
-        <v>295</v>
+        <v>374</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
@@ -6586,10 +6610,10 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>375</v>
+        <v>294</v>
       </c>
       <c r="D285" t="s">
-        <v>376</v>
+        <v>295</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
@@ -6597,10 +6621,10 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>557</v>
+        <v>375</v>
       </c>
       <c r="D286" t="s">
-        <v>572</v>
+        <v>376</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
@@ -6608,10 +6632,10 @@
         <v>284</v>
       </c>
       <c r="B287" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="D287" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
@@ -6619,10 +6643,10 @@
         <v>284</v>
       </c>
       <c r="B288" t="s">
-        <v>377</v>
+        <v>567</v>
       </c>
       <c r="D288" t="s">
-        <v>378</v>
+        <v>579</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
@@ -6630,10 +6654,10 @@
         <v>284</v>
       </c>
       <c r="B289" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D289" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
@@ -6641,10 +6665,10 @@
         <v>284</v>
       </c>
       <c r="B290" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D290" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
@@ -6652,10 +6676,10 @@
         <v>284</v>
       </c>
       <c r="B291" t="s">
-        <v>230</v>
+        <v>381</v>
       </c>
       <c r="D291" t="s">
-        <v>231</v>
+        <v>382</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -6663,10 +6687,10 @@
         <v>284</v>
       </c>
       <c r="B292" t="s">
-        <v>634</v>
+        <v>230</v>
       </c>
       <c r="D292" t="s">
-        <v>643</v>
+        <v>231</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
@@ -6674,10 +6698,10 @@
         <v>284</v>
       </c>
       <c r="B293" t="s">
-        <v>383</v>
+        <v>634</v>
       </c>
       <c r="D293" t="s">
-        <v>384</v>
+        <v>643</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
@@ -6685,10 +6709,10 @@
         <v>284</v>
       </c>
       <c r="B294" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D294" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
@@ -6696,10 +6720,10 @@
         <v>284</v>
       </c>
       <c r="B295" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D295" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
@@ -6707,10 +6731,10 @@
         <v>284</v>
       </c>
       <c r="B296" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D296" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -6718,10 +6742,10 @@
         <v>284</v>
       </c>
       <c r="B297" t="s">
-        <v>17</v>
+        <v>389</v>
       </c>
       <c r="D297" t="s">
-        <v>164</v>
+        <v>390</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
@@ -6729,10 +6753,10 @@
         <v>284</v>
       </c>
       <c r="B298" t="s">
-        <v>391</v>
+        <v>17</v>
       </c>
       <c r="D298" t="s">
-        <v>392</v>
+        <v>164</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -6740,10 +6764,10 @@
         <v>284</v>
       </c>
       <c r="B299" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D299" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
@@ -6751,10 +6775,10 @@
         <v>284</v>
       </c>
       <c r="B300" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D300" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
@@ -6762,10 +6786,10 @@
         <v>284</v>
       </c>
       <c r="B301" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D301" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
@@ -6773,10 +6797,10 @@
         <v>284</v>
       </c>
       <c r="B302" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D302" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
@@ -6784,10 +6808,10 @@
         <v>284</v>
       </c>
       <c r="B303" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D303" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
@@ -6795,10 +6819,10 @@
         <v>284</v>
       </c>
       <c r="B304" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D304" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
@@ -6806,10 +6830,10 @@
         <v>284</v>
       </c>
       <c r="B305" t="s">
-        <v>633</v>
+        <v>403</v>
       </c>
       <c r="D305" t="s">
-        <v>646</v>
+        <v>404</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
@@ -6817,10 +6841,10 @@
         <v>284</v>
       </c>
       <c r="B306" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D306" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
@@ -6828,10 +6852,10 @@
         <v>284</v>
       </c>
       <c r="B307" t="s">
-        <v>850</v>
+        <v>630</v>
       </c>
       <c r="D307" t="s">
-        <v>851</v>
+        <v>643</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
@@ -6839,10 +6863,10 @@
         <v>284</v>
       </c>
       <c r="B308" t="s">
-        <v>405</v>
+        <v>850</v>
       </c>
       <c r="D308" t="s">
-        <v>406</v>
+        <v>851</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
@@ -6850,10 +6874,10 @@
         <v>284</v>
       </c>
       <c r="B309" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D309" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
@@ -6861,10 +6885,10 @@
         <v>284</v>
       </c>
       <c r="B310" t="s">
-        <v>508</v>
+        <v>409</v>
       </c>
       <c r="D310" t="s">
-        <v>509</v>
+        <v>410</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
@@ -6872,10 +6896,10 @@
         <v>284</v>
       </c>
       <c r="B311" t="s">
-        <v>560</v>
+        <v>508</v>
       </c>
       <c r="D311" t="s">
-        <v>574</v>
+        <v>509</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
@@ -6883,10 +6907,10 @@
         <v>284</v>
       </c>
       <c r="B312" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="D312" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
@@ -6894,10 +6918,10 @@
         <v>284</v>
       </c>
       <c r="B313" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="D313" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
@@ -6905,10 +6929,10 @@
         <v>284</v>
       </c>
       <c r="B314" t="s">
-        <v>505</v>
+        <v>552</v>
       </c>
       <c r="D314" t="s">
-        <v>506</v>
+        <v>551</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
@@ -6916,10 +6940,10 @@
         <v>284</v>
       </c>
       <c r="B315" t="s">
-        <v>411</v>
+        <v>505</v>
       </c>
       <c r="D315" t="s">
-        <v>411</v>
+        <v>506</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
@@ -6927,10 +6951,10 @@
         <v>284</v>
       </c>
       <c r="B316" t="s">
-        <v>624</v>
+        <v>411</v>
       </c>
       <c r="D316" t="s">
-        <v>625</v>
+        <v>411</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
@@ -6938,10 +6962,10 @@
         <v>284</v>
       </c>
       <c r="B317" t="s">
-        <v>669</v>
+        <v>624</v>
       </c>
       <c r="D317" t="s">
-        <v>670</v>
+        <v>625</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
@@ -6949,10 +6973,10 @@
         <v>284</v>
       </c>
       <c r="B318" t="s">
-        <v>412</v>
+        <v>669</v>
       </c>
       <c r="D318" t="s">
-        <v>413</v>
+        <v>670</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
@@ -6960,10 +6984,10 @@
         <v>284</v>
       </c>
       <c r="B319" t="s">
-        <v>632</v>
+        <v>412</v>
       </c>
       <c r="D319" t="s">
-        <v>645</v>
+        <v>413</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
@@ -6971,10 +6995,10 @@
         <v>284</v>
       </c>
       <c r="B320" t="s">
-        <v>414</v>
+        <v>632</v>
       </c>
       <c r="D320" t="s">
-        <v>415</v>
+        <v>645</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
@@ -6982,10 +7006,10 @@
         <v>284</v>
       </c>
       <c r="B321" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D321" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -6993,10 +7017,10 @@
         <v>284</v>
       </c>
       <c r="B322" t="s">
-        <v>553</v>
+        <v>416</v>
       </c>
       <c r="D322" t="s">
-        <v>568</v>
+        <v>417</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
@@ -7004,21 +7028,21 @@
         <v>284</v>
       </c>
       <c r="B323" t="s">
-        <v>418</v>
+        <v>553</v>
       </c>
       <c r="D323" t="s">
-        <v>419</v>
+        <v>568</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B324" t="s">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="D324" t="s">
-        <v>22</v>
+        <v>419</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -7026,10 +7050,10 @@
         <v>420</v>
       </c>
       <c r="B325" t="s">
-        <v>421</v>
+        <v>21</v>
       </c>
       <c r="D325" t="s">
-        <v>421</v>
+        <v>22</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -7037,10 +7061,10 @@
         <v>420</v>
       </c>
       <c r="B326" t="s">
-        <v>30</v>
+        <v>421</v>
       </c>
       <c r="D326" t="s">
-        <v>31</v>
+        <v>421</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -7048,10 +7072,10 @@
         <v>420</v>
       </c>
       <c r="B327" t="s">
-        <v>546</v>
+        <v>30</v>
       </c>
       <c r="D327" t="s">
-        <v>422</v>
+        <v>31</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -7059,10 +7083,10 @@
         <v>420</v>
       </c>
       <c r="B328" t="s">
-        <v>44</v>
+        <v>546</v>
       </c>
       <c r="D328" t="s">
-        <v>45</v>
+        <v>422</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
@@ -7070,10 +7094,10 @@
         <v>420</v>
       </c>
       <c r="B329" t="s">
-        <v>589</v>
+        <v>44</v>
       </c>
       <c r="D329" t="s">
-        <v>610</v>
+        <v>45</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
@@ -7081,10 +7105,10 @@
         <v>420</v>
       </c>
       <c r="B330" t="s">
-        <v>846</v>
+        <v>589</v>
       </c>
       <c r="D330" t="s">
-        <v>846</v>
+        <v>610</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
@@ -7092,10 +7116,10 @@
         <v>420</v>
       </c>
       <c r="B331" t="s">
-        <v>50</v>
+        <v>846</v>
       </c>
       <c r="D331" t="s">
-        <v>51</v>
+        <v>846</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -7103,10 +7127,10 @@
         <v>420</v>
       </c>
       <c r="B332" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D332" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
@@ -7114,10 +7138,10 @@
         <v>420</v>
       </c>
       <c r="B333" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D333" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
@@ -7125,10 +7149,10 @@
         <v>420</v>
       </c>
       <c r="B334" t="s">
-        <v>296</v>
+        <v>52</v>
       </c>
       <c r="D334" t="s">
-        <v>519</v>
+        <v>53</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -7136,10 +7160,10 @@
         <v>420</v>
       </c>
       <c r="B335" t="s">
-        <v>523</v>
+        <v>296</v>
       </c>
       <c r="D335" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -7147,10 +7171,10 @@
         <v>420</v>
       </c>
       <c r="B336" t="s">
-        <v>423</v>
+        <v>523</v>
       </c>
       <c r="D336" t="s">
-        <v>424</v>
+        <v>520</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -7158,10 +7182,10 @@
         <v>420</v>
       </c>
       <c r="B337" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D337" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
@@ -7169,10 +7193,10 @@
         <v>420</v>
       </c>
       <c r="B338" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D338" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
@@ -7180,10 +7204,10 @@
         <v>420</v>
       </c>
       <c r="B339" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D339" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -7191,10 +7215,10 @@
         <v>420</v>
       </c>
       <c r="B340" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D340" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
@@ -7202,10 +7226,10 @@
         <v>420</v>
       </c>
       <c r="B341" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D341" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -7213,10 +7237,10 @@
         <v>420</v>
       </c>
       <c r="B342" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D342" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
@@ -7224,10 +7248,10 @@
         <v>420</v>
       </c>
       <c r="B343" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D343" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -7235,10 +7259,10 @@
         <v>420</v>
       </c>
       <c r="B344" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D344" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -7246,10 +7270,10 @@
         <v>420</v>
       </c>
       <c r="B345" t="s">
-        <v>61</v>
+        <v>439</v>
       </c>
       <c r="D345" t="s">
-        <v>62</v>
+        <v>440</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
@@ -7257,10 +7281,10 @@
         <v>420</v>
       </c>
       <c r="B346" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D346" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
@@ -7268,10 +7292,10 @@
         <v>420</v>
       </c>
       <c r="B347" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D347" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -7279,10 +7303,10 @@
         <v>420</v>
       </c>
       <c r="B348" t="s">
-        <v>671</v>
+        <v>63</v>
       </c>
       <c r="D348" t="s">
-        <v>672</v>
+        <v>64</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
@@ -7290,10 +7314,10 @@
         <v>420</v>
       </c>
       <c r="B349" t="s">
-        <v>441</v>
+        <v>671</v>
       </c>
       <c r="D349" t="s">
-        <v>442</v>
+        <v>672</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
@@ -7301,10 +7325,10 @@
         <v>420</v>
       </c>
       <c r="B350" t="s">
-        <v>588</v>
+        <v>441</v>
       </c>
       <c r="D350" t="s">
-        <v>609</v>
+        <v>442</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
@@ -7312,10 +7336,10 @@
         <v>420</v>
       </c>
       <c r="B351" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D351" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
@@ -7323,10 +7347,10 @@
         <v>420</v>
       </c>
       <c r="B352" t="s">
-        <v>75</v>
+        <v>587</v>
       </c>
       <c r="D352" t="s">
-        <v>76</v>
+        <v>608</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
@@ -7334,10 +7358,10 @@
         <v>420</v>
       </c>
       <c r="B353" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D353" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
@@ -7345,10 +7369,10 @@
         <v>420</v>
       </c>
       <c r="B354" t="s">
-        <v>326</v>
+        <v>77</v>
       </c>
       <c r="D354" t="s">
-        <v>327</v>
+        <v>78</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
@@ -7356,10 +7380,10 @@
         <v>420</v>
       </c>
       <c r="B355" t="s">
-        <v>449</v>
+        <v>326</v>
       </c>
       <c r="D355" t="s">
-        <v>443</v>
+        <v>327</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
@@ -7367,10 +7391,10 @@
         <v>420</v>
       </c>
       <c r="B356" t="s">
-        <v>545</v>
+        <v>449</v>
       </c>
       <c r="D356" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
@@ -7378,10 +7402,10 @@
         <v>420</v>
       </c>
       <c r="B357" t="s">
-        <v>585</v>
+        <v>545</v>
       </c>
       <c r="D357" t="s">
-        <v>606</v>
+        <v>444</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
@@ -7389,10 +7413,10 @@
         <v>420</v>
       </c>
       <c r="B358" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D358" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
@@ -7400,10 +7424,10 @@
         <v>420</v>
       </c>
       <c r="B359" t="s">
-        <v>445</v>
+        <v>586</v>
       </c>
       <c r="D359" t="s">
-        <v>446</v>
+        <v>607</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
@@ -7411,10 +7435,10 @@
         <v>420</v>
       </c>
       <c r="B360" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D360" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
@@ -7422,10 +7446,10 @@
         <v>420</v>
       </c>
       <c r="B361" t="s">
-        <v>654</v>
+        <v>447</v>
       </c>
       <c r="D361" t="s">
-        <v>655</v>
+        <v>448</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
@@ -7433,10 +7457,10 @@
         <v>420</v>
       </c>
       <c r="B362" t="s">
-        <v>332</v>
+        <v>654</v>
       </c>
       <c r="D362" t="s">
-        <v>333</v>
+        <v>655</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
@@ -7444,10 +7468,10 @@
         <v>420</v>
       </c>
       <c r="B363" t="s">
-        <v>101</v>
+        <v>332</v>
       </c>
       <c r="D363" t="s">
-        <v>102</v>
+        <v>333</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
@@ -7455,10 +7479,10 @@
         <v>420</v>
       </c>
       <c r="B364" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D364" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
@@ -7466,10 +7490,10 @@
         <v>420</v>
       </c>
       <c r="B365" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D365" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
@@ -7477,10 +7501,10 @@
         <v>420</v>
       </c>
       <c r="B366" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D366" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -7488,10 +7512,10 @@
         <v>420</v>
       </c>
       <c r="B367" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D367" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
@@ -7499,10 +7523,10 @@
         <v>420</v>
       </c>
       <c r="B368" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D368" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
@@ -7510,10 +7534,10 @@
         <v>420</v>
       </c>
       <c r="B369" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D369" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -7521,10 +7545,10 @@
         <v>420</v>
       </c>
       <c r="B370" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D370" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
@@ -7532,10 +7556,10 @@
         <v>420</v>
       </c>
       <c r="B371" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D371" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
@@ -7543,10 +7567,10 @@
         <v>420</v>
       </c>
       <c r="B372" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D372" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -7554,10 +7578,10 @@
         <v>420</v>
       </c>
       <c r="B373" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D373" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
@@ -7565,10 +7589,10 @@
         <v>420</v>
       </c>
       <c r="B374" t="s">
-        <v>450</v>
+        <v>121</v>
       </c>
       <c r="D374" t="s">
-        <v>451</v>
+        <v>122</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -7576,10 +7600,10 @@
         <v>420</v>
       </c>
       <c r="B375" t="s">
-        <v>549</v>
+        <v>450</v>
       </c>
       <c r="D375" t="s">
-        <v>550</v>
+        <v>451</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -7587,10 +7611,10 @@
         <v>420</v>
       </c>
       <c r="B376" t="s">
-        <v>129</v>
+        <v>549</v>
       </c>
       <c r="D376" t="s">
-        <v>130</v>
+        <v>550</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
@@ -7598,10 +7622,10 @@
         <v>420</v>
       </c>
       <c r="B377" t="s">
-        <v>592</v>
+        <v>129</v>
       </c>
       <c r="D377" t="s">
-        <v>612</v>
+        <v>130</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
@@ -7609,10 +7633,10 @@
         <v>420</v>
       </c>
       <c r="B378" t="s">
-        <v>622</v>
+        <v>592</v>
       </c>
       <c r="D378" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
@@ -7620,10 +7644,10 @@
         <v>420</v>
       </c>
       <c r="B379" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="D379" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
@@ -7631,10 +7655,10 @@
         <v>420</v>
       </c>
       <c r="B380" t="s">
-        <v>452</v>
+        <v>591</v>
       </c>
       <c r="D380" t="s">
-        <v>453</v>
+        <v>626</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
@@ -7642,10 +7666,10 @@
         <v>420</v>
       </c>
       <c r="B381" t="s">
-        <v>598</v>
+        <v>452</v>
       </c>
       <c r="D381" t="s">
-        <v>618</v>
+        <v>453</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
@@ -7653,10 +7677,10 @@
         <v>420</v>
       </c>
       <c r="B382" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="D382" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
@@ -7664,10 +7688,10 @@
         <v>420</v>
       </c>
       <c r="B383" t="s">
-        <v>659</v>
+        <v>590</v>
       </c>
       <c r="D383" t="s">
-        <v>660</v>
+        <v>611</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
@@ -7675,10 +7699,10 @@
         <v>420</v>
       </c>
       <c r="B384" t="s">
-        <v>595</v>
+        <v>659</v>
       </c>
       <c r="D384" t="s">
-        <v>615</v>
+        <v>660</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
@@ -7686,10 +7710,10 @@
         <v>420</v>
       </c>
       <c r="B385" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="D385" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
@@ -7697,10 +7721,10 @@
         <v>420</v>
       </c>
       <c r="B386" t="s">
-        <v>455</v>
+        <v>584</v>
       </c>
       <c r="D386" t="s">
-        <v>456</v>
+        <v>605</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
@@ -7708,10 +7732,10 @@
         <v>420</v>
       </c>
       <c r="B387" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D387" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
@@ -7719,10 +7743,10 @@
         <v>420</v>
       </c>
       <c r="B388" t="s">
-        <v>362</v>
+        <v>457</v>
       </c>
       <c r="D388" t="s">
-        <v>362</v>
+        <v>454</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
@@ -7730,10 +7754,10 @@
         <v>420</v>
       </c>
       <c r="B389" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D389" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
@@ -7741,10 +7765,10 @@
         <v>420</v>
       </c>
       <c r="B390" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D390" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
@@ -7752,10 +7776,10 @@
         <v>420</v>
       </c>
       <c r="B391" t="s">
-        <v>596</v>
+        <v>369</v>
       </c>
       <c r="D391" t="s">
-        <v>616</v>
+        <v>370</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
@@ -7763,10 +7787,10 @@
         <v>420</v>
       </c>
       <c r="B392" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D392" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
@@ -7774,10 +7798,10 @@
         <v>420</v>
       </c>
       <c r="B393" t="s">
-        <v>377</v>
+        <v>597</v>
       </c>
       <c r="D393" t="s">
-        <v>378</v>
+        <v>617</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -7785,10 +7809,10 @@
         <v>420</v>
       </c>
       <c r="B394" t="s">
-        <v>156</v>
+        <v>377</v>
       </c>
       <c r="D394" t="s">
-        <v>157</v>
+        <v>378</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
@@ -7796,10 +7820,10 @@
         <v>420</v>
       </c>
       <c r="B395" t="s">
-        <v>379</v>
+        <v>156</v>
       </c>
       <c r="D395" t="s">
-        <v>380</v>
+        <v>157</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
@@ -7807,10 +7831,10 @@
         <v>420</v>
       </c>
       <c r="B396" t="s">
-        <v>656</v>
+        <v>379</v>
       </c>
       <c r="D396" t="s">
-        <v>657</v>
+        <v>380</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
@@ -7818,10 +7842,10 @@
         <v>420</v>
       </c>
       <c r="B397" t="s">
-        <v>17</v>
+        <v>656</v>
       </c>
       <c r="D397" t="s">
-        <v>164</v>
+        <v>657</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
@@ -7829,10 +7853,10 @@
         <v>420</v>
       </c>
       <c r="B398" t="s">
-        <v>458</v>
+        <v>17</v>
       </c>
       <c r="D398" t="s">
-        <v>459</v>
+        <v>164</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
@@ -7840,10 +7864,10 @@
         <v>420</v>
       </c>
       <c r="B399" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D399" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
@@ -7851,10 +7875,10 @@
         <v>420</v>
       </c>
       <c r="B400" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D400" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
@@ -7862,10 +7886,10 @@
         <v>420</v>
       </c>
       <c r="B401" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D401" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
@@ -7873,10 +7897,10 @@
         <v>420</v>
       </c>
       <c r="B402" t="s">
-        <v>399</v>
+        <v>464</v>
       </c>
       <c r="D402" t="s">
-        <v>400</v>
+        <v>465</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
@@ -7884,10 +7908,10 @@
         <v>420</v>
       </c>
       <c r="B403" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="D403" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
@@ -7895,10 +7919,10 @@
         <v>420</v>
       </c>
       <c r="B404" t="s">
-        <v>466</v>
+        <v>407</v>
       </c>
       <c r="D404" t="s">
-        <v>467</v>
+        <v>408</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
@@ -7906,10 +7930,10 @@
         <v>420</v>
       </c>
       <c r="B405" t="s">
-        <v>187</v>
+        <v>466</v>
       </c>
       <c r="D405" t="s">
-        <v>188</v>
+        <v>467</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
@@ -7917,10 +7941,10 @@
         <v>420</v>
       </c>
       <c r="B406" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D406" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
@@ -7928,10 +7952,10 @@
         <v>420</v>
       </c>
       <c r="B407" t="s">
-        <v>601</v>
+        <v>196</v>
       </c>
       <c r="D407" t="s">
-        <v>621</v>
+        <v>197</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
@@ -7939,10 +7963,10 @@
         <v>420</v>
       </c>
       <c r="B408" t="s">
-        <v>468</v>
+        <v>601</v>
       </c>
       <c r="D408" t="s">
-        <v>469</v>
+        <v>621</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
@@ -7950,10 +7974,10 @@
         <v>420</v>
       </c>
       <c r="B409" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D409" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
@@ -7961,10 +7985,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D410" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
@@ -7972,10 +7996,10 @@
         <v>420</v>
       </c>
       <c r="B411" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D411" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
@@ -7983,10 +8007,10 @@
         <v>420</v>
       </c>
       <c r="B412" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D412" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
@@ -7994,10 +8018,10 @@
         <v>420</v>
       </c>
       <c r="B413" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D413" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
@@ -8005,10 +8029,10 @@
         <v>420</v>
       </c>
       <c r="B414" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D414" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
@@ -8016,10 +8040,10 @@
         <v>420</v>
       </c>
       <c r="B415" t="s">
-        <v>599</v>
+        <v>480</v>
       </c>
       <c r="D415" t="s">
-        <v>619</v>
+        <v>481</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
@@ -8027,10 +8051,10 @@
         <v>420</v>
       </c>
       <c r="B416" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D416" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
@@ -8038,10 +8062,10 @@
         <v>420</v>
       </c>
       <c r="B417" t="s">
-        <v>482</v>
+        <v>600</v>
       </c>
       <c r="D417" t="s">
-        <v>483</v>
+        <v>620</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
@@ -8049,10 +8073,10 @@
         <v>420</v>
       </c>
       <c r="B418" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D418" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
@@ -8060,10 +8084,10 @@
         <v>420</v>
       </c>
       <c r="B419" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D419" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
@@ -8071,10 +8095,10 @@
         <v>420</v>
       </c>
       <c r="B420" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D420" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
@@ -8082,10 +8106,10 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D421" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
@@ -8093,10 +8117,10 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D422" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
@@ -8104,10 +8128,10 @@
         <v>420</v>
       </c>
       <c r="B423" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D423" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
@@ -8115,10 +8139,10 @@
         <v>420</v>
       </c>
       <c r="B424" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D424" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
@@ -8126,10 +8150,10 @@
         <v>420</v>
       </c>
       <c r="B425" t="s">
-        <v>582</v>
+        <v>496</v>
       </c>
       <c r="D425" t="s">
-        <v>658</v>
+        <v>497</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
@@ -8137,10 +8161,10 @@
         <v>420</v>
       </c>
       <c r="B426" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D426" t="s">
-        <v>604</v>
+        <v>658</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
@@ -8148,10 +8172,10 @@
         <v>420</v>
       </c>
       <c r="B427" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D427" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
@@ -8159,10 +8183,10 @@
         <v>420</v>
       </c>
       <c r="B428" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D428" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
@@ -8170,10 +8194,10 @@
         <v>420</v>
       </c>
       <c r="B429" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="D429" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
@@ -8181,21 +8205,21 @@
         <v>420</v>
       </c>
       <c r="B430" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D430" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>284</v>
+        <v>420</v>
       </c>
       <c r="B431" t="s">
-        <v>725</v>
+        <v>593</v>
       </c>
       <c r="D431" t="s">
-        <v>726</v>
+        <v>613</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
@@ -8203,10 +8227,10 @@
         <v>284</v>
       </c>
       <c r="B432" t="s">
-        <v>549</v>
+        <v>725</v>
       </c>
       <c r="D432" t="s">
-        <v>550</v>
+        <v>726</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.25">
@@ -8214,10 +8238,10 @@
         <v>284</v>
       </c>
       <c r="B433" t="s">
-        <v>654</v>
+        <v>549</v>
       </c>
       <c r="D433" t="s">
-        <v>655</v>
+        <v>550</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
@@ -8225,10 +8249,10 @@
         <v>284</v>
       </c>
       <c r="B434" t="s">
-        <v>727</v>
+        <v>654</v>
       </c>
       <c r="D434" t="s">
-        <v>728</v>
+        <v>655</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
@@ -8236,10 +8260,10 @@
         <v>284</v>
       </c>
       <c r="B435" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D435" t="s">
-        <v>657</v>
+        <v>728</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
@@ -8247,10 +8271,10 @@
         <v>284</v>
       </c>
       <c r="B436" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D436" t="s">
-        <v>731</v>
+        <v>657</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
@@ -8258,10 +8282,10 @@
         <v>284</v>
       </c>
       <c r="B437" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D437" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
@@ -8269,10 +8293,10 @@
         <v>284</v>
       </c>
       <c r="B438" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D438" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
@@ -8280,7 +8304,7 @@
         <v>284</v>
       </c>
       <c r="B439" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D439" t="s">
         <v>735</v>
@@ -8291,10 +8315,10 @@
         <v>284</v>
       </c>
       <c r="B440" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D440" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.25">
@@ -8302,10 +8326,10 @@
         <v>284</v>
       </c>
       <c r="B441" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D441" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
@@ -8313,10 +8337,10 @@
         <v>284</v>
       </c>
       <c r="B442" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D442" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
@@ -8324,10 +8348,10 @@
         <v>284</v>
       </c>
       <c r="B443" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D443" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.25">
@@ -8335,10 +8359,10 @@
         <v>284</v>
       </c>
       <c r="B444" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D444" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.25">
@@ -8346,10 +8370,10 @@
         <v>284</v>
       </c>
       <c r="B445" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D445" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.25">
@@ -8357,10 +8381,10 @@
         <v>284</v>
       </c>
       <c r="B446" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D446" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
@@ -8368,10 +8392,10 @@
         <v>284</v>
       </c>
       <c r="B447" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D447" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.25">
@@ -8379,10 +8403,10 @@
         <v>284</v>
       </c>
       <c r="B448" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D448" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
@@ -8390,10 +8414,10 @@
         <v>284</v>
       </c>
       <c r="B449" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D449" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
@@ -8401,10 +8425,10 @@
         <v>284</v>
       </c>
       <c r="B450" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D450" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
@@ -8412,10 +8436,10 @@
         <v>284</v>
       </c>
       <c r="B451" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D451" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
@@ -8423,10 +8447,10 @@
         <v>284</v>
       </c>
       <c r="B452" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D452" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
@@ -8434,10 +8458,10 @@
         <v>284</v>
       </c>
       <c r="B453" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D453" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
@@ -8445,10 +8469,10 @@
         <v>284</v>
       </c>
       <c r="B454" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D454" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
@@ -8456,10 +8480,10 @@
         <v>284</v>
       </c>
       <c r="B455" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D455" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
@@ -8467,10 +8491,10 @@
         <v>284</v>
       </c>
       <c r="B456" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D456" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
@@ -8478,10 +8502,10 @@
         <v>284</v>
       </c>
       <c r="B457" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D457" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
@@ -8489,10 +8513,10 @@
         <v>284</v>
       </c>
       <c r="B458" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D458" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
@@ -8500,10 +8524,10 @@
         <v>284</v>
       </c>
       <c r="B459" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D459" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
@@ -8511,10 +8535,10 @@
         <v>284</v>
       </c>
       <c r="B460" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D460" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
@@ -8522,10 +8546,10 @@
         <v>284</v>
       </c>
       <c r="B461" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D461" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
@@ -8533,10 +8557,10 @@
         <v>284</v>
       </c>
       <c r="B462" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D462" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
@@ -8544,10 +8568,10 @@
         <v>284</v>
       </c>
       <c r="B463" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D463" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
@@ -8555,10 +8579,10 @@
         <v>284</v>
       </c>
       <c r="B464" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D464" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
@@ -8566,10 +8590,10 @@
         <v>284</v>
       </c>
       <c r="B465" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D465" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
@@ -8577,10 +8601,10 @@
         <v>284</v>
       </c>
       <c r="B466" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D466" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
@@ -8588,10 +8612,10 @@
         <v>284</v>
       </c>
       <c r="B467" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D467" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
@@ -8599,10 +8623,10 @@
         <v>284</v>
       </c>
       <c r="B468" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D468" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
@@ -8610,10 +8634,10 @@
         <v>284</v>
       </c>
       <c r="B469" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D469" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
@@ -8621,10 +8645,10 @@
         <v>284</v>
       </c>
       <c r="B470" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D470" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
@@ -8632,10 +8656,10 @@
         <v>284</v>
       </c>
       <c r="B471" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D471" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
@@ -8643,10 +8667,10 @@
         <v>284</v>
       </c>
       <c r="B472" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D472" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
@@ -8654,10 +8678,10 @@
         <v>284</v>
       </c>
       <c r="B473" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D473" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
@@ -8665,10 +8689,10 @@
         <v>284</v>
       </c>
       <c r="B474" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D474" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
@@ -8676,10 +8700,10 @@
         <v>284</v>
       </c>
       <c r="B475" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D475" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
@@ -8687,10 +8711,10 @@
         <v>284</v>
       </c>
       <c r="B476" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D476" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
@@ -8698,10 +8722,10 @@
         <v>284</v>
       </c>
       <c r="B477" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D477" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
@@ -8709,10 +8733,10 @@
         <v>284</v>
       </c>
       <c r="B478" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="D478" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
@@ -8720,10 +8744,10 @@
         <v>284</v>
       </c>
       <c r="B479" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="D479" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
@@ -8731,10 +8755,10 @@
         <v>284</v>
       </c>
       <c r="B480" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="D480" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
@@ -8742,10 +8766,10 @@
         <v>284</v>
       </c>
       <c r="B481" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="D481" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
@@ -8753,10 +8777,10 @@
         <v>284</v>
       </c>
       <c r="B482" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D482" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
@@ -8764,10 +8788,10 @@
         <v>284</v>
       </c>
       <c r="B483" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="D483" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
@@ -8775,10 +8799,10 @@
         <v>284</v>
       </c>
       <c r="B484" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="D484" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
@@ -8786,10 +8810,10 @@
         <v>284</v>
       </c>
       <c r="B485" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D485" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.25">
@@ -8797,10 +8821,10 @@
         <v>284</v>
       </c>
       <c r="B486" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D486" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.25">
@@ -8808,10 +8832,10 @@
         <v>284</v>
       </c>
       <c r="B487" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D487" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.25">
@@ -8819,10 +8843,10 @@
         <v>284</v>
       </c>
       <c r="B488" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D488" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
@@ -8830,10 +8854,10 @@
         <v>284</v>
       </c>
       <c r="B489" t="s">
-        <v>79</v>
+        <v>833</v>
       </c>
       <c r="D489" t="s">
-        <v>80</v>
+        <v>834</v>
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.25">
@@ -8841,10 +8865,10 @@
         <v>284</v>
       </c>
       <c r="B490" t="s">
-        <v>835</v>
+        <v>79</v>
       </c>
       <c r="D490" t="s">
-        <v>836</v>
+        <v>80</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.25">
@@ -8852,21 +8876,21 @@
         <v>284</v>
       </c>
       <c r="B491" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D491" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>420</v>
+        <v>284</v>
       </c>
       <c r="B492" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D492" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
@@ -8874,10 +8898,10 @@
         <v>420</v>
       </c>
       <c r="B493" t="s">
-        <v>739</v>
+        <v>839</v>
       </c>
       <c r="D493" t="s">
-        <v>740</v>
+        <v>840</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
@@ -8885,10 +8909,10 @@
         <v>420</v>
       </c>
       <c r="B494" t="s">
-        <v>841</v>
+        <v>739</v>
       </c>
       <c r="D494" t="s">
-        <v>157</v>
+        <v>740</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
@@ -8896,10 +8920,10 @@
         <v>420</v>
       </c>
       <c r="B495" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D495" t="s">
-        <v>843</v>
+        <v>157</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
@@ -8907,10 +8931,10 @@
         <v>420</v>
       </c>
       <c r="B496" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D496" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
@@ -8918,10 +8942,10 @@
         <v>420</v>
       </c>
       <c r="B497" t="s">
-        <v>737</v>
+        <v>844</v>
       </c>
       <c r="D497" t="s">
-        <v>738</v>
+        <v>845</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
@@ -8929,10 +8953,10 @@
         <v>420</v>
       </c>
       <c r="B498" t="s">
-        <v>385</v>
+        <v>737</v>
       </c>
       <c r="D498" t="s">
-        <v>386</v>
+        <v>738</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
@@ -8940,10 +8964,10 @@
         <v>420</v>
       </c>
       <c r="B499" t="s">
-        <v>309</v>
+        <v>385</v>
       </c>
       <c r="D499" t="s">
-        <v>310</v>
+        <v>386</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
@@ -8951,10 +8975,10 @@
         <v>420</v>
       </c>
       <c r="B500" t="s">
-        <v>727</v>
+        <v>309</v>
       </c>
       <c r="D500" t="s">
-        <v>728</v>
+        <v>310</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.25">
@@ -8962,28 +8986,72 @@
         <v>420</v>
       </c>
       <c r="B501" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D501" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>284</v>
+        <v>420</v>
       </c>
       <c r="B502" t="s">
+        <v>730</v>
+      </c>
+      <c r="D502" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>284</v>
+      </c>
+      <c r="B503" t="s">
         <v>847</v>
       </c>
-      <c r="D502" t="s">
+      <c r="D503" t="s">
         <v>848</v>
       </c>
     </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>284</v>
+      </c>
+      <c r="B504" t="s">
+        <v>854</v>
+      </c>
+      <c r="D504" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>420</v>
+      </c>
+      <c r="B505" t="s">
+        <v>856</v>
+      </c>
+      <c r="D505" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>420</v>
+      </c>
+      <c r="B506" t="s">
+        <v>858</v>
+      </c>
+      <c r="D506" t="s">
+        <v>859</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D502" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D501">
-    <sortCondition ref="A2:A501"/>
-    <sortCondition ref="B2:B501"/>
+  <autoFilter ref="A1:D503" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D502">
+    <sortCondition ref="A2:A502"/>
+    <sortCondition ref="B2:B502"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_dev\Seal-Report\Repository\Settings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA82394C-1BFF-463E-833F-A0B18AC5DD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F9D3C3-4BA4-4C47-8825-7D726F72D5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18270" yWindow="2220" windowWidth="24375" windowHeight="15855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18615" yWindow="2565" windowWidth="24375" windowHeight="15855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Translations" sheetId="1" r:id="rId1"/>
@@ -2273,12 +2273,6 @@
     <t>Masquer le panneau</t>
   </si>
   <si>
-    <t>Ask the AI assistant…</t>
-  </si>
-  <si>
-    <t>Posez une question à l'assistant IA…</t>
-  </si>
-  <si>
     <t>Confirm Deletion</t>
   </si>
   <si>
@@ -2616,6 +2610,12 @@
   </si>
   <si>
     <t>Copier, coller et envoyer</t>
+  </si>
+  <si>
+    <t>Ask the AI agent…</t>
+  </si>
+  <si>
+    <t>Posez une question à l'agent IA…</t>
   </si>
 </sst>
 </file>
@@ -5719,10 +5719,10 @@
         <v>284</v>
       </c>
       <c r="B204" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D204" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
@@ -5829,10 +5829,10 @@
         <v>284</v>
       </c>
       <c r="B214" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D214" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -6863,10 +6863,10 @@
         <v>284</v>
       </c>
       <c r="B308" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D308" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
@@ -7116,10 +7116,10 @@
         <v>420</v>
       </c>
       <c r="B331" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D331" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -8370,10 +8370,10 @@
         <v>284</v>
       </c>
       <c r="B445" t="s">
-        <v>745</v>
+        <v>858</v>
       </c>
       <c r="D445" t="s">
-        <v>746</v>
+        <v>859</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.25">
@@ -8381,10 +8381,10 @@
         <v>284</v>
       </c>
       <c r="B446" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D446" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
@@ -8392,10 +8392,10 @@
         <v>284</v>
       </c>
       <c r="B447" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D447" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.25">
@@ -8403,10 +8403,10 @@
         <v>284</v>
       </c>
       <c r="B448" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D448" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
@@ -8414,10 +8414,10 @@
         <v>284</v>
       </c>
       <c r="B449" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D449" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
@@ -8425,10 +8425,10 @@
         <v>284</v>
       </c>
       <c r="B450" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D450" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
@@ -8436,10 +8436,10 @@
         <v>284</v>
       </c>
       <c r="B451" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D451" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
@@ -8447,10 +8447,10 @@
         <v>284</v>
       </c>
       <c r="B452" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D452" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
@@ -8458,10 +8458,10 @@
         <v>284</v>
       </c>
       <c r="B453" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D453" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
@@ -8469,10 +8469,10 @@
         <v>284</v>
       </c>
       <c r="B454" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D454" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
@@ -8480,10 +8480,10 @@
         <v>284</v>
       </c>
       <c r="B455" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D455" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
@@ -8491,10 +8491,10 @@
         <v>284</v>
       </c>
       <c r="B456" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D456" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
@@ -8502,10 +8502,10 @@
         <v>284</v>
       </c>
       <c r="B457" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D457" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
@@ -8513,10 +8513,10 @@
         <v>284</v>
       </c>
       <c r="B458" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D458" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
@@ -8524,10 +8524,10 @@
         <v>284</v>
       </c>
       <c r="B459" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D459" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
@@ -8535,10 +8535,10 @@
         <v>284</v>
       </c>
       <c r="B460" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D460" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
@@ -8546,10 +8546,10 @@
         <v>284</v>
       </c>
       <c r="B461" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D461" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
@@ -8557,10 +8557,10 @@
         <v>284</v>
       </c>
       <c r="B462" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D462" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
@@ -8568,10 +8568,10 @@
         <v>284</v>
       </c>
       <c r="B463" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D463" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
@@ -8579,10 +8579,10 @@
         <v>284</v>
       </c>
       <c r="B464" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D464" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
@@ -8590,10 +8590,10 @@
         <v>284</v>
       </c>
       <c r="B465" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D465" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
@@ -8601,10 +8601,10 @@
         <v>284</v>
       </c>
       <c r="B466" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D466" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
@@ -8612,10 +8612,10 @@
         <v>284</v>
       </c>
       <c r="B467" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D467" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
@@ -8623,10 +8623,10 @@
         <v>284</v>
       </c>
       <c r="B468" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D468" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
@@ -8634,10 +8634,10 @@
         <v>284</v>
       </c>
       <c r="B469" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D469" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
@@ -8645,10 +8645,10 @@
         <v>284</v>
       </c>
       <c r="B470" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D470" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
@@ -8656,10 +8656,10 @@
         <v>284</v>
       </c>
       <c r="B471" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D471" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
@@ -8667,10 +8667,10 @@
         <v>284</v>
       </c>
       <c r="B472" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D472" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
@@ -8678,10 +8678,10 @@
         <v>284</v>
       </c>
       <c r="B473" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D473" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
@@ -8689,10 +8689,10 @@
         <v>284</v>
       </c>
       <c r="B474" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D474" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
@@ -8700,10 +8700,10 @@
         <v>284</v>
       </c>
       <c r="B475" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D475" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
@@ -8711,10 +8711,10 @@
         <v>284</v>
       </c>
       <c r="B476" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D476" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
@@ -8722,10 +8722,10 @@
         <v>284</v>
       </c>
       <c r="B477" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D477" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
@@ -8733,10 +8733,10 @@
         <v>284</v>
       </c>
       <c r="B478" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D478" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
@@ -8744,10 +8744,10 @@
         <v>284</v>
       </c>
       <c r="B479" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="D479" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
@@ -8755,10 +8755,10 @@
         <v>284</v>
       </c>
       <c r="B480" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="D480" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
@@ -8766,10 +8766,10 @@
         <v>284</v>
       </c>
       <c r="B481" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="D481" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
@@ -8777,10 +8777,10 @@
         <v>284</v>
       </c>
       <c r="B482" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="D482" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
@@ -8788,10 +8788,10 @@
         <v>284</v>
       </c>
       <c r="B483" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D483" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
@@ -8799,10 +8799,10 @@
         <v>284</v>
       </c>
       <c r="B484" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="D484" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
@@ -8810,10 +8810,10 @@
         <v>284</v>
       </c>
       <c r="B485" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="D485" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.25">
@@ -8821,10 +8821,10 @@
         <v>284</v>
       </c>
       <c r="B486" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D486" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.25">
@@ -8832,10 +8832,10 @@
         <v>284</v>
       </c>
       <c r="B487" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D487" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.25">
@@ -8843,10 +8843,10 @@
         <v>284</v>
       </c>
       <c r="B488" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D488" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
@@ -8854,10 +8854,10 @@
         <v>284</v>
       </c>
       <c r="B489" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D489" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.25">
@@ -8876,10 +8876,10 @@
         <v>284</v>
       </c>
       <c r="B491" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D491" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.25">
@@ -8887,10 +8887,10 @@
         <v>284</v>
       </c>
       <c r="B492" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D492" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
@@ -8898,10 +8898,10 @@
         <v>420</v>
       </c>
       <c r="B493" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D493" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
@@ -8920,7 +8920,7 @@
         <v>420</v>
       </c>
       <c r="B495" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="D495" t="s">
         <v>157</v>
@@ -8931,10 +8931,10 @@
         <v>420</v>
       </c>
       <c r="B496" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="D496" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
@@ -8942,10 +8942,10 @@
         <v>420</v>
       </c>
       <c r="B497" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D497" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
@@ -9008,10 +9008,10 @@
         <v>284</v>
       </c>
       <c r="B503" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D503" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
@@ -9019,10 +9019,10 @@
         <v>284</v>
       </c>
       <c r="B504" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D504" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
@@ -9030,10 +9030,10 @@
         <v>420</v>
       </c>
       <c r="B505" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D505" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
@@ -9041,10 +9041,10 @@
         <v>420</v>
       </c>
       <c r="B506" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D506" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
   </sheetData>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -3470,7 +3470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D506"/>
+  <dimension ref="A1:D507"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -9047,6 +9047,28 @@
         <v>857</v>
       </c>
     </row>
+    <row r="507" spans="1:4">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>BIN</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Recycle Bin</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Corbeille</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D502">

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D508"/>
+  <dimension ref="A1:D512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9583,6 +9583,74 @@
         </is>
       </c>
     </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Paste shortcut</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Coller le raccourci</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Shortcut to</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Raccourci vers</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Shortcut target not found</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Cible du raccourci introuvable</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>shortcut(s) created</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>raccourci(s) créé(s)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D512"/>
+  <dimension ref="A1:D506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -962,102 +962,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NVD3</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(right axis)</t>
+          <t>!=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(axe de droite)</t>
+          <t>!=</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVD3</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Expanded</t>
+          <t># of % selected</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Etendue</t>
+          <t># de % sélectionné</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVD3</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grouped</t>
+          <t>(filtered from _MAX_)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Groupée</t>
+          <t>(filtré de _MAX_)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NVD3</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Re-scale y-axis</t>
+          <t>&lt;</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rééchelonner l'axe y</t>
+          <t>&lt;</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NVD3</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stacked</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Empilée</t>
+          <t>&lt;=</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NVD3</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stream</t>
+          <t>=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Flux</t>
+          <t>=</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>!=</t>
+          <t>&gt;</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>!=</t>
+          <t>&gt;</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t># of % selected</t>
+          <t>&gt;=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t># de % sélectionné</t>
+          <t>&gt;=</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(filtered from _MAX_)</t>
+          <t>A value is required for</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(filtré de _MAX_)</t>
+          <t>Une valeur est requise pour</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>&lt;</t>
+          <t>Tout</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>All selected</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>Tout est sélectionné</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>and</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>et</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>&gt;</t>
+          <t>Auto Fit columns</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>&gt;</t>
+          <t>Ajustement automatique des colonnes</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>&gt;=</t>
+          <t>Auto Scroll enabled</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>&gt;=</t>
+          <t>Défilement automatique</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A value is required for</t>
+          <t>Average of</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Une valeur est requise pour</t>
+          <t>Moyenne de</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Back to top</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tout</t>
+          <t>Retour en haut</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>All selected</t>
+          <t>Between</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tout est sélectionné</t>
+          <t>Dans l'intervalle</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>et</t>
+          <t>Annuler</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Auto Fit columns</t>
+          <t>Cancelling report...</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ajustement automatique des colonnes</t>
+          <t>Annulation...</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Auto Scroll enabled</t>
+          <t>Charts</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Défilement automatique</t>
+          <t>Graphes</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Average of</t>
+          <t>Clear selection</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Moyenne de</t>
+          <t>Effacer la sélection</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Back to top</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Retour en haut</t>
+          <t>Fermer</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Between</t>
+          <t>Contains</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Dans l'intervalle</t>
+          <t>Contient</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Contains all</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Annuler</t>
+          <t>Contient tout</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cancelling report...</t>
+          <t>Contains any</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Annulation...</t>
+          <t>Contient au moins</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Charts</t>
+          <t>Count Distinct of</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Graphes</t>
+          <t>Nombre distinct de</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Clear selection</t>
+          <t>Count of</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Effacer la sélection</t>
+          <t>Nombre de</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Decrement</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fermer</t>
+          <t>Décrémenter</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Contains</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Contient</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Contains all</t>
+          <t>Display header footer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Contient tout</t>
+          <t>Afficher l'en-tête et le pied de page</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Contains any</t>
+          <t>Display: Execution messages</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Contient au moins</t>
+          <t>Affichage : Messages d'exécution</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Count Distinct of</t>
+          <t>Display: Execution messages</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Nombre distinct de</t>
+          <t>Affichage : Messages d'exécution</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Count of</t>
+          <t>Display: Information messages</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Nombre de</t>
+          <t>Affichage : Messages d'information</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Decrement</t>
+          <t>Display: Information messages</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Décrémenter</t>
+          <t>Affichage : Messages d'information</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Does not contain</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Ne contient pas</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Display header footer</t>
+          <t>Does not contain all</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Afficher l'en-tête et le pied de page</t>
+          <t>Ne contient pas tout</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Display: Execution messages</t>
+          <t>Does not contain any</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Affichage : Messages d'exécution</t>
+          <t>Ne contient pas au moins</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Display: Execution messages</t>
+          <t>Drill &lt;</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Affichage : Messages d'exécution</t>
+          <t>Navigation &lt;</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Display: Information messages</t>
+          <t>Drill &gt;</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Affichage : Messages d'information</t>
+          <t>Navigation &gt;</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Display: Information messages</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Affichage : Messages d'information</t>
+          <t>Durée</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Does not contain</t>
+          <t>Duration (seconds)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ne contient pas</t>
+          <t>Durée (secondes)</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Does not contain all</t>
+          <t>Email sent to '{0}'</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ne contient pas tout</t>
+          <t>Courriel envoyé à '{0}'</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Does not contain any</t>
+          <t>Ends with</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ne contient pas au moins</t>
+          <t>Se termine par</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Drill &lt;</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Navigation &lt;</t>
+          <t>Egale</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Drill &gt;</t>
+          <t>Execute</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Navigation &gt;</t>
+          <t>Exécuter</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Executing report...</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Durée</t>
+          <t>Exécution...</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Duration (seconds)</t>
+          <t>Execution date</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Durée (secondes)</t>
+          <t>Date d'exécution</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Email sent to '{0}'</t>
+          <t>Execution duration</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Courriel envoyé à '{0}'</t>
+          <t>Durée d'exécution</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ends with</t>
+          <t>execution messages</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Se termine par</t>
+          <t>les messages d'exécution</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Equals</t>
+          <t>Export messages...</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Egale</t>
+          <t>Exporter les messages...</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Execute</t>
+          <t>Filter:</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Exécuter</t>
+          <t>Filtre:</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Executing report...</t>
+          <t>Go to today</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Exécution...</t>
+          <t>Aujourd'hui</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Execution date</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Date d'exécution</t>
+          <t>But</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Execution duration</t>
+          <t>Hide</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Durée d'exécution</t>
+          <t>Cacher</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>execution messages</t>
+          <t>HTML Print: Show messages</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>les messages d'exécution</t>
+          <t>Impression HTML : Afficher les messages</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Export messages...</t>
+          <t>HTML Print: Show messages</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Exporter les messages...</t>
+          <t>Impression HTML : Afficher les messages</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Filter:</t>
+          <t>HTML Print: Show report information</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Filtre:</t>
+          <t>Impression HTML : Afficher les informations du rapport</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Go to today</t>
+          <t>HTML Print: Show report information</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Aujourd'hui</t>
+          <t>Impression HTML : Afficher les informations du rapport</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>HTML to PDF</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>But</t>
+          <t>HTML en PDF</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hide</t>
+          <t>Increment</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cacher</t>
+          <t>Incrémenter</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HTML Print: Show messages</t>
+          <t>Information panel enabled</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Impression HTML : Afficher les messages</t>
+          <t>Panneau d'information activé</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HTML Print: Show messages</t>
+          <t>Information panel enabled and shown</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Impression HTML : Afficher les messages</t>
+          <t>Panneau d'information activé et affiché</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HTML Print: Show report information</t>
+          <t>Information panel hidden</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Impression HTML : Afficher les informations du rapport</t>
+          <t>Panneau d'information masqué</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HTML Print: Show report information</t>
+          <t>Invalid date</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Impression HTML : Afficher les informations du rapport</t>
+          <t>Date invalide</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HTML to PDF</t>
+          <t>Invalid numeric value</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>HTML en PDF</t>
+          <t>Valeur numérique invalide</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Increment</t>
+          <t>Is between</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Incrémenter</t>
+          <t>Est entre</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Information panel enabled</t>
+          <t>Is Blank</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Panneau d'information activé</t>
+          <t>Est vide</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Information panel enabled and shown</t>
+          <t>Is different from</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Panneau d'information activé et affiché</t>
+          <t>Est différent de</t>
         </is>
       </c>
     </row>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Information panel hidden</t>
+          <t>Is empty</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Panneau d'information masqué</t>
+          <t>Est vide</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2140,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Invalid date</t>
+          <t>Is greater or equal than</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Date invalide</t>
+          <t>Est plus grand ou égal à</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Invalid numeric value</t>
+          <t>Is greater than</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Valeur numérique invalide</t>
+          <t>Est plus grand que</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Is between</t>
+          <t>Is not between</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Est entre</t>
+          <t>N'est pas entre</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Is Blank</t>
+          <t>Is Not Blank</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Est vide</t>
+          <t>N'est pas vide</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Is different from</t>
+          <t>Is not empty</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Est différent de</t>
+          <t>N'est pas vide</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Is empty</t>
+          <t>Is not Null</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Est vide</t>
+          <t>N'est pas Null</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Is greater or equal than</t>
+          <t>Is Null</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Est plus grand ou égal à</t>
+          <t>Est Null</t>
         </is>
       </c>
     </row>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Is greater than</t>
+          <t>Is smaller or equal than</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Est plus grand que</t>
+          <t>Est plus petit ou égal à</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Is not between</t>
+          <t>Is smaller than</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>N'est pas entre</t>
+          <t>Est plus petit que</t>
         </is>
       </c>
     </row>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Is Not Blank</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>N'est pas vide</t>
+          <t>Paysage</t>
         </is>
       </c>
     </row>
@@ -2310,12 +2310,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Is not empty</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>N'est pas vide</t>
+          <t>Journal</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Is not Null</t>
+          <t>Maximum of</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>N'est pas Null</t>
+          <t>Maximum de</t>
         </is>
       </c>
     </row>
@@ -2344,12 +2344,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Is Null</t>
+          <t>Messages panel enabled</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Est Null</t>
+          <t>Panneau de messages activé</t>
         </is>
       </c>
     </row>
@@ -2361,12 +2361,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Is smaller or equal than</t>
+          <t>Messages panel enabled and shown</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Est plus petit ou égal à</t>
+          <t>Panneau de messages activé et affiché</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2378,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Is smaller than</t>
+          <t>Messages panel enabled and shown only during execution</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Est plus petit que</t>
+          <t>Panneau de messages activé et affiché uniquement pendant l'exécution</t>
         </is>
       </c>
     </row>
@@ -2395,12 +2395,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Landscape</t>
+          <t>Messages panel hidden</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Paysage</t>
+          <t>Panneau de messages masqué</t>
         </is>
       </c>
     </row>
@@ -2412,12 +2412,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Logs</t>
+          <t>Minimum of</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Journal</t>
+          <t>Minimum de</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Maximum of</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Maximum de</t>
+          <t>Modèle</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Messages panel enabled</t>
+          <t>Model loaded...</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Panneau de messages activé</t>
+          <t>Modèle chargé</t>
         </is>
       </c>
     </row>
@@ -2463,12 +2463,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Messages panel enabled and shown</t>
+          <t>Models loaded...</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Panneau de messages activé et affiché</t>
+          <t>Modèles chargés</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Messages panel enabled and shown only during execution</t>
+          <t>New report</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Panneau de messages activé et affiché uniquement pendant l'exécution</t>
+          <t>Nouveau rapport</t>
         </is>
       </c>
     </row>
@@ -2497,12 +2497,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Messages panel hidden</t>
+          <t>Next Century</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Panneau de messages masqué</t>
+          <t>Siècle suivant</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Minimum of</t>
+          <t>Next Decade</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Minimum de</t>
+          <t>Décennie suivante</t>
         </is>
       </c>
     </row>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Next Month</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Modèle</t>
+          <t>Mois suivant</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Model loaded...</t>
+          <t>Next Year</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Modèle chargé</t>
+          <t>Année suivante</t>
         </is>
       </c>
     </row>
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Models loaded...</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Modèles chargés</t>
+          <t>Non</t>
         </is>
       </c>
     </row>
@@ -2582,12 +2582,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>New report</t>
+          <t>No records</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Nouveau rapport</t>
+          <t>Aucun enregistrement</t>
         </is>
       </c>
     </row>
@@ -2599,12 +2599,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Next Century</t>
+          <t>No records. The report output generation has been cancelled.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Siècle suivant</t>
+          <t>Aucun enregistrement. La  génération a été annulée.</t>
         </is>
       </c>
     </row>
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Next Decade</t>
+          <t>No reports</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Décennie suivante</t>
+          <t>Pas de rapports</t>
         </is>
       </c>
     </row>
@@ -2633,12 +2633,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Next Month</t>
+          <t>No rows</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Mois suivant</t>
+          <t>Pas de lignes</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Next Year</t>
+          <t>Not Between</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Année suivante</t>
+          <t>En dehors de l'intervalle</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Contains</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Ne contient pas</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>No records</t>
+          <t>Now</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Aucun enregistrement</t>
+          <t>Maintenant</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2701,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>No records. The report output generation has been cancelled.</t>
+          <t>Options</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Aucun enregistrement. La  génération a été annulée.</t>
+          <t>Options</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>No reports</t>
+          <t>or</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Pas de rapports</t>
+          <t>ou</t>
         </is>
       </c>
     </row>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>No rows</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Pas de lignes</t>
+          <t>Page</t>
         </is>
       </c>
     </row>
@@ -2752,12 +2752,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Not Between</t>
+          <t>Page &amp;p; of &amp;P;</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>En dehors de l'intervalle</t>
+          <t>Page &amp;p; de &amp;P;</t>
         </is>
       </c>
     </row>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Not Contains</t>
+          <t>Page orientation</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Ne contient pas</t>
+          <t>Orientation de la page</t>
         </is>
       </c>
     </row>
@@ -2786,12 +2786,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Now</t>
+          <t>Page size</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Maintenant</t>
+          <t>Taille de la page</t>
         </is>
       </c>
     </row>
@@ -2803,12 +2803,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Options</t>
+          <t>Pages</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Options</t>
+          <t>Pages</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>Pick Hour</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ou</t>
+          <t>Heure</t>
         </is>
       </c>
     </row>
@@ -2837,12 +2837,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Pick Minute</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Minute</t>
         </is>
       </c>
     </row>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Page &amp;p; of &amp;P;</t>
+          <t>Pick Second</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Page &amp;p; de &amp;P;</t>
+          <t>Seconde</t>
         </is>
       </c>
     </row>
@@ -2871,12 +2871,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Page orientation</t>
+          <t>Please enter a value</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Orientation de la page</t>
+          <t>Veuillez entrer une valeur</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Page size</t>
+          <t>Please enter at least a value</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Taille de la page</t>
+          <t>Veuillez entrer au moins une valeur</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t>Please find the report '{0}' in attachment.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Pages</t>
+          <t xml:space="preserve">Veuillez trouver le rapport '{0}' en attachement. </t>
         </is>
       </c>
     </row>
@@ -2922,12 +2922,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Pick Hour</t>
+          <t>Please find your authentication code</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Heure</t>
+          <t>Veuillez trouver votre code pour la connexion</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Pick Minute</t>
+          <t>Please wait, the report result is being generated in another window</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Minute</t>
+          <t>Veuillez patienter, votre rapport est en train d'être généré dans une autre fenêtre</t>
         </is>
       </c>
     </row>
@@ -2956,12 +2956,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Pick Second</t>
+          <t>Previous Century</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Seconde</t>
+          <t>Siècle précédent</t>
         </is>
       </c>
     </row>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Please enter a value</t>
+          <t>Previous Decade</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Veuillez entrer une valeur</t>
+          <t>Décennie précédente</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Please enter at least a value</t>
+          <t>Previous Month</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Veuillez entrer au moins une valeur</t>
+          <t>Mois précédent</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Please find the report '{0}' in attachment.</t>
+          <t>Previous Year</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Veuillez trouver le rapport '{0}' en attachement. </t>
+          <t>Année précédente</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Please find your authentication code</t>
+          <t>Print: Page orientation</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Veuillez trouver votre code pour la connexion</t>
+          <t>Impression : Orientation de la page</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Please wait, the report result is being generated in another window</t>
+          <t>Print: Show logo</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Veuillez patienter, votre rapport est en train d'être généré dans une autre fenêtre</t>
+          <t>Impression : Afficher le logo</t>
         </is>
       </c>
     </row>
@@ -3058,12 +3058,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Previous Century</t>
+          <t>Processing</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Siècle précédent</t>
+          <t>En cours</t>
         </is>
       </c>
     </row>
@@ -3075,12 +3075,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Previous Decade</t>
+          <t>Processing...</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Décennie précédente</t>
+          <t>En cours…</t>
         </is>
       </c>
     </row>
@@ -3092,12 +3092,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Previous Month</t>
+          <t>Records</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mois précédent</t>
+          <t>Enregistrements</t>
         </is>
       </c>
     </row>
@@ -3109,12 +3109,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Previous Year</t>
+          <t>Refresh</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Année précédente</t>
+          <t>Rafraîchir</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Print: Page orientation</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Impression : Orientation de la page</t>
+          <t>Rapport</t>
         </is>
       </c>
     </row>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Print: Show logo</t>
+          <t>Report description</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Impression : Afficher le logo</t>
+          <t>Description du rapport</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Report has been cancelled</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>En cours</t>
+          <t>Le rapport a été annulé</t>
         </is>
       </c>
     </row>
@@ -3177,12 +3177,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Processing...</t>
+          <t>report information</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>En cours…</t>
+          <t>les informations</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Records</t>
+          <t>report restrictions</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Enregistrements</t>
+          <t>les restrictions du rapport</t>
         </is>
       </c>
     </row>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Refresh</t>
+          <t>Report result generated in '{0}'</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Rafraîchir</t>
+          <t>Rapport généré dans  '{0}'</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Report result options</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Rapport</t>
+          <t>Options du résultat du rapport</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Report description</t>
+          <t>report result panel</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Description du rapport</t>
+          <t>le panneau des résultats</t>
         </is>
       </c>
     </row>
@@ -3262,12 +3262,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Report has been cancelled</t>
+          <t>Report summary</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Le rapport a été annulé</t>
+          <t>Résumé du rapport</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3279,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>report information</t>
+          <t>Restrictions</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>les informations</t>
+          <t>Restrictions</t>
         </is>
       </c>
     </row>
@@ -3296,12 +3296,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>report restrictions</t>
+          <t>Results</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>les restrictions du rapport</t>
+          <t>Résultats</t>
         </is>
       </c>
     </row>
@@ -3313,12 +3313,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Report result generated in '{0}'</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Rapport généré dans  '{0}'</t>
+          <t>Échelle</t>
         </is>
       </c>
     </row>
@@ -3330,12 +3330,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Report result options</t>
+          <t>second</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Options du résultat du rapport</t>
+          <t>seconde</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>report result panel</t>
+          <t>seconds</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>le panneau des résultats</t>
+          <t>secondes</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Report summary</t>
+          <t>Select all</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Résumé du rapport</t>
+          <t>Tout</t>
         </is>
       </c>
     </row>
@@ -3381,12 +3381,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Restrictions</t>
+          <t>Select Decade</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Restrictions</t>
+          <t>Sélectionner la décennie</t>
         </is>
       </c>
     </row>
@@ -3398,12 +3398,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Results</t>
+          <t>Select Month</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Résultats</t>
+          <t>Sélectionner le mois</t>
         </is>
       </c>
     </row>
@@ -3415,12 +3415,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Select Time</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Échelle</t>
+          <t>Sélectionner l'heure</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>second</t>
+          <t>Select Year</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>seconde</t>
+          <t>Sélectionner l'année</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>Show</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>secondes</t>
+          <t>Montrer</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Select all</t>
+          <t>Show _MENU_ reports</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Tout</t>
+          <t>Afficher _MENU_ rapports</t>
         </is>
       </c>
     </row>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Select Decade</t>
+          <t>Show _MENU_ rows</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Sélectionner la décennie</t>
+          <t>Afficher _MENU_ lignes</t>
         </is>
       </c>
     </row>
@@ -3500,12 +3500,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Select Month</t>
+          <t>Show messages</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Sélectionner le mois</t>
+          <t>Afficher les messages</t>
         </is>
       </c>
     </row>
@@ -3517,12 +3517,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Select Time</t>
+          <t>Show messages</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Sélectionner l'heure</t>
+          <t>Afficher les messages</t>
         </is>
       </c>
     </row>
@@ -3534,12 +3534,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Select Year</t>
+          <t>Show report information</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Sélectionner l'année</t>
+          <t>Afficher les informations du rapport</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Show</t>
+          <t>Show report information</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Montrer</t>
+          <t>Afficher les informations du rapport</t>
         </is>
       </c>
     </row>
@@ -3568,12 +3568,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Show _MENU_ reports</t>
+          <t>Show/Hide Restrictions</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Afficher _MENU_ rapports</t>
+          <t>Afficher/Cacher les restrictions</t>
         </is>
       </c>
     </row>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Show _MENU_ rows</t>
+          <t>Showing _START_ to _END_ of _TOTAL_</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Afficher _MENU_ lignes</t>
+          <t>Affichage de _START_ à _END_ sur _TOTAL_</t>
         </is>
       </c>
     </row>
@@ -3602,12 +3602,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Show messages</t>
+          <t>Showing 0 to 0 of 0</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Afficher les messages</t>
+          <t>Affichage de 0 à 0 sur 0</t>
         </is>
       </c>
     </row>
@@ -3619,12 +3619,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Show messages</t>
+          <t>Starting execution...</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Afficher les messages</t>
+          <t>Exécution...</t>
         </is>
       </c>
     </row>
@@ -3636,12 +3636,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Show report information</t>
+          <t>Starts with</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Afficher les informations du rapport</t>
+          <t>Commence par</t>
         </is>
       </c>
     </row>
@@ -3653,12 +3653,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Show report information</t>
+          <t>Subtotal</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Afficher les informations du rapport</t>
+          <t>Sous-total</t>
         </is>
       </c>
     </row>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Show/Hide Restrictions</t>
+          <t>Sum of</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Afficher/Cacher les restrictions</t>
+          <t>Somme de</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Showing _START_ to _END_ of _TOTAL_</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Affichage de _START_ à _END_ sur _TOTAL_</t>
+          <t>Sommaire</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Showing 0 to 0 of 0</t>
+          <t>Table of Contents</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Affichage de 0 à 0 sur 0</t>
+          <t>Sommaire</t>
         </is>
       </c>
     </row>
@@ -3721,12 +3721,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Starting execution...</t>
+          <t>Tabs to show</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Exécution...</t>
+          <t>Onglets visibles</t>
         </is>
       </c>
     </row>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Starts with</t>
+          <t>Task executed...</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Commence par</t>
+          <t>Tâche exécutée</t>
         </is>
       </c>
     </row>
@@ -3755,12 +3755,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Subtotal</t>
+          <t>Tasks executed...</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Sous-total</t>
+          <t>Tâches exécutées</t>
         </is>
       </c>
     </row>
@@ -3772,12 +3772,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Sum of</t>
+          <t>The report has been generated.</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Somme de</t>
+          <t>Le rapport a été généré.</t>
         </is>
       </c>
     </row>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>This report has execution errors. Please check details in the Logs Files...</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Sommaire</t>
+          <t>Ce rapport a des erreurs d'exécutions. Veuillez consulter les détails dans les journaux.</t>
         </is>
       </c>
     </row>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Table of Contents</t>
+          <t>ThisHour</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Sommaire</t>
+          <t>CetteHeure</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Tabs to show</t>
+          <t>ThisMinute</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Onglets visibles</t>
+          <t>CetteMinute</t>
         </is>
       </c>
     </row>
@@ -3840,12 +3840,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Task executed...</t>
+          <t>ThisMonth</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Tâche exécutée</t>
+          <t>CeMois</t>
         </is>
       </c>
     </row>
@@ -3857,12 +3857,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Tasks executed...</t>
+          <t>ThisQuarter</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Tâches exécutées</t>
+          <t>CeTrimestre</t>
         </is>
       </c>
     </row>
@@ -3874,12 +3874,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>The report has been generated.</t>
+          <t>ThisSemester</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Le rapport a été généré.</t>
+          <t>CeSemestre</t>
         </is>
       </c>
     </row>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>This report has execution errors. Please check details in the Logs Files...</t>
+          <t>ThisWeek</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Ce rapport a des erreurs d'exécutions. Veuillez consulter les détails dans les journaux.</t>
+          <t>CetteSemaine</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ThisHour</t>
+          <t>ThisYear</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>CetteHeure</t>
+          <t>CetteAnnée</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ThisMinute</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>CetteMinute</t>
+          <t>Aujourdhui</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ThisMonth</t>
+          <t>Toggle Period</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>CeMois</t>
+          <t>Changer la période</t>
         </is>
       </c>
     </row>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ThisQuarter</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>CeTrimestre</t>
+          <t>Total</t>
         </is>
       </c>
     </row>
@@ -3976,12 +3976,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ThisSemester</t>
+          <t>Use the date format '{0}' or one of the following keywords:</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>CeSemestre</t>
+          <t>Utiliser le format de date '{0}' ou bien l'un des mots clés suivants:</t>
         </is>
       </c>
     </row>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ThisWeek</t>
+          <t>View</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>CetteSemaine</t>
+          <t>Vue</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4010,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ThisYear</t>
+          <t>View CSV Result</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>CetteAnnée</t>
+          <t>Afficher le résultat CSV</t>
         </is>
       </c>
     </row>
@@ -4027,12 +4027,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>View Excel Converter Result</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Aujourdhui</t>
+          <t>Afficher le résultat Conversion Excel</t>
         </is>
       </c>
     </row>
@@ -4044,12 +4044,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Toggle Period</t>
+          <t>View Excel Result</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Changer la période</t>
+          <t>Afficher le résultat Excel</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4061,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>View HTML Print Result</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Afficher le résultat Impression HTML</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Use the date format '{0}' or one of the following keywords:</t>
+          <t>View HTML Result</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Utiliser le format de date '{0}' ou bien l'un des mots clés suivants:</t>
+          <t>Afficher le résultat HTML</t>
         </is>
       </c>
     </row>
@@ -4095,12 +4095,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>View HTML to PDF Result</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Vue</t>
+          <t>Afficher le résultat HTML en PDF</t>
         </is>
       </c>
     </row>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>View CSV Result</t>
+          <t>View Json Result</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Afficher le résultat CSV</t>
+          <t>Afficher le résultat Json</t>
         </is>
       </c>
     </row>
@@ -4129,12 +4129,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>View Excel Converter Result</t>
+          <t>View PDF Converter Result</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Afficher le résultat Conversion Excel</t>
+          <t>Afficher le résultat Conversion PDF</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>View Excel Result</t>
+          <t>View PDF Result</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Afficher le résultat Excel</t>
+          <t>Afficher le résultat PDF</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>View HTML Print Result</t>
+          <t>View report result file</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Afficher le résultat Impression HTML</t>
+          <t>Afficher le résultat du rapport</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>View HTML Result</t>
+          <t>View Text Result</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Afficher le résultat HTML</t>
+          <t>Afficher le résultat Texte</t>
         </is>
       </c>
     </row>
@@ -4197,12 +4197,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>View HTML to PDF Result</t>
+          <t>View XML Result</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Afficher le résultat HTML en PDF</t>
+          <t>Afficher le résultat XML</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>View Json Result</t>
+          <t>Warning: The maximum number of records is reached</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Afficher le résultat Json</t>
+          <t>Attention: Le nombre maximum d'enregistrements est atteint</t>
         </is>
       </c>
     </row>
@@ -4231,114 +4231,114 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>View PDF Converter Result</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Afficher le résultat Conversion PDF</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>View PDF Result</t>
+          <t>Add</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Afficher le résultat PDF</t>
+          <t>Ajouter</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>View report result file</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Afficher le résultat du rapport</t>
+          <t>Tout</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>View Text Result</t>
+          <t>Auto-Refresh (seconds)</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Afficher le résultat Texte</t>
+          <t>Actualiser (secondes)</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>View XML Result</t>
+          <t>Assistants</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Afficher le résultat XML</t>
+          <t>Assistants</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Warning: The maximum number of records is reached</t>
+          <t>Back to login with user name and password</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Attention: Le nombre maximum d'enregistrements est atteint</t>
+          <t>Retour à la connexion avec nom d'utilisateur et mot de passe</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Annuler</t>
         </is>
       </c>
     </row>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Ajouter</t>
+          <t>Modifier le mot de passe</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Tout</t>
+          <t>Modifier le mot de passe</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Auto-Refresh (seconds)</t>
+          <t>Change your password</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Actualiser (secondes)</t>
+          <t>Changez votre mot de passe</t>
         </is>
       </c>
     </row>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Assistants</t>
+          <t>Chart sort</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Assistants</t>
+          <t>Tri graphe</t>
         </is>
       </c>
     </row>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Back to login with user name and password</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Retour à la connexion avec nom d'utilisateur et mot de passe</t>
+          <t>Fermer</t>
         </is>
       </c>
     </row>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Annuler</t>
+          <t>Couleur</t>
         </is>
       </c>
     </row>
@@ -4452,12 +4452,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Confirm your new password</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Modifier le mot de passe</t>
+          <t>Confirmez votre nouveau mot de passe</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Change password</t>
+          <t>Configuration and security</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Modifier le mot de passe</t>
+          <t>Configuration et sécurité</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Change your password</t>
+          <t>Copy</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Changez votre mot de passe</t>
+          <t>Copier</t>
         </is>
       </c>
     </row>
@@ -4503,12 +4503,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Chart sort</t>
+          <t>Create in folder</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Tri graphe</t>
+          <t>Créer dans le répertoire</t>
         </is>
       </c>
     </row>
@@ -4520,12 +4520,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Create new folder</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Fermer</t>
+          <t>Créer un répertoire</t>
         </is>
       </c>
     </row>
@@ -4537,12 +4537,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>CSS Format</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Couleur</t>
+          <t>Format CSS</t>
         </is>
       </c>
     </row>
@@ -4554,12 +4554,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Confirm your new password</t>
+          <t>Culture</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Confirmez votre nouveau mot de passe</t>
+          <t>Culture</t>
         </is>
       </c>
     </row>
@@ -4571,12 +4571,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Configuration and security</t>
+          <t>Current password</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Configuration et sécurité</t>
+          <t>Mot de passe actuel</t>
         </is>
       </c>
     </row>
@@ -4588,12 +4588,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Copy</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Copier</t>
+          <t>Couper</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Create in folder</t>
+          <t>Data source connections</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Créer dans le répertoire</t>
+          <t>Connexions des sources de données</t>
         </is>
       </c>
     </row>
@@ -4622,12 +4622,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Create new folder</t>
+          <t>Default view</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Créer un répertoire</t>
+          <t>Vue par défaut</t>
         </is>
       </c>
     </row>
@@ -4639,12 +4639,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>CSS Format</t>
+          <t>Delete</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Format CSS</t>
+          <t>Supprimer</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4656,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Delete folder</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Supprimer le répertoire</t>
         </is>
       </c>
     </row>
@@ -4673,12 +4673,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Current password</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Mot de passe actuel</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
@@ -4690,12 +4690,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Cut</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Couper</t>
+          <t>Périphérique</t>
         </is>
       </c>
     </row>
@@ -4707,12 +4707,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Data source connections</t>
+          <t>Disconnect</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Connexions des sources de données</t>
+          <t>Déconnecter</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Default view</t>
+          <t>Display options</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Vue par défaut</t>
+          <t>Options d'affichage</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Delete</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Supprimer</t>
+          <t>Editer</t>
         </is>
       </c>
     </row>
@@ -4758,12 +4758,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Delete folder</t>
+          <t>Edit configuration</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Supprimer le répertoire</t>
+          <t>Editer la configuration</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Edit entry</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Modifier un enregistrement</t>
         </is>
       </c>
     </row>
@@ -4792,12 +4792,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Edit profile</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Périphérique</t>
+          <t>Editer le profil</t>
         </is>
       </c>
     </row>
@@ -4809,12 +4809,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Disconnect</t>
+          <t>Edition</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Déconnecter</t>
+          <t>Edition</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Display options</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Options d'affichage</t>
+          <t>Courriel</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Enter password</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Editer</t>
+          <t>Entrer le mot de passe</t>
         </is>
       </c>
     </row>
@@ -4860,12 +4860,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Edit configuration</t>
+          <t>Enter user name</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Editer la configuration</t>
+          <t>Entrer le nom d'utilisateur</t>
         </is>
       </c>
     </row>
@@ -4877,12 +4877,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Edit entry</t>
+          <t>Enter your current password</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Modifier un enregistrement</t>
+          <t>Entrez votre mot de passe actuel</t>
         </is>
       </c>
     </row>
@@ -4894,12 +4894,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Edit profile</t>
+          <t>Enter your new file name</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Editer le profil</t>
+          <t>Entrer un nouveau nom de fichier</t>
         </is>
       </c>
     </row>
@@ -4911,12 +4911,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Edition</t>
+          <t>Enter your new password</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Edition</t>
+          <t>Entrez votre nouveau mot de passe</t>
         </is>
       </c>
     </row>
@@ -4928,12 +4928,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Enter your security code</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Courriel</t>
+          <t>Entrer votre code de sécurité</t>
         </is>
       </c>
     </row>
@@ -4945,12 +4945,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Enter password</t>
+          <t>Enter your user identifier or email</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Entrer le mot de passe</t>
+          <t>Entrez votre identifiant ou votre e-mail</t>
         </is>
       </c>
     </row>
@@ -4962,12 +4962,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Enter user name</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Entrer le nom d'utilisateur</t>
+          <t>Erreur</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4979,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Enter your current password</t>
+          <t>Error: only files (and not reports) can be copied to this folder.</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Entrez votre mot de passe actuel</t>
+          <t>Erreur: Seulement les fichiers (et non les rapports) peuvent être copiés dans ce répertoire.</t>
         </is>
       </c>
     </row>
@@ -4996,12 +4996,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Enter your new file name</t>
+          <t>Error: the destination file name contains invalid characters.</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Entrer un nouveau nom de fichier</t>
+          <t>Erreur: Le nom du fichier destination contient des caractères invalides.</t>
         </is>
       </c>
     </row>
@@ -5013,12 +5013,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Enter your new password</t>
+          <t>Error: the destination folder name contains invalid characters.</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Entrez votre nouveau mot de passe</t>
+          <t>Erreur: Le nom du répertoire destination contient des caractères invalides.</t>
         </is>
       </c>
     </row>
@@ -5030,12 +5030,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Enter your security code</t>
+          <t>Expand in Treeview</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Entrer votre code de sécurité</t>
+          <t>Ouvrir dans le Treeview</t>
         </is>
       </c>
     </row>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Enter your user identifier or email</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Entrez votre identifiant ou votre e-mail</t>
+          <t>Exporter</t>
         </is>
       </c>
     </row>
@@ -5064,12 +5064,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Files only</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Erreur</t>
+          <t>Fichiers uniquement</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Error: only files (and not reports) can be copied to this folder.</t>
+          <t>Folder Permissions</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Erreur: Seulement les fichiers (et non les rapports) peuvent être copiés dans ce répertoire.</t>
+          <t>Droits des répertoires</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Error: the destination file name contains invalid characters.</t>
+          <t>Folders</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Erreur: Le nom du fichier destination contient des caractères invalides.</t>
+          <t>Répertoire</t>
         </is>
       </c>
     </row>
@@ -5115,12 +5115,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Error: the destination folder name contains invalid characters.</t>
+          <t>Forget your password ?</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Erreur: Le nom du répertoire destination contient des caractères invalides.</t>
+          <t>Mot de passe oublié ?</t>
         </is>
       </c>
     </row>
@@ -5132,12 +5132,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Expand in Treeview</t>
+          <t>Group name</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Ouvrir dans le Treeview</t>
+          <t>Nom du groupe</t>
         </is>
       </c>
     </row>
@@ -5149,12 +5149,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Group name</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Exporter</t>
+          <t>Nom du groupe</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5166,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Files only</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Fichiers uniquement</t>
+          <t>Groupes</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Folder Permissions</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Droits des répertoires</t>
+          <t>Groupes</t>
         </is>
       </c>
     </row>
@@ -5200,12 +5200,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Folders</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Répertoire</t>
+          <t>Hauteur</t>
         </is>
       </c>
     </row>
@@ -5217,12 +5217,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Forget your password ?</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Mot de passe oublié ?</t>
+          <t>Icône</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Group name</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Nom du groupe</t>
+          <t>Information</t>
         </is>
       </c>
     </row>
@@ -5251,12 +5251,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Group name</t>
+          <t>Invalid security code</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Nom du groupe</t>
+          <t>Code sécurité invalide</t>
         </is>
       </c>
     </row>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Invalid user name or password</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Groupes</t>
+          <t>Utilisateur ou mot de passe invalide</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Is dynamic</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Groupes</t>
+          <t>Dynamique</t>
         </is>
       </c>
     </row>
@@ -5302,12 +5302,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Last execution at</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Hauteur</t>
+          <t>Dernière exécution à</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Licensed to</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Icône</t>
+          <t>Licence pour</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Connexion</t>
         </is>
       </c>
     </row>
@@ -5353,12 +5353,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Invalid security code</t>
+          <t>Login ID</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Code sécurité invalide</t>
+          <t>Identifiant utilisateur</t>
         </is>
       </c>
     </row>
@@ -5370,12 +5370,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Invalid user name or password</t>
+          <t>Logins</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Utilisateur ou mot de passe invalide</t>
+          <t>Utilisateurs</t>
         </is>
       </c>
     </row>
@@ -5387,12 +5387,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Is dynamic</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Dynamique</t>
+          <t>Déconnexion</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Last execution at</t>
+          <t>Logout the user</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Dernière exécution à</t>
+          <t>Déconnecte l'utilisateur</t>
         </is>
       </c>
     </row>
@@ -5421,12 +5421,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Licensed to</t>
+          <t>Manage Folders</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Licence pour</t>
+          <t>Gérer les répertoires</t>
         </is>
       </c>
     </row>
@@ -5438,12 +5438,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Manage sub-folders</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Connexion</t>
+          <t>Gérer les sous-répertoires</t>
         </is>
       </c>
     </row>
@@ -5455,12 +5455,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Login ID</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Identifiant utilisateur</t>
+          <t>Nom</t>
         </is>
       </c>
     </row>
@@ -5472,12 +5472,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Logins</t>
+          <t>New</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Utilisateurs</t>
+          <t>Nouveau</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5489,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Logout</t>
+          <t>New folder name</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Déconnexion</t>
+          <t>Nouveau répertoire</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Logout the user</t>
+          <t>New folder path</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Déconnecte l'utilisateur</t>
+          <t>Nouveau chemin du répertoire</t>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Manage Folders</t>
+          <t>New password</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Gérer les répertoires</t>
+          <t>Nouveau mot de passe</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Manage sub-folders</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Gérer les sous-répertoires</t>
+          <t>Aucun</t>
         </is>
       </c>
     </row>
@@ -5557,12 +5557,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Nom</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>On startup</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Nouveau</t>
+          <t>Au démarrage</t>
         </is>
       </c>
     </row>
@@ -5591,12 +5591,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>New folder name</t>
+          <t>Optional chart title</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Nouveau répertoire</t>
+          <t>Titre optionnel du graphe</t>
         </is>
       </c>
     </row>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>New folder path</t>
+          <t>Optional menu name</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Nouveau chemin du répertoire</t>
+          <t>Nom optionnel du menu</t>
         </is>
       </c>
     </row>
@@ -5625,12 +5625,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>New password</t>
+          <t>Output</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Nouveau mot de passe</t>
+          <t>Destination</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Aucun</t>
+          <t>Mot de passe</t>
         </is>
       </c>
     </row>
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Paste</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Coller</t>
         </is>
       </c>
     </row>
@@ -5676,12 +5676,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>On startup</t>
+          <t>PDF Conversion delay</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Au démarrage</t>
+          <t>Délai pour la conversion PDF</t>
         </is>
       </c>
     </row>
@@ -5693,12 +5693,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Optional chart title</t>
+          <t>Personal</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Titre optionnel du graphe</t>
+          <t>Personnel</t>
         </is>
       </c>
     </row>
@@ -5710,12 +5710,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Optional menu name</t>
+          <t>Personal folder</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Nom optionnel du menu</t>
+          <t>Répertoire personnel</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5727,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Destination</t>
+          <t>Téléphone</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Please wait</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Mot de passe</t>
+          <t>Veuillez patienter</t>
         </is>
       </c>
     </row>
@@ -5761,12 +5761,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Paste</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Coller</t>
+          <t>Profil</t>
         </is>
       </c>
     </row>
@@ -5778,12 +5778,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PDF Conversion delay</t>
+          <t>Profile information</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Délai pour la conversion PDF</t>
+          <t>Profil utilisateur</t>
         </is>
       </c>
     </row>
@@ -5795,12 +5795,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Refresh</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Personnel</t>
+          <t>Rafraîchir</t>
         </is>
       </c>
     </row>
@@ -5812,12 +5812,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Personal folder</t>
+          <t>Re-init your password</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Répertoire personnel</t>
+          <t>Réinitialisez votre mot de passe</t>
         </is>
       </c>
     </row>
@@ -5829,12 +5829,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Reload and execute</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Téléphone</t>
+          <t>Recharger et exécuter</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Please wait</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Veuillez patienter</t>
+          <t>Renommer</t>
         </is>
       </c>
     </row>
@@ -5863,12 +5863,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Rename or move folder</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Profil</t>
+          <t>Renommer ou déplacer le répertoire</t>
         </is>
       </c>
     </row>
@@ -5880,12 +5880,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Profile information</t>
+          <t>Rename, move or copy</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Profil utilisateur</t>
+          <t>Renommer, déplacer ou copier</t>
         </is>
       </c>
     </row>
@@ -5897,12 +5897,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Refresh</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Rafraîchir</t>
+          <t>Rapport</t>
         </is>
       </c>
     </row>
@@ -5914,12 +5914,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Re-init your password</t>
+          <t>Report execution mode</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Réinitialisez votre mot de passe</t>
+          <t>Mode d'exécution des rapports</t>
         </is>
       </c>
     </row>
@@ -5931,12 +5931,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Reload and execute</t>
+          <t>Report name</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Recharger et exécuter</t>
+          <t>Nom du rapport</t>
         </is>
       </c>
     </row>
@@ -5948,12 +5948,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Report title</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Renommer</t>
+          <t>Titre du rapport</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Rename or move folder</t>
+          <t>Report title if different from report name</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Renommer ou déplacer le répertoire</t>
+          <t>Titre du rapport si différent du nom</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Rename, move or copy</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Renommer, déplacer ou copier</t>
+          <t>Rapports</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Reports menu</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Rapport</t>
+          <t>Menu des rapports</t>
         </is>
       </c>
     </row>
@@ -6016,12 +6016,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Report execution mode</t>
+          <t>Repository connection</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Mode d'exécution des rapports</t>
+          <t>Connexion du Repository</t>
         </is>
       </c>
     </row>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Report name</t>
+          <t>Reset password</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Nom du rapport</t>
+          <t>Réinitialiser le mot de passe</t>
         </is>
       </c>
     </row>
@@ -6050,12 +6050,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Report title</t>
+          <t>Reset your password</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Titre du rapport</t>
+          <t>Réinitialisez votre mot de passe</t>
         </is>
       </c>
     </row>
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Report title if different from report name</t>
+          <t>Rights</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Titre du rapport si différent du nom</t>
+          <t>Droits</t>
         </is>
       </c>
     </row>
@@ -6084,12 +6084,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Rapports</t>
+          <t>Enregistrer</t>
         </is>
       </c>
     </row>
@@ -6101,12 +6101,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Reports menu</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Menu des rapports</t>
+          <t>Rechercher</t>
         </is>
       </c>
     </row>
@@ -6118,12 +6118,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Repository connection</t>
+          <t>Security code</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Connexion du Repository</t>
+          <t>Code de sécurité</t>
         </is>
       </c>
     </row>
@@ -6135,12 +6135,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Reset password</t>
+          <t>Show sub-folders</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Réinitialiser le mot de passe</t>
+          <t>Montrer les sous-répertoires</t>
         </is>
       </c>
     </row>
@@ -6152,12 +6152,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Reset your password</t>
+          <t>Startup report name</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Réinitialisez votre mot de passe</t>
+          <t>Nom du rapport au démarrage</t>
         </is>
       </c>
     </row>
@@ -6169,12 +6169,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Rights</t>
+          <t>The favorite has been updated</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Droits</t>
+          <t>Le favori a été mis à jour</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Two-Factor Authentication</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Enregistrer</t>
+          <t>Authentification 2-Facteurs</t>
         </is>
       </c>
     </row>
@@ -6203,12 +6203,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Rechercher</t>
+          <t>Type</t>
         </is>
       </c>
     </row>
@@ -6220,12 +6220,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Security code</t>
+          <t>Type a new password</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Code de sécurité</t>
+          <t>Entrez un nouveau mot de passe</t>
         </is>
       </c>
     </row>
@@ -6237,12 +6237,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Show sub-folders</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Montrer les sous-répertoires</t>
+          <t>Charger</t>
         </is>
       </c>
     </row>
@@ -6254,12 +6254,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Startup report name</t>
+          <t>User groups</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Nom du rapport au démarrage</t>
+          <t>Groupes utilisateur</t>
         </is>
       </c>
     </row>
@@ -6271,12 +6271,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>The favorite has been updated</t>
+          <t>User identifier or email</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Le favori a été mis à jour</t>
+          <t>Identifiant ou e-mail</t>
         </is>
       </c>
     </row>
@@ -6288,12 +6288,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Two-Factor Authentication</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Authentification 2-Facteurs</t>
+          <t>Nom d'utilisateur</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Utilisateurs</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6322,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Type a new password</t>
+          <t>Web product name</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Entrez un nouveau mot de passe</t>
+          <t>Nom du produit Web</t>
         </is>
       </c>
     </row>
@@ -6339,114 +6339,114 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Upload</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Charger</t>
+          <t>Largueur</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>User groups</t>
+          <t># of % selected</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Groupes utilisateur</t>
+          <t># de % sélectionné</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>User identifier or email</t>
+          <t>Actions</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Identifiant ou e-mail</t>
+          <t>Actions</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>All selected</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Nom d'utilisateur</t>
+          <t>Tout est sélectionné</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>Allow only execution in a new window</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Utilisateurs</t>
+          <t>Autoriser seulement l'exécution dans une nouvelle fenêtre</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Web product name</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Nom du produit Web</t>
+          <t>Annuler</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Configuration for</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Largueur</t>
+          <t>Configuration pour</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t># of % selected</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t># de % sélectionné</t>
+          <t>Configuration</t>
         </is>
       </c>
     </row>
@@ -6475,12 +6475,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Contains</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Contient</t>
         </is>
       </c>
     </row>
@@ -6492,12 +6492,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>All selected</t>
+          <t>Contains all</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Tout est sélectionné</t>
+          <t>Contient tout</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Allow only execution in a new window</t>
+          <t>Contains any</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Autoriser seulement l'exécution dans une nouvelle fenêtre</t>
+          <t>Contient au moins</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Copy</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Annuler</t>
+          <t>Copie</t>
         </is>
       </c>
     </row>
@@ -6543,12 +6543,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Configuration for</t>
+          <t>Copy of</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Configuration pour</t>
+          <t>Copie de</t>
         </is>
       </c>
     </row>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Copy to</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Copier vers</t>
         </is>
       </c>
     </row>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Contains</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Contient</t>
+          <t>Défaut</t>
         </is>
       </c>
     </row>
@@ -6594,12 +6594,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Contains all</t>
+          <t>Default culture</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Contient tout</t>
+          <t>Culture par défaut</t>
         </is>
       </c>
     </row>
@@ -6611,12 +6611,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Contains any</t>
+          <t>Default mode</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Contient au moins</t>
+          <t>Mode par défaut</t>
         </is>
       </c>
     </row>
@@ -6628,12 +6628,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Copy</t>
+          <t>Default report connection</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Copie</t>
+          <t>Connexion du rapport</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Copy of</t>
+          <t>Default repository connection</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Copie de</t>
+          <t>Connexion du repository</t>
         </is>
       </c>
     </row>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Copy to</t>
+          <t>Default startup</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Copier vers</t>
+          <t>Démarrage par défaut</t>
         </is>
       </c>
     </row>
@@ -6679,12 +6679,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Do not execute report</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Défaut</t>
+          <t>Ne pas exécuter de rapport</t>
         </is>
       </c>
     </row>
@@ -6696,12 +6696,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Default culture</t>
+          <t>Do you really want to delete the reports or files selected ?</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Culture par défaut</t>
+          <t>Voulez-vous vraiment effacer les rapports et fichiers sélectionnés ?</t>
         </is>
       </c>
     </row>
@@ -6713,12 +6713,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Default mode</t>
+          <t>Does not contain</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Mode par défaut</t>
+          <t>Ne contient pas</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Default report connection</t>
+          <t>Does not contain all</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Connexion du rapport</t>
+          <t>Ne contient pas tout</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Default repository connection</t>
+          <t>Does not contain any</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Connexion du repository</t>
+          <t>Ne contient pas au moins</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Default startup</t>
+          <t>Download report</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Démarrage par défaut</t>
+          <t>Télécharger le rapport</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Do not execute report</t>
+          <t>Edit report</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Ne pas exécuter de rapport</t>
+          <t>Editer le rapport</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Do you really want to delete the reports or files selected ?</t>
+          <t>Edit reports / Manage files</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Voulez-vous vraiment effacer les rapports et fichiers sélectionnés ?</t>
+          <t>Modifier les rapports / Gérer les fichiers</t>
         </is>
       </c>
     </row>
@@ -6815,12 +6815,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Does not contain</t>
+          <t>Edit schedules / View files</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Ne contient pas</t>
+          <t>Modifier les planifications / Voir les fichiers</t>
         </is>
       </c>
     </row>
@@ -6832,12 +6832,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Does not contain all</t>
+          <t>Ends with</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Ne contient pas tout</t>
+          <t>Se termine par</t>
         </is>
       </c>
     </row>
@@ -6849,12 +6849,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Does not contain any</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Ne contient pas au moins</t>
+          <t>Egale</t>
         </is>
       </c>
     </row>
@@ -6866,12 +6866,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Download report</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Télécharger le rapport</t>
+          <t>Erreur</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Edit report</t>
+          <t>Execute report in a new window</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Editer le rapport</t>
+          <t>Exécuter le rapport dans une nouvelle fenêtre</t>
         </is>
       </c>
     </row>
@@ -6900,12 +6900,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Edit reports / Manage files</t>
+          <t>Execute report in the current window</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Modifier les rapports / Gérer les fichiers</t>
+          <t>Exécuter le rapport dans la fenêtre en cours</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Edit schedules / View files</t>
+          <t>Execute reports / View files</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Modifier les planifications / Voir les fichiers</t>
+          <t>Exécuter les rapports / Voir les fichiers</t>
         </is>
       </c>
     </row>
@@ -6934,12 +6934,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Ends with</t>
+          <t>Execute reports and outputs / View files</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Se termine par</t>
+          <t>Exécuter les rapports et les sorties / Voir les fichiers</t>
         </is>
       </c>
     </row>
@@ -6951,12 +6951,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Equals</t>
+          <t>Execute the last report</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Egale</t>
+          <t>Exécuter le dernier rapport</t>
         </is>
       </c>
     </row>
@@ -6968,12 +6968,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Execute the report</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Erreur</t>
+          <t>Exécuter le rapport</t>
         </is>
       </c>
     </row>
@@ -6985,12 +6985,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Execute report in a new window</t>
+          <t>Favorites</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Exécuter le rapport dans une nouvelle fenêtre</t>
+          <t>Favoris</t>
         </is>
       </c>
     </row>
@@ -7002,12 +7002,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Execute report in the current window</t>
+          <t>Folder</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Exécuter le rapport dans la fenêtre en cours</t>
+          <t>Répertoire</t>
         </is>
       </c>
     </row>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Execute reports / View files</t>
+          <t>Is between</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Exécuter les rapports / Voir les fichiers</t>
+          <t>Est entre</t>
         </is>
       </c>
     </row>
@@ -7036,12 +7036,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Execute reports and outputs / View files</t>
+          <t>Is different from</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Exécuter les rapports et les sorties / Voir les fichiers</t>
+          <t>Est différent de</t>
         </is>
       </c>
     </row>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Execute the last report</t>
+          <t>Is empty</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Exécuter le dernier rapport</t>
+          <t>Est vide</t>
         </is>
       </c>
     </row>
@@ -7070,12 +7070,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Execute the report</t>
+          <t>Is greater or equal than</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Exécuter le rapport</t>
+          <t>Est plus grand ou égal à</t>
         </is>
       </c>
     </row>
@@ -7087,12 +7087,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Favorites</t>
+          <t>Is greater than</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Favoris</t>
+          <t>Est plus grand que</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Folder</t>
+          <t>Is not between</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Répertoire</t>
+          <t>N'est pas entre</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Is between</t>
+          <t>Is not empty</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Est entre</t>
+          <t>N'est pas vide</t>
         </is>
       </c>
     </row>
@@ -7138,12 +7138,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Is different from</t>
+          <t>Is not Null</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Est différent de</t>
+          <t>N'est pas Null</t>
         </is>
       </c>
     </row>
@@ -7155,12 +7155,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Is empty</t>
+          <t>Is Null</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Est vide</t>
+          <t>Est Null</t>
         </is>
       </c>
     </row>
@@ -7172,12 +7172,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Is greater or equal than</t>
+          <t>Is smaller or equal than</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Est plus grand ou égal à</t>
+          <t>Est plus petit ou égal à</t>
         </is>
       </c>
     </row>
@@ -7189,12 +7189,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Is greater than</t>
+          <t>Is smaller than</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Est plus grand que</t>
+          <t>Est plus petit que</t>
         </is>
       </c>
     </row>
@@ -7206,12 +7206,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Is not between</t>
+          <t>Last modification</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>N'est pas entre</t>
+          <t>Dernière modification</t>
         </is>
       </c>
     </row>
@@ -7223,12 +7223,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Is not empty</t>
+          <t>Mark as favorite</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>N'est pas vide</t>
+          <t>Mettre en favori</t>
         </is>
       </c>
     </row>
@@ -7240,12 +7240,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Is not Null</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>N'est pas Null</t>
+          <t>Modèle</t>
         </is>
       </c>
     </row>
@@ -7257,12 +7257,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Is Null</t>
+          <t>New folder configuration</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Est Null</t>
+          <t>Nouvelle configuration de dossier</t>
         </is>
       </c>
     </row>
@@ -7274,12 +7274,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Is smaller or equal than</t>
+          <t>New group</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Est plus petit ou égal à</t>
+          <t>Nouveau groupe</t>
         </is>
       </c>
     </row>
@@ -7291,12 +7291,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Is smaller than</t>
+          <t>New login</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Est plus petit que</t>
+          <t>Nouvel utilisateur</t>
         </is>
       </c>
     </row>
@@ -7308,12 +7308,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Last modification</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Dernière modification</t>
+          <t>Non</t>
         </is>
       </c>
     </row>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Mark as favorite</t>
+          <t>No download (except files) or upload</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Mettre en favori</t>
+          <t>Pas de téléchargement (sauf fichiers) ni de téléversement</t>
         </is>
       </c>
     </row>
@@ -7342,12 +7342,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>No folder configuration</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Modèle</t>
+          <t>Aucune configuration de dossier</t>
         </is>
       </c>
     </row>
@@ -7359,12 +7359,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>New folder configuration</t>
+          <t>No login</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Nouvelle configuration de dossier</t>
+          <t>Aucun utilisateur</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>New group</t>
+          <t>No personal folder</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Nouveau groupe</t>
+          <t>Aucun dossier personnel</t>
         </is>
       </c>
     </row>
@@ -7393,12 +7393,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>New login</t>
+          <t>No right</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Nouvel utilisateur</t>
+          <t>Aucun droit</t>
         </is>
       </c>
     </row>
@@ -7410,12 +7410,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Aucun</t>
         </is>
       </c>
     </row>
@@ -7427,12 +7427,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>No download (except files) or upload</t>
+          <t>Not sorted</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Pas de téléchargement (sauf fichiers) ni de téléversement</t>
+          <t>Pas de tri</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>No folder configuration</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Aucune configuration de dossier</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>No login</t>
+          <t>Options</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Aucun utilisateur</t>
+          <t>Options</t>
         </is>
       </c>
     </row>
@@ -7478,12 +7478,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>No personal folder</t>
+          <t>Output</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Aucun dossier personnel</t>
+          <t>Destination</t>
         </is>
       </c>
     </row>
@@ -7495,12 +7495,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>No right</t>
+          <t>Personal folder for files only</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Aucun droit</t>
+          <t>Dossier personnel uniquement pour les fichiers</t>
         </is>
       </c>
     </row>
@@ -7512,12 +7512,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Personal folder for reports and files</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Aucun</t>
+          <t>Dossier personnel pour les rapports et les fichiers</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7529,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Not sorted</t>
+          <t>Please wait</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Pas de tri</t>
+          <t>Veuillez patienter</t>
         </is>
       </c>
     </row>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Processing</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>En cours</t>
         </is>
       </c>
     </row>
@@ -7563,12 +7563,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Options</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Options</t>
+          <t>Profil</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Recents</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Destination</t>
+          <t>Récents</t>
         </is>
       </c>
     </row>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Personal folder for files only</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Dossier personnel uniquement pour les fichiers</t>
+          <t>Rapport</t>
         </is>
       </c>
     </row>
@@ -7614,12 +7614,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Personal folder for reports and files</t>
+          <t>report(s) or file(s) cut in the clipboard</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Dossier personnel pour les rapports et les fichiers</t>
+          <t>rapport(s) ou fichier(s) ont été coupés dans le presse-papier</t>
         </is>
       </c>
     </row>
@@ -7631,12 +7631,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Please wait</t>
+          <t>report(s) or file(s) have been deleted</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Veuillez patienter</t>
+          <t>rapport(s) ou fichier(s) ont été effacés</t>
         </is>
       </c>
     </row>
@@ -7648,12 +7648,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>report(s) or file(s) processed</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>En cours</t>
+          <t>rapport(s) ou fichier(s) ont été traités</t>
         </is>
       </c>
     </row>
@@ -7665,12 +7665,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>report(s) or files(s) copied in the clipboard</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Profil</t>
+          <t>rapport(s) ou fichier(s) ont été copiés dans le presse-papier</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Recents</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Récents</t>
+          <t>Rapports</t>
         </is>
       </c>
     </row>
@@ -7699,12 +7699,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Rapport</t>
+          <t>Planification</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>report(s) or file(s) cut in the clipboard</t>
+          <t>Server Version</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>rapport(s) ou fichier(s) ont été coupés dans le presse-papier</t>
+          <t>Version du serveur</t>
         </is>
       </c>
     </row>
@@ -7733,12 +7733,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>report(s) or file(s) have been deleted</t>
+          <t>Show _MENU_ reports</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>rapport(s) ou fichier(s) ont été effacés</t>
+          <t>Afficher _MENU_ rapports</t>
         </is>
       </c>
     </row>
@@ -7750,12 +7750,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>report(s) or file(s) processed</t>
+          <t>Starts with</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>rapport(s) ou fichier(s) ont été traités</t>
+          <t>Commence par</t>
         </is>
       </c>
     </row>
@@ -7767,12 +7767,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>report(s) or files(s) copied in the clipboard</t>
+          <t>The configuration has been saved. Please login again if you are impacted by the security.</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>rapport(s) ou fichier(s) ont été copiés dans le presse-papier</t>
+          <t>La configuration a été enregistrée. Veuillez vous reconnecter si vous êtes concerné par la sécurité.</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>The folder has been created</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Rapports</t>
+          <t>Le répertoire a été créé</t>
         </is>
       </c>
     </row>
@@ -7801,12 +7801,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>The folder has been deleted</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Planification</t>
+          <t>Le répertoire a été effacé</t>
         </is>
       </c>
     </row>
@@ -7818,12 +7818,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Server Version</t>
+          <t>The folder has been renamed</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Version du serveur</t>
+          <t>Le répertoire a été renommé</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Show _MENU_ reports</t>
+          <t>The folder has been updated</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Afficher _MENU_ rapports</t>
+          <t>Le répertoire a été mis à jour</t>
         </is>
       </c>
     </row>
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Starts with</t>
+          <t>The report or file has been renamed</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Commence par</t>
+          <t>Le rapport ou le fichier a été renommé</t>
         </is>
       </c>
     </row>
@@ -7869,12 +7869,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>The configuration has been saved. Please login again if you are impacted by the security.</t>
+          <t>Toggle Report or Folders view</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>La configuration a été enregistrée. Veuillez vous reconnecter si vous êtes concerné par la sécurité.</t>
+          <t>Voir le rapport ou les répertoires</t>
         </is>
       </c>
     </row>
@@ -7886,12 +7886,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>The folder has been created</t>
+          <t>Unexpected error on server</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Le répertoire a été créé</t>
+          <t>Erreur sur le serveur</t>
         </is>
       </c>
     </row>
@@ -7903,12 +7903,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>The folder has been deleted</t>
+          <t>User can download reports</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Le répertoire a été effacé</t>
+          <t>L'utilisateur peut télécharger les rapports</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>The folder has been renamed</t>
+          <t>User can download reports and upload reports and files</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Le répertoire a été renommé</t>
+          <t>L'utilisateur peut télécharger les rapports et téléverser des rapports et des fichiers</t>
         </is>
       </c>
     </row>
@@ -7937,12 +7937,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>The folder has been updated</t>
+          <t>View</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Le répertoire a été mis à jour</t>
+          <t>Vue</t>
         </is>
       </c>
     </row>
@@ -7954,12 +7954,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>The report or file has been renamed</t>
+          <t>View Folders</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Le rapport ou le fichier a été renommé</t>
+          <t>Voir les répertoires</t>
         </is>
       </c>
     </row>
@@ -7971,12 +7971,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Toggle Report or Folders view</t>
+          <t>View Report</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Voir le rapport ou les répertoires</t>
+          <t>Voir le rapport</t>
         </is>
       </c>
     </row>
@@ -7988,12 +7988,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Unexpected error on server</t>
+          <t>View reports</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Erreur sur le serveur</t>
+          <t>Voir les rapports</t>
         </is>
       </c>
     </row>
@@ -8005,12 +8005,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>User can download reports</t>
+          <t>Views and outputs</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>L'utilisateur peut télécharger les rapports</t>
+          <t>Vues et destinations</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>User can download reports and upload reports and files</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>L'utilisateur peut télécharger les rapports et téléverser des rapports et des fichiers</t>
+          <t>Avertissement</t>
         </is>
       </c>
     </row>
@@ -8039,12 +8039,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Web Interface Version</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Vue</t>
+          <t>Version de l'interface Web</t>
         </is>
       </c>
     </row>
@@ -8056,12 +8056,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>View Folders</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Voir les répertoires</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -8073,12 +8073,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>View Report</t>
+          <t>Yes (Folder is expanded in the tree view)</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Voir le rapport</t>
+          <t>Oui (Le dossier est ouvert dans l'arborescence)</t>
         </is>
       </c>
     </row>
@@ -8090,12 +8090,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>View reports</t>
+          <t>Yes (Only files can be stored)</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Voir les rapports</t>
+          <t>Oui (Seuls les fichiers peuvent être stockés)</t>
         </is>
       </c>
     </row>
@@ -8107,12 +8107,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Views and outputs</t>
+          <t>Yes (User can browse sub-folders)</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Vues et destinations</t>
+          <t>Oui (L'utilisateur peut parcourir les sous-dossiers)</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Yes (User can create and edit sub-folders)</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Avertissement</t>
+          <t>Oui (L'utilisateur peut créer et modifier des sous-dossiers)</t>
         </is>
       </c>
     </row>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Web Interface Version</t>
+          <t>Yes (User can edit his profile)</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Version de l'interface Web</t>
+          <t>Oui (L'utilisateur peut modifier son profil)</t>
         </is>
       </c>
     </row>
@@ -8158,114 +8158,114 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (User is administrator of the Web Server)</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Oui (L'utilisateur est administrateur du serveur Web)</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Yes (Folder is expanded in the tree view)</t>
+          <t>Select assistant</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Oui (Le dossier est ouvert dans l'arborescence)</t>
+          <t>Sélectionner l'assistant</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Yes (Only files can be stored)</t>
+          <t>Mark as favorite</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Oui (Seuls les fichiers peuvent être stockés)</t>
+          <t>Mettre en favori</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Yes (User can browse sub-folders)</t>
+          <t>Favorites</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Oui (L'utilisateur peut parcourir les sous-dossiers)</t>
+          <t>Favoris</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Yes (User can create and edit sub-folders)</t>
+          <t>No favorites yet</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Oui (L'utilisateur peut créer et modifier des sous-dossiers)</t>
+          <t>Aucun favori pour le moment</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Yes (User can edit his profile)</t>
+          <t>Recent</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Oui (L'utilisateur peut modifier son profil)</t>
+          <t>Récents</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Yes (User is administrator of the Web Server)</t>
+          <t>No recent items</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Oui (L'utilisateur est administrateur du serveur Web)</t>
+          <t>Aucun élément récent</t>
         </is>
       </c>
     </row>
@@ -8277,12 +8277,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Select assistant</t>
+          <t>New conversation</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Sélectionner l'assistant</t>
+          <t>Nouvelle conversation</t>
         </is>
       </c>
     </row>
@@ -8294,12 +8294,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Mark as favorite</t>
+          <t>Sample prompts</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Mettre en favori</t>
+          <t>Exemples de prompts</t>
         </is>
       </c>
     </row>
@@ -8311,12 +8311,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Favorites</t>
+          <t>Sample Prompts</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Favoris</t>
+          <t>Exemples de prompts</t>
         </is>
       </c>
     </row>
@@ -8328,12 +8328,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>No favorites yet</t>
+          <t>No sample prompts defined</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Aucun favori pour le moment</t>
+          <t>Aucun exemple de prompt défini</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8345,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Recent</t>
+          <t>AI Assistant</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Récents</t>
+          <t>Assistant IA</t>
         </is>
       </c>
     </row>
@@ -8362,12 +8362,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>No recent items</t>
+          <t>Favorites &amp; Recent</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Aucun élément récent</t>
+          <t>Favoris et récents</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>New conversation</t>
+          <t>Hide panel</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Nouvelle conversation</t>
+          <t>Masquer le panneau</t>
         </is>
       </c>
     </row>
@@ -8396,12 +8396,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Sample prompts</t>
+          <t>Ask the AI agent…</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Exemples de prompts</t>
+          <t>Posez une question à l'agent IA…</t>
         </is>
       </c>
     </row>
@@ -8413,12 +8413,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Sample Prompts</t>
+          <t>Confirm Deletion</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Exemples de prompts</t>
+          <t>Confirmer la suppression</t>
         </is>
       </c>
     </row>
@@ -8430,12 +8430,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>No sample prompts defined</t>
+          <t>This action is irreversible. Are you sure you want to delete this item?</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Aucun exemple de prompt défini</t>
+          <t>Cette action est irréversible. Voulez-vous vraiment supprimer cet élément ?</t>
         </is>
       </c>
     </row>
@@ -8447,12 +8447,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>AI Assistant</t>
+          <t>Data Source</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Assistant IA</t>
+          <t>Source de données</t>
         </is>
       </c>
     </row>
@@ -8464,12 +8464,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Favorites &amp; Recent</t>
+          <t>Report Assistants</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Favoris et récents</t>
+          <t>Assistants de rapport</t>
         </is>
       </c>
     </row>
@@ -8481,12 +8481,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Hide panel</t>
+          <t>Select Tables or Views</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Masquer le panneau</t>
+          <t>Sélectionner les tables ou les vues</t>
         </is>
       </c>
     </row>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Ask the AI agent…</t>
+          <t>Filter tables...</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Posez une question à l'agent IA…</t>
+          <t>Filtrer les tables...</t>
         </is>
       </c>
     </row>
@@ -8515,12 +8515,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Confirm Deletion</t>
+          <t>Select All</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Confirmer la suppression</t>
+          <t>Tout sélectionner</t>
         </is>
       </c>
     </row>
@@ -8532,12 +8532,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>This action is irreversible. Are you sure you want to delete this item?</t>
+          <t>Deselect All</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Cette action est irréversible. Voulez-vous vraiment supprimer cet élément ?</t>
+          <t>Tout désélectionner</t>
         </is>
       </c>
     </row>
@@ -8549,12 +8549,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Data Source</t>
+          <t>tables selected</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Source de données</t>
+          <t>tables sélectionnées</t>
         </is>
       </c>
     </row>
@@ -8566,12 +8566,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Report Assistants</t>
+          <t>Prompt Shortcuts</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Assistants de rapport</t>
+          <t>Raccourcis de prompts</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Select Tables or Views</t>
+          <t>How can Seal AI help you today ?</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Sélectionner les tables ou les vues</t>
+          <t>Comment Seal AI peut-il vous aider aujourd'hui ?</t>
         </is>
       </c>
     </row>
@@ -8600,12 +8600,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Filter tables...</t>
+          <t>No current items available</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Filtrer les tables...</t>
+          <t>Aucun élément courant disponible</t>
         </is>
       </c>
     </row>
@@ -8617,12 +8617,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Select All</t>
+          <t>Current items will appear here when saved</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Tout sélectionner</t>
+          <t>Les éléments courants apparaîtront ici une fois enregistrés</t>
         </is>
       </c>
     </row>
@@ -8634,12 +8634,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Deselect All</t>
+          <t>Drafts</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Tout désélectionner</t>
+          <t>Brouillons</t>
         </is>
       </c>
     </row>
@@ -8651,12 +8651,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>tables selected</t>
+          <t>No draft items available</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>tables sélectionnées</t>
+          <t>Aucun brouillon disponible</t>
         </is>
       </c>
     </row>
@@ -8668,12 +8668,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Prompt Shortcuts</t>
+          <t>Upload files or create new items with the assistant to see them here</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Raccourcis de prompts</t>
+          <t>Téléversez des fichiers ou créez des éléments avec l'assistant pour les voir ici</t>
         </is>
       </c>
     </row>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>How can Seal AI help you today ?</t>
+          <t>Item Details</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Comment Seal AI peut-il vous aider aujourd'hui ?</t>
+          <t>Détails de l'élément</t>
         </is>
       </c>
     </row>
@@ -8702,12 +8702,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>No current items available</t>
+          <t>Loading detail. Please wait...</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Aucun élément courant disponible</t>
+          <t>Chargement des détails. Veuillez patienter...</t>
         </is>
       </c>
     </row>
@@ -8719,12 +8719,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Current items will appear here when saved</t>
+          <t>Select a row from the table to view its details</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Les éléments courants apparaîtront ici une fois enregistrés</t>
+          <t>Sélectionnez une ligne du tableau pour afficher ses détails</t>
         </is>
       </c>
     </row>
@@ -8736,12 +8736,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Drafts</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Brouillons</t>
+          <t>Vérifier</t>
         </is>
       </c>
     </row>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>No draft items available</t>
+          <t>Download</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Aucun brouillon disponible</t>
+          <t>Télécharger</t>
         </is>
       </c>
     </row>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Upload files or create new items with the assistant to see them here</t>
+          <t>Reports Assistant</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Téléversez des fichiers ou créez des éléments avec l'assistant pour les voir ici</t>
+          <t>Assistant de rapports</t>
         </is>
       </c>
     </row>
@@ -8787,12 +8787,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Item Details</t>
+          <t>Connection type</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Détails de l'élément</t>
+          <t>Type de connexion</t>
         </is>
       </c>
     </row>
@@ -8804,12 +8804,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Loading detail. Please wait...</t>
+          <t>Connection string</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Chargement des détails. Veuillez patienter...</t>
+          <t>Chaîne de connexion</t>
         </is>
       </c>
     </row>
@@ -8821,12 +8821,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Select a row from the table to view its details</t>
+          <t>Tables or views</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Sélectionnez une ligne du tableau pour afficher ses détails</t>
+          <t>Tables ou vues</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Report Assistant</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Vérifier</t>
+          <t>Assistant de rapport</t>
         </is>
       </c>
     </row>
@@ -8855,12 +8855,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>AI Provider</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Télécharger</t>
+          <t>Fournisseur IA</t>
         </is>
       </c>
     </row>
@@ -8872,12 +8872,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Reports Assistant</t>
+          <t>AI model</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Assistant de rapports</t>
+          <t>Modèle IA</t>
         </is>
       </c>
     </row>
@@ -8889,12 +8889,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Connection type</t>
+          <t>AI model name (overrides default))</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Type de connexion</t>
+          <t>Nom du modèle IA (remplace la valeur par défaut)</t>
         </is>
       </c>
     </row>
@@ -8906,12 +8906,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Connection string</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Chaîne de connexion</t>
+          <t>Température</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Tables or views</t>
+          <t>Model temperature</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Tables ou vues</t>
+          <t>Température du modèle</t>
         </is>
       </c>
     </row>
@@ -8940,12 +8940,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Report Assistant</t>
+          <t>System prompt</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Assistant de rapport</t>
+          <t>Prompt système</t>
         </is>
       </c>
     </row>
@@ -8957,12 +8957,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>AI Provider</t>
+          <t>Optional sytem prompt for the assistant</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Fournisseur IA</t>
+          <t>Prompt système optionnel pour l'assistant</t>
         </is>
       </c>
     </row>
@@ -8974,12 +8974,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>AI model</t>
+          <t>User prompt</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Modèle IA</t>
+          <t>Prompt utilisateur</t>
         </is>
       </c>
     </row>
@@ -8991,12 +8991,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>AI model name (overrides default))</t>
+          <t>Default user prompts (if empty default values configured are taken)</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Nom du modèle IA (remplace la valeur par défaut)</t>
+          <t>Prompts utilisateur par défaut (si vide, les valeurs par défaut configurées sont utilisées)</t>
         </is>
       </c>
     </row>
@@ -9008,12 +9008,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>User Groups allowed (No selection means no restriction)</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Température</t>
+          <t>Groupes d'utilisateurs autorisés (aucune sélection = aucune restriction)</t>
         </is>
       </c>
     </row>
@@ -9025,12 +9025,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Model temperature</t>
+          <t>Scan options</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Température du modèle</t>
+          <t>Options d'analyse</t>
         </is>
       </c>
     </row>
@@ -9042,12 +9042,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>System prompt</t>
+          <t>When to scan</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Prompt système</t>
+          <t>Quand analyser</t>
         </is>
       </c>
     </row>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Optional sytem prompt for the assistant</t>
+          <t>Cache duration (days)</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Prompt système optionnel pour l'assistant</t>
+          <t>Durée du cache (jours)</t>
         </is>
       </c>
     </row>
@@ -9076,12 +9076,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>User prompt</t>
+          <t>Cache duration (days) for scanned data</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Prompt utilisateur</t>
+          <t>Durée du cache (jours) pour les données analysées</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Default user prompts (if empty default values configured are taken)</t>
+          <t>Tables to scan (no selection means all tables)</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Prompts utilisateur par défaut (si vide, les valeurs par défaut configurées sont utilisées)</t>
+          <t>Tables à analyser (aucune sélection = toutes les tables)</t>
         </is>
       </c>
     </row>
@@ -9110,12 +9110,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>User Groups allowed (No selection means no restriction)</t>
+          <t>Records to scan</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Groupes d'utilisateurs autorisés (aucune sélection = aucune restriction)</t>
+          <t>Enregistrements à analyser</t>
         </is>
       </c>
     </row>
@@ -9127,12 +9127,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Scan options</t>
+          <t>Number of records used for scan</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Options d'analyse</t>
+          <t>Nombre d'enregistrements utilisés pour l'analyse</t>
         </is>
       </c>
     </row>
@@ -9144,12 +9144,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>When to scan</t>
+          <t>Scan Data Now</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Quand analyser</t>
+          <t>Analyser les données maintenant</t>
         </is>
       </c>
     </row>
@@ -9161,12 +9161,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Cache duration (days)</t>
+          <t>Execute</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Durée du cache (jours)</t>
+          <t>Exécuter</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Cache duration (days) for scanned data</t>
+          <t>Elements:</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Durée du cache (jours) pour les données analysées</t>
+          <t>Éléments :</t>
         </is>
       </c>
     </row>
@@ -9195,114 +9195,114 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Tables to scan (no selection means all tables)</t>
+          <t>Restrictions:</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Tables à analyser (aucune sélection = toutes les tables)</t>
+          <t>Restrictions :</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Records to scan</t>
+          <t>Hide AI Assistant</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Enregistrements à analyser</t>
+          <t>Masquer l'assistant IA</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Number of records used for scan</t>
+          <t>AI Assistant</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Nombre d'enregistrements utilisés pour l'analyse</t>
+          <t>Assistant IA</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Scan Data Now</t>
+          <t>Running</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Analyser les données maintenant</t>
+          <t>En cours</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Execute</t>
+          <t>Request cancelled.</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Exécuter</t>
+          <t>Demande annulée.</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Elements:</t>
+          <t>Remove from favorites</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Éléments :</t>
+          <t>Retirer des favoris</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Restrictions:</t>
+          <t>No sample prompts defined</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Restrictions :</t>
+          <t>Aucun exemple de prompt défini</t>
         </is>
       </c>
     </row>
@@ -9314,12 +9314,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Hide AI Assistant</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Masquer l'assistant IA</t>
+          <t>Renommer</t>
         </is>
       </c>
     </row>
@@ -9331,12 +9331,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>AI Assistant</t>
+          <t>Delete</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Assistant IA</t>
+          <t>Supprimer</t>
         </is>
       </c>
     </row>
@@ -9348,12 +9348,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Running</t>
+          <t>No favorites yet</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>En cours</t>
+          <t>Aucun favori pour le moment</t>
         </is>
       </c>
     </row>
@@ -9365,46 +9365,46 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Request cancelled.</t>
+          <t>No recent items</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Demande annulée.</t>
+          <t>Aucun élément récent</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Remove from favorites</t>
+          <t>Download/Upload</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Retirer des favoris</t>
+          <t>Télécharger/Téléverser</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>No sample prompts defined</t>
+          <t>Drag to resize</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Aucun exemple de prompt défini</t>
+          <t>Glisser pour redimensionner</t>
         </is>
       </c>
     </row>
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Copy and paste</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Renommer</t>
+          <t>Copier et coller</t>
         </is>
       </c>
     </row>
@@ -9433,29 +9433,34 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Delete</t>
+          <t>Copy, paste and send</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Supprimer</t>
+          <t>Copier, coller et envoyer</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>No favorites yet</t>
+          <t>BIN</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Recycle Bin</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Aucun favori pour le moment</t>
+          <t>Corbeille</t>
         </is>
       </c>
     </row>
@@ -9467,12 +9472,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>No recent items</t>
+          <t>Rewind to here</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Aucun élément récent</t>
+          <t>Revenir à ce message</t>
         </is>
       </c>
     </row>
@@ -9484,29 +9489,29 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Download/Upload</t>
+          <t>Paste shortcut</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Télécharger/Téléverser</t>
+          <t>Coller le raccourci</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Drag to resize</t>
+          <t>Shortcut to</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Glisser pour redimensionner</t>
+          <t>Raccourci vers</t>
         </is>
       </c>
     </row>
@@ -9518,12 +9523,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Copy and paste</t>
+          <t>Shortcut target not found</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Copier et coller</t>
+          <t>Cible du raccourci introuvable</t>
         </is>
       </c>
     </row>
@@ -9535,117 +9540,10 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Copy, paste and send</t>
+          <t>shortcut(s) created</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
-        <is>
-          <t>Copier, coller et envoyer</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>BIN</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>Recycle Bin</t>
-        </is>
-      </c>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>Corbeille</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>Rewind to here</t>
-        </is>
-      </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>Revenir à ce message</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>Paste shortcut</t>
-        </is>
-      </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>Coller le raccourci</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>Shortcut to</t>
-        </is>
-      </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>Raccourci vers</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>Shortcut target not found</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>Cible du raccourci introuvable</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>shortcut(s) created</t>
-        </is>
-      </c>
-      <c r="D512" t="inlineStr">
         <is>
           <t>raccourci(s) créé(s)</t>
         </is>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D506"/>
+  <dimension ref="A1:D479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Configuration and security</t>
+          <t>Copy</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Configuration et sécurité</t>
+          <t>Copier</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Copy</t>
+          <t>Create in folder</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Copier</t>
+          <t>Créer dans le répertoire</t>
         </is>
       </c>
     </row>
@@ -4503,12 +4503,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Create in folder</t>
+          <t>Create new folder</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Créer dans le répertoire</t>
+          <t>Créer un répertoire</t>
         </is>
       </c>
     </row>
@@ -4520,12 +4520,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Create new folder</t>
+          <t>CSS Format</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Créer un répertoire</t>
+          <t>Format CSS</t>
         </is>
       </c>
     </row>
@@ -4537,12 +4537,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>CSS Format</t>
+          <t>Culture</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Format CSS</t>
+          <t>Culture</t>
         </is>
       </c>
     </row>
@@ -4554,12 +4554,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Current password</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Mot de passe actuel</t>
         </is>
       </c>
     </row>
@@ -4571,12 +4571,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Current password</t>
+          <t>Cut</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Mot de passe actuel</t>
+          <t>Couper</t>
         </is>
       </c>
     </row>
@@ -4588,12 +4588,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Cut</t>
+          <t>Data source connections</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Couper</t>
+          <t>Connexions des sources de données</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Data source connections</t>
+          <t>Default view</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Connexions des sources de données</t>
+          <t>Vue par défaut</t>
         </is>
       </c>
     </row>
@@ -4622,12 +4622,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Default view</t>
+          <t>Delete</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Vue par défaut</t>
+          <t>Supprimer</t>
         </is>
       </c>
     </row>
@@ -4639,12 +4639,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Delete</t>
+          <t>Delete folder</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Supprimer</t>
+          <t>Supprimer le répertoire</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4656,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Delete folder</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Supprimer le répertoire</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
@@ -4673,12 +4673,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Périphérique</t>
         </is>
       </c>
     </row>
@@ -4690,12 +4690,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Disconnect</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Périphérique</t>
+          <t>Déconnecter</t>
         </is>
       </c>
     </row>
@@ -4707,12 +4707,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Disconnect</t>
+          <t>Display options</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Déconnecter</t>
+          <t>Options d'affichage</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Display options</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Options d'affichage</t>
+          <t>Editer</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Edit entry</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Editer</t>
+          <t>Modifier un enregistrement</t>
         </is>
       </c>
     </row>
@@ -4758,12 +4758,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Edit configuration</t>
+          <t>Edition</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Editer la configuration</t>
+          <t>Edition</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Edit entry</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Modifier un enregistrement</t>
+          <t>Courriel</t>
         </is>
       </c>
     </row>
@@ -4792,12 +4792,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Edit profile</t>
+          <t>Enter password</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Editer le profil</t>
+          <t>Entrer le mot de passe</t>
         </is>
       </c>
     </row>
@@ -4809,12 +4809,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Edition</t>
+          <t>Enter user name</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Edition</t>
+          <t>Entrer le nom d'utilisateur</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Enter your current password</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Courriel</t>
+          <t>Entrez votre mot de passe actuel</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Enter password</t>
+          <t>Enter your new file name</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Entrer le mot de passe</t>
+          <t>Entrer un nouveau nom de fichier</t>
         </is>
       </c>
     </row>
@@ -4860,12 +4860,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Enter user name</t>
+          <t>Enter your new password</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Entrer le nom d'utilisateur</t>
+          <t>Entrez votre nouveau mot de passe</t>
         </is>
       </c>
     </row>
@@ -4877,12 +4877,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Enter your current password</t>
+          <t>Enter your security code</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Entrez votre mot de passe actuel</t>
+          <t>Entrer votre code de sécurité</t>
         </is>
       </c>
     </row>
@@ -4894,12 +4894,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Enter your new file name</t>
+          <t>Enter your user identifier or email</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Entrer un nouveau nom de fichier</t>
+          <t>Entrez votre identifiant ou votre e-mail</t>
         </is>
       </c>
     </row>
@@ -4911,12 +4911,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Enter your new password</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Entrez votre nouveau mot de passe</t>
+          <t>Erreur</t>
         </is>
       </c>
     </row>
@@ -4928,12 +4928,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Enter your security code</t>
+          <t>Error: only files (and not reports) can be copied to this folder.</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Entrer votre code de sécurité</t>
+          <t>Erreur: Seulement les fichiers (et non les rapports) peuvent être copiés dans ce répertoire.</t>
         </is>
       </c>
     </row>
@@ -4945,12 +4945,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Enter your user identifier or email</t>
+          <t>Error: the destination file name contains invalid characters.</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Entrez votre identifiant ou votre e-mail</t>
+          <t>Erreur: Le nom du fichier destination contient des caractères invalides.</t>
         </is>
       </c>
     </row>
@@ -4962,12 +4962,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Error: the destination folder name contains invalid characters.</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Erreur</t>
+          <t>Erreur: Le nom du répertoire destination contient des caractères invalides.</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4979,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Error: only files (and not reports) can be copied to this folder.</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Erreur: Seulement les fichiers (et non les rapports) peuvent être copiés dans ce répertoire.</t>
+          <t>Exporter</t>
         </is>
       </c>
     </row>
@@ -4996,12 +4996,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Error: the destination file name contains invalid characters.</t>
+          <t>Folders</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Erreur: Le nom du fichier destination contient des caractères invalides.</t>
+          <t>Répertoire</t>
         </is>
       </c>
     </row>
@@ -5013,12 +5013,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Error: the destination folder name contains invalid characters.</t>
+          <t>Forget your password ?</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Erreur: Le nom du répertoire destination contient des caractères invalides.</t>
+          <t>Mot de passe oublié ?</t>
         </is>
       </c>
     </row>
@@ -5030,12 +5030,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Expand in Treeview</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Ouvrir dans le Treeview</t>
+          <t>Groupes</t>
         </is>
       </c>
     </row>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Exporter</t>
+          <t>Groupes</t>
         </is>
       </c>
     </row>
@@ -5064,12 +5064,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Files only</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Fichiers uniquement</t>
+          <t>Hauteur</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Folder Permissions</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Droits des répertoires</t>
+          <t>Icône</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Folders</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Répertoire</t>
+          <t>Information</t>
         </is>
       </c>
     </row>
@@ -5115,12 +5115,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Forget your password ?</t>
+          <t>Invalid security code</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Mot de passe oublié ?</t>
+          <t>Code sécurité invalide</t>
         </is>
       </c>
     </row>
@@ -5132,12 +5132,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Group name</t>
+          <t>Invalid user name or password</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Nom du groupe</t>
+          <t>Utilisateur ou mot de passe invalide</t>
         </is>
       </c>
     </row>
@@ -5149,12 +5149,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Group name</t>
+          <t>Is dynamic</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Nom du groupe</t>
+          <t>Dynamique</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5166,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Last execution at</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Groupes</t>
+          <t>Dernière exécution à</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Licensed to</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Groupes</t>
+          <t>Licence pour</t>
         </is>
       </c>
     </row>
@@ -5200,12 +5200,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Hauteur</t>
+          <t>Connexion</t>
         </is>
       </c>
     </row>
@@ -5217,12 +5217,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Logins</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Icône</t>
+          <t>Utilisateurs</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Logout</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Déconnexion</t>
         </is>
       </c>
     </row>
@@ -5251,12 +5251,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Invalid security code</t>
+          <t>Logout the user</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Code sécurité invalide</t>
+          <t>Déconnecte l'utilisateur</t>
         </is>
       </c>
     </row>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Invalid user name or password</t>
+          <t>Manage Folders</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Utilisateur ou mot de passe invalide</t>
+          <t>Gérer les répertoires</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Is dynamic</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Dynamique</t>
+          <t>Nom</t>
         </is>
       </c>
     </row>
@@ -5302,12 +5302,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Last execution at</t>
+          <t>New</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Dernière exécution à</t>
+          <t>Nouveau</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Licensed to</t>
+          <t>New folder name</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Licence pour</t>
+          <t>Nouveau répertoire</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>New folder path</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Connexion</t>
+          <t>Nouveau chemin du répertoire</t>
         </is>
       </c>
     </row>
@@ -5353,12 +5353,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Login ID</t>
+          <t>New password</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Identifiant utilisateur</t>
+          <t>Nouveau mot de passe</t>
         </is>
       </c>
     </row>
@@ -5370,12 +5370,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Logins</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Utilisateurs</t>
+          <t>Aucun</t>
         </is>
       </c>
     </row>
@@ -5387,12 +5387,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Logout</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Déconnexion</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Logout the user</t>
+          <t>On startup</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Déconnecte l'utilisateur</t>
+          <t>Au démarrage</t>
         </is>
       </c>
     </row>
@@ -5421,12 +5421,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Manage Folders</t>
+          <t>Optional chart title</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Gérer les répertoires</t>
+          <t>Titre optionnel du graphe</t>
         </is>
       </c>
     </row>
@@ -5438,12 +5438,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Manage sub-folders</t>
+          <t>Optional menu name</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Gérer les sous-répertoires</t>
+          <t>Nom optionnel du menu</t>
         </is>
       </c>
     </row>
@@ -5455,12 +5455,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Output</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Nom</t>
+          <t>Destination</t>
         </is>
       </c>
     </row>
@@ -5472,12 +5472,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Nouveau</t>
+          <t>Mot de passe</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5489,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>New folder name</t>
+          <t>Paste</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Nouveau répertoire</t>
+          <t>Coller</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>New folder path</t>
+          <t>PDF Conversion delay</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Nouveau chemin du répertoire</t>
+          <t>Délai pour la conversion PDF</t>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>New password</t>
+          <t>Personal</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Nouveau mot de passe</t>
+          <t>Personnel</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Aucun</t>
+          <t>Téléphone</t>
         </is>
       </c>
     </row>
@@ -5557,12 +5557,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Please wait</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Veuillez patienter</t>
         </is>
       </c>
     </row>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>On startup</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Au démarrage</t>
+          <t>Profil</t>
         </is>
       </c>
     </row>
@@ -5591,12 +5591,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Optional chart title</t>
+          <t>Profile information</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Titre optionnel du graphe</t>
+          <t>Profil utilisateur</t>
         </is>
       </c>
     </row>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Optional menu name</t>
+          <t>Refresh</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Nom optionnel du menu</t>
+          <t>Rafraîchir</t>
         </is>
       </c>
     </row>
@@ -5625,12 +5625,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>Re-init your password</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Destination</t>
+          <t>Réinitialisez votre mot de passe</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Reload and execute</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Mot de passe</t>
+          <t>Recharger et exécuter</t>
         </is>
       </c>
     </row>
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Paste</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Coller</t>
+          <t>Renommer</t>
         </is>
       </c>
     </row>
@@ -5676,12 +5676,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PDF Conversion delay</t>
+          <t>Rename or move folder</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Délai pour la conversion PDF</t>
+          <t>Renommer ou déplacer le répertoire</t>
         </is>
       </c>
     </row>
@@ -5693,12 +5693,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Rename, move or copy</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Personnel</t>
+          <t>Renommer, déplacer ou copier</t>
         </is>
       </c>
     </row>
@@ -5710,12 +5710,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Personal folder</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Répertoire personnel</t>
+          <t>Rapport</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5727,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Report execution mode</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Téléphone</t>
+          <t>Mode d'exécution des rapports</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Please wait</t>
+          <t>Report name</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Veuillez patienter</t>
+          <t>Nom du rapport</t>
         </is>
       </c>
     </row>
@@ -5761,12 +5761,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>Report title</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Profil</t>
+          <t>Titre du rapport</t>
         </is>
       </c>
     </row>
@@ -5778,12 +5778,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Profile information</t>
+          <t>Report title if different from report name</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Profil utilisateur</t>
+          <t>Titre du rapport si différent du nom</t>
         </is>
       </c>
     </row>
@@ -5795,12 +5795,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Refresh</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Rafraîchir</t>
+          <t>Rapports</t>
         </is>
       </c>
     </row>
@@ -5812,12 +5812,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Re-init your password</t>
+          <t>Reports menu</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Réinitialisez votre mot de passe</t>
+          <t>Menu des rapports</t>
         </is>
       </c>
     </row>
@@ -5829,12 +5829,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Reload and execute</t>
+          <t>Repository connection</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Recharger et exécuter</t>
+          <t>Connexion du Repository</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Rename</t>
+          <t>Reset password</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Renommer</t>
+          <t>Réinitialiser le mot de passe</t>
         </is>
       </c>
     </row>
@@ -5863,12 +5863,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Rename or move folder</t>
+          <t>Reset your password</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Renommer ou déplacer le répertoire</t>
+          <t>Réinitialisez votre mot de passe</t>
         </is>
       </c>
     </row>
@@ -5880,12 +5880,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Rename, move or copy</t>
+          <t>Rights</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Renommer, déplacer ou copier</t>
+          <t>Droits</t>
         </is>
       </c>
     </row>
@@ -5897,12 +5897,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Rapport</t>
+          <t>Enregistrer</t>
         </is>
       </c>
     </row>
@@ -5914,12 +5914,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Report execution mode</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Mode d'exécution des rapports</t>
+          <t>Rechercher</t>
         </is>
       </c>
     </row>
@@ -5931,12 +5931,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Report name</t>
+          <t>Security code</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Nom du rapport</t>
+          <t>Code de sécurité</t>
         </is>
       </c>
     </row>
@@ -5948,12 +5948,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Report title</t>
+          <t>Startup report name</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Titre du rapport</t>
+          <t>Nom du rapport au démarrage</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Report title if different from report name</t>
+          <t>The favorite has been updated</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Titre du rapport si différent du nom</t>
+          <t>Le favori a été mis à jour</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Two-Factor Authentication</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Rapports</t>
+          <t>Authentification 2-Facteurs</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Reports menu</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Menu des rapports</t>
+          <t>Type</t>
         </is>
       </c>
     </row>
@@ -6016,12 +6016,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Repository connection</t>
+          <t>Type a new password</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Connexion du Repository</t>
+          <t>Entrez un nouveau mot de passe</t>
         </is>
       </c>
     </row>
@@ -6033,12 +6033,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Reset password</t>
+          <t>Upload</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Réinitialiser le mot de passe</t>
+          <t>Charger</t>
         </is>
       </c>
     </row>
@@ -6050,12 +6050,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Reset your password</t>
+          <t>User groups</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Réinitialisez votre mot de passe</t>
+          <t>Groupes utilisateur</t>
         </is>
       </c>
     </row>
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Rights</t>
+          <t>User identifier or email</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Droits</t>
+          <t>Identifiant ou e-mail</t>
         </is>
       </c>
     </row>
@@ -6084,12 +6084,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>User name</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Enregistrer</t>
+          <t>Nom d'utilisateur</t>
         </is>
       </c>
     </row>
@@ -6101,12 +6101,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Rechercher</t>
+          <t>Utilisateurs</t>
         </is>
       </c>
     </row>
@@ -6118,233 +6118,233 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Security code</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Code de sécurité</t>
+          <t>Largueur</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Show sub-folders</t>
+          <t># of % selected</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Montrer les sous-répertoires</t>
+          <t># de % sélectionné</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Startup report name</t>
+          <t>Actions</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Nom du rapport au démarrage</t>
+          <t>Actions</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>The favorite has been updated</t>
+          <t>All selected</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Le favori a été mis à jour</t>
+          <t>Tout est sélectionné</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Two-Factor Authentication</t>
+          <t>Allow only execution in a new window</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Authentification 2-Facteurs</t>
+          <t>Autoriser seulement l'exécution dans une nouvelle fenêtre</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Annuler</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Type a new password</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Entrez un nouveau mot de passe</t>
+          <t>Configuration</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Upload</t>
+          <t>Contains</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Charger</t>
+          <t>Contient</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>User groups</t>
+          <t>Contains all</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Groupes utilisateur</t>
+          <t>Contient tout</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>User identifier or email</t>
+          <t>Contains any</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Identifiant ou e-mail</t>
+          <t>Contient au moins</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>User name</t>
+          <t>Copy</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Nom d'utilisateur</t>
+          <t>Copie</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>Copy of</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Utilisateurs</t>
+          <t>Copie de</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Web product name</t>
+          <t>Copy to</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Nom du produit Web</t>
+          <t>Copier vers</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Largueur</t>
+          <t>Défaut</t>
         </is>
       </c>
     </row>
@@ -6356,12 +6356,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t># of % selected</t>
+          <t>Default culture</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t># de % sélectionné</t>
+          <t>Culture par défaut</t>
         </is>
       </c>
     </row>
@@ -6373,12 +6373,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Default mode</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Mode par défaut</t>
         </is>
       </c>
     </row>
@@ -6390,12 +6390,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>All selected</t>
+          <t>Default report connection</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Tout est sélectionné</t>
+          <t>Connexion du rapport</t>
         </is>
       </c>
     </row>
@@ -6407,12 +6407,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Allow only execution in a new window</t>
+          <t>Default repository connection</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Autoriser seulement l'exécution dans une nouvelle fenêtre</t>
+          <t>Connexion du repository</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Default startup</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Annuler</t>
+          <t>Démarrage par défaut</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Configuration for</t>
+          <t>Do not execute report</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Configuration pour</t>
+          <t>Ne pas exécuter de rapport</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Do you really want to delete the reports or files selected ?</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Voulez-vous vraiment effacer les rapports et fichiers sélectionnés ?</t>
         </is>
       </c>
     </row>
@@ -6475,12 +6475,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Contains</t>
+          <t>Does not contain</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Contient</t>
+          <t>Ne contient pas</t>
         </is>
       </c>
     </row>
@@ -6492,12 +6492,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Contains all</t>
+          <t>Does not contain all</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Contient tout</t>
+          <t>Ne contient pas tout</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Contains any</t>
+          <t>Does not contain any</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Contient au moins</t>
+          <t>Ne contient pas au moins</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Copy</t>
+          <t>Download report</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Copie</t>
+          <t>Télécharger le rapport</t>
         </is>
       </c>
     </row>
@@ -6543,12 +6543,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Copy of</t>
+          <t>Edit report</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Copie de</t>
+          <t>Editer le rapport</t>
         </is>
       </c>
     </row>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Copy to</t>
+          <t>Edit reports / Manage files</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Copier vers</t>
+          <t>Modifier les rapports / Gérer les fichiers</t>
         </is>
       </c>
     </row>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Edit schedules / View files</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Défaut</t>
+          <t>Modifier les planifications / Voir les fichiers</t>
         </is>
       </c>
     </row>
@@ -6594,12 +6594,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Default culture</t>
+          <t>Ends with</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Culture par défaut</t>
+          <t>Se termine par</t>
         </is>
       </c>
     </row>
@@ -6611,12 +6611,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Default mode</t>
+          <t>Equals</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Mode par défaut</t>
+          <t>Egale</t>
         </is>
       </c>
     </row>
@@ -6628,12 +6628,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Default report connection</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Connexion du rapport</t>
+          <t>Erreur</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Default repository connection</t>
+          <t>Execute report in a new window</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Connexion du repository</t>
+          <t>Exécuter le rapport dans une nouvelle fenêtre</t>
         </is>
       </c>
     </row>
@@ -6662,12 +6662,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Default startup</t>
+          <t>Execute report in the current window</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Démarrage par défaut</t>
+          <t>Exécuter le rapport dans la fenêtre en cours</t>
         </is>
       </c>
     </row>
@@ -6679,12 +6679,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Do not execute report</t>
+          <t>Execute reports / View files</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Ne pas exécuter de rapport</t>
+          <t>Exécuter les rapports / Voir les fichiers</t>
         </is>
       </c>
     </row>
@@ -6696,12 +6696,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Do you really want to delete the reports or files selected ?</t>
+          <t>Execute reports and outputs / View files</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Voulez-vous vraiment effacer les rapports et fichiers sélectionnés ?</t>
+          <t>Exécuter les rapports et les sorties / Voir les fichiers</t>
         </is>
       </c>
     </row>
@@ -6713,12 +6713,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Does not contain</t>
+          <t>Execute the last report</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Ne contient pas</t>
+          <t>Exécuter le dernier rapport</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Does not contain all</t>
+          <t>Execute the report</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Ne contient pas tout</t>
+          <t>Exécuter le rapport</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Does not contain any</t>
+          <t>Favorites</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Ne contient pas au moins</t>
+          <t>Favoris</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Download report</t>
+          <t>Folder</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Télécharger le rapport</t>
+          <t>Répertoire</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Edit report</t>
+          <t>Is between</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Editer le rapport</t>
+          <t>Est entre</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Edit reports / Manage files</t>
+          <t>Is different from</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Modifier les rapports / Gérer les fichiers</t>
+          <t>Est différent de</t>
         </is>
       </c>
     </row>
@@ -6815,12 +6815,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Edit schedules / View files</t>
+          <t>Is empty</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Modifier les planifications / Voir les fichiers</t>
+          <t>Est vide</t>
         </is>
       </c>
     </row>
@@ -6832,12 +6832,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Ends with</t>
+          <t>Is greater or equal than</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Se termine par</t>
+          <t>Est plus grand ou égal à</t>
         </is>
       </c>
     </row>
@@ -6849,12 +6849,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Equals</t>
+          <t>Is greater than</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Egale</t>
+          <t>Est plus grand que</t>
         </is>
       </c>
     </row>
@@ -6866,12 +6866,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Is not between</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Erreur</t>
+          <t>N'est pas entre</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Execute report in a new window</t>
+          <t>Is not empty</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Exécuter le rapport dans une nouvelle fenêtre</t>
+          <t>N'est pas vide</t>
         </is>
       </c>
     </row>
@@ -6900,12 +6900,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Execute report in the current window</t>
+          <t>Is not Null</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Exécuter le rapport dans la fenêtre en cours</t>
+          <t>N'est pas Null</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Execute reports / View files</t>
+          <t>Is Null</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Exécuter les rapports / Voir les fichiers</t>
+          <t>Est Null</t>
         </is>
       </c>
     </row>
@@ -6934,12 +6934,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Execute reports and outputs / View files</t>
+          <t>Is smaller or equal than</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Exécuter les rapports et les sorties / Voir les fichiers</t>
+          <t>Est plus petit ou égal à</t>
         </is>
       </c>
     </row>
@@ -6951,12 +6951,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Execute the last report</t>
+          <t>Is smaller than</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Exécuter le dernier rapport</t>
+          <t>Est plus petit que</t>
         </is>
       </c>
     </row>
@@ -6968,12 +6968,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Execute the report</t>
+          <t>Last modification</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Exécuter le rapport</t>
+          <t>Dernière modification</t>
         </is>
       </c>
     </row>
@@ -6985,12 +6985,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Favorites</t>
+          <t>Mark as favorite</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Favoris</t>
+          <t>Mettre en favori</t>
         </is>
       </c>
     </row>
@@ -7002,12 +7002,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Folder</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Répertoire</t>
+          <t>Modèle</t>
         </is>
       </c>
     </row>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Is between</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Est entre</t>
+          <t>Non</t>
         </is>
       </c>
     </row>
@@ -7036,12 +7036,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Is different from</t>
+          <t>No personal folder</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Est différent de</t>
+          <t>Aucun dossier personnel</t>
         </is>
       </c>
     </row>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Is empty</t>
+          <t>No right</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Est vide</t>
+          <t>Aucun droit</t>
         </is>
       </c>
     </row>
@@ -7070,12 +7070,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Is greater or equal than</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Est plus grand ou égal à</t>
+          <t>Aucun</t>
         </is>
       </c>
     </row>
@@ -7087,12 +7087,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Is greater than</t>
+          <t>Not sorted</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Est plus grand que</t>
+          <t>Pas de tri</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Is not between</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>N'est pas entre</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Is not empty</t>
+          <t>Options</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>N'est pas vide</t>
+          <t>Options</t>
         </is>
       </c>
     </row>
@@ -7138,12 +7138,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Is not Null</t>
+          <t>Output</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>N'est pas Null</t>
+          <t>Destination</t>
         </is>
       </c>
     </row>
@@ -7155,12 +7155,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Is Null</t>
+          <t>Personal folder for files only</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Est Null</t>
+          <t>Dossier personnel uniquement pour les fichiers</t>
         </is>
       </c>
     </row>
@@ -7172,12 +7172,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Is smaller or equal than</t>
+          <t>Personal folder for reports and files</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Est plus petit ou égal à</t>
+          <t>Dossier personnel pour les rapports et les fichiers</t>
         </is>
       </c>
     </row>
@@ -7189,12 +7189,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Is smaller than</t>
+          <t>Please wait</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Est plus petit que</t>
+          <t>Veuillez patienter</t>
         </is>
       </c>
     </row>
@@ -7206,12 +7206,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Last modification</t>
+          <t>Processing</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Dernière modification</t>
+          <t>En cours</t>
         </is>
       </c>
     </row>
@@ -7223,12 +7223,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Mark as favorite</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Mettre en favori</t>
+          <t>Profil</t>
         </is>
       </c>
     </row>
@@ -7240,12 +7240,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Recents</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Modèle</t>
+          <t>Récents</t>
         </is>
       </c>
     </row>
@@ -7257,12 +7257,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>New folder configuration</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Nouvelle configuration de dossier</t>
+          <t>Rapport</t>
         </is>
       </c>
     </row>
@@ -7274,12 +7274,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>New group</t>
+          <t>report(s) or file(s) cut in the clipboard</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Nouveau groupe</t>
+          <t>rapport(s) ou fichier(s) ont été coupés dans le presse-papier</t>
         </is>
       </c>
     </row>
@@ -7291,12 +7291,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>New login</t>
+          <t>report(s) or file(s) have been deleted</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Nouvel utilisateur</t>
+          <t>rapport(s) ou fichier(s) ont été effacés</t>
         </is>
       </c>
     </row>
@@ -7308,12 +7308,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>report(s) or file(s) processed</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>rapport(s) ou fichier(s) ont été traités</t>
         </is>
       </c>
     </row>
@@ -7325,12 +7325,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>No download (except files) or upload</t>
+          <t>report(s) or files(s) copied in the clipboard</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Pas de téléchargement (sauf fichiers) ni de téléversement</t>
+          <t>rapport(s) ou fichier(s) ont été copiés dans le presse-papier</t>
         </is>
       </c>
     </row>
@@ -7342,12 +7342,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>No folder configuration</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Aucune configuration de dossier</t>
+          <t>Rapports</t>
         </is>
       </c>
     </row>
@@ -7359,12 +7359,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>No login</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Aucun utilisateur</t>
+          <t>Planification</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>No personal folder</t>
+          <t>Server Version</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Aucun dossier personnel</t>
+          <t>Version du serveur</t>
         </is>
       </c>
     </row>
@@ -7393,12 +7393,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>No right</t>
+          <t>Show _MENU_ reports</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Aucun droit</t>
+          <t>Afficher _MENU_ rapports</t>
         </is>
       </c>
     </row>
@@ -7410,12 +7410,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Starts with</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Aucun</t>
+          <t>Commence par</t>
         </is>
       </c>
     </row>
@@ -7427,12 +7427,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Not sorted</t>
+          <t>The folder has been created</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Pas de tri</t>
+          <t>Le répertoire a été créé</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>The folder has been deleted</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Le répertoire a été effacé</t>
         </is>
       </c>
     </row>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Options</t>
+          <t>The folder has been renamed</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Options</t>
+          <t>Le répertoire a été renommé</t>
         </is>
       </c>
     </row>
@@ -7478,12 +7478,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>The folder has been updated</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Destination</t>
+          <t>Le répertoire a été mis à jour</t>
         </is>
       </c>
     </row>
@@ -7495,12 +7495,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Personal folder for files only</t>
+          <t>The report or file has been renamed</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Dossier personnel uniquement pour les fichiers</t>
+          <t>Le rapport ou le fichier a été renommé</t>
         </is>
       </c>
     </row>
@@ -7512,12 +7512,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Personal folder for reports and files</t>
+          <t>Toggle Report or Folders view</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Dossier personnel pour les rapports et les fichiers</t>
+          <t>Voir le rapport ou les répertoires</t>
         </is>
       </c>
     </row>
@@ -7529,12 +7529,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Please wait</t>
+          <t>Unexpected error on server</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Veuillez patienter</t>
+          <t>Erreur sur le serveur</t>
         </is>
       </c>
     </row>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>View</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>En cours</t>
+          <t>Vue</t>
         </is>
       </c>
     </row>
@@ -7563,12 +7563,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Profile</t>
+          <t>View Folders</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Profil</t>
+          <t>Voir les répertoires</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Recents</t>
+          <t>View Report</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Récents</t>
+          <t>Voir le rapport</t>
         </is>
       </c>
     </row>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>View reports</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Rapport</t>
+          <t>Voir les rapports</t>
         </is>
       </c>
     </row>
@@ -7614,12 +7614,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>report(s) or file(s) cut in the clipboard</t>
+          <t>Views and outputs</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>rapport(s) ou fichier(s) ont été coupés dans le presse-papier</t>
+          <t>Vues et destinations</t>
         </is>
       </c>
     </row>
@@ -7631,12 +7631,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>report(s) or file(s) have been deleted</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>rapport(s) ou fichier(s) ont été effacés</t>
+          <t>Avertissement</t>
         </is>
       </c>
     </row>
@@ -7648,12 +7648,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>report(s) or file(s) processed</t>
+          <t>Web Interface Version</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>rapport(s) ou fichier(s) ont été traités</t>
+          <t>Version de l'interface Web</t>
         </is>
       </c>
     </row>
@@ -7665,505 +7665,505 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>report(s) or files(s) copied in the clipboard</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>rapport(s) ou fichier(s) ont été copiés dans le presse-papier</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Select assistant</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Rapports</t>
+          <t>Sélectionner l'assistant</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Mark as favorite</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Planification</t>
+          <t>Mettre en favori</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Server Version</t>
+          <t>Favorites</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Version du serveur</t>
+          <t>Favoris</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Show _MENU_ reports</t>
+          <t>No favorites yet</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Afficher _MENU_ rapports</t>
+          <t>Aucun favori pour le moment</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Starts with</t>
+          <t>Recent</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Commence par</t>
+          <t>Récents</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>The configuration has been saved. Please login again if you are impacted by the security.</t>
+          <t>No recent items</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>La configuration a été enregistrée. Veuillez vous reconnecter si vous êtes concerné par la sécurité.</t>
+          <t>Aucun élément récent</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>The folder has been created</t>
+          <t>New conversation</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Le répertoire a été créé</t>
+          <t>Nouvelle conversation</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>The folder has been deleted</t>
+          <t>Sample prompts</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Le répertoire a été effacé</t>
+          <t>Exemples de prompts</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>The folder has been renamed</t>
+          <t>Sample Prompts</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Le répertoire a été renommé</t>
+          <t>Exemples de prompts</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>The folder has been updated</t>
+          <t>No sample prompts defined</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Le répertoire a été mis à jour</t>
+          <t>Aucun exemple de prompt défini</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>The report or file has been renamed</t>
+          <t>AI Assistant</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Le rapport ou le fichier a été renommé</t>
+          <t>Assistant IA</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Toggle Report or Folders view</t>
+          <t>Favorites &amp; Recent</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Voir le rapport ou les répertoires</t>
+          <t>Favoris et récents</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Unexpected error on server</t>
+          <t>Hide panel</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Erreur sur le serveur</t>
+          <t>Masquer le panneau</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>User can download reports</t>
+          <t>Ask the AI agent…</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>L'utilisateur peut télécharger les rapports</t>
+          <t>Posez une question à l'agent IA…</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>User can download reports and upload reports and files</t>
+          <t>Confirm Deletion</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>L'utilisateur peut télécharger les rapports et téléverser des rapports et des fichiers</t>
+          <t>Confirmer la suppression</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>This action is irreversible. Are you sure you want to delete this item?</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Vue</t>
+          <t>Cette action est irréversible. Voulez-vous vraiment supprimer cet élément ?</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>View Folders</t>
+          <t>Data Source</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Voir les répertoires</t>
+          <t>Source de données</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>View Report</t>
+          <t>Report Assistants</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Voir le rapport</t>
+          <t>Assistants de rapport</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>View reports</t>
+          <t>Select Tables or Views</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Voir les rapports</t>
+          <t>Sélectionner les tables ou les vues</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Views and outputs</t>
+          <t>Filter tables...</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Vues et destinations</t>
+          <t>Filtrer les tables...</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Select All</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Avertissement</t>
+          <t>Tout sélectionner</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Web Interface Version</t>
+          <t>Deselect All</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Version de l'interface Web</t>
+          <t>Tout désélectionner</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>tables selected</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>tables sélectionnées</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Yes (Folder is expanded in the tree view)</t>
+          <t>Prompt Shortcuts</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Oui (Le dossier est ouvert dans l'arborescence)</t>
+          <t>Raccourcis de prompts</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Yes (Only files can be stored)</t>
+          <t>How can Seal AI help you today ?</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Oui (Seuls les fichiers peuvent être stockés)</t>
+          <t>Comment Seal AI peut-il vous aider aujourd'hui ?</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Yes (User can browse sub-folders)</t>
+          <t>No current items available</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Oui (L'utilisateur peut parcourir les sous-dossiers)</t>
+          <t>Aucun élément courant disponible</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Yes (User can create and edit sub-folders)</t>
+          <t>Current items will appear here when saved</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Oui (L'utilisateur peut créer et modifier des sous-dossiers)</t>
+          <t>Les éléments courants apparaîtront ici une fois enregistrés</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Yes (User can edit his profile)</t>
+          <t>Drafts</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Oui (L'utilisateur peut modifier son profil)</t>
+          <t>Brouillons</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>WebJS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Yes (User is administrator of the Web Server)</t>
+          <t>No draft items available</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Oui (L'utilisateur est administrateur du serveur Web)</t>
+          <t>Aucun brouillon disponible</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Select assistant</t>
+          <t>Upload files or create new items with the assistant to see them here</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Sélectionner l'assistant</t>
+          <t>Téléversez des fichiers ou créez des éléments avec l'assistant pour les voir ici</t>
         </is>
       </c>
     </row>
@@ -8192,12 +8192,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Mark as favorite</t>
+          <t>Item Details</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Mettre en favori</t>
+          <t>Détails de l'élément</t>
         </is>
       </c>
     </row>
@@ -8209,12 +8209,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Favorites</t>
+          <t>Loading detail. Please wait...</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Favoris</t>
+          <t>Chargement des détails. Veuillez patienter...</t>
         </is>
       </c>
     </row>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>No favorites yet</t>
+          <t>Select a row from the table to view its details</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Aucun favori pour le moment</t>
+          <t>Sélectionnez une ligne du tableau pour afficher ses détails</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Recent</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Récents</t>
+          <t>Vérifier</t>
         </is>
       </c>
     </row>
@@ -8260,12 +8260,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>No recent items</t>
+          <t>Download</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Aucun élément récent</t>
+          <t>Télécharger</t>
         </is>
       </c>
     </row>
@@ -8277,12 +8277,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>New conversation</t>
+          <t>Reports Assistant</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Nouvelle conversation</t>
+          <t>Assistant de rapports</t>
         </is>
       </c>
     </row>
@@ -8294,12 +8294,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Sample prompts</t>
+          <t>Connection type</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Exemples de prompts</t>
+          <t>Type de connexion</t>
         </is>
       </c>
     </row>
@@ -8311,12 +8311,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Sample Prompts</t>
+          <t>Connection string</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Exemples de prompts</t>
+          <t>Chaîne de connexion</t>
         </is>
       </c>
     </row>
@@ -8328,12 +8328,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>No sample prompts defined</t>
+          <t>Tables or views</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Aucun exemple de prompt défini</t>
+          <t>Tables ou vues</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8345,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>AI Assistant</t>
+          <t>Report Assistant</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Assistant IA</t>
+          <t>Assistant de rapport</t>
         </is>
       </c>
     </row>
@@ -8362,12 +8362,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Favorites &amp; Recent</t>
+          <t>AI Provider</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Favoris et récents</t>
+          <t>Fournisseur IA</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Hide panel</t>
+          <t>AI model</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Masquer le panneau</t>
+          <t>Modèle IA</t>
         </is>
       </c>
     </row>
@@ -8396,12 +8396,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Ask the AI agent…</t>
+          <t>AI model name (overrides default))</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Posez une question à l'agent IA…</t>
+          <t>Nom du modèle IA (remplace la valeur par défaut)</t>
         </is>
       </c>
     </row>
@@ -8413,12 +8413,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Confirm Deletion</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Confirmer la suppression</t>
+          <t>Température</t>
         </is>
       </c>
     </row>
@@ -8430,12 +8430,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>This action is irreversible. Are you sure you want to delete this item?</t>
+          <t>Model temperature</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Cette action est irréversible. Voulez-vous vraiment supprimer cet élément ?</t>
+          <t>Température du modèle</t>
         </is>
       </c>
     </row>
@@ -8447,12 +8447,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Data Source</t>
+          <t>System prompt</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Source de données</t>
+          <t>Prompt système</t>
         </is>
       </c>
     </row>
@@ -8464,12 +8464,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Report Assistants</t>
+          <t>Optional sytem prompt for the assistant</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Assistants de rapport</t>
+          <t>Prompt système optionnel pour l'assistant</t>
         </is>
       </c>
     </row>
@@ -8481,12 +8481,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Select Tables or Views</t>
+          <t>User prompt</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Sélectionner les tables ou les vues</t>
+          <t>Prompt utilisateur</t>
         </is>
       </c>
     </row>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Filter tables...</t>
+          <t>Default user prompts (if empty default values configured are taken)</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Filtrer les tables...</t>
+          <t>Prompts utilisateur par défaut (si vide, les valeurs par défaut configurées sont utilisées)</t>
         </is>
       </c>
     </row>
@@ -8515,12 +8515,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Select All</t>
+          <t>User Groups allowed (No selection means no restriction)</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Tout sélectionner</t>
+          <t>Groupes d'utilisateurs autorisés (aucune sélection = aucune restriction)</t>
         </is>
       </c>
     </row>
@@ -8532,12 +8532,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Deselect All</t>
+          <t>Scan options</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Tout désélectionner</t>
+          <t>Options d'analyse</t>
         </is>
       </c>
     </row>
@@ -8549,12 +8549,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>tables selected</t>
+          <t>When to scan</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>tables sélectionnées</t>
+          <t>Quand analyser</t>
         </is>
       </c>
     </row>
@@ -8566,12 +8566,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Prompt Shortcuts</t>
+          <t>Cache duration (days)</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Raccourcis de prompts</t>
+          <t>Durée du cache (jours)</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>How can Seal AI help you today ?</t>
+          <t>Cache duration (days) for scanned data</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Comment Seal AI peut-il vous aider aujourd'hui ?</t>
+          <t>Durée du cache (jours) pour les données analysées</t>
         </is>
       </c>
     </row>
@@ -8600,12 +8600,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>No current items available</t>
+          <t>Tables to scan (no selection means all tables)</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Aucun élément courant disponible</t>
+          <t>Tables à analyser (aucune sélection = toutes les tables)</t>
         </is>
       </c>
     </row>
@@ -8617,12 +8617,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Current items will appear here when saved</t>
+          <t>Records to scan</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Les éléments courants apparaîtront ici une fois enregistrés</t>
+          <t>Enregistrements à analyser</t>
         </is>
       </c>
     </row>
@@ -8634,12 +8634,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Drafts</t>
+          <t>Number of records used for scan</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Brouillons</t>
+          <t>Nombre d'enregistrements utilisés pour l'analyse</t>
         </is>
       </c>
     </row>
@@ -8651,12 +8651,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>No draft items available</t>
+          <t>Scan Data Now</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Aucun brouillon disponible</t>
+          <t>Analyser les données maintenant</t>
         </is>
       </c>
     </row>
@@ -8668,12 +8668,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Upload files or create new items with the assistant to see them here</t>
+          <t>Execute</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Téléversez des fichiers ou créez des éléments avec l'assistant pour les voir ici</t>
+          <t>Exécuter</t>
         </is>
       </c>
     </row>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Item Details</t>
+          <t>Elements:</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Détails de l'élément</t>
+          <t>Éléments :</t>
         </is>
       </c>
     </row>
@@ -8702,182 +8702,182 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Loading detail. Please wait...</t>
+          <t>Restrictions:</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Chargement des détails. Veuillez patienter...</t>
+          <t>Restrictions :</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Select a row from the table to view its details</t>
+          <t>Hide AI Assistant</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Sélectionnez une ligne du tableau pour afficher ses détails</t>
+          <t>Masquer l'assistant IA</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>AI Assistant</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Vérifier</t>
+          <t>Assistant IA</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Running</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Télécharger</t>
+          <t>En cours</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Reports Assistant</t>
+          <t>Request cancelled.</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Assistant de rapports</t>
+          <t>Demande annulée.</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Connection type</t>
+          <t>Remove from favorites</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Type de connexion</t>
+          <t>Retirer des favoris</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Connection string</t>
+          <t>No sample prompts defined</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Chaîne de connexion</t>
+          <t>Aucun exemple de prompt défini</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Tables or views</t>
+          <t>Rename</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Tables ou vues</t>
+          <t>Renommer</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Report Assistant</t>
+          <t>Delete</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Assistant de rapport</t>
+          <t>Supprimer</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>AI Provider</t>
+          <t>No favorites yet</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Fournisseur IA</t>
+          <t>Aucun favori pour le moment</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>AI model</t>
+          <t>No recent items</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Modèle IA</t>
+          <t>Aucun élément récent</t>
         </is>
       </c>
     </row>
@@ -8889,46 +8889,46 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>AI model name (overrides default))</t>
+          <t>Drag to resize</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Nom du modèle IA (remplace la valeur par défaut)</t>
+          <t>Glisser pour redimensionner</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Copy and paste</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Température</t>
+          <t>Copier et coller</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Model temperature</t>
+          <t>Copy, paste and send</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Température du modèle</t>
+          <t>Copier, coller et envoyer</t>
         </is>
       </c>
     </row>
@@ -8940,29 +8940,34 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>System prompt</t>
+          <t>BIN</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Recycle Bin</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Prompt système</t>
+          <t>Corbeille</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Optional sytem prompt for the assistant</t>
+          <t>Rewind to here</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Prompt système optionnel pour l'assistant</t>
+          <t>Revenir à ce message</t>
         </is>
       </c>
     </row>
@@ -8974,63 +8979,63 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>User prompt</t>
+          <t>Paste shortcut</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Prompt utilisateur</t>
+          <t>Coller le raccourci</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Default user prompts (if empty default values configured are taken)</t>
+          <t>Shortcut to</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Prompts utilisateur par défaut (si vide, les valeurs par défaut configurées sont utilisées)</t>
+          <t>Raccourci vers</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>User Groups allowed (No selection means no restriction)</t>
+          <t>Shortcut target not found</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Groupes d'utilisateurs autorisés (aucune sélection = aucune restriction)</t>
+          <t>Cible du raccourci introuvable</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Scan options</t>
+          <t>shortcut(s) created</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Options d'analyse</t>
+          <t>raccourci(s) créé(s)</t>
         </is>
       </c>
     </row>
@@ -9042,510 +9047,46 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>When to scan</t>
+          <t>Empty recycle bin</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Quand analyser</t>
+          <t>Vider la corbeille</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Cache duration (days)</t>
+          <t>Do you really want to permanently delete all items in the recycle bin ?</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Durée du cache (jours)</t>
+          <t>Voulez-vous vraiment supprimer définitivement tous les éléments de la corbeille ?</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>WebJS</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Cache duration (days) for scanned data</t>
+          <t>The recycle bin has been emptied</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Durée du cache (jours) pour les données analysées</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>Tables to scan (no selection means all tables)</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>Tables à analyser (aucune sélection = toutes les tables)</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>Records to scan</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>Enregistrements à analyser</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>Number of records used for scan</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>Nombre d'enregistrements utilisés pour l'analyse</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>Scan Data Now</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>Analyser les données maintenant</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>Execute</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>Exécuter</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>Elements:</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>Éléments :</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>Restrictions:</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>Restrictions :</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>Hide AI Assistant</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>Masquer l'assistant IA</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>AI Assistant</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>Assistant IA</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>Running</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>En cours</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>Request cancelled.</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>Demande annulée.</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>Remove from favorites</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>Retirer des favoris</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>No sample prompts defined</t>
-        </is>
-      </c>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>Aucun exemple de prompt défini</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>Rename</t>
-        </is>
-      </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>Renommer</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>Delete</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>Supprimer</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>No favorites yet</t>
-        </is>
-      </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>Aucun favori pour le moment</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>No recent items</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>Aucun élément récent</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>Download/Upload</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>Télécharger/Téléverser</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>Drag to resize</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>Glisser pour redimensionner</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>Copy and paste</t>
-        </is>
-      </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>Copier et coller</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>Copy, paste and send</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>Copier, coller et envoyer</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>BIN</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>Recycle Bin</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>Corbeille</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>Rewind to here</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>Revenir à ce message</t>
-        </is>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>Paste shortcut</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>Coller le raccourci</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>Shortcut to</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>Raccourci vers</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>Shortcut target not found</t>
-        </is>
-      </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>Cible du raccourci introuvable</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>WebJS</t>
-        </is>
-      </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>shortcut(s) created</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>raccourci(s) créé(s)</t>
+          <t>La corbeille a été vidée</t>
         </is>
       </c>
     </row>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D479"/>
+  <dimension ref="A1:D481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9090,6 +9090,40 @@
         </is>
       </c>
     </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Thinking</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Réflexion</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Thought for {0} steps</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Réflexion en {0} étapes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D481"/>
+  <dimension ref="A1:D483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9124,6 +9124,40 @@
         </is>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Task: only the tasks are executed</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Tâche : seules les tâches sont exécutées</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>This report has a schedule</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Ce rapport possède une planification</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D483"/>
+  <dimension ref="A1:D486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9158,6 +9158,57 @@
         </is>
       </c>
     </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Messages</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Messages</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Show/Hide Guide</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Afficher/Cacher le guide</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D486"/>
+  <dimension ref="A1:D490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9209,6 +9209,74 @@
         </is>
       </c>
     </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Show Restrictions</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Afficher les restrictions</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Hide Restrictions</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Masquer les restrictions</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Show Guide</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Afficher le guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Hide Guide</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Masquer le guide</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Repository/Settings/Translations.xlsx
+++ b/Repository/Settings/Translations.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D490"/>
+  <dimension ref="A1:D496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9277,6 +9277,108 @@
         </is>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>tokens</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>jetons</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>coût</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>A security code has been sent by Email at</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Un code de sécurité a été envoyé par Email à</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>A security code has been sent by SMS at</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Un code de sécurité a été envoyé par SMS à</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Copy for Excel</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Copier pour Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>WebJS</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Download CSV</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Télécharger en CSV</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D503"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
